--- a/ActionGame-リファクタリング-/Data/CSV/Stage/Stage.xlsx
+++ b/ActionGame-リファクタリング-/Data/CSV/Stage/Stage.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\2409404\Desktop\GameProject\ActionGame-リファクタリング-\Data\CSV\Stage\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1DD9167-2650-4759-899C-4B4D28401D50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{200CF403-D42D-43B0-9AB7-BA7F855918DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5925" yWindow="3975" windowWidth="21600" windowHeight="11295" xr2:uid="{62A58253-9505-4C17-A0D0-B4C12E04E8CC}"/>
+    <workbookView xWindow="7200" yWindow="1890" windowWidth="21600" windowHeight="11295" xr2:uid="{62A58253-9505-4C17-A0D0-B4C12E04E8CC}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -392,15 +392,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{592BFE65-1919-4E86-A258-49B12076C0A7}">
-  <dimension ref="A1:M3"/>
+  <dimension ref="A1:L10"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="13" width="3.625" customWidth="1"/>
+    <col min="1" max="12" width="3.625" customWidth="1"/>
+    <col min="13" max="13" width="9" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="B1">
         <v>0</v>
@@ -418,30 +419,27 @@
         <v>0</v>
       </c>
       <c r="G1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L1">
-        <v>0</v>
-      </c>
-      <c r="M1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B2">
         <v>100</v>
@@ -459,39 +457,36 @@
         <v>0</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L2">
-        <v>0</v>
-      </c>
-      <c r="M2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A3">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B3">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="C3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D3">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="E3">
         <v>0</v>
@@ -500,25 +495,288 @@
         <v>0</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L3">
-        <v>0</v>
-      </c>
-      <c r="M3">
-        <v>0</v>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A4">
+        <v>100</v>
+      </c>
+      <c r="B4">
+        <v>100</v>
+      </c>
+      <c r="C4">
+        <v>0</v>
+      </c>
+      <c r="D4">
+        <v>0</v>
+      </c>
+      <c r="E4">
+        <v>0</v>
+      </c>
+      <c r="F4">
+        <v>0</v>
+      </c>
+      <c r="G4">
+        <v>1</v>
+      </c>
+      <c r="H4">
+        <v>1</v>
+      </c>
+      <c r="I4">
+        <v>1</v>
+      </c>
+      <c r="J4">
+        <v>1</v>
+      </c>
+      <c r="K4">
+        <v>1</v>
+      </c>
+      <c r="L4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A5">
+        <v>100</v>
+      </c>
+      <c r="B5">
+        <v>0</v>
+      </c>
+      <c r="C5">
+        <v>100</v>
+      </c>
+      <c r="D5">
+        <v>0</v>
+      </c>
+      <c r="E5">
+        <v>0</v>
+      </c>
+      <c r="F5">
+        <v>0</v>
+      </c>
+      <c r="G5">
+        <v>1</v>
+      </c>
+      <c r="H5">
+        <v>1</v>
+      </c>
+      <c r="I5">
+        <v>1</v>
+      </c>
+      <c r="J5">
+        <v>1</v>
+      </c>
+      <c r="K5">
+        <v>1</v>
+      </c>
+      <c r="L5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A6">
+        <v>0</v>
+      </c>
+      <c r="B6">
+        <v>100</v>
+      </c>
+      <c r="C6">
+        <v>100</v>
+      </c>
+      <c r="D6">
+        <v>0</v>
+      </c>
+      <c r="E6">
+        <v>0</v>
+      </c>
+      <c r="F6">
+        <v>0</v>
+      </c>
+      <c r="G6">
+        <v>1</v>
+      </c>
+      <c r="H6">
+        <v>1</v>
+      </c>
+      <c r="I6">
+        <v>1</v>
+      </c>
+      <c r="J6">
+        <v>1</v>
+      </c>
+      <c r="K6">
+        <v>1</v>
+      </c>
+      <c r="L6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A7">
+        <v>100</v>
+      </c>
+      <c r="B7">
+        <v>100</v>
+      </c>
+      <c r="C7">
+        <v>100</v>
+      </c>
+      <c r="D7">
+        <v>0</v>
+      </c>
+      <c r="E7">
+        <v>0</v>
+      </c>
+      <c r="F7">
+        <v>0</v>
+      </c>
+      <c r="G7">
+        <v>1</v>
+      </c>
+      <c r="H7">
+        <v>1</v>
+      </c>
+      <c r="I7">
+        <v>1</v>
+      </c>
+      <c r="J7">
+        <v>1</v>
+      </c>
+      <c r="K7">
+        <v>1</v>
+      </c>
+      <c r="L7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A8">
+        <v>-100</v>
+      </c>
+      <c r="B8">
+        <v>0</v>
+      </c>
+      <c r="C8">
+        <v>0</v>
+      </c>
+      <c r="D8">
+        <v>0</v>
+      </c>
+      <c r="E8">
+        <v>0</v>
+      </c>
+      <c r="F8">
+        <v>0</v>
+      </c>
+      <c r="G8">
+        <v>1</v>
+      </c>
+      <c r="H8">
+        <v>1</v>
+      </c>
+      <c r="I8">
+        <v>1</v>
+      </c>
+      <c r="J8">
+        <v>1</v>
+      </c>
+      <c r="K8">
+        <v>1</v>
+      </c>
+      <c r="L8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A9">
+        <v>0</v>
+      </c>
+      <c r="B9">
+        <v>-100</v>
+      </c>
+      <c r="C9">
+        <v>0</v>
+      </c>
+      <c r="D9">
+        <v>0</v>
+      </c>
+      <c r="E9">
+        <v>0</v>
+      </c>
+      <c r="F9">
+        <v>0</v>
+      </c>
+      <c r="G9">
+        <v>1</v>
+      </c>
+      <c r="H9">
+        <v>1</v>
+      </c>
+      <c r="I9">
+        <v>1</v>
+      </c>
+      <c r="J9">
+        <v>1</v>
+      </c>
+      <c r="K9">
+        <v>1</v>
+      </c>
+      <c r="L9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A10">
+        <v>0</v>
+      </c>
+      <c r="B10">
+        <v>0</v>
+      </c>
+      <c r="C10">
+        <v>-100</v>
+      </c>
+      <c r="D10">
+        <v>0</v>
+      </c>
+      <c r="E10">
+        <v>0</v>
+      </c>
+      <c r="F10">
+        <v>0</v>
+      </c>
+      <c r="G10">
+        <v>1</v>
+      </c>
+      <c r="H10">
+        <v>1</v>
+      </c>
+      <c r="I10">
+        <v>1</v>
+      </c>
+      <c r="J10">
+        <v>1</v>
+      </c>
+      <c r="K10">
+        <v>1</v>
+      </c>
+      <c r="L10">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/ActionGame-リファクタリング-/Data/CSV/Stage/Stage.xlsx
+++ b/ActionGame-リファクタリング-/Data/CSV/Stage/Stage.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\2409404\Desktop\GameProject\ActionGame-リファクタリング-\Data\CSV\Stage\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{200CF403-D42D-43B0-9AB7-BA7F855918DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7FC1E35-0A3E-4B39-B680-3D9547622E77}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7200" yWindow="1890" windowWidth="21600" windowHeight="11295" xr2:uid="{62A58253-9505-4C17-A0D0-B4C12E04E8CC}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{62A58253-9505-4C17-A0D0-B4C12E04E8CC}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -392,7 +392,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{592BFE65-1919-4E86-A258-49B12076C0A7}">
-  <dimension ref="A1:L10"/>
+  <dimension ref="A1:L27"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="12" width="3.625" customWidth="1"/>
@@ -401,7 +401,7 @@
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A1">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="B1">
         <v>0</v>
@@ -428,27 +428,30 @@
         <v>1</v>
       </c>
       <c r="J1">
-        <v>1</v>
+        <f>G1*2</f>
+        <v>2</v>
       </c>
       <c r="K1">
-        <v>1</v>
+        <f t="shared" ref="K1:L1" si="0">H1*2</f>
+        <v>2</v>
       </c>
       <c r="L1">
-        <v>1</v>
+        <f t="shared" si="0"/>
+        <v>2</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A2">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="B2">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="C2">
         <v>0</v>
       </c>
       <c r="D2">
-        <v>0</v>
+        <v>0.78</v>
       </c>
       <c r="E2">
         <v>0</v>
@@ -457,7 +460,7 @@
         <v>0</v>
       </c>
       <c r="G2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H2">
         <v>1</v>
@@ -466,27 +469,30 @@
         <v>1</v>
       </c>
       <c r="J2">
-        <v>1</v>
+        <f t="shared" ref="J2:J27" si="1">G2*2</f>
+        <v>4</v>
       </c>
       <c r="K2">
-        <v>1</v>
+        <f t="shared" ref="K2:K27" si="2">H2*2</f>
+        <v>2</v>
       </c>
       <c r="L2">
-        <v>1</v>
+        <f t="shared" ref="L2:L27" si="3">I2*2</f>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="B3">
         <v>0</v>
       </c>
       <c r="C3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="D3">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="E3">
         <v>0</v>
@@ -495,7 +501,7 @@
         <v>0</v>
       </c>
       <c r="G3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H3">
         <v>1</v>
@@ -504,18 +510,21 @@
         <v>1</v>
       </c>
       <c r="J3">
-        <v>1</v>
+        <f t="shared" si="1"/>
+        <v>4</v>
       </c>
       <c r="K3">
-        <v>1</v>
+        <f t="shared" si="2"/>
+        <v>2</v>
       </c>
       <c r="L3">
-        <v>1</v>
+        <f t="shared" si="3"/>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A4">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="B4">
         <v>100</v>
@@ -527,7 +536,7 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>0.78</v>
       </c>
       <c r="F4">
         <v>0</v>
@@ -536,36 +545,39 @@
         <v>1</v>
       </c>
       <c r="H4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I4">
         <v>1</v>
       </c>
       <c r="J4">
-        <v>1</v>
+        <f t="shared" si="1"/>
+        <v>2</v>
       </c>
       <c r="K4">
-        <v>1</v>
+        <f t="shared" si="2"/>
+        <v>4</v>
       </c>
       <c r="L4">
-        <v>1</v>
+        <f t="shared" si="3"/>
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A5">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="B5">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="C5">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="D5">
         <v>0</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="F5">
         <v>0</v>
@@ -574,138 +586,150 @@
         <v>1</v>
       </c>
       <c r="H5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I5">
         <v>1</v>
       </c>
       <c r="J5">
-        <v>1</v>
+        <f t="shared" si="1"/>
+        <v>2</v>
       </c>
       <c r="K5">
-        <v>1</v>
+        <f t="shared" si="2"/>
+        <v>4</v>
       </c>
       <c r="L5">
-        <v>1</v>
+        <f t="shared" si="3"/>
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A6">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="B6">
         <v>100</v>
       </c>
       <c r="C6">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="D6">
-        <v>0</v>
+        <v>0.78</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>0.78</v>
       </c>
       <c r="F6">
         <v>0</v>
       </c>
       <c r="G6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I6">
         <v>1</v>
       </c>
       <c r="J6">
-        <v>1</v>
+        <f t="shared" si="1"/>
+        <v>4</v>
       </c>
       <c r="K6">
-        <v>1</v>
+        <f t="shared" si="2"/>
+        <v>4</v>
       </c>
       <c r="L6">
-        <v>1</v>
+        <f t="shared" si="3"/>
+        <v>2</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A7">
-        <v>100</v>
+        <v>-100</v>
       </c>
       <c r="B7">
         <v>100</v>
       </c>
       <c r="C7">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="D7">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="E7">
-        <v>0</v>
+        <v>0.78</v>
       </c>
       <c r="F7">
         <v>0</v>
       </c>
       <c r="G7">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H7">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I7">
         <v>1</v>
       </c>
       <c r="J7">
-        <v>1</v>
+        <f t="shared" si="1"/>
+        <v>4</v>
       </c>
       <c r="K7">
-        <v>1</v>
+        <f t="shared" si="2"/>
+        <v>4</v>
       </c>
       <c r="L7">
-        <v>1</v>
+        <f t="shared" si="3"/>
+        <v>2</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A8">
-        <v>-100</v>
+        <v>100</v>
       </c>
       <c r="B8">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="C8">
         <v>0</v>
       </c>
       <c r="D8">
-        <v>0</v>
+        <v>0.78</v>
       </c>
       <c r="E8">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="F8">
         <v>0</v>
       </c>
       <c r="G8">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H8">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I8">
         <v>1</v>
       </c>
       <c r="J8">
-        <v>1</v>
+        <f t="shared" si="1"/>
+        <v>4</v>
       </c>
       <c r="K8">
-        <v>1</v>
+        <f t="shared" si="2"/>
+        <v>4</v>
       </c>
       <c r="L8">
-        <v>1</v>
+        <f t="shared" si="3"/>
+        <v>2</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A9">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="B9">
         <v>-100</v>
@@ -714,31 +738,34 @@
         <v>0</v>
       </c>
       <c r="D9">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="E9">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="F9">
         <v>0</v>
       </c>
       <c r="G9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I9">
         <v>1</v>
       </c>
       <c r="J9">
-        <v>1</v>
+        <f t="shared" si="1"/>
+        <v>4</v>
       </c>
       <c r="K9">
-        <v>1</v>
+        <f t="shared" si="2"/>
+        <v>4</v>
       </c>
       <c r="L9">
-        <v>1</v>
+        <f t="shared" si="3"/>
+        <v>2</v>
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.4">
@@ -749,7 +776,7 @@
         <v>0</v>
       </c>
       <c r="C10">
-        <v>-100</v>
+        <v>100</v>
       </c>
       <c r="D10">
         <v>0</v>
@@ -758,7 +785,7 @@
         <v>0</v>
       </c>
       <c r="F10">
-        <v>0</v>
+        <v>0.78</v>
       </c>
       <c r="G10">
         <v>1</v>
@@ -767,16 +794,716 @@
         <v>1</v>
       </c>
       <c r="I10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J10">
-        <v>1</v>
+        <f t="shared" si="1"/>
+        <v>2</v>
       </c>
       <c r="K10">
-        <v>1</v>
+        <f t="shared" si="2"/>
+        <v>2</v>
       </c>
       <c r="L10">
-        <v>1</v>
+        <f t="shared" si="3"/>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A11">
+        <v>100</v>
+      </c>
+      <c r="B11">
+        <v>0</v>
+      </c>
+      <c r="C11">
+        <v>100</v>
+      </c>
+      <c r="D11">
+        <v>0.78</v>
+      </c>
+      <c r="E11">
+        <v>0</v>
+      </c>
+      <c r="F11">
+        <v>0.78</v>
+      </c>
+      <c r="G11">
+        <v>2</v>
+      </c>
+      <c r="H11">
+        <v>1</v>
+      </c>
+      <c r="I11">
+        <v>2</v>
+      </c>
+      <c r="J11">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+      <c r="K11">
+        <f t="shared" si="2"/>
+        <v>2</v>
+      </c>
+      <c r="L11">
+        <f t="shared" si="3"/>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A12">
+        <v>-100</v>
+      </c>
+      <c r="B12">
+        <v>0</v>
+      </c>
+      <c r="C12">
+        <v>100</v>
+      </c>
+      <c r="D12">
+        <v>2.35</v>
+      </c>
+      <c r="E12">
+        <v>0</v>
+      </c>
+      <c r="F12">
+        <v>0.78</v>
+      </c>
+      <c r="G12">
+        <v>2</v>
+      </c>
+      <c r="H12">
+        <v>1</v>
+      </c>
+      <c r="I12">
+        <v>2</v>
+      </c>
+      <c r="J12">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+      <c r="K12">
+        <f t="shared" si="2"/>
+        <v>2</v>
+      </c>
+      <c r="L12">
+        <f t="shared" si="3"/>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A13">
+        <v>0</v>
+      </c>
+      <c r="B13">
+        <v>100</v>
+      </c>
+      <c r="C13">
+        <v>100</v>
+      </c>
+      <c r="D13">
+        <v>0</v>
+      </c>
+      <c r="E13">
+        <v>0.78</v>
+      </c>
+      <c r="F13">
+        <v>0.78</v>
+      </c>
+      <c r="G13">
+        <v>1</v>
+      </c>
+      <c r="H13">
+        <v>2</v>
+      </c>
+      <c r="I13">
+        <v>2</v>
+      </c>
+      <c r="J13">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+      <c r="K13">
+        <f t="shared" si="2"/>
+        <v>4</v>
+      </c>
+      <c r="L13">
+        <f t="shared" si="3"/>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A14">
+        <v>0</v>
+      </c>
+      <c r="B14">
+        <v>-100</v>
+      </c>
+      <c r="C14">
+        <v>100</v>
+      </c>
+      <c r="D14">
+        <v>0</v>
+      </c>
+      <c r="E14">
+        <v>2.35</v>
+      </c>
+      <c r="F14">
+        <v>0.78</v>
+      </c>
+      <c r="G14">
+        <v>1</v>
+      </c>
+      <c r="H14">
+        <v>2</v>
+      </c>
+      <c r="I14">
+        <v>2</v>
+      </c>
+      <c r="J14">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+      <c r="K14">
+        <f t="shared" si="2"/>
+        <v>4</v>
+      </c>
+      <c r="L14">
+        <f t="shared" si="3"/>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A15">
+        <v>100</v>
+      </c>
+      <c r="B15">
+        <v>100</v>
+      </c>
+      <c r="C15">
+        <v>100</v>
+      </c>
+      <c r="D15">
+        <v>0.78</v>
+      </c>
+      <c r="E15">
+        <v>0.78</v>
+      </c>
+      <c r="F15">
+        <v>0.78</v>
+      </c>
+      <c r="G15">
+        <v>2</v>
+      </c>
+      <c r="H15">
+        <v>2</v>
+      </c>
+      <c r="I15">
+        <v>2</v>
+      </c>
+      <c r="J15">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+      <c r="K15">
+        <f t="shared" si="2"/>
+        <v>4</v>
+      </c>
+      <c r="L15">
+        <f t="shared" si="3"/>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A16">
+        <v>-100</v>
+      </c>
+      <c r="B16">
+        <v>100</v>
+      </c>
+      <c r="C16">
+        <v>100</v>
+      </c>
+      <c r="D16">
+        <v>2.35</v>
+      </c>
+      <c r="E16">
+        <v>0.78</v>
+      </c>
+      <c r="F16">
+        <v>0.78</v>
+      </c>
+      <c r="G16">
+        <v>2</v>
+      </c>
+      <c r="H16">
+        <v>2</v>
+      </c>
+      <c r="I16">
+        <v>2</v>
+      </c>
+      <c r="J16">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+      <c r="K16">
+        <f t="shared" si="2"/>
+        <v>4</v>
+      </c>
+      <c r="L16">
+        <f t="shared" si="3"/>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A17">
+        <v>100</v>
+      </c>
+      <c r="B17">
+        <v>-100</v>
+      </c>
+      <c r="C17">
+        <v>100</v>
+      </c>
+      <c r="D17">
+        <v>0.78</v>
+      </c>
+      <c r="E17">
+        <v>2.35</v>
+      </c>
+      <c r="F17">
+        <v>0.78</v>
+      </c>
+      <c r="G17">
+        <v>2</v>
+      </c>
+      <c r="H17">
+        <v>2</v>
+      </c>
+      <c r="I17">
+        <v>2</v>
+      </c>
+      <c r="J17">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+      <c r="K17">
+        <f t="shared" si="2"/>
+        <v>4</v>
+      </c>
+      <c r="L17">
+        <f t="shared" si="3"/>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A18">
+        <v>-100</v>
+      </c>
+      <c r="B18">
+        <v>-100</v>
+      </c>
+      <c r="C18">
+        <v>100</v>
+      </c>
+      <c r="D18">
+        <v>2.35</v>
+      </c>
+      <c r="E18">
+        <v>2.35</v>
+      </c>
+      <c r="F18">
+        <v>0.78</v>
+      </c>
+      <c r="G18">
+        <v>2</v>
+      </c>
+      <c r="H18">
+        <v>2</v>
+      </c>
+      <c r="I18">
+        <v>2</v>
+      </c>
+      <c r="J18">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+      <c r="K18">
+        <f t="shared" si="2"/>
+        <v>4</v>
+      </c>
+      <c r="L18">
+        <f t="shared" si="3"/>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A19">
+        <v>0</v>
+      </c>
+      <c r="B19">
+        <v>0</v>
+      </c>
+      <c r="C19">
+        <v>-100</v>
+      </c>
+      <c r="D19">
+        <v>0</v>
+      </c>
+      <c r="E19">
+        <v>0</v>
+      </c>
+      <c r="F19">
+        <v>2.35</v>
+      </c>
+      <c r="G19">
+        <v>1</v>
+      </c>
+      <c r="H19">
+        <v>1</v>
+      </c>
+      <c r="I19">
+        <v>2</v>
+      </c>
+      <c r="J19">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+      <c r="K19">
+        <f t="shared" si="2"/>
+        <v>2</v>
+      </c>
+      <c r="L19">
+        <f t="shared" si="3"/>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A20">
+        <v>100</v>
+      </c>
+      <c r="B20">
+        <v>0</v>
+      </c>
+      <c r="C20">
+        <v>-100</v>
+      </c>
+      <c r="D20">
+        <v>0.78</v>
+      </c>
+      <c r="E20">
+        <v>0</v>
+      </c>
+      <c r="F20">
+        <v>2.35</v>
+      </c>
+      <c r="G20">
+        <v>2</v>
+      </c>
+      <c r="H20">
+        <v>1</v>
+      </c>
+      <c r="I20">
+        <v>2</v>
+      </c>
+      <c r="J20">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+      <c r="K20">
+        <f t="shared" si="2"/>
+        <v>2</v>
+      </c>
+      <c r="L20">
+        <f t="shared" si="3"/>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A21">
+        <v>-100</v>
+      </c>
+      <c r="B21">
+        <v>0</v>
+      </c>
+      <c r="C21">
+        <v>-100</v>
+      </c>
+      <c r="D21">
+        <v>2.35</v>
+      </c>
+      <c r="E21">
+        <v>0</v>
+      </c>
+      <c r="F21">
+        <v>2.35</v>
+      </c>
+      <c r="G21">
+        <v>2</v>
+      </c>
+      <c r="H21">
+        <v>1</v>
+      </c>
+      <c r="I21">
+        <v>2</v>
+      </c>
+      <c r="J21">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+      <c r="K21">
+        <f t="shared" si="2"/>
+        <v>2</v>
+      </c>
+      <c r="L21">
+        <f t="shared" si="3"/>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A22">
+        <v>0</v>
+      </c>
+      <c r="B22">
+        <v>100</v>
+      </c>
+      <c r="C22">
+        <v>-100</v>
+      </c>
+      <c r="D22">
+        <v>0</v>
+      </c>
+      <c r="E22">
+        <v>0.78</v>
+      </c>
+      <c r="F22">
+        <v>2.35</v>
+      </c>
+      <c r="G22">
+        <v>1</v>
+      </c>
+      <c r="H22">
+        <v>2</v>
+      </c>
+      <c r="I22">
+        <v>2</v>
+      </c>
+      <c r="J22">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+      <c r="K22">
+        <f t="shared" si="2"/>
+        <v>4</v>
+      </c>
+      <c r="L22">
+        <f t="shared" si="3"/>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A23">
+        <v>0</v>
+      </c>
+      <c r="B23">
+        <v>-100</v>
+      </c>
+      <c r="C23">
+        <v>-100</v>
+      </c>
+      <c r="D23">
+        <v>0</v>
+      </c>
+      <c r="E23">
+        <v>2.35</v>
+      </c>
+      <c r="F23">
+        <v>2.35</v>
+      </c>
+      <c r="G23">
+        <v>1</v>
+      </c>
+      <c r="H23">
+        <v>2</v>
+      </c>
+      <c r="I23">
+        <v>2</v>
+      </c>
+      <c r="J23">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+      <c r="K23">
+        <f t="shared" si="2"/>
+        <v>4</v>
+      </c>
+      <c r="L23">
+        <f t="shared" si="3"/>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A24">
+        <v>100</v>
+      </c>
+      <c r="B24">
+        <v>100</v>
+      </c>
+      <c r="C24">
+        <v>-100</v>
+      </c>
+      <c r="D24">
+        <v>0.78</v>
+      </c>
+      <c r="E24">
+        <v>0.78</v>
+      </c>
+      <c r="F24">
+        <v>2.35</v>
+      </c>
+      <c r="G24">
+        <v>2</v>
+      </c>
+      <c r="H24">
+        <v>2</v>
+      </c>
+      <c r="I24">
+        <v>2</v>
+      </c>
+      <c r="J24">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+      <c r="K24">
+        <f t="shared" si="2"/>
+        <v>4</v>
+      </c>
+      <c r="L24">
+        <f t="shared" si="3"/>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A25">
+        <v>-100</v>
+      </c>
+      <c r="B25">
+        <v>100</v>
+      </c>
+      <c r="C25">
+        <v>-100</v>
+      </c>
+      <c r="D25">
+        <v>2.35</v>
+      </c>
+      <c r="E25">
+        <v>0.78</v>
+      </c>
+      <c r="F25">
+        <v>2.35</v>
+      </c>
+      <c r="G25">
+        <v>2</v>
+      </c>
+      <c r="H25">
+        <v>2</v>
+      </c>
+      <c r="I25">
+        <v>2</v>
+      </c>
+      <c r="J25">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+      <c r="K25">
+        <f t="shared" si="2"/>
+        <v>4</v>
+      </c>
+      <c r="L25">
+        <f t="shared" si="3"/>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A26">
+        <v>100</v>
+      </c>
+      <c r="B26">
+        <v>-100</v>
+      </c>
+      <c r="C26">
+        <v>-100</v>
+      </c>
+      <c r="D26">
+        <v>0.78</v>
+      </c>
+      <c r="E26">
+        <v>2.35</v>
+      </c>
+      <c r="F26">
+        <v>2.35</v>
+      </c>
+      <c r="G26">
+        <v>2</v>
+      </c>
+      <c r="H26">
+        <v>2</v>
+      </c>
+      <c r="I26">
+        <v>2</v>
+      </c>
+      <c r="J26">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+      <c r="K26">
+        <f t="shared" si="2"/>
+        <v>4</v>
+      </c>
+      <c r="L26">
+        <f t="shared" si="3"/>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A27">
+        <v>-100</v>
+      </c>
+      <c r="B27">
+        <v>-100</v>
+      </c>
+      <c r="C27">
+        <v>-100</v>
+      </c>
+      <c r="D27">
+        <v>2.35</v>
+      </c>
+      <c r="E27">
+        <v>2.35</v>
+      </c>
+      <c r="F27">
+        <v>2.35</v>
+      </c>
+      <c r="G27">
+        <v>2</v>
+      </c>
+      <c r="H27">
+        <v>2</v>
+      </c>
+      <c r="I27">
+        <v>2</v>
+      </c>
+      <c r="J27">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+      <c r="K27">
+        <f t="shared" si="2"/>
+        <v>4</v>
+      </c>
+      <c r="L27">
+        <f t="shared" si="3"/>
+        <v>4</v>
       </c>
     </row>
   </sheetData>

--- a/ActionGame-リファクタリング-/Data/CSV/Stage/Stage.xlsx
+++ b/ActionGame-リファクタリング-/Data/CSV/Stage/Stage.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\2409404\Desktop\GameProject\ActionGame-リファクタリング-\Data\CSV\Stage\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7FC1E35-0A3E-4B39-B680-3D9547622E77}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60E85ED2-C4FD-431C-9C0F-10DDC9FC2CF9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{62A58253-9505-4C17-A0D0-B4C12E04E8CC}"/>
   </bookViews>
@@ -428,16 +428,16 @@
         <v>1</v>
       </c>
       <c r="J1">
-        <f>G1*2</f>
-        <v>2</v>
+        <f>G1*20</f>
+        <v>20</v>
       </c>
       <c r="K1">
-        <f t="shared" ref="K1:L1" si="0">H1*2</f>
-        <v>2</v>
+        <f t="shared" ref="K1:L1" si="0">H1*20</f>
+        <v>20</v>
       </c>
       <c r="L1">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>20</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.4">
@@ -451,7 +451,7 @@
         <v>0</v>
       </c>
       <c r="D2">
-        <v>0.78</v>
+        <v>0</v>
       </c>
       <c r="E2">
         <v>0</v>
@@ -460,7 +460,7 @@
         <v>0</v>
       </c>
       <c r="G2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H2">
         <v>1</v>
@@ -469,16 +469,16 @@
         <v>1</v>
       </c>
       <c r="J2">
-        <f t="shared" ref="J2:J27" si="1">G2*2</f>
-        <v>4</v>
+        <f t="shared" ref="J2:J27" si="1">G2*20</f>
+        <v>20</v>
       </c>
       <c r="K2">
-        <f t="shared" ref="K2:K27" si="2">H2*2</f>
-        <v>2</v>
+        <f t="shared" ref="K2:K27" si="2">H2*20</f>
+        <v>20</v>
       </c>
       <c r="L2">
-        <f t="shared" ref="L2:L27" si="3">I2*2</f>
-        <v>2</v>
+        <f t="shared" ref="L2:L27" si="3">I2*20</f>
+        <v>20</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.4">
@@ -492,7 +492,7 @@
         <v>0</v>
       </c>
       <c r="D3">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="E3">
         <v>0</v>
@@ -501,7 +501,7 @@
         <v>0</v>
       </c>
       <c r="G3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H3">
         <v>1</v>
@@ -511,15 +511,15 @@
       </c>
       <c r="J3">
         <f t="shared" si="1"/>
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="K3">
         <f t="shared" si="2"/>
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="L3">
         <f t="shared" si="3"/>
-        <v>2</v>
+        <v>20</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.4">
@@ -536,7 +536,7 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>0.78</v>
+        <v>0</v>
       </c>
       <c r="F4">
         <v>0</v>
@@ -545,22 +545,22 @@
         <v>1</v>
       </c>
       <c r="H4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I4">
         <v>1</v>
       </c>
       <c r="J4">
         <f t="shared" si="1"/>
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="K4">
         <f t="shared" si="2"/>
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="L4">
         <f t="shared" si="3"/>
-        <v>2</v>
+        <v>20</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.4">
@@ -577,7 +577,7 @@
         <v>0</v>
       </c>
       <c r="E5">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="F5">
         <v>0</v>
@@ -586,22 +586,22 @@
         <v>1</v>
       </c>
       <c r="H5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I5">
         <v>1</v>
       </c>
       <c r="J5">
         <f t="shared" si="1"/>
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="K5">
         <f t="shared" si="2"/>
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="L5">
         <f t="shared" si="3"/>
-        <v>2</v>
+        <v>20</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.4">
@@ -615,34 +615,34 @@
         <v>0</v>
       </c>
       <c r="D6">
-        <v>0.78</v>
+        <v>0</v>
       </c>
       <c r="E6">
-        <v>0.78</v>
+        <v>0</v>
       </c>
       <c r="F6">
         <v>0</v>
       </c>
       <c r="G6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I6">
         <v>1</v>
       </c>
       <c r="J6">
         <f t="shared" si="1"/>
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="K6">
         <f t="shared" si="2"/>
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="L6">
         <f t="shared" si="3"/>
-        <v>2</v>
+        <v>20</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.4">
@@ -656,34 +656,34 @@
         <v>0</v>
       </c>
       <c r="D7">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="E7">
-        <v>0.78</v>
+        <v>0</v>
       </c>
       <c r="F7">
         <v>0</v>
       </c>
       <c r="G7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I7">
         <v>1</v>
       </c>
       <c r="J7">
         <f t="shared" si="1"/>
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="K7">
         <f t="shared" si="2"/>
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="L7">
         <f t="shared" si="3"/>
-        <v>2</v>
+        <v>20</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.4">
@@ -697,34 +697,34 @@
         <v>0</v>
       </c>
       <c r="D8">
-        <v>0.78</v>
+        <v>0</v>
       </c>
       <c r="E8">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="F8">
         <v>0</v>
       </c>
       <c r="G8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I8">
         <v>1</v>
       </c>
       <c r="J8">
         <f t="shared" si="1"/>
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="K8">
         <f t="shared" si="2"/>
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="L8">
         <f t="shared" si="3"/>
-        <v>2</v>
+        <v>20</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.4">
@@ -738,34 +738,34 @@
         <v>0</v>
       </c>
       <c r="D9">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="E9">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="F9">
         <v>0</v>
       </c>
       <c r="G9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I9">
         <v>1</v>
       </c>
       <c r="J9">
         <f t="shared" si="1"/>
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="K9">
         <f t="shared" si="2"/>
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="L9">
         <f t="shared" si="3"/>
-        <v>2</v>
+        <v>20</v>
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.4">
@@ -785,7 +785,7 @@
         <v>0</v>
       </c>
       <c r="F10">
-        <v>0.78</v>
+        <v>0</v>
       </c>
       <c r="G10">
         <v>1</v>
@@ -794,19 +794,19 @@
         <v>1</v>
       </c>
       <c r="I10">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J10">
         <f t="shared" si="1"/>
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="K10">
         <f t="shared" si="2"/>
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="L10">
         <f t="shared" si="3"/>
-        <v>4</v>
+        <v>20</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.4">
@@ -820,34 +820,34 @@
         <v>100</v>
       </c>
       <c r="D11">
-        <v>0.78</v>
+        <v>0</v>
       </c>
       <c r="E11">
         <v>0</v>
       </c>
       <c r="F11">
-        <v>0.78</v>
+        <v>0</v>
       </c>
       <c r="G11">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H11">
         <v>1</v>
       </c>
       <c r="I11">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J11">
         <f t="shared" si="1"/>
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="K11">
         <f t="shared" si="2"/>
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="L11">
         <f t="shared" si="3"/>
-        <v>4</v>
+        <v>20</v>
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.4">
@@ -861,34 +861,34 @@
         <v>100</v>
       </c>
       <c r="D12">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="E12">
         <v>0</v>
       </c>
       <c r="F12">
-        <v>0.78</v>
+        <v>0</v>
       </c>
       <c r="G12">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H12">
         <v>1</v>
       </c>
       <c r="I12">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J12">
         <f t="shared" si="1"/>
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="K12">
         <f t="shared" si="2"/>
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="L12">
         <f t="shared" si="3"/>
-        <v>4</v>
+        <v>20</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.4">
@@ -905,31 +905,31 @@
         <v>0</v>
       </c>
       <c r="E13">
-        <v>0.78</v>
+        <v>0</v>
       </c>
       <c r="F13">
-        <v>0.78</v>
+        <v>0</v>
       </c>
       <c r="G13">
         <v>1</v>
       </c>
       <c r="H13">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I13">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J13">
         <f t="shared" si="1"/>
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="K13">
         <f t="shared" si="2"/>
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="L13">
         <f t="shared" si="3"/>
-        <v>4</v>
+        <v>20</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.4">
@@ -946,31 +946,31 @@
         <v>0</v>
       </c>
       <c r="E14">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="F14">
-        <v>0.78</v>
+        <v>0</v>
       </c>
       <c r="G14">
         <v>1</v>
       </c>
       <c r="H14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J14">
         <f t="shared" si="1"/>
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="K14">
         <f t="shared" si="2"/>
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="L14">
         <f t="shared" si="3"/>
-        <v>4</v>
+        <v>20</v>
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.4">
@@ -984,34 +984,34 @@
         <v>100</v>
       </c>
       <c r="D15">
-        <v>0.78</v>
+        <v>0</v>
       </c>
       <c r="E15">
-        <v>0.78</v>
+        <v>0</v>
       </c>
       <c r="F15">
-        <v>0.78</v>
+        <v>0</v>
       </c>
       <c r="G15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J15">
         <f t="shared" si="1"/>
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="K15">
         <f t="shared" si="2"/>
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="L15">
         <f t="shared" si="3"/>
-        <v>4</v>
+        <v>20</v>
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.4">
@@ -1025,34 +1025,34 @@
         <v>100</v>
       </c>
       <c r="D16">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="E16">
-        <v>0.78</v>
+        <v>0</v>
       </c>
       <c r="F16">
-        <v>0.78</v>
+        <v>0</v>
       </c>
       <c r="G16">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H16">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I16">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J16">
         <f t="shared" si="1"/>
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="K16">
         <f t="shared" si="2"/>
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="L16">
         <f t="shared" si="3"/>
-        <v>4</v>
+        <v>20</v>
       </c>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.4">
@@ -1066,34 +1066,34 @@
         <v>100</v>
       </c>
       <c r="D17">
-        <v>0.78</v>
+        <v>0</v>
       </c>
       <c r="E17">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="F17">
-        <v>0.78</v>
+        <v>0</v>
       </c>
       <c r="G17">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H17">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I17">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J17">
         <f t="shared" si="1"/>
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="K17">
         <f t="shared" si="2"/>
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="L17">
         <f t="shared" si="3"/>
-        <v>4</v>
+        <v>20</v>
       </c>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.4">
@@ -1107,34 +1107,34 @@
         <v>100</v>
       </c>
       <c r="D18">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="E18">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="F18">
-        <v>0.78</v>
+        <v>0</v>
       </c>
       <c r="G18">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H18">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I18">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J18">
         <f t="shared" si="1"/>
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="K18">
         <f t="shared" si="2"/>
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="L18">
         <f t="shared" si="3"/>
-        <v>4</v>
+        <v>20</v>
       </c>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.4">
@@ -1154,7 +1154,7 @@
         <v>0</v>
       </c>
       <c r="F19">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="G19">
         <v>1</v>
@@ -1163,19 +1163,19 @@
         <v>1</v>
       </c>
       <c r="I19">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J19">
         <f t="shared" si="1"/>
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="K19">
         <f t="shared" si="2"/>
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="L19">
         <f t="shared" si="3"/>
-        <v>4</v>
+        <v>20</v>
       </c>
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.4">
@@ -1189,34 +1189,34 @@
         <v>-100</v>
       </c>
       <c r="D20">
-        <v>0.78</v>
+        <v>0</v>
       </c>
       <c r="E20">
         <v>0</v>
       </c>
       <c r="F20">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="G20">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H20">
         <v>1</v>
       </c>
       <c r="I20">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J20">
         <f t="shared" si="1"/>
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="K20">
         <f t="shared" si="2"/>
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="L20">
         <f t="shared" si="3"/>
-        <v>4</v>
+        <v>20</v>
       </c>
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.4">
@@ -1230,34 +1230,34 @@
         <v>-100</v>
       </c>
       <c r="D21">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="E21">
         <v>0</v>
       </c>
       <c r="F21">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="G21">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H21">
         <v>1</v>
       </c>
       <c r="I21">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J21">
         <f t="shared" si="1"/>
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="K21">
         <f t="shared" si="2"/>
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="L21">
         <f t="shared" si="3"/>
-        <v>4</v>
+        <v>20</v>
       </c>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.4">
@@ -1274,31 +1274,31 @@
         <v>0</v>
       </c>
       <c r="E22">
-        <v>0.78</v>
+        <v>0</v>
       </c>
       <c r="F22">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="G22">
         <v>1</v>
       </c>
       <c r="H22">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I22">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J22">
         <f t="shared" si="1"/>
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="K22">
         <f t="shared" si="2"/>
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="L22">
         <f t="shared" si="3"/>
-        <v>4</v>
+        <v>20</v>
       </c>
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.4">
@@ -1315,31 +1315,31 @@
         <v>0</v>
       </c>
       <c r="E23">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="F23">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="G23">
         <v>1</v>
       </c>
       <c r="H23">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I23">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J23">
         <f t="shared" si="1"/>
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="K23">
         <f t="shared" si="2"/>
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="L23">
         <f t="shared" si="3"/>
-        <v>4</v>
+        <v>20</v>
       </c>
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.4">
@@ -1353,34 +1353,34 @@
         <v>-100</v>
       </c>
       <c r="D24">
-        <v>0.78</v>
+        <v>0</v>
       </c>
       <c r="E24">
-        <v>0.78</v>
+        <v>0</v>
       </c>
       <c r="F24">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="G24">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H24">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I24">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J24">
         <f t="shared" si="1"/>
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="K24">
         <f t="shared" si="2"/>
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="L24">
         <f t="shared" si="3"/>
-        <v>4</v>
+        <v>20</v>
       </c>
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.4">
@@ -1394,34 +1394,34 @@
         <v>-100</v>
       </c>
       <c r="D25">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="E25">
-        <v>0.78</v>
+        <v>0</v>
       </c>
       <c r="F25">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="G25">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H25">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I25">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J25">
         <f t="shared" si="1"/>
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="K25">
         <f t="shared" si="2"/>
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="L25">
         <f t="shared" si="3"/>
-        <v>4</v>
+        <v>20</v>
       </c>
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.4">
@@ -1435,34 +1435,34 @@
         <v>-100</v>
       </c>
       <c r="D26">
-        <v>0.78</v>
+        <v>0</v>
       </c>
       <c r="E26">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="F26">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="G26">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H26">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I26">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J26">
         <f t="shared" si="1"/>
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="K26">
         <f t="shared" si="2"/>
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="L26">
         <f t="shared" si="3"/>
-        <v>4</v>
+        <v>20</v>
       </c>
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.4">
@@ -1476,34 +1476,34 @@
         <v>-100</v>
       </c>
       <c r="D27">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="E27">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="F27">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="G27">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H27">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I27">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J27">
         <f t="shared" si="1"/>
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="K27">
         <f t="shared" si="2"/>
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="L27">
         <f t="shared" si="3"/>
-        <v>4</v>
+        <v>20</v>
       </c>
     </row>
   </sheetData>

--- a/ActionGame-リファクタリング-/Data/CSV/Stage/Stage.xlsx
+++ b/ActionGame-リファクタリング-/Data/CSV/Stage/Stage.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\2409404\Desktop\GameProject\ActionGame-リファクタリング-\Data\CSV\Stage\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60E85ED2-C4FD-431C-9C0F-10DDC9FC2CF9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43986174-F172-4118-BDDB-FEEF2944ED11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{62A58253-9505-4C17-A0D0-B4C12E04E8CC}"/>
   </bookViews>
@@ -419,17 +419,17 @@
         <v>0</v>
       </c>
       <c r="G1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H1">
         <v>1</v>
       </c>
       <c r="I1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J1">
         <f>G1*20</f>
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="K1">
         <f t="shared" ref="K1:L1" si="0">H1*20</f>
@@ -437,12 +437,12 @@
       </c>
       <c r="L1">
         <f t="shared" si="0"/>
-        <v>20</v>
+        <v>40</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A2">
-        <v>100</v>
+        <v>40</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -460,17 +460,17 @@
         <v>0</v>
       </c>
       <c r="G2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H2">
         <v>1</v>
       </c>
       <c r="I2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J2">
         <f t="shared" ref="J2:J27" si="1">G2*20</f>
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="K2">
         <f t="shared" ref="K2:K27" si="2">H2*20</f>
@@ -478,28 +478,10 @@
       </c>
       <c r="L2">
         <f t="shared" ref="L2:L27" si="3">I2*20</f>
-        <v>20</v>
+        <v>40</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="A3">
-        <v>-100</v>
-      </c>
-      <c r="B3">
-        <v>0</v>
-      </c>
-      <c r="C3">
-        <v>0</v>
-      </c>
-      <c r="D3">
-        <v>0</v>
-      </c>
-      <c r="E3">
-        <v>0</v>
-      </c>
-      <c r="F3">
-        <v>0</v>
-      </c>
       <c r="G3">
         <v>1</v>
       </c>
@@ -523,24 +505,6 @@
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="A4">
-        <v>0</v>
-      </c>
-      <c r="B4">
-        <v>100</v>
-      </c>
-      <c r="C4">
-        <v>0</v>
-      </c>
-      <c r="D4">
-        <v>0</v>
-      </c>
-      <c r="E4">
-        <v>0</v>
-      </c>
-      <c r="F4">
-        <v>0</v>
-      </c>
       <c r="G4">
         <v>1</v>
       </c>
@@ -564,24 +528,6 @@
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="A5">
-        <v>0</v>
-      </c>
-      <c r="B5">
-        <v>-100</v>
-      </c>
-      <c r="C5">
-        <v>0</v>
-      </c>
-      <c r="D5">
-        <v>0</v>
-      </c>
-      <c r="E5">
-        <v>0</v>
-      </c>
-      <c r="F5">
-        <v>0</v>
-      </c>
       <c r="G5">
         <v>1</v>
       </c>
@@ -605,24 +551,6 @@
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="A6">
-        <v>100</v>
-      </c>
-      <c r="B6">
-        <v>100</v>
-      </c>
-      <c r="C6">
-        <v>0</v>
-      </c>
-      <c r="D6">
-        <v>0</v>
-      </c>
-      <c r="E6">
-        <v>0</v>
-      </c>
-      <c r="F6">
-        <v>0</v>
-      </c>
       <c r="G6">
         <v>1</v>
       </c>
@@ -646,24 +574,6 @@
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="A7">
-        <v>-100</v>
-      </c>
-      <c r="B7">
-        <v>100</v>
-      </c>
-      <c r="C7">
-        <v>0</v>
-      </c>
-      <c r="D7">
-        <v>0</v>
-      </c>
-      <c r="E7">
-        <v>0</v>
-      </c>
-      <c r="F7">
-        <v>0</v>
-      </c>
       <c r="G7">
         <v>1</v>
       </c>
@@ -687,24 +597,6 @@
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="A8">
-        <v>100</v>
-      </c>
-      <c r="B8">
-        <v>-100</v>
-      </c>
-      <c r="C8">
-        <v>0</v>
-      </c>
-      <c r="D8">
-        <v>0</v>
-      </c>
-      <c r="E8">
-        <v>0</v>
-      </c>
-      <c r="F8">
-        <v>0</v>
-      </c>
       <c r="G8">
         <v>1</v>
       </c>
@@ -728,24 +620,6 @@
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="A9">
-        <v>-100</v>
-      </c>
-      <c r="B9">
-        <v>-100</v>
-      </c>
-      <c r="C9">
-        <v>0</v>
-      </c>
-      <c r="D9">
-        <v>0</v>
-      </c>
-      <c r="E9">
-        <v>0</v>
-      </c>
-      <c r="F9">
-        <v>0</v>
-      </c>
       <c r="G9">
         <v>1</v>
       </c>
@@ -769,24 +643,6 @@
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="A10">
-        <v>0</v>
-      </c>
-      <c r="B10">
-        <v>0</v>
-      </c>
-      <c r="C10">
-        <v>100</v>
-      </c>
-      <c r="D10">
-        <v>0</v>
-      </c>
-      <c r="E10">
-        <v>0</v>
-      </c>
-      <c r="F10">
-        <v>0</v>
-      </c>
       <c r="G10">
         <v>1</v>
       </c>
@@ -810,24 +666,6 @@
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="A11">
-        <v>100</v>
-      </c>
-      <c r="B11">
-        <v>0</v>
-      </c>
-      <c r="C11">
-        <v>100</v>
-      </c>
-      <c r="D11">
-        <v>0</v>
-      </c>
-      <c r="E11">
-        <v>0</v>
-      </c>
-      <c r="F11">
-        <v>0</v>
-      </c>
       <c r="G11">
         <v>1</v>
       </c>
@@ -851,24 +689,6 @@
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="A12">
-        <v>-100</v>
-      </c>
-      <c r="B12">
-        <v>0</v>
-      </c>
-      <c r="C12">
-        <v>100</v>
-      </c>
-      <c r="D12">
-        <v>0</v>
-      </c>
-      <c r="E12">
-        <v>0</v>
-      </c>
-      <c r="F12">
-        <v>0</v>
-      </c>
       <c r="G12">
         <v>1</v>
       </c>
@@ -892,24 +712,6 @@
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="A13">
-        <v>0</v>
-      </c>
-      <c r="B13">
-        <v>100</v>
-      </c>
-      <c r="C13">
-        <v>100</v>
-      </c>
-      <c r="D13">
-        <v>0</v>
-      </c>
-      <c r="E13">
-        <v>0</v>
-      </c>
-      <c r="F13">
-        <v>0</v>
-      </c>
       <c r="G13">
         <v>1</v>
       </c>
@@ -933,24 +735,6 @@
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="A14">
-        <v>0</v>
-      </c>
-      <c r="B14">
-        <v>-100</v>
-      </c>
-      <c r="C14">
-        <v>100</v>
-      </c>
-      <c r="D14">
-        <v>0</v>
-      </c>
-      <c r="E14">
-        <v>0</v>
-      </c>
-      <c r="F14">
-        <v>0</v>
-      </c>
       <c r="G14">
         <v>1</v>
       </c>
@@ -974,24 +758,6 @@
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="A15">
-        <v>100</v>
-      </c>
-      <c r="B15">
-        <v>100</v>
-      </c>
-      <c r="C15">
-        <v>100</v>
-      </c>
-      <c r="D15">
-        <v>0</v>
-      </c>
-      <c r="E15">
-        <v>0</v>
-      </c>
-      <c r="F15">
-        <v>0</v>
-      </c>
       <c r="G15">
         <v>1</v>
       </c>
@@ -1015,24 +781,6 @@
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="A16">
-        <v>-100</v>
-      </c>
-      <c r="B16">
-        <v>100</v>
-      </c>
-      <c r="C16">
-        <v>100</v>
-      </c>
-      <c r="D16">
-        <v>0</v>
-      </c>
-      <c r="E16">
-        <v>0</v>
-      </c>
-      <c r="F16">
-        <v>0</v>
-      </c>
       <c r="G16">
         <v>1</v>
       </c>
@@ -1055,25 +803,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="A17">
-        <v>100</v>
-      </c>
-      <c r="B17">
-        <v>-100</v>
-      </c>
-      <c r="C17">
-        <v>100</v>
-      </c>
-      <c r="D17">
-        <v>0</v>
-      </c>
-      <c r="E17">
-        <v>0</v>
-      </c>
-      <c r="F17">
-        <v>0</v>
-      </c>
+    <row r="17" spans="7:12" x14ac:dyDescent="0.4">
       <c r="G17">
         <v>1</v>
       </c>
@@ -1096,25 +826,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="A18">
-        <v>-100</v>
-      </c>
-      <c r="B18">
-        <v>-100</v>
-      </c>
-      <c r="C18">
-        <v>100</v>
-      </c>
-      <c r="D18">
-        <v>0</v>
-      </c>
-      <c r="E18">
-        <v>0</v>
-      </c>
-      <c r="F18">
-        <v>0</v>
-      </c>
+    <row r="18" spans="7:12" x14ac:dyDescent="0.4">
       <c r="G18">
         <v>1</v>
       </c>
@@ -1137,25 +849,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="A19">
-        <v>0</v>
-      </c>
-      <c r="B19">
-        <v>0</v>
-      </c>
-      <c r="C19">
-        <v>-100</v>
-      </c>
-      <c r="D19">
-        <v>0</v>
-      </c>
-      <c r="E19">
-        <v>0</v>
-      </c>
-      <c r="F19">
-        <v>0</v>
-      </c>
+    <row r="19" spans="7:12" x14ac:dyDescent="0.4">
       <c r="G19">
         <v>1</v>
       </c>
@@ -1178,25 +872,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="A20">
-        <v>100</v>
-      </c>
-      <c r="B20">
-        <v>0</v>
-      </c>
-      <c r="C20">
-        <v>-100</v>
-      </c>
-      <c r="D20">
-        <v>0</v>
-      </c>
-      <c r="E20">
-        <v>0</v>
-      </c>
-      <c r="F20">
-        <v>0</v>
-      </c>
+    <row r="20" spans="7:12" x14ac:dyDescent="0.4">
       <c r="G20">
         <v>1</v>
       </c>
@@ -1219,25 +895,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="A21">
-        <v>-100</v>
-      </c>
-      <c r="B21">
-        <v>0</v>
-      </c>
-      <c r="C21">
-        <v>-100</v>
-      </c>
-      <c r="D21">
-        <v>0</v>
-      </c>
-      <c r="E21">
-        <v>0</v>
-      </c>
-      <c r="F21">
-        <v>0</v>
-      </c>
+    <row r="21" spans="7:12" x14ac:dyDescent="0.4">
       <c r="G21">
         <v>1</v>
       </c>
@@ -1260,25 +918,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="A22">
-        <v>0</v>
-      </c>
-      <c r="B22">
-        <v>100</v>
-      </c>
-      <c r="C22">
-        <v>-100</v>
-      </c>
-      <c r="D22">
-        <v>0</v>
-      </c>
-      <c r="E22">
-        <v>0</v>
-      </c>
-      <c r="F22">
-        <v>0</v>
-      </c>
+    <row r="22" spans="7:12" x14ac:dyDescent="0.4">
       <c r="G22">
         <v>1</v>
       </c>
@@ -1301,25 +941,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="A23">
-        <v>0</v>
-      </c>
-      <c r="B23">
-        <v>-100</v>
-      </c>
-      <c r="C23">
-        <v>-100</v>
-      </c>
-      <c r="D23">
-        <v>0</v>
-      </c>
-      <c r="E23">
-        <v>0</v>
-      </c>
-      <c r="F23">
-        <v>0</v>
-      </c>
+    <row r="23" spans="7:12" x14ac:dyDescent="0.4">
       <c r="G23">
         <v>1</v>
       </c>
@@ -1342,25 +964,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="A24">
-        <v>100</v>
-      </c>
-      <c r="B24">
-        <v>100</v>
-      </c>
-      <c r="C24">
-        <v>-100</v>
-      </c>
-      <c r="D24">
-        <v>0</v>
-      </c>
-      <c r="E24">
-        <v>0</v>
-      </c>
-      <c r="F24">
-        <v>0</v>
-      </c>
+    <row r="24" spans="7:12" x14ac:dyDescent="0.4">
       <c r="G24">
         <v>1</v>
       </c>
@@ -1383,25 +987,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="A25">
-        <v>-100</v>
-      </c>
-      <c r="B25">
-        <v>100</v>
-      </c>
-      <c r="C25">
-        <v>-100</v>
-      </c>
-      <c r="D25">
-        <v>0</v>
-      </c>
-      <c r="E25">
-        <v>0</v>
-      </c>
-      <c r="F25">
-        <v>0</v>
-      </c>
+    <row r="25" spans="7:12" x14ac:dyDescent="0.4">
       <c r="G25">
         <v>1</v>
       </c>
@@ -1424,25 +1010,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="A26">
-        <v>100</v>
-      </c>
-      <c r="B26">
-        <v>-100</v>
-      </c>
-      <c r="C26">
-        <v>-100</v>
-      </c>
-      <c r="D26">
-        <v>0</v>
-      </c>
-      <c r="E26">
-        <v>0</v>
-      </c>
-      <c r="F26">
-        <v>0</v>
-      </c>
+    <row r="26" spans="7:12" x14ac:dyDescent="0.4">
       <c r="G26">
         <v>1</v>
       </c>
@@ -1465,25 +1033,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="A27">
-        <v>-100</v>
-      </c>
-      <c r="B27">
-        <v>-100</v>
-      </c>
-      <c r="C27">
-        <v>-100</v>
-      </c>
-      <c r="D27">
-        <v>0</v>
-      </c>
-      <c r="E27">
-        <v>0</v>
-      </c>
-      <c r="F27">
-        <v>0</v>
-      </c>
+    <row r="27" spans="7:12" x14ac:dyDescent="0.4">
       <c r="G27">
         <v>1</v>
       </c>

--- a/ActionGame-リファクタリング-/Data/CSV/Stage/Stage.xlsx
+++ b/ActionGame-リファクタリング-/Data/CSV/Stage/Stage.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\2409404\Desktop\GameProject\ActionGame-リファクタリング-\Data\CSV\Stage\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ita20\OneDrive\デスクトップ\GameProject\ActionGame-リファクタリング-\Data\CSV\Stage\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43986174-F172-4118-BDDB-FEEF2944ED11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9490E59B-2444-40D3-A899-25FF6C93663B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{62A58253-9505-4C17-A0D0-B4C12E04E8CC}"/>
+    <workbookView xWindow="3060" yWindow="3180" windowWidth="21600" windowHeight="11295" xr2:uid="{62A58253-9505-4C17-A0D0-B4C12E04E8CC}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -96,9 +96,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office テーマ">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 テーマ">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -136,7 +136,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -242,7 +242,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -384,7 +384,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -392,10 +392,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{592BFE65-1919-4E86-A258-49B12076C0A7}">
-  <dimension ref="A1:L27"/>
+  <dimension ref="A1:L100"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="12" width="3.625" customWidth="1"/>
+    <col min="1" max="12" width="5.625" customWidth="1"/>
     <col min="13" max="13" width="9" customWidth="1"/>
   </cols>
   <sheetData>
@@ -407,7 +407,7 @@
         <v>0</v>
       </c>
       <c r="C1">
-        <v>0</v>
+        <v>-20</v>
       </c>
       <c r="D1">
         <v>0</v>
@@ -419,17 +419,17 @@
         <v>0</v>
       </c>
       <c r="G1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H1">
         <v>1</v>
       </c>
       <c r="I1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J1">
         <f>G1*20</f>
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="K1">
         <f t="shared" ref="K1:L1" si="0">H1*20</f>
@@ -437,18 +437,18 @@
       </c>
       <c r="L1">
         <f t="shared" si="0"/>
-        <v>40</v>
+        <v>20</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A2">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="B2">
         <v>0</v>
       </c>
       <c r="C2">
-        <v>0</v>
+        <v>-40</v>
       </c>
       <c r="D2">
         <v>0</v>
@@ -460,17 +460,17 @@
         <v>0</v>
       </c>
       <c r="G2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H2">
         <v>1</v>
       </c>
       <c r="I2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J2">
         <f t="shared" ref="J2:J27" si="1">G2*20</f>
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="K2">
         <f t="shared" ref="K2:K27" si="2">H2*20</f>
@@ -478,12 +478,30 @@
       </c>
       <c r="L2">
         <f t="shared" ref="L2:L27" si="3">I2*20</f>
-        <v>40</v>
+        <v>20</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A3">
+        <v>0</v>
+      </c>
+      <c r="B3">
+        <v>0</v>
+      </c>
+      <c r="C3">
+        <v>-60</v>
+      </c>
+      <c r="D3">
+        <v>0</v>
+      </c>
+      <c r="E3">
+        <v>0</v>
+      </c>
+      <c r="F3">
+        <v>0</v>
+      </c>
       <c r="G3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H3">
         <v>1</v>
@@ -493,7 +511,7 @@
       </c>
       <c r="J3">
         <f t="shared" si="1"/>
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="K3">
         <f t="shared" si="2"/>
@@ -505,8 +523,26 @@
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A4">
+        <v>0</v>
+      </c>
+      <c r="B4">
+        <v>0</v>
+      </c>
+      <c r="C4">
+        <v>-80</v>
+      </c>
+      <c r="D4">
+        <v>0</v>
+      </c>
+      <c r="E4">
+        <v>0</v>
+      </c>
+      <c r="F4">
+        <v>0</v>
+      </c>
       <c r="G4">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H4">
         <v>1</v>
@@ -516,7 +552,7 @@
       </c>
       <c r="J4">
         <f t="shared" si="1"/>
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="K4">
         <f t="shared" si="2"/>
@@ -528,6 +564,24 @@
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A5">
+        <v>20</v>
+      </c>
+      <c r="B5">
+        <v>20</v>
+      </c>
+      <c r="C5">
+        <v>-140</v>
+      </c>
+      <c r="D5">
+        <v>0</v>
+      </c>
+      <c r="E5">
+        <v>0</v>
+      </c>
+      <c r="F5">
+        <v>0</v>
+      </c>
       <c r="G5">
         <v>1</v>
       </c>
@@ -535,7 +589,7 @@
         <v>1</v>
       </c>
       <c r="I5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J5">
         <f t="shared" si="1"/>
@@ -547,10 +601,28 @@
       </c>
       <c r="L5">
         <f t="shared" si="3"/>
-        <v>20</v>
+        <v>60</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A6">
+        <v>0</v>
+      </c>
+      <c r="B6">
+        <v>20</v>
+      </c>
+      <c r="C6">
+        <v>-140</v>
+      </c>
+      <c r="D6">
+        <v>0</v>
+      </c>
+      <c r="E6">
+        <v>0</v>
+      </c>
+      <c r="F6">
+        <v>0</v>
+      </c>
       <c r="G6">
         <v>1</v>
       </c>
@@ -558,7 +630,7 @@
         <v>1</v>
       </c>
       <c r="I6">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J6">
         <f t="shared" si="1"/>
@@ -570,10 +642,28 @@
       </c>
       <c r="L6">
         <f t="shared" si="3"/>
-        <v>20</v>
+        <v>60</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A7">
+        <v>-20</v>
+      </c>
+      <c r="B7">
+        <v>20</v>
+      </c>
+      <c r="C7">
+        <v>-140</v>
+      </c>
+      <c r="D7">
+        <v>0</v>
+      </c>
+      <c r="E7">
+        <v>0</v>
+      </c>
+      <c r="F7">
+        <v>0</v>
+      </c>
       <c r="G7">
         <v>1</v>
       </c>
@@ -581,7 +671,7 @@
         <v>1</v>
       </c>
       <c r="I7">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J7">
         <f t="shared" si="1"/>
@@ -593,10 +683,28 @@
       </c>
       <c r="L7">
         <f t="shared" si="3"/>
-        <v>20</v>
+        <v>60</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A8">
+        <v>-40</v>
+      </c>
+      <c r="B8">
+        <v>20</v>
+      </c>
+      <c r="C8">
+        <v>-140</v>
+      </c>
+      <c r="D8">
+        <v>0</v>
+      </c>
+      <c r="E8">
+        <v>0</v>
+      </c>
+      <c r="F8">
+        <v>0</v>
+      </c>
       <c r="G8">
         <v>1</v>
       </c>
@@ -604,7 +712,7 @@
         <v>1</v>
       </c>
       <c r="I8">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J8">
         <f t="shared" si="1"/>
@@ -616,10 +724,28 @@
       </c>
       <c r="L8">
         <f t="shared" si="3"/>
-        <v>20</v>
+        <v>60</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A9">
+        <v>-60</v>
+      </c>
+      <c r="B9">
+        <v>20</v>
+      </c>
+      <c r="C9">
+        <v>-140</v>
+      </c>
+      <c r="D9">
+        <v>0</v>
+      </c>
+      <c r="E9">
+        <v>0</v>
+      </c>
+      <c r="F9">
+        <v>0</v>
+      </c>
       <c r="G9">
         <v>1</v>
       </c>
@@ -627,7 +753,7 @@
         <v>1</v>
       </c>
       <c r="I9">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J9">
         <f t="shared" si="1"/>
@@ -639,10 +765,28 @@
       </c>
       <c r="L9">
         <f t="shared" si="3"/>
-        <v>20</v>
+        <v>60</v>
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A10">
+        <v>-80</v>
+      </c>
+      <c r="B10">
+        <v>20</v>
+      </c>
+      <c r="C10">
+        <v>-140</v>
+      </c>
+      <c r="D10">
+        <v>0</v>
+      </c>
+      <c r="E10">
+        <v>0</v>
+      </c>
+      <c r="F10">
+        <v>0</v>
+      </c>
       <c r="G10">
         <v>1</v>
       </c>
@@ -650,7 +794,7 @@
         <v>1</v>
       </c>
       <c r="I10">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J10">
         <f t="shared" si="1"/>
@@ -662,10 +806,28 @@
       </c>
       <c r="L10">
         <f t="shared" si="3"/>
-        <v>20</v>
+        <v>60</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A11">
+        <v>-100</v>
+      </c>
+      <c r="B11">
+        <v>20</v>
+      </c>
+      <c r="C11">
+        <v>-140</v>
+      </c>
+      <c r="D11">
+        <v>0</v>
+      </c>
+      <c r="E11">
+        <v>0</v>
+      </c>
+      <c r="F11">
+        <v>0</v>
+      </c>
       <c r="G11">
         <v>1</v>
       </c>
@@ -673,7 +835,7 @@
         <v>1</v>
       </c>
       <c r="I11">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J11">
         <f t="shared" si="1"/>
@@ -685,10 +847,28 @@
       </c>
       <c r="L11">
         <f t="shared" si="3"/>
-        <v>20</v>
+        <v>60</v>
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A12">
+        <v>-120</v>
+      </c>
+      <c r="B12">
+        <v>20</v>
+      </c>
+      <c r="C12">
+        <v>-140</v>
+      </c>
+      <c r="D12">
+        <v>0</v>
+      </c>
+      <c r="E12">
+        <v>0</v>
+      </c>
+      <c r="F12">
+        <v>0</v>
+      </c>
       <c r="G12">
         <v>1</v>
       </c>
@@ -696,7 +876,7 @@
         <v>1</v>
       </c>
       <c r="I12">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J12">
         <f t="shared" si="1"/>
@@ -708,10 +888,28 @@
       </c>
       <c r="L12">
         <f t="shared" si="3"/>
-        <v>20</v>
+        <v>60</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A13">
+        <v>-140</v>
+      </c>
+      <c r="B13">
+        <v>20</v>
+      </c>
+      <c r="C13">
+        <v>-140</v>
+      </c>
+      <c r="D13">
+        <v>0</v>
+      </c>
+      <c r="E13">
+        <v>0</v>
+      </c>
+      <c r="F13">
+        <v>0</v>
+      </c>
       <c r="G13">
         <v>1</v>
       </c>
@@ -719,7 +917,7 @@
         <v>1</v>
       </c>
       <c r="I13">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J13">
         <f t="shared" si="1"/>
@@ -731,10 +929,28 @@
       </c>
       <c r="L13">
         <f t="shared" si="3"/>
-        <v>20</v>
+        <v>60</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A14">
+        <v>-160</v>
+      </c>
+      <c r="B14">
+        <v>20</v>
+      </c>
+      <c r="C14">
+        <v>-140</v>
+      </c>
+      <c r="D14">
+        <v>0</v>
+      </c>
+      <c r="E14">
+        <v>0</v>
+      </c>
+      <c r="F14">
+        <v>0</v>
+      </c>
       <c r="G14">
         <v>1</v>
       </c>
@@ -742,7 +958,7 @@
         <v>1</v>
       </c>
       <c r="I14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J14">
         <f t="shared" si="1"/>
@@ -754,10 +970,28 @@
       </c>
       <c r="L14">
         <f t="shared" si="3"/>
-        <v>20</v>
+        <v>60</v>
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A15">
+        <v>-180</v>
+      </c>
+      <c r="B15">
+        <v>20</v>
+      </c>
+      <c r="C15">
+        <v>-140</v>
+      </c>
+      <c r="D15">
+        <v>0</v>
+      </c>
+      <c r="E15">
+        <v>0</v>
+      </c>
+      <c r="F15">
+        <v>0</v>
+      </c>
       <c r="G15">
         <v>1</v>
       </c>
@@ -765,7 +999,7 @@
         <v>1</v>
       </c>
       <c r="I15">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J15">
         <f t="shared" si="1"/>
@@ -777,10 +1011,28 @@
       </c>
       <c r="L15">
         <f t="shared" si="3"/>
-        <v>20</v>
+        <v>60</v>
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A16">
+        <v>-200</v>
+      </c>
+      <c r="B16">
+        <v>20</v>
+      </c>
+      <c r="C16">
+        <v>-140</v>
+      </c>
+      <c r="D16">
+        <v>0</v>
+      </c>
+      <c r="E16">
+        <v>0</v>
+      </c>
+      <c r="F16">
+        <v>0</v>
+      </c>
       <c r="G16">
         <v>1</v>
       </c>
@@ -788,7 +1040,7 @@
         <v>1</v>
       </c>
       <c r="I16">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J16">
         <f t="shared" si="1"/>
@@ -800,12 +1052,30 @@
       </c>
       <c r="L16">
         <f t="shared" si="3"/>
-        <v>20</v>
-      </c>
-    </row>
-    <row r="17" spans="7:12" x14ac:dyDescent="0.4">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A17">
+        <v>-180</v>
+      </c>
+      <c r="B17">
+        <v>20</v>
+      </c>
+      <c r="C17">
+        <v>-180</v>
+      </c>
+      <c r="D17">
+        <v>0</v>
+      </c>
+      <c r="E17">
+        <v>0</v>
+      </c>
+      <c r="F17">
+        <v>0</v>
+      </c>
       <c r="G17">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H17">
         <v>1</v>
@@ -815,7 +1085,7 @@
       </c>
       <c r="J17">
         <f t="shared" si="1"/>
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="K17">
         <f t="shared" si="2"/>
@@ -826,9 +1096,27 @@
         <v>20</v>
       </c>
     </row>
-    <row r="18" spans="7:12" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A18">
+        <v>-180</v>
+      </c>
+      <c r="B18">
+        <v>20</v>
+      </c>
+      <c r="C18">
+        <v>-200</v>
+      </c>
+      <c r="D18">
+        <v>0</v>
+      </c>
+      <c r="E18">
+        <v>0</v>
+      </c>
+      <c r="F18">
+        <v>0</v>
+      </c>
       <c r="G18">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H18">
         <v>1</v>
@@ -838,7 +1126,7 @@
       </c>
       <c r="J18">
         <f t="shared" si="1"/>
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="K18">
         <f t="shared" si="2"/>
@@ -849,9 +1137,27 @@
         <v>20</v>
       </c>
     </row>
-    <row r="19" spans="7:12" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A19">
+        <v>-180</v>
+      </c>
+      <c r="B19">
+        <v>20</v>
+      </c>
+      <c r="C19">
+        <v>-220</v>
+      </c>
+      <c r="D19">
+        <v>0</v>
+      </c>
+      <c r="E19">
+        <v>0</v>
+      </c>
+      <c r="F19">
+        <v>0</v>
+      </c>
       <c r="G19">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H19">
         <v>1</v>
@@ -861,7 +1167,7 @@
       </c>
       <c r="J19">
         <f t="shared" si="1"/>
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="K19">
         <f t="shared" si="2"/>
@@ -872,9 +1178,27 @@
         <v>20</v>
       </c>
     </row>
-    <row r="20" spans="7:12" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A20">
+        <v>-180</v>
+      </c>
+      <c r="B20">
+        <v>20</v>
+      </c>
+      <c r="C20">
+        <v>-240</v>
+      </c>
+      <c r="D20">
+        <v>0</v>
+      </c>
+      <c r="E20">
+        <v>0</v>
+      </c>
+      <c r="F20">
+        <v>0</v>
+      </c>
       <c r="G20">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H20">
         <v>1</v>
@@ -884,7 +1208,7 @@
       </c>
       <c r="J20">
         <f t="shared" si="1"/>
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="K20">
         <f t="shared" si="2"/>
@@ -895,9 +1219,27 @@
         <v>20</v>
       </c>
     </row>
-    <row r="21" spans="7:12" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A21">
+        <v>-180</v>
+      </c>
+      <c r="B21">
+        <v>20</v>
+      </c>
+      <c r="C21">
+        <v>-260</v>
+      </c>
+      <c r="D21">
+        <v>0</v>
+      </c>
+      <c r="E21">
+        <v>0</v>
+      </c>
+      <c r="F21">
+        <v>0</v>
+      </c>
       <c r="G21">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H21">
         <v>1</v>
@@ -907,7 +1249,7 @@
       </c>
       <c r="J21">
         <f t="shared" si="1"/>
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="K21">
         <f t="shared" si="2"/>
@@ -918,7 +1260,25 @@
         <v>20</v>
       </c>
     </row>
-    <row r="22" spans="7:12" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A22">
+        <v>-200</v>
+      </c>
+      <c r="B22">
+        <v>20</v>
+      </c>
+      <c r="C22">
+        <v>-300</v>
+      </c>
+      <c r="D22">
+        <v>0</v>
+      </c>
+      <c r="E22">
+        <v>0</v>
+      </c>
+      <c r="F22">
+        <v>0</v>
+      </c>
       <c r="G22">
         <v>1</v>
       </c>
@@ -926,7 +1286,7 @@
         <v>1</v>
       </c>
       <c r="I22">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J22">
         <f t="shared" si="1"/>
@@ -938,10 +1298,28 @@
       </c>
       <c r="L22">
         <f t="shared" si="3"/>
-        <v>20</v>
-      </c>
-    </row>
-    <row r="23" spans="7:12" x14ac:dyDescent="0.4">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A23">
+        <v>-180</v>
+      </c>
+      <c r="B23">
+        <v>20</v>
+      </c>
+      <c r="C23">
+        <v>-300</v>
+      </c>
+      <c r="D23">
+        <v>0</v>
+      </c>
+      <c r="E23">
+        <v>0</v>
+      </c>
+      <c r="F23">
+        <v>0</v>
+      </c>
       <c r="G23">
         <v>1</v>
       </c>
@@ -949,7 +1327,7 @@
         <v>1</v>
       </c>
       <c r="I23">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J23">
         <f t="shared" si="1"/>
@@ -961,10 +1339,28 @@
       </c>
       <c r="L23">
         <f t="shared" si="3"/>
-        <v>20</v>
-      </c>
-    </row>
-    <row r="24" spans="7:12" x14ac:dyDescent="0.4">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A24">
+        <v>-160</v>
+      </c>
+      <c r="B24">
+        <v>20</v>
+      </c>
+      <c r="C24">
+        <v>-300</v>
+      </c>
+      <c r="D24">
+        <v>0</v>
+      </c>
+      <c r="E24">
+        <v>0</v>
+      </c>
+      <c r="F24">
+        <v>0</v>
+      </c>
       <c r="G24">
         <v>1</v>
       </c>
@@ -972,7 +1368,7 @@
         <v>1</v>
       </c>
       <c r="I24">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J24">
         <f t="shared" si="1"/>
@@ -984,10 +1380,28 @@
       </c>
       <c r="L24">
         <f t="shared" si="3"/>
-        <v>20</v>
-      </c>
-    </row>
-    <row r="25" spans="7:12" x14ac:dyDescent="0.4">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A25">
+        <v>-140</v>
+      </c>
+      <c r="B25">
+        <v>20</v>
+      </c>
+      <c r="C25">
+        <v>-300</v>
+      </c>
+      <c r="D25">
+        <v>0</v>
+      </c>
+      <c r="E25">
+        <v>0</v>
+      </c>
+      <c r="F25">
+        <v>0</v>
+      </c>
       <c r="G25">
         <v>1</v>
       </c>
@@ -995,7 +1409,7 @@
         <v>1</v>
       </c>
       <c r="I25">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J25">
         <f t="shared" si="1"/>
@@ -1007,10 +1421,28 @@
       </c>
       <c r="L25">
         <f t="shared" si="3"/>
-        <v>20</v>
-      </c>
-    </row>
-    <row r="26" spans="7:12" x14ac:dyDescent="0.4">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A26">
+        <v>-120</v>
+      </c>
+      <c r="B26">
+        <v>20</v>
+      </c>
+      <c r="C26">
+        <v>-300</v>
+      </c>
+      <c r="D26">
+        <v>0</v>
+      </c>
+      <c r="E26">
+        <v>0</v>
+      </c>
+      <c r="F26">
+        <v>0</v>
+      </c>
       <c r="G26">
         <v>1</v>
       </c>
@@ -1018,7 +1450,7 @@
         <v>1</v>
       </c>
       <c r="I26">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J26">
         <f t="shared" si="1"/>
@@ -1030,10 +1462,28 @@
       </c>
       <c r="L26">
         <f t="shared" si="3"/>
-        <v>20</v>
-      </c>
-    </row>
-    <row r="27" spans="7:12" x14ac:dyDescent="0.4">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A27">
+        <v>-100</v>
+      </c>
+      <c r="B27">
+        <v>20</v>
+      </c>
+      <c r="C27">
+        <v>-300</v>
+      </c>
+      <c r="D27">
+        <v>0</v>
+      </c>
+      <c r="E27">
+        <v>0</v>
+      </c>
+      <c r="F27">
+        <v>0</v>
+      </c>
       <c r="G27">
         <v>1</v>
       </c>
@@ -1041,7 +1491,7 @@
         <v>1</v>
       </c>
       <c r="I27">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J27">
         <f t="shared" si="1"/>
@@ -1053,6 +1503,2531 @@
       </c>
       <c r="L27">
         <f t="shared" si="3"/>
+        <v>60</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A28">
+        <v>-60</v>
+      </c>
+      <c r="B28">
+        <v>40</v>
+      </c>
+      <c r="C28">
+        <v>-300</v>
+      </c>
+      <c r="D28">
+        <v>0</v>
+      </c>
+      <c r="E28">
+        <v>0</v>
+      </c>
+      <c r="F28">
+        <v>0</v>
+      </c>
+      <c r="G28">
+        <v>1</v>
+      </c>
+      <c r="H28">
+        <v>1</v>
+      </c>
+      <c r="I28">
+        <v>3</v>
+      </c>
+      <c r="J28">
+        <f t="shared" ref="J28:J91" si="4">G28*20</f>
+        <v>20</v>
+      </c>
+      <c r="K28">
+        <f t="shared" ref="K28:K91" si="5">H28*20</f>
+        <v>20</v>
+      </c>
+      <c r="L28">
+        <f t="shared" ref="L28:L91" si="6">I28*20</f>
+        <v>60</v>
+      </c>
+    </row>
+    <row r="29" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A29">
+        <v>-40</v>
+      </c>
+      <c r="B29">
+        <v>40</v>
+      </c>
+      <c r="C29">
+        <v>-300</v>
+      </c>
+      <c r="D29">
+        <v>0</v>
+      </c>
+      <c r="E29">
+        <v>0</v>
+      </c>
+      <c r="F29">
+        <v>0</v>
+      </c>
+      <c r="G29">
+        <v>1</v>
+      </c>
+      <c r="H29">
+        <v>1</v>
+      </c>
+      <c r="I29">
+        <v>3</v>
+      </c>
+      <c r="J29">
+        <f t="shared" si="4"/>
+        <v>20</v>
+      </c>
+      <c r="K29">
+        <f t="shared" si="5"/>
+        <v>20</v>
+      </c>
+      <c r="L29">
+        <f t="shared" si="6"/>
+        <v>60</v>
+      </c>
+    </row>
+    <row r="30" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A30">
+        <v>-20</v>
+      </c>
+      <c r="B30">
+        <v>40</v>
+      </c>
+      <c r="C30">
+        <v>-300</v>
+      </c>
+      <c r="D30">
+        <v>0</v>
+      </c>
+      <c r="E30">
+        <v>0</v>
+      </c>
+      <c r="F30">
+        <v>0</v>
+      </c>
+      <c r="G30">
+        <v>1</v>
+      </c>
+      <c r="H30">
+        <v>1</v>
+      </c>
+      <c r="I30">
+        <v>3</v>
+      </c>
+      <c r="J30">
+        <f t="shared" si="4"/>
+        <v>20</v>
+      </c>
+      <c r="K30">
+        <f t="shared" si="5"/>
+        <v>20</v>
+      </c>
+      <c r="L30">
+        <f t="shared" si="6"/>
+        <v>60</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A31">
+        <v>20</v>
+      </c>
+      <c r="B31">
+        <v>60</v>
+      </c>
+      <c r="C31">
+        <v>-300</v>
+      </c>
+      <c r="D31">
+        <v>0</v>
+      </c>
+      <c r="E31">
+        <v>0</v>
+      </c>
+      <c r="F31">
+        <v>0</v>
+      </c>
+      <c r="G31">
+        <v>1</v>
+      </c>
+      <c r="H31">
+        <v>1</v>
+      </c>
+      <c r="I31">
+        <v>3</v>
+      </c>
+      <c r="J31">
+        <f t="shared" si="4"/>
+        <v>20</v>
+      </c>
+      <c r="K31">
+        <f t="shared" si="5"/>
+        <v>20</v>
+      </c>
+      <c r="L31">
+        <f t="shared" si="6"/>
+        <v>60</v>
+      </c>
+    </row>
+    <row r="32" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A32">
+        <v>40</v>
+      </c>
+      <c r="B32">
+        <v>60</v>
+      </c>
+      <c r="C32">
+        <v>-300</v>
+      </c>
+      <c r="D32">
+        <v>0</v>
+      </c>
+      <c r="E32">
+        <v>0</v>
+      </c>
+      <c r="F32">
+        <v>0</v>
+      </c>
+      <c r="G32">
+        <v>1</v>
+      </c>
+      <c r="H32">
+        <v>1</v>
+      </c>
+      <c r="I32">
+        <v>3</v>
+      </c>
+      <c r="J32">
+        <f t="shared" si="4"/>
+        <v>20</v>
+      </c>
+      <c r="K32">
+        <f t="shared" si="5"/>
+        <v>20</v>
+      </c>
+      <c r="L32">
+        <f t="shared" si="6"/>
+        <v>60</v>
+      </c>
+    </row>
+    <row r="33" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A33">
+        <v>60</v>
+      </c>
+      <c r="B33">
+        <v>60</v>
+      </c>
+      <c r="C33">
+        <v>-300</v>
+      </c>
+      <c r="D33">
+        <v>0</v>
+      </c>
+      <c r="E33">
+        <v>0</v>
+      </c>
+      <c r="F33">
+        <v>0</v>
+      </c>
+      <c r="G33">
+        <v>1</v>
+      </c>
+      <c r="H33">
+        <v>1</v>
+      </c>
+      <c r="I33">
+        <v>3</v>
+      </c>
+      <c r="J33">
+        <f t="shared" si="4"/>
+        <v>20</v>
+      </c>
+      <c r="K33">
+        <f t="shared" si="5"/>
+        <v>20</v>
+      </c>
+      <c r="L33">
+        <f t="shared" si="6"/>
+        <v>60</v>
+      </c>
+    </row>
+    <row r="34" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A34">
+        <v>100</v>
+      </c>
+      <c r="B34">
+        <v>80</v>
+      </c>
+      <c r="C34">
+        <v>-300</v>
+      </c>
+      <c r="D34">
+        <v>0</v>
+      </c>
+      <c r="E34">
+        <v>0</v>
+      </c>
+      <c r="F34">
+        <v>0</v>
+      </c>
+      <c r="G34">
+        <v>1</v>
+      </c>
+      <c r="H34">
+        <v>1</v>
+      </c>
+      <c r="I34">
+        <v>3</v>
+      </c>
+      <c r="J34">
+        <f t="shared" si="4"/>
+        <v>20</v>
+      </c>
+      <c r="K34">
+        <f t="shared" si="5"/>
+        <v>20</v>
+      </c>
+      <c r="L34">
+        <f t="shared" si="6"/>
+        <v>60</v>
+      </c>
+    </row>
+    <row r="35" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A35">
+        <v>120</v>
+      </c>
+      <c r="B35">
+        <v>80</v>
+      </c>
+      <c r="C35">
+        <v>-300</v>
+      </c>
+      <c r="D35">
+        <v>0</v>
+      </c>
+      <c r="E35">
+        <v>0</v>
+      </c>
+      <c r="F35">
+        <v>0</v>
+      </c>
+      <c r="G35">
+        <v>1</v>
+      </c>
+      <c r="H35">
+        <v>1</v>
+      </c>
+      <c r="I35">
+        <v>3</v>
+      </c>
+      <c r="J35">
+        <f t="shared" si="4"/>
+        <v>20</v>
+      </c>
+      <c r="K35">
+        <f t="shared" si="5"/>
+        <v>20</v>
+      </c>
+      <c r="L35">
+        <f t="shared" si="6"/>
+        <v>60</v>
+      </c>
+    </row>
+    <row r="36" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A36">
+        <v>140</v>
+      </c>
+      <c r="B36">
+        <v>80</v>
+      </c>
+      <c r="C36">
+        <v>-300</v>
+      </c>
+      <c r="D36">
+        <v>0</v>
+      </c>
+      <c r="E36">
+        <v>0</v>
+      </c>
+      <c r="F36">
+        <v>0</v>
+      </c>
+      <c r="G36">
+        <v>1</v>
+      </c>
+      <c r="H36">
+        <v>1</v>
+      </c>
+      <c r="I36">
+        <v>3</v>
+      </c>
+      <c r="J36">
+        <f t="shared" si="4"/>
+        <v>20</v>
+      </c>
+      <c r="K36">
+        <f t="shared" si="5"/>
+        <v>20</v>
+      </c>
+      <c r="L36">
+        <f t="shared" si="6"/>
+        <v>60</v>
+      </c>
+    </row>
+    <row r="37" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A37">
+        <v>180</v>
+      </c>
+      <c r="B37">
+        <v>100</v>
+      </c>
+      <c r="C37">
+        <v>-300</v>
+      </c>
+      <c r="D37">
+        <v>0</v>
+      </c>
+      <c r="E37">
+        <v>0</v>
+      </c>
+      <c r="F37">
+        <v>0</v>
+      </c>
+      <c r="G37">
+        <v>1</v>
+      </c>
+      <c r="H37">
+        <v>1</v>
+      </c>
+      <c r="I37">
+        <v>3</v>
+      </c>
+      <c r="J37">
+        <f t="shared" si="4"/>
+        <v>20</v>
+      </c>
+      <c r="K37">
+        <f t="shared" si="5"/>
+        <v>20</v>
+      </c>
+      <c r="L37">
+        <f t="shared" si="6"/>
+        <v>60</v>
+      </c>
+    </row>
+    <row r="38" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A38">
+        <v>200</v>
+      </c>
+      <c r="B38">
+        <v>100</v>
+      </c>
+      <c r="C38">
+        <v>-300</v>
+      </c>
+      <c r="D38">
+        <v>0</v>
+      </c>
+      <c r="E38">
+        <v>0</v>
+      </c>
+      <c r="F38">
+        <v>0</v>
+      </c>
+      <c r="G38">
+        <v>1</v>
+      </c>
+      <c r="H38">
+        <v>1</v>
+      </c>
+      <c r="I38">
+        <v>3</v>
+      </c>
+      <c r="J38">
+        <f t="shared" si="4"/>
+        <v>20</v>
+      </c>
+      <c r="K38">
+        <f t="shared" si="5"/>
+        <v>20</v>
+      </c>
+      <c r="L38">
+        <f t="shared" si="6"/>
+        <v>60</v>
+      </c>
+    </row>
+    <row r="39" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A39">
+        <v>220</v>
+      </c>
+      <c r="B39">
+        <v>100</v>
+      </c>
+      <c r="C39">
+        <v>-300</v>
+      </c>
+      <c r="D39">
+        <v>0</v>
+      </c>
+      <c r="E39">
+        <v>0</v>
+      </c>
+      <c r="F39">
+        <v>0</v>
+      </c>
+      <c r="G39">
+        <v>1</v>
+      </c>
+      <c r="H39">
+        <v>1</v>
+      </c>
+      <c r="I39">
+        <v>3</v>
+      </c>
+      <c r="J39">
+        <f t="shared" si="4"/>
+        <v>20</v>
+      </c>
+      <c r="K39">
+        <f t="shared" si="5"/>
+        <v>20</v>
+      </c>
+      <c r="L39">
+        <f t="shared" si="6"/>
+        <v>60</v>
+      </c>
+    </row>
+    <row r="40" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A40">
+        <v>260</v>
+      </c>
+      <c r="B40">
+        <v>100</v>
+      </c>
+      <c r="C40">
+        <v>-320</v>
+      </c>
+      <c r="D40">
+        <v>0</v>
+      </c>
+      <c r="E40">
+        <v>0</v>
+      </c>
+      <c r="F40">
+        <v>0</v>
+      </c>
+      <c r="G40">
+        <v>3</v>
+      </c>
+      <c r="H40">
+        <v>1</v>
+      </c>
+      <c r="I40">
+        <v>1</v>
+      </c>
+      <c r="J40">
+        <f t="shared" si="4"/>
+        <v>60</v>
+      </c>
+      <c r="K40">
+        <f t="shared" si="5"/>
+        <v>20</v>
+      </c>
+      <c r="L40">
+        <f t="shared" si="6"/>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="41" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A41">
+        <v>260</v>
+      </c>
+      <c r="B41">
+        <v>100</v>
+      </c>
+      <c r="C41">
+        <v>-300</v>
+      </c>
+      <c r="D41">
+        <v>0</v>
+      </c>
+      <c r="E41">
+        <v>0</v>
+      </c>
+      <c r="F41">
+        <v>0</v>
+      </c>
+      <c r="G41">
+        <v>3</v>
+      </c>
+      <c r="H41">
+        <v>1</v>
+      </c>
+      <c r="I41">
+        <v>1</v>
+      </c>
+      <c r="J41">
+        <f t="shared" si="4"/>
+        <v>60</v>
+      </c>
+      <c r="K41">
+        <f t="shared" si="5"/>
+        <v>20</v>
+      </c>
+      <c r="L41">
+        <f t="shared" si="6"/>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="42" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A42">
+        <v>260</v>
+      </c>
+      <c r="B42">
+        <v>100</v>
+      </c>
+      <c r="C42">
+        <v>-280</v>
+      </c>
+      <c r="D42">
+        <v>0</v>
+      </c>
+      <c r="E42">
+        <v>0</v>
+      </c>
+      <c r="F42">
+        <v>0</v>
+      </c>
+      <c r="G42">
+        <v>3</v>
+      </c>
+      <c r="H42">
+        <v>1</v>
+      </c>
+      <c r="I42">
+        <v>1</v>
+      </c>
+      <c r="J42">
+        <f t="shared" si="4"/>
+        <v>60</v>
+      </c>
+      <c r="K42">
+        <f t="shared" si="5"/>
+        <v>20</v>
+      </c>
+      <c r="L42">
+        <f t="shared" si="6"/>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="43" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A43">
+        <v>260</v>
+      </c>
+      <c r="B43">
+        <v>100</v>
+      </c>
+      <c r="C43">
+        <v>-260</v>
+      </c>
+      <c r="D43">
+        <v>0</v>
+      </c>
+      <c r="E43">
+        <v>0</v>
+      </c>
+      <c r="F43">
+        <v>0</v>
+      </c>
+      <c r="G43">
+        <v>3</v>
+      </c>
+      <c r="H43">
+        <v>1</v>
+      </c>
+      <c r="I43">
+        <v>1</v>
+      </c>
+      <c r="J43">
+        <f t="shared" si="4"/>
+        <v>60</v>
+      </c>
+      <c r="K43">
+        <f t="shared" si="5"/>
+        <v>20</v>
+      </c>
+      <c r="L43">
+        <f t="shared" si="6"/>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="44" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A44">
+        <v>260</v>
+      </c>
+      <c r="B44">
+        <v>100</v>
+      </c>
+      <c r="C44">
+        <v>-240</v>
+      </c>
+      <c r="D44">
+        <v>0</v>
+      </c>
+      <c r="E44">
+        <v>0</v>
+      </c>
+      <c r="F44">
+        <v>0</v>
+      </c>
+      <c r="G44">
+        <v>3</v>
+      </c>
+      <c r="H44">
+        <v>1</v>
+      </c>
+      <c r="I44">
+        <v>1</v>
+      </c>
+      <c r="J44">
+        <f t="shared" si="4"/>
+        <v>60</v>
+      </c>
+      <c r="K44">
+        <f t="shared" si="5"/>
+        <v>20</v>
+      </c>
+      <c r="L44">
+        <f t="shared" si="6"/>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="45" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A45">
+        <v>260</v>
+      </c>
+      <c r="B45">
+        <v>100</v>
+      </c>
+      <c r="C45">
+        <v>-220</v>
+      </c>
+      <c r="D45">
+        <v>0</v>
+      </c>
+      <c r="E45">
+        <v>0</v>
+      </c>
+      <c r="F45">
+        <v>0</v>
+      </c>
+      <c r="G45">
+        <v>3</v>
+      </c>
+      <c r="H45">
+        <v>1</v>
+      </c>
+      <c r="I45">
+        <v>1</v>
+      </c>
+      <c r="J45">
+        <f t="shared" si="4"/>
+        <v>60</v>
+      </c>
+      <c r="K45">
+        <f t="shared" si="5"/>
+        <v>20</v>
+      </c>
+      <c r="L45">
+        <f t="shared" si="6"/>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="46" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A46">
+        <v>260</v>
+      </c>
+      <c r="B46">
+        <v>100</v>
+      </c>
+      <c r="C46">
+        <v>-200</v>
+      </c>
+      <c r="D46">
+        <v>0</v>
+      </c>
+      <c r="E46">
+        <v>0</v>
+      </c>
+      <c r="F46">
+        <v>0</v>
+      </c>
+      <c r="G46">
+        <v>3</v>
+      </c>
+      <c r="H46">
+        <v>1</v>
+      </c>
+      <c r="I46">
+        <v>1</v>
+      </c>
+      <c r="J46">
+        <f t="shared" si="4"/>
+        <v>60</v>
+      </c>
+      <c r="K46">
+        <f t="shared" si="5"/>
+        <v>20</v>
+      </c>
+      <c r="L46">
+        <f t="shared" si="6"/>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="47" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A47">
+        <v>260</v>
+      </c>
+      <c r="B47">
+        <v>100</v>
+      </c>
+      <c r="C47">
+        <v>-180</v>
+      </c>
+      <c r="D47">
+        <v>0</v>
+      </c>
+      <c r="E47">
+        <v>0</v>
+      </c>
+      <c r="F47">
+        <v>0</v>
+      </c>
+      <c r="G47">
+        <v>3</v>
+      </c>
+      <c r="H47">
+        <v>1</v>
+      </c>
+      <c r="I47">
+        <v>1</v>
+      </c>
+      <c r="J47">
+        <f t="shared" si="4"/>
+        <v>60</v>
+      </c>
+      <c r="K47">
+        <f t="shared" si="5"/>
+        <v>20</v>
+      </c>
+      <c r="L47">
+        <f t="shared" si="6"/>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="48" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A48">
+        <v>260</v>
+      </c>
+      <c r="B48">
+        <v>100</v>
+      </c>
+      <c r="C48">
+        <v>-160</v>
+      </c>
+      <c r="D48">
+        <v>0</v>
+      </c>
+      <c r="E48">
+        <v>0</v>
+      </c>
+      <c r="F48">
+        <v>0</v>
+      </c>
+      <c r="G48">
+        <v>3</v>
+      </c>
+      <c r="H48">
+        <v>1</v>
+      </c>
+      <c r="I48">
+        <v>1</v>
+      </c>
+      <c r="J48">
+        <f t="shared" si="4"/>
+        <v>60</v>
+      </c>
+      <c r="K48">
+        <f t="shared" si="5"/>
+        <v>20</v>
+      </c>
+      <c r="L48">
+        <f t="shared" si="6"/>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="49" spans="4:12" x14ac:dyDescent="0.4">
+      <c r="D49">
+        <v>0</v>
+      </c>
+      <c r="E49">
+        <v>0</v>
+      </c>
+      <c r="F49">
+        <v>0</v>
+      </c>
+      <c r="G49">
+        <v>1</v>
+      </c>
+      <c r="H49">
+        <v>1</v>
+      </c>
+      <c r="I49">
+        <v>1</v>
+      </c>
+      <c r="J49">
+        <f t="shared" si="4"/>
+        <v>20</v>
+      </c>
+      <c r="K49">
+        <f t="shared" si="5"/>
+        <v>20</v>
+      </c>
+      <c r="L49">
+        <f t="shared" si="6"/>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="50" spans="4:12" x14ac:dyDescent="0.4">
+      <c r="D50">
+        <v>0</v>
+      </c>
+      <c r="E50">
+        <v>0</v>
+      </c>
+      <c r="F50">
+        <v>0</v>
+      </c>
+      <c r="G50">
+        <v>1</v>
+      </c>
+      <c r="H50">
+        <v>1</v>
+      </c>
+      <c r="I50">
+        <v>1</v>
+      </c>
+      <c r="J50">
+        <f t="shared" si="4"/>
+        <v>20</v>
+      </c>
+      <c r="K50">
+        <f t="shared" si="5"/>
+        <v>20</v>
+      </c>
+      <c r="L50">
+        <f t="shared" si="6"/>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="51" spans="4:12" x14ac:dyDescent="0.4">
+      <c r="D51">
+        <v>0</v>
+      </c>
+      <c r="E51">
+        <v>0</v>
+      </c>
+      <c r="F51">
+        <v>0</v>
+      </c>
+      <c r="G51">
+        <v>1</v>
+      </c>
+      <c r="H51">
+        <v>1</v>
+      </c>
+      <c r="I51">
+        <v>1</v>
+      </c>
+      <c r="J51">
+        <f t="shared" si="4"/>
+        <v>20</v>
+      </c>
+      <c r="K51">
+        <f t="shared" si="5"/>
+        <v>20</v>
+      </c>
+      <c r="L51">
+        <f t="shared" si="6"/>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="52" spans="4:12" x14ac:dyDescent="0.4">
+      <c r="D52">
+        <v>0</v>
+      </c>
+      <c r="E52">
+        <v>0</v>
+      </c>
+      <c r="F52">
+        <v>0</v>
+      </c>
+      <c r="G52">
+        <v>1</v>
+      </c>
+      <c r="H52">
+        <v>1</v>
+      </c>
+      <c r="I52">
+        <v>1</v>
+      </c>
+      <c r="J52">
+        <f t="shared" si="4"/>
+        <v>20</v>
+      </c>
+      <c r="K52">
+        <f t="shared" si="5"/>
+        <v>20</v>
+      </c>
+      <c r="L52">
+        <f t="shared" si="6"/>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="53" spans="4:12" x14ac:dyDescent="0.4">
+      <c r="D53">
+        <v>0</v>
+      </c>
+      <c r="E53">
+        <v>0</v>
+      </c>
+      <c r="F53">
+        <v>0</v>
+      </c>
+      <c r="G53">
+        <v>1</v>
+      </c>
+      <c r="H53">
+        <v>1</v>
+      </c>
+      <c r="I53">
+        <v>1</v>
+      </c>
+      <c r="J53">
+        <f t="shared" si="4"/>
+        <v>20</v>
+      </c>
+      <c r="K53">
+        <f t="shared" si="5"/>
+        <v>20</v>
+      </c>
+      <c r="L53">
+        <f t="shared" si="6"/>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="54" spans="4:12" x14ac:dyDescent="0.4">
+      <c r="D54">
+        <v>0</v>
+      </c>
+      <c r="E54">
+        <v>0</v>
+      </c>
+      <c r="F54">
+        <v>0</v>
+      </c>
+      <c r="G54">
+        <v>1</v>
+      </c>
+      <c r="H54">
+        <v>1</v>
+      </c>
+      <c r="I54">
+        <v>1</v>
+      </c>
+      <c r="J54">
+        <f t="shared" si="4"/>
+        <v>20</v>
+      </c>
+      <c r="K54">
+        <f t="shared" si="5"/>
+        <v>20</v>
+      </c>
+      <c r="L54">
+        <f t="shared" si="6"/>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="55" spans="4:12" x14ac:dyDescent="0.4">
+      <c r="D55">
+        <v>0</v>
+      </c>
+      <c r="E55">
+        <v>0</v>
+      </c>
+      <c r="F55">
+        <v>0</v>
+      </c>
+      <c r="G55">
+        <v>1</v>
+      </c>
+      <c r="H55">
+        <v>1</v>
+      </c>
+      <c r="I55">
+        <v>1</v>
+      </c>
+      <c r="J55">
+        <f t="shared" si="4"/>
+        <v>20</v>
+      </c>
+      <c r="K55">
+        <f t="shared" si="5"/>
+        <v>20</v>
+      </c>
+      <c r="L55">
+        <f t="shared" si="6"/>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="56" spans="4:12" x14ac:dyDescent="0.4">
+      <c r="D56">
+        <v>0</v>
+      </c>
+      <c r="E56">
+        <v>0</v>
+      </c>
+      <c r="F56">
+        <v>0</v>
+      </c>
+      <c r="G56">
+        <v>1</v>
+      </c>
+      <c r="H56">
+        <v>1</v>
+      </c>
+      <c r="I56">
+        <v>1</v>
+      </c>
+      <c r="J56">
+        <f t="shared" si="4"/>
+        <v>20</v>
+      </c>
+      <c r="K56">
+        <f t="shared" si="5"/>
+        <v>20</v>
+      </c>
+      <c r="L56">
+        <f t="shared" si="6"/>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="57" spans="4:12" x14ac:dyDescent="0.4">
+      <c r="D57">
+        <v>0</v>
+      </c>
+      <c r="E57">
+        <v>0</v>
+      </c>
+      <c r="F57">
+        <v>0</v>
+      </c>
+      <c r="G57">
+        <v>1</v>
+      </c>
+      <c r="H57">
+        <v>1</v>
+      </c>
+      <c r="I57">
+        <v>1</v>
+      </c>
+      <c r="J57">
+        <f t="shared" si="4"/>
+        <v>20</v>
+      </c>
+      <c r="K57">
+        <f t="shared" si="5"/>
+        <v>20</v>
+      </c>
+      <c r="L57">
+        <f t="shared" si="6"/>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="58" spans="4:12" x14ac:dyDescent="0.4">
+      <c r="D58">
+        <v>0</v>
+      </c>
+      <c r="E58">
+        <v>0</v>
+      </c>
+      <c r="F58">
+        <v>0</v>
+      </c>
+      <c r="G58">
+        <v>1</v>
+      </c>
+      <c r="H58">
+        <v>1</v>
+      </c>
+      <c r="I58">
+        <v>1</v>
+      </c>
+      <c r="J58">
+        <f t="shared" si="4"/>
+        <v>20</v>
+      </c>
+      <c r="K58">
+        <f t="shared" si="5"/>
+        <v>20</v>
+      </c>
+      <c r="L58">
+        <f t="shared" si="6"/>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="59" spans="4:12" x14ac:dyDescent="0.4">
+      <c r="D59">
+        <v>0</v>
+      </c>
+      <c r="E59">
+        <v>0</v>
+      </c>
+      <c r="F59">
+        <v>0</v>
+      </c>
+      <c r="G59">
+        <v>1</v>
+      </c>
+      <c r="H59">
+        <v>1</v>
+      </c>
+      <c r="I59">
+        <v>1</v>
+      </c>
+      <c r="J59">
+        <f t="shared" si="4"/>
+        <v>20</v>
+      </c>
+      <c r="K59">
+        <f t="shared" si="5"/>
+        <v>20</v>
+      </c>
+      <c r="L59">
+        <f t="shared" si="6"/>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="60" spans="4:12" x14ac:dyDescent="0.4">
+      <c r="D60">
+        <v>0</v>
+      </c>
+      <c r="E60">
+        <v>0</v>
+      </c>
+      <c r="F60">
+        <v>0</v>
+      </c>
+      <c r="G60">
+        <v>1</v>
+      </c>
+      <c r="H60">
+        <v>1</v>
+      </c>
+      <c r="I60">
+        <v>1</v>
+      </c>
+      <c r="J60">
+        <f t="shared" si="4"/>
+        <v>20</v>
+      </c>
+      <c r="K60">
+        <f t="shared" si="5"/>
+        <v>20</v>
+      </c>
+      <c r="L60">
+        <f t="shared" si="6"/>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="61" spans="4:12" x14ac:dyDescent="0.4">
+      <c r="D61">
+        <v>0</v>
+      </c>
+      <c r="E61">
+        <v>0</v>
+      </c>
+      <c r="F61">
+        <v>0</v>
+      </c>
+      <c r="G61">
+        <v>1</v>
+      </c>
+      <c r="H61">
+        <v>1</v>
+      </c>
+      <c r="I61">
+        <v>1</v>
+      </c>
+      <c r="J61">
+        <f t="shared" si="4"/>
+        <v>20</v>
+      </c>
+      <c r="K61">
+        <f t="shared" si="5"/>
+        <v>20</v>
+      </c>
+      <c r="L61">
+        <f t="shared" si="6"/>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="62" spans="4:12" x14ac:dyDescent="0.4">
+      <c r="D62">
+        <v>0</v>
+      </c>
+      <c r="E62">
+        <v>0</v>
+      </c>
+      <c r="F62">
+        <v>0</v>
+      </c>
+      <c r="G62">
+        <v>1</v>
+      </c>
+      <c r="H62">
+        <v>1</v>
+      </c>
+      <c r="I62">
+        <v>1</v>
+      </c>
+      <c r="J62">
+        <f t="shared" si="4"/>
+        <v>20</v>
+      </c>
+      <c r="K62">
+        <f t="shared" si="5"/>
+        <v>20</v>
+      </c>
+      <c r="L62">
+        <f t="shared" si="6"/>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="63" spans="4:12" x14ac:dyDescent="0.4">
+      <c r="D63">
+        <v>0</v>
+      </c>
+      <c r="E63">
+        <v>0</v>
+      </c>
+      <c r="F63">
+        <v>0</v>
+      </c>
+      <c r="G63">
+        <v>1</v>
+      </c>
+      <c r="H63">
+        <v>1</v>
+      </c>
+      <c r="I63">
+        <v>1</v>
+      </c>
+      <c r="J63">
+        <f t="shared" si="4"/>
+        <v>20</v>
+      </c>
+      <c r="K63">
+        <f t="shared" si="5"/>
+        <v>20</v>
+      </c>
+      <c r="L63">
+        <f t="shared" si="6"/>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="64" spans="4:12" x14ac:dyDescent="0.4">
+      <c r="D64">
+        <v>0</v>
+      </c>
+      <c r="E64">
+        <v>0</v>
+      </c>
+      <c r="F64">
+        <v>0</v>
+      </c>
+      <c r="G64">
+        <v>1</v>
+      </c>
+      <c r="H64">
+        <v>1</v>
+      </c>
+      <c r="I64">
+        <v>1</v>
+      </c>
+      <c r="J64">
+        <f t="shared" si="4"/>
+        <v>20</v>
+      </c>
+      <c r="K64">
+        <f t="shared" si="5"/>
+        <v>20</v>
+      </c>
+      <c r="L64">
+        <f t="shared" si="6"/>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="65" spans="4:12" x14ac:dyDescent="0.4">
+      <c r="D65">
+        <v>0</v>
+      </c>
+      <c r="E65">
+        <v>0</v>
+      </c>
+      <c r="F65">
+        <v>0</v>
+      </c>
+      <c r="G65">
+        <v>1</v>
+      </c>
+      <c r="H65">
+        <v>1</v>
+      </c>
+      <c r="I65">
+        <v>1</v>
+      </c>
+      <c r="J65">
+        <f t="shared" si="4"/>
+        <v>20</v>
+      </c>
+      <c r="K65">
+        <f t="shared" si="5"/>
+        <v>20</v>
+      </c>
+      <c r="L65">
+        <f t="shared" si="6"/>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="66" spans="4:12" x14ac:dyDescent="0.4">
+      <c r="D66">
+        <v>0</v>
+      </c>
+      <c r="E66">
+        <v>0</v>
+      </c>
+      <c r="F66">
+        <v>0</v>
+      </c>
+      <c r="G66">
+        <v>1</v>
+      </c>
+      <c r="H66">
+        <v>1</v>
+      </c>
+      <c r="I66">
+        <v>1</v>
+      </c>
+      <c r="J66">
+        <f t="shared" si="4"/>
+        <v>20</v>
+      </c>
+      <c r="K66">
+        <f t="shared" si="5"/>
+        <v>20</v>
+      </c>
+      <c r="L66">
+        <f t="shared" si="6"/>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="67" spans="4:12" x14ac:dyDescent="0.4">
+      <c r="D67">
+        <v>0</v>
+      </c>
+      <c r="E67">
+        <v>0</v>
+      </c>
+      <c r="F67">
+        <v>0</v>
+      </c>
+      <c r="G67">
+        <v>1</v>
+      </c>
+      <c r="H67">
+        <v>1</v>
+      </c>
+      <c r="I67">
+        <v>1</v>
+      </c>
+      <c r="J67">
+        <f t="shared" si="4"/>
+        <v>20</v>
+      </c>
+      <c r="K67">
+        <f t="shared" si="5"/>
+        <v>20</v>
+      </c>
+      <c r="L67">
+        <f t="shared" si="6"/>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="68" spans="4:12" x14ac:dyDescent="0.4">
+      <c r="D68">
+        <v>0</v>
+      </c>
+      <c r="E68">
+        <v>0</v>
+      </c>
+      <c r="F68">
+        <v>0</v>
+      </c>
+      <c r="G68">
+        <v>1</v>
+      </c>
+      <c r="H68">
+        <v>1</v>
+      </c>
+      <c r="I68">
+        <v>1</v>
+      </c>
+      <c r="J68">
+        <f t="shared" si="4"/>
+        <v>20</v>
+      </c>
+      <c r="K68">
+        <f t="shared" si="5"/>
+        <v>20</v>
+      </c>
+      <c r="L68">
+        <f t="shared" si="6"/>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="69" spans="4:12" x14ac:dyDescent="0.4">
+      <c r="D69">
+        <v>0</v>
+      </c>
+      <c r="E69">
+        <v>0</v>
+      </c>
+      <c r="F69">
+        <v>0</v>
+      </c>
+      <c r="G69">
+        <v>1</v>
+      </c>
+      <c r="H69">
+        <v>1</v>
+      </c>
+      <c r="I69">
+        <v>1</v>
+      </c>
+      <c r="J69">
+        <f t="shared" si="4"/>
+        <v>20</v>
+      </c>
+      <c r="K69">
+        <f t="shared" si="5"/>
+        <v>20</v>
+      </c>
+      <c r="L69">
+        <f t="shared" si="6"/>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="70" spans="4:12" x14ac:dyDescent="0.4">
+      <c r="D70">
+        <v>0</v>
+      </c>
+      <c r="E70">
+        <v>0</v>
+      </c>
+      <c r="F70">
+        <v>0</v>
+      </c>
+      <c r="G70">
+        <v>1</v>
+      </c>
+      <c r="H70">
+        <v>1</v>
+      </c>
+      <c r="I70">
+        <v>1</v>
+      </c>
+      <c r="J70">
+        <f t="shared" si="4"/>
+        <v>20</v>
+      </c>
+      <c r="K70">
+        <f t="shared" si="5"/>
+        <v>20</v>
+      </c>
+      <c r="L70">
+        <f t="shared" si="6"/>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="71" spans="4:12" x14ac:dyDescent="0.4">
+      <c r="D71">
+        <v>0</v>
+      </c>
+      <c r="E71">
+        <v>0</v>
+      </c>
+      <c r="F71">
+        <v>0</v>
+      </c>
+      <c r="G71">
+        <v>1</v>
+      </c>
+      <c r="H71">
+        <v>1</v>
+      </c>
+      <c r="I71">
+        <v>1</v>
+      </c>
+      <c r="J71">
+        <f t="shared" si="4"/>
+        <v>20</v>
+      </c>
+      <c r="K71">
+        <f t="shared" si="5"/>
+        <v>20</v>
+      </c>
+      <c r="L71">
+        <f t="shared" si="6"/>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="72" spans="4:12" x14ac:dyDescent="0.4">
+      <c r="D72">
+        <v>0</v>
+      </c>
+      <c r="E72">
+        <v>0</v>
+      </c>
+      <c r="F72">
+        <v>0</v>
+      </c>
+      <c r="G72">
+        <v>1</v>
+      </c>
+      <c r="H72">
+        <v>1</v>
+      </c>
+      <c r="I72">
+        <v>1</v>
+      </c>
+      <c r="J72">
+        <f t="shared" si="4"/>
+        <v>20</v>
+      </c>
+      <c r="K72">
+        <f t="shared" si="5"/>
+        <v>20</v>
+      </c>
+      <c r="L72">
+        <f t="shared" si="6"/>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="73" spans="4:12" x14ac:dyDescent="0.4">
+      <c r="D73">
+        <v>0</v>
+      </c>
+      <c r="E73">
+        <v>0</v>
+      </c>
+      <c r="F73">
+        <v>0</v>
+      </c>
+      <c r="G73">
+        <v>1</v>
+      </c>
+      <c r="H73">
+        <v>1</v>
+      </c>
+      <c r="I73">
+        <v>1</v>
+      </c>
+      <c r="J73">
+        <f t="shared" si="4"/>
+        <v>20</v>
+      </c>
+      <c r="K73">
+        <f t="shared" si="5"/>
+        <v>20</v>
+      </c>
+      <c r="L73">
+        <f t="shared" si="6"/>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="74" spans="4:12" x14ac:dyDescent="0.4">
+      <c r="D74">
+        <v>0</v>
+      </c>
+      <c r="E74">
+        <v>0</v>
+      </c>
+      <c r="F74">
+        <v>0</v>
+      </c>
+      <c r="G74">
+        <v>1</v>
+      </c>
+      <c r="H74">
+        <v>1</v>
+      </c>
+      <c r="I74">
+        <v>1</v>
+      </c>
+      <c r="J74">
+        <f t="shared" si="4"/>
+        <v>20</v>
+      </c>
+      <c r="K74">
+        <f t="shared" si="5"/>
+        <v>20</v>
+      </c>
+      <c r="L74">
+        <f t="shared" si="6"/>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="75" spans="4:12" x14ac:dyDescent="0.4">
+      <c r="D75">
+        <v>0</v>
+      </c>
+      <c r="E75">
+        <v>0</v>
+      </c>
+      <c r="F75">
+        <v>0</v>
+      </c>
+      <c r="G75">
+        <v>1</v>
+      </c>
+      <c r="H75">
+        <v>1</v>
+      </c>
+      <c r="I75">
+        <v>1</v>
+      </c>
+      <c r="J75">
+        <f t="shared" si="4"/>
+        <v>20</v>
+      </c>
+      <c r="K75">
+        <f t="shared" si="5"/>
+        <v>20</v>
+      </c>
+      <c r="L75">
+        <f t="shared" si="6"/>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="76" spans="4:12" x14ac:dyDescent="0.4">
+      <c r="D76">
+        <v>0</v>
+      </c>
+      <c r="E76">
+        <v>0</v>
+      </c>
+      <c r="F76">
+        <v>0</v>
+      </c>
+      <c r="G76">
+        <v>1</v>
+      </c>
+      <c r="H76">
+        <v>1</v>
+      </c>
+      <c r="I76">
+        <v>1</v>
+      </c>
+      <c r="J76">
+        <f t="shared" si="4"/>
+        <v>20</v>
+      </c>
+      <c r="K76">
+        <f t="shared" si="5"/>
+        <v>20</v>
+      </c>
+      <c r="L76">
+        <f t="shared" si="6"/>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="77" spans="4:12" x14ac:dyDescent="0.4">
+      <c r="D77">
+        <v>0</v>
+      </c>
+      <c r="E77">
+        <v>0</v>
+      </c>
+      <c r="F77">
+        <v>0</v>
+      </c>
+      <c r="G77">
+        <v>1</v>
+      </c>
+      <c r="H77">
+        <v>1</v>
+      </c>
+      <c r="I77">
+        <v>1</v>
+      </c>
+      <c r="J77">
+        <f t="shared" si="4"/>
+        <v>20</v>
+      </c>
+      <c r="K77">
+        <f t="shared" si="5"/>
+        <v>20</v>
+      </c>
+      <c r="L77">
+        <f t="shared" si="6"/>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="78" spans="4:12" x14ac:dyDescent="0.4">
+      <c r="D78">
+        <v>0</v>
+      </c>
+      <c r="E78">
+        <v>0</v>
+      </c>
+      <c r="F78">
+        <v>0</v>
+      </c>
+      <c r="G78">
+        <v>1</v>
+      </c>
+      <c r="H78">
+        <v>1</v>
+      </c>
+      <c r="I78">
+        <v>1</v>
+      </c>
+      <c r="J78">
+        <f t="shared" si="4"/>
+        <v>20</v>
+      </c>
+      <c r="K78">
+        <f t="shared" si="5"/>
+        <v>20</v>
+      </c>
+      <c r="L78">
+        <f t="shared" si="6"/>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="79" spans="4:12" x14ac:dyDescent="0.4">
+      <c r="D79">
+        <v>0</v>
+      </c>
+      <c r="E79">
+        <v>0</v>
+      </c>
+      <c r="F79">
+        <v>0</v>
+      </c>
+      <c r="G79">
+        <v>1</v>
+      </c>
+      <c r="H79">
+        <v>1</v>
+      </c>
+      <c r="I79">
+        <v>1</v>
+      </c>
+      <c r="J79">
+        <f t="shared" si="4"/>
+        <v>20</v>
+      </c>
+      <c r="K79">
+        <f t="shared" si="5"/>
+        <v>20</v>
+      </c>
+      <c r="L79">
+        <f t="shared" si="6"/>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="80" spans="4:12" x14ac:dyDescent="0.4">
+      <c r="D80">
+        <v>0</v>
+      </c>
+      <c r="E80">
+        <v>0</v>
+      </c>
+      <c r="F80">
+        <v>0</v>
+      </c>
+      <c r="G80">
+        <v>1</v>
+      </c>
+      <c r="H80">
+        <v>1</v>
+      </c>
+      <c r="I80">
+        <v>1</v>
+      </c>
+      <c r="J80">
+        <f t="shared" si="4"/>
+        <v>20</v>
+      </c>
+      <c r="K80">
+        <f t="shared" si="5"/>
+        <v>20</v>
+      </c>
+      <c r="L80">
+        <f t="shared" si="6"/>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="81" spans="4:12" x14ac:dyDescent="0.4">
+      <c r="D81">
+        <v>0</v>
+      </c>
+      <c r="E81">
+        <v>0</v>
+      </c>
+      <c r="F81">
+        <v>0</v>
+      </c>
+      <c r="G81">
+        <v>1</v>
+      </c>
+      <c r="H81">
+        <v>1</v>
+      </c>
+      <c r="I81">
+        <v>1</v>
+      </c>
+      <c r="J81">
+        <f t="shared" si="4"/>
+        <v>20</v>
+      </c>
+      <c r="K81">
+        <f t="shared" si="5"/>
+        <v>20</v>
+      </c>
+      <c r="L81">
+        <f t="shared" si="6"/>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="82" spans="4:12" x14ac:dyDescent="0.4">
+      <c r="D82">
+        <v>0</v>
+      </c>
+      <c r="E82">
+        <v>0</v>
+      </c>
+      <c r="F82">
+        <v>0</v>
+      </c>
+      <c r="G82">
+        <v>1</v>
+      </c>
+      <c r="H82">
+        <v>1</v>
+      </c>
+      <c r="I82">
+        <v>1</v>
+      </c>
+      <c r="J82">
+        <f t="shared" si="4"/>
+        <v>20</v>
+      </c>
+      <c r="K82">
+        <f t="shared" si="5"/>
+        <v>20</v>
+      </c>
+      <c r="L82">
+        <f t="shared" si="6"/>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="83" spans="4:12" x14ac:dyDescent="0.4">
+      <c r="D83">
+        <v>0</v>
+      </c>
+      <c r="E83">
+        <v>0</v>
+      </c>
+      <c r="F83">
+        <v>0</v>
+      </c>
+      <c r="G83">
+        <v>1</v>
+      </c>
+      <c r="H83">
+        <v>1</v>
+      </c>
+      <c r="I83">
+        <v>1</v>
+      </c>
+      <c r="J83">
+        <f t="shared" si="4"/>
+        <v>20</v>
+      </c>
+      <c r="K83">
+        <f t="shared" si="5"/>
+        <v>20</v>
+      </c>
+      <c r="L83">
+        <f t="shared" si="6"/>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="84" spans="4:12" x14ac:dyDescent="0.4">
+      <c r="D84">
+        <v>0</v>
+      </c>
+      <c r="E84">
+        <v>0</v>
+      </c>
+      <c r="F84">
+        <v>0</v>
+      </c>
+      <c r="G84">
+        <v>1</v>
+      </c>
+      <c r="H84">
+        <v>1</v>
+      </c>
+      <c r="I84">
+        <v>1</v>
+      </c>
+      <c r="J84">
+        <f t="shared" si="4"/>
+        <v>20</v>
+      </c>
+      <c r="K84">
+        <f t="shared" si="5"/>
+        <v>20</v>
+      </c>
+      <c r="L84">
+        <f t="shared" si="6"/>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="85" spans="4:12" x14ac:dyDescent="0.4">
+      <c r="D85">
+        <v>0</v>
+      </c>
+      <c r="E85">
+        <v>0</v>
+      </c>
+      <c r="F85">
+        <v>0</v>
+      </c>
+      <c r="G85">
+        <v>1</v>
+      </c>
+      <c r="H85">
+        <v>1</v>
+      </c>
+      <c r="I85">
+        <v>1</v>
+      </c>
+      <c r="J85">
+        <f t="shared" si="4"/>
+        <v>20</v>
+      </c>
+      <c r="K85">
+        <f t="shared" si="5"/>
+        <v>20</v>
+      </c>
+      <c r="L85">
+        <f t="shared" si="6"/>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="86" spans="4:12" x14ac:dyDescent="0.4">
+      <c r="D86">
+        <v>0</v>
+      </c>
+      <c r="E86">
+        <v>0</v>
+      </c>
+      <c r="F86">
+        <v>0</v>
+      </c>
+      <c r="G86">
+        <v>1</v>
+      </c>
+      <c r="H86">
+        <v>1</v>
+      </c>
+      <c r="I86">
+        <v>1</v>
+      </c>
+      <c r="J86">
+        <f t="shared" si="4"/>
+        <v>20</v>
+      </c>
+      <c r="K86">
+        <f t="shared" si="5"/>
+        <v>20</v>
+      </c>
+      <c r="L86">
+        <f t="shared" si="6"/>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="87" spans="4:12" x14ac:dyDescent="0.4">
+      <c r="D87">
+        <v>0</v>
+      </c>
+      <c r="E87">
+        <v>0</v>
+      </c>
+      <c r="F87">
+        <v>0</v>
+      </c>
+      <c r="G87">
+        <v>1</v>
+      </c>
+      <c r="H87">
+        <v>1</v>
+      </c>
+      <c r="I87">
+        <v>1</v>
+      </c>
+      <c r="J87">
+        <f t="shared" si="4"/>
+        <v>20</v>
+      </c>
+      <c r="K87">
+        <f t="shared" si="5"/>
+        <v>20</v>
+      </c>
+      <c r="L87">
+        <f t="shared" si="6"/>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="88" spans="4:12" x14ac:dyDescent="0.4">
+      <c r="D88">
+        <v>0</v>
+      </c>
+      <c r="E88">
+        <v>0</v>
+      </c>
+      <c r="F88">
+        <v>0</v>
+      </c>
+      <c r="G88">
+        <v>1</v>
+      </c>
+      <c r="H88">
+        <v>1</v>
+      </c>
+      <c r="I88">
+        <v>1</v>
+      </c>
+      <c r="J88">
+        <f t="shared" si="4"/>
+        <v>20</v>
+      </c>
+      <c r="K88">
+        <f t="shared" si="5"/>
+        <v>20</v>
+      </c>
+      <c r="L88">
+        <f t="shared" si="6"/>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="89" spans="4:12" x14ac:dyDescent="0.4">
+      <c r="D89">
+        <v>0</v>
+      </c>
+      <c r="E89">
+        <v>0</v>
+      </c>
+      <c r="F89">
+        <v>0</v>
+      </c>
+      <c r="G89">
+        <v>1</v>
+      </c>
+      <c r="H89">
+        <v>1</v>
+      </c>
+      <c r="I89">
+        <v>1</v>
+      </c>
+      <c r="J89">
+        <f t="shared" si="4"/>
+        <v>20</v>
+      </c>
+      <c r="K89">
+        <f t="shared" si="5"/>
+        <v>20</v>
+      </c>
+      <c r="L89">
+        <f t="shared" si="6"/>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="90" spans="4:12" x14ac:dyDescent="0.4">
+      <c r="D90">
+        <v>0</v>
+      </c>
+      <c r="E90">
+        <v>0</v>
+      </c>
+      <c r="F90">
+        <v>0</v>
+      </c>
+      <c r="G90">
+        <v>1</v>
+      </c>
+      <c r="H90">
+        <v>1</v>
+      </c>
+      <c r="I90">
+        <v>1</v>
+      </c>
+      <c r="J90">
+        <f t="shared" si="4"/>
+        <v>20</v>
+      </c>
+      <c r="K90">
+        <f t="shared" si="5"/>
+        <v>20</v>
+      </c>
+      <c r="L90">
+        <f t="shared" si="6"/>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="91" spans="4:12" x14ac:dyDescent="0.4">
+      <c r="D91">
+        <v>0</v>
+      </c>
+      <c r="E91">
+        <v>0</v>
+      </c>
+      <c r="F91">
+        <v>0</v>
+      </c>
+      <c r="G91">
+        <v>1</v>
+      </c>
+      <c r="H91">
+        <v>1</v>
+      </c>
+      <c r="I91">
+        <v>1</v>
+      </c>
+      <c r="J91">
+        <f t="shared" si="4"/>
+        <v>20</v>
+      </c>
+      <c r="K91">
+        <f t="shared" si="5"/>
+        <v>20</v>
+      </c>
+      <c r="L91">
+        <f t="shared" si="6"/>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="92" spans="4:12" x14ac:dyDescent="0.4">
+      <c r="D92">
+        <v>0</v>
+      </c>
+      <c r="E92">
+        <v>0</v>
+      </c>
+      <c r="F92">
+        <v>0</v>
+      </c>
+      <c r="G92">
+        <v>1</v>
+      </c>
+      <c r="H92">
+        <v>1</v>
+      </c>
+      <c r="I92">
+        <v>1</v>
+      </c>
+      <c r="J92">
+        <f t="shared" ref="J92:J100" si="7">G92*20</f>
+        <v>20</v>
+      </c>
+      <c r="K92">
+        <f t="shared" ref="K92:K100" si="8">H92*20</f>
+        <v>20</v>
+      </c>
+      <c r="L92">
+        <f t="shared" ref="L92:L100" si="9">I92*20</f>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="93" spans="4:12" x14ac:dyDescent="0.4">
+      <c r="D93">
+        <v>0</v>
+      </c>
+      <c r="E93">
+        <v>0</v>
+      </c>
+      <c r="F93">
+        <v>0</v>
+      </c>
+      <c r="G93">
+        <v>1</v>
+      </c>
+      <c r="H93">
+        <v>1</v>
+      </c>
+      <c r="I93">
+        <v>1</v>
+      </c>
+      <c r="J93">
+        <f t="shared" si="7"/>
+        <v>20</v>
+      </c>
+      <c r="K93">
+        <f t="shared" si="8"/>
+        <v>20</v>
+      </c>
+      <c r="L93">
+        <f t="shared" si="9"/>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="94" spans="4:12" x14ac:dyDescent="0.4">
+      <c r="D94">
+        <v>0</v>
+      </c>
+      <c r="E94">
+        <v>0</v>
+      </c>
+      <c r="F94">
+        <v>0</v>
+      </c>
+      <c r="G94">
+        <v>1</v>
+      </c>
+      <c r="H94">
+        <v>1</v>
+      </c>
+      <c r="I94">
+        <v>1</v>
+      </c>
+      <c r="J94">
+        <f t="shared" si="7"/>
+        <v>20</v>
+      </c>
+      <c r="K94">
+        <f t="shared" si="8"/>
+        <v>20</v>
+      </c>
+      <c r="L94">
+        <f t="shared" si="9"/>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="95" spans="4:12" x14ac:dyDescent="0.4">
+      <c r="D95">
+        <v>0</v>
+      </c>
+      <c r="E95">
+        <v>0</v>
+      </c>
+      <c r="F95">
+        <v>0</v>
+      </c>
+      <c r="G95">
+        <v>1</v>
+      </c>
+      <c r="H95">
+        <v>1</v>
+      </c>
+      <c r="I95">
+        <v>1</v>
+      </c>
+      <c r="J95">
+        <f t="shared" si="7"/>
+        <v>20</v>
+      </c>
+      <c r="K95">
+        <f t="shared" si="8"/>
+        <v>20</v>
+      </c>
+      <c r="L95">
+        <f t="shared" si="9"/>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="96" spans="4:12" x14ac:dyDescent="0.4">
+      <c r="D96">
+        <v>0</v>
+      </c>
+      <c r="E96">
+        <v>0</v>
+      </c>
+      <c r="F96">
+        <v>0</v>
+      </c>
+      <c r="G96">
+        <v>1</v>
+      </c>
+      <c r="H96">
+        <v>1</v>
+      </c>
+      <c r="I96">
+        <v>1</v>
+      </c>
+      <c r="J96">
+        <f t="shared" si="7"/>
+        <v>20</v>
+      </c>
+      <c r="K96">
+        <f t="shared" si="8"/>
+        <v>20</v>
+      </c>
+      <c r="L96">
+        <f t="shared" si="9"/>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="97" spans="4:12" x14ac:dyDescent="0.4">
+      <c r="D97">
+        <v>0</v>
+      </c>
+      <c r="E97">
+        <v>0</v>
+      </c>
+      <c r="F97">
+        <v>0</v>
+      </c>
+      <c r="G97">
+        <v>1</v>
+      </c>
+      <c r="H97">
+        <v>1</v>
+      </c>
+      <c r="I97">
+        <v>1</v>
+      </c>
+      <c r="J97">
+        <f t="shared" si="7"/>
+        <v>20</v>
+      </c>
+      <c r="K97">
+        <f t="shared" si="8"/>
+        <v>20</v>
+      </c>
+      <c r="L97">
+        <f t="shared" si="9"/>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="98" spans="4:12" x14ac:dyDescent="0.4">
+      <c r="D98">
+        <v>0</v>
+      </c>
+      <c r="E98">
+        <v>0</v>
+      </c>
+      <c r="F98">
+        <v>0</v>
+      </c>
+      <c r="G98">
+        <v>1</v>
+      </c>
+      <c r="H98">
+        <v>1</v>
+      </c>
+      <c r="I98">
+        <v>1</v>
+      </c>
+      <c r="J98">
+        <f t="shared" si="7"/>
+        <v>20</v>
+      </c>
+      <c r="K98">
+        <f t="shared" si="8"/>
+        <v>20</v>
+      </c>
+      <c r="L98">
+        <f t="shared" si="9"/>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="99" spans="4:12" x14ac:dyDescent="0.4">
+      <c r="D99">
+        <v>0</v>
+      </c>
+      <c r="E99">
+        <v>0</v>
+      </c>
+      <c r="F99">
+        <v>0</v>
+      </c>
+      <c r="G99">
+        <v>1</v>
+      </c>
+      <c r="H99">
+        <v>1</v>
+      </c>
+      <c r="I99">
+        <v>1</v>
+      </c>
+      <c r="J99">
+        <f t="shared" si="7"/>
+        <v>20</v>
+      </c>
+      <c r="K99">
+        <f t="shared" si="8"/>
+        <v>20</v>
+      </c>
+      <c r="L99">
+        <f t="shared" si="9"/>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="100" spans="4:12" x14ac:dyDescent="0.4">
+      <c r="D100">
+        <v>0</v>
+      </c>
+      <c r="E100">
+        <v>0</v>
+      </c>
+      <c r="F100">
+        <v>0</v>
+      </c>
+      <c r="G100">
+        <v>1</v>
+      </c>
+      <c r="H100">
+        <v>1</v>
+      </c>
+      <c r="I100">
+        <v>1</v>
+      </c>
+      <c r="J100">
+        <f t="shared" si="7"/>
+        <v>20</v>
+      </c>
+      <c r="K100">
+        <f t="shared" si="8"/>
+        <v>20</v>
+      </c>
+      <c r="L100">
+        <f t="shared" si="9"/>
         <v>20</v>
       </c>
     </row>

--- a/ActionGame-リファクタリング-/Data/CSV/Stage/Stage.xlsx
+++ b/ActionGame-リファクタリング-/Data/CSV/Stage/Stage.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ita20\OneDrive\デスクトップ\GameProject\ActionGame-リファクタリング-\Data\CSV\Stage\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\2409404\Desktop\GameProject\ActionGame-リファクタリング-\Data\CSV\Stage\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9490E59B-2444-40D3-A899-25FF6C93663B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{861323BE-9803-4571-9A5D-05C22795EC55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3060" yWindow="3180" windowWidth="21600" windowHeight="11295" xr2:uid="{62A58253-9505-4C17-A0D0-B4C12E04E8CC}"/>
+    <workbookView xWindow="0" yWindow="4185" windowWidth="21600" windowHeight="11295" xr2:uid="{62A58253-9505-4C17-A0D0-B4C12E04E8CC}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -96,9 +96,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 テーマ">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office テーマ">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -136,7 +136,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -242,7 +242,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -384,7 +384,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -2367,7 +2367,16 @@
         <v>20</v>
       </c>
     </row>
-    <row r="49" spans="4:12" x14ac:dyDescent="0.4">
+    <row r="49" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A49">
+        <v>340</v>
+      </c>
+      <c r="B49">
+        <v>120</v>
+      </c>
+      <c r="C49">
+        <v>-120</v>
+      </c>
       <c r="D49">
         <v>0</v>
       </c>
@@ -2378,7 +2387,7 @@
         <v>0</v>
       </c>
       <c r="G49">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H49">
         <v>1</v>
@@ -2388,7 +2397,7 @@
       </c>
       <c r="J49">
         <f t="shared" si="4"/>
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="K49">
         <f t="shared" si="5"/>
@@ -2399,7 +2408,16 @@
         <v>20</v>
       </c>
     </row>
-    <row r="50" spans="4:12" x14ac:dyDescent="0.4">
+    <row r="50" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A50">
+        <v>340</v>
+      </c>
+      <c r="B50">
+        <v>120</v>
+      </c>
+      <c r="C50">
+        <v>-100</v>
+      </c>
       <c r="D50">
         <v>0</v>
       </c>
@@ -2410,7 +2428,7 @@
         <v>0</v>
       </c>
       <c r="G50">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H50">
         <v>1</v>
@@ -2420,7 +2438,7 @@
       </c>
       <c r="J50">
         <f t="shared" si="4"/>
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="K50">
         <f t="shared" si="5"/>
@@ -2431,7 +2449,16 @@
         <v>20</v>
       </c>
     </row>
-    <row r="51" spans="4:12" x14ac:dyDescent="0.4">
+    <row r="51" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A51">
+        <v>340</v>
+      </c>
+      <c r="B51">
+        <v>120</v>
+      </c>
+      <c r="C51">
+        <v>-80</v>
+      </c>
       <c r="D51">
         <v>0</v>
       </c>
@@ -2442,7 +2469,7 @@
         <v>0</v>
       </c>
       <c r="G51">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H51">
         <v>1</v>
@@ -2452,7 +2479,7 @@
       </c>
       <c r="J51">
         <f t="shared" si="4"/>
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="K51">
         <f t="shared" si="5"/>
@@ -2463,7 +2490,16 @@
         <v>20</v>
       </c>
     </row>
-    <row r="52" spans="4:12" x14ac:dyDescent="0.4">
+    <row r="52" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A52">
+        <v>420</v>
+      </c>
+      <c r="B52">
+        <v>140</v>
+      </c>
+      <c r="C52">
+        <v>-40</v>
+      </c>
       <c r="D52">
         <v>0</v>
       </c>
@@ -2474,7 +2510,7 @@
         <v>0</v>
       </c>
       <c r="G52">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H52">
         <v>1</v>
@@ -2484,7 +2520,7 @@
       </c>
       <c r="J52">
         <f t="shared" si="4"/>
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="K52">
         <f t="shared" si="5"/>
@@ -2495,7 +2531,16 @@
         <v>20</v>
       </c>
     </row>
-    <row r="53" spans="4:12" x14ac:dyDescent="0.4">
+    <row r="53" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A53">
+        <v>420</v>
+      </c>
+      <c r="B53">
+        <v>140</v>
+      </c>
+      <c r="C53">
+        <v>-20</v>
+      </c>
       <c r="D53">
         <v>0</v>
       </c>
@@ -2506,7 +2551,7 @@
         <v>0</v>
       </c>
       <c r="G53">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H53">
         <v>1</v>
@@ -2516,7 +2561,7 @@
       </c>
       <c r="J53">
         <f t="shared" si="4"/>
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="K53">
         <f t="shared" si="5"/>
@@ -2527,7 +2572,16 @@
         <v>20</v>
       </c>
     </row>
-    <row r="54" spans="4:12" x14ac:dyDescent="0.4">
+    <row r="54" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A54">
+        <v>420</v>
+      </c>
+      <c r="B54">
+        <v>140</v>
+      </c>
+      <c r="C54">
+        <v>0</v>
+      </c>
       <c r="D54">
         <v>0</v>
       </c>
@@ -2538,7 +2592,7 @@
         <v>0</v>
       </c>
       <c r="G54">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H54">
         <v>1</v>
@@ -2548,7 +2602,7 @@
       </c>
       <c r="J54">
         <f t="shared" si="4"/>
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="K54">
         <f t="shared" si="5"/>
@@ -2559,7 +2613,16 @@
         <v>20</v>
       </c>
     </row>
-    <row r="55" spans="4:12" x14ac:dyDescent="0.4">
+    <row r="55" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A55">
+        <v>420</v>
+      </c>
+      <c r="B55">
+        <v>160</v>
+      </c>
+      <c r="C55">
+        <v>60</v>
+      </c>
       <c r="D55">
         <v>0</v>
       </c>
@@ -2570,7 +2633,7 @@
         <v>0</v>
       </c>
       <c r="G55">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H55">
         <v>1</v>
@@ -2580,7 +2643,7 @@
       </c>
       <c r="J55">
         <f t="shared" si="4"/>
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="K55">
         <f t="shared" si="5"/>
@@ -2591,7 +2654,16 @@
         <v>20</v>
       </c>
     </row>
-    <row r="56" spans="4:12" x14ac:dyDescent="0.4">
+    <row r="56" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A56">
+        <v>420</v>
+      </c>
+      <c r="B56">
+        <v>160</v>
+      </c>
+      <c r="C56">
+        <v>80</v>
+      </c>
       <c r="D56">
         <v>0</v>
       </c>
@@ -2602,7 +2674,7 @@
         <v>0</v>
       </c>
       <c r="G56">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H56">
         <v>1</v>
@@ -2612,7 +2684,7 @@
       </c>
       <c r="J56">
         <f t="shared" si="4"/>
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="K56">
         <f t="shared" si="5"/>
@@ -2623,7 +2695,16 @@
         <v>20</v>
       </c>
     </row>
-    <row r="57" spans="4:12" x14ac:dyDescent="0.4">
+    <row r="57" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A57">
+        <v>420</v>
+      </c>
+      <c r="B57">
+        <v>160</v>
+      </c>
+      <c r="C57">
+        <v>100</v>
+      </c>
       <c r="D57">
         <v>0</v>
       </c>
@@ -2634,7 +2715,7 @@
         <v>0</v>
       </c>
       <c r="G57">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H57">
         <v>1</v>
@@ -2644,7 +2725,7 @@
       </c>
       <c r="J57">
         <f t="shared" si="4"/>
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="K57">
         <f t="shared" si="5"/>
@@ -2655,7 +2736,16 @@
         <v>20</v>
       </c>
     </row>
-    <row r="58" spans="4:12" x14ac:dyDescent="0.4">
+    <row r="58" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A58">
+        <v>420</v>
+      </c>
+      <c r="B58">
+        <v>180</v>
+      </c>
+      <c r="C58">
+        <v>160</v>
+      </c>
       <c r="D58">
         <v>0</v>
       </c>
@@ -2666,7 +2756,7 @@
         <v>0</v>
       </c>
       <c r="G58">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H58">
         <v>1</v>
@@ -2676,7 +2766,7 @@
       </c>
       <c r="J58">
         <f t="shared" si="4"/>
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="K58">
         <f t="shared" si="5"/>
@@ -2687,7 +2777,16 @@
         <v>20</v>
       </c>
     </row>
-    <row r="59" spans="4:12" x14ac:dyDescent="0.4">
+    <row r="59" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A59">
+        <v>420</v>
+      </c>
+      <c r="B59">
+        <v>180</v>
+      </c>
+      <c r="C59">
+        <v>180</v>
+      </c>
       <c r="D59">
         <v>0</v>
       </c>
@@ -2698,7 +2797,7 @@
         <v>0</v>
       </c>
       <c r="G59">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H59">
         <v>1</v>
@@ -2708,7 +2807,7 @@
       </c>
       <c r="J59">
         <f t="shared" si="4"/>
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="K59">
         <f t="shared" si="5"/>
@@ -2719,7 +2818,16 @@
         <v>20</v>
       </c>
     </row>
-    <row r="60" spans="4:12" x14ac:dyDescent="0.4">
+    <row r="60" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A60">
+        <v>420</v>
+      </c>
+      <c r="B60">
+        <v>180</v>
+      </c>
+      <c r="C60">
+        <v>200</v>
+      </c>
       <c r="D60">
         <v>0</v>
       </c>
@@ -2730,7 +2838,7 @@
         <v>0</v>
       </c>
       <c r="G60">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H60">
         <v>1</v>
@@ -2740,7 +2848,7 @@
       </c>
       <c r="J60">
         <f t="shared" si="4"/>
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="K60">
         <f t="shared" si="5"/>
@@ -2751,7 +2859,16 @@
         <v>20</v>
       </c>
     </row>
-    <row r="61" spans="4:12" x14ac:dyDescent="0.4">
+    <row r="61" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A61">
+        <v>420</v>
+      </c>
+      <c r="B61">
+        <v>180</v>
+      </c>
+      <c r="C61">
+        <v>240</v>
+      </c>
       <c r="D61">
         <v>0</v>
       </c>
@@ -2762,17 +2879,17 @@
         <v>0</v>
       </c>
       <c r="G61">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H61">
         <v>1</v>
       </c>
       <c r="I61">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J61">
         <f t="shared" si="4"/>
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="K61">
         <f t="shared" si="5"/>
@@ -2780,10 +2897,10 @@
       </c>
       <c r="L61">
         <f t="shared" si="6"/>
-        <v>20</v>
-      </c>
-    </row>
-    <row r="62" spans="4:12" x14ac:dyDescent="0.4">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="62" spans="1:12" x14ac:dyDescent="0.4">
       <c r="D62">
         <v>0</v>
       </c>
@@ -2815,7 +2932,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="63" spans="4:12" x14ac:dyDescent="0.4">
+    <row r="63" spans="1:12" x14ac:dyDescent="0.4">
       <c r="D63">
         <v>0</v>
       </c>
@@ -2847,7 +2964,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="64" spans="4:12" x14ac:dyDescent="0.4">
+    <row r="64" spans="1:12" x14ac:dyDescent="0.4">
       <c r="D64">
         <v>0</v>
       </c>

--- a/ActionGame-リファクタリング-/Data/CSV/Stage/Stage.xlsx
+++ b/ActionGame-リファクタリング-/Data/CSV/Stage/Stage.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\2409404\Desktop\GameProject\ActionGame-リファクタリング-\Data\CSV\Stage\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ita20\OneDrive\デスクトップ\GameProject\ActionGame-リファクタリング-\Data\CSV\Stage\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{861323BE-9803-4571-9A5D-05C22795EC55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{012FE5E8-A356-4935-96C9-507751FC9FA0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="4185" windowWidth="21600" windowHeight="11295" xr2:uid="{62A58253-9505-4C17-A0D0-B4C12E04E8CC}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{62A58253-9505-4C17-A0D0-B4C12E04E8CC}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -96,9 +96,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office テーマ">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 テーマ">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -136,7 +136,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -242,7 +242,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -384,7 +384,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -392,14 +392,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{592BFE65-1919-4E86-A258-49B12076C0A7}">
-  <dimension ref="A1:L100"/>
+  <dimension ref="A1:P100"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="12" width="5.625" customWidth="1"/>
-    <col min="13" max="13" width="9" customWidth="1"/>
+    <col min="1" max="16" width="5.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A1">
         <v>0</v>
       </c>
@@ -439,8 +438,20 @@
         <f t="shared" si="0"/>
         <v>20</v>
       </c>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="M1">
+        <v>0</v>
+      </c>
+      <c r="N1">
+        <v>0</v>
+      </c>
+      <c r="O1">
+        <v>0</v>
+      </c>
+      <c r="P1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A2">
         <v>0</v>
       </c>
@@ -480,8 +491,20 @@
         <f t="shared" ref="L2:L27" si="3">I2*20</f>
         <v>20</v>
       </c>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>0</v>
+      </c>
+      <c r="O2">
+        <v>0</v>
+      </c>
+      <c r="P2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A3">
         <v>0</v>
       </c>
@@ -521,8 +544,20 @@
         <f t="shared" si="3"/>
         <v>20</v>
       </c>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="M3">
+        <v>0</v>
+      </c>
+      <c r="N3">
+        <v>0</v>
+      </c>
+      <c r="O3">
+        <v>0</v>
+      </c>
+      <c r="P3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A4">
         <v>0</v>
       </c>
@@ -562,8 +597,20 @@
         <f t="shared" si="3"/>
         <v>20</v>
       </c>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="M4">
+        <v>0</v>
+      </c>
+      <c r="N4">
+        <v>0</v>
+      </c>
+      <c r="O4">
+        <v>0</v>
+      </c>
+      <c r="P4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A5">
         <v>20</v>
       </c>
@@ -603,8 +650,20 @@
         <f t="shared" si="3"/>
         <v>60</v>
       </c>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="M5">
+        <v>0</v>
+      </c>
+      <c r="N5">
+        <v>0</v>
+      </c>
+      <c r="O5">
+        <v>0</v>
+      </c>
+      <c r="P5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A6">
         <v>0</v>
       </c>
@@ -644,8 +703,20 @@
         <f t="shared" si="3"/>
         <v>60</v>
       </c>
-    </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="M6">
+        <v>0</v>
+      </c>
+      <c r="N6">
+        <v>0</v>
+      </c>
+      <c r="O6">
+        <v>0</v>
+      </c>
+      <c r="P6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A7">
         <v>-20</v>
       </c>
@@ -685,8 +756,20 @@
         <f t="shared" si="3"/>
         <v>60</v>
       </c>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="M7">
+        <v>0</v>
+      </c>
+      <c r="N7">
+        <v>0</v>
+      </c>
+      <c r="O7">
+        <v>0</v>
+      </c>
+      <c r="P7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A8">
         <v>-40</v>
       </c>
@@ -726,8 +809,20 @@
         <f t="shared" si="3"/>
         <v>60</v>
       </c>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="M8">
+        <v>0</v>
+      </c>
+      <c r="N8">
+        <v>0</v>
+      </c>
+      <c r="O8">
+        <v>0</v>
+      </c>
+      <c r="P8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A9">
         <v>-60</v>
       </c>
@@ -767,8 +862,20 @@
         <f t="shared" si="3"/>
         <v>60</v>
       </c>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="M9">
+        <v>0</v>
+      </c>
+      <c r="N9">
+        <v>0</v>
+      </c>
+      <c r="O9">
+        <v>0</v>
+      </c>
+      <c r="P9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A10">
         <v>-80</v>
       </c>
@@ -808,8 +915,20 @@
         <f t="shared" si="3"/>
         <v>60</v>
       </c>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="M10">
+        <v>0</v>
+      </c>
+      <c r="N10">
+        <v>0</v>
+      </c>
+      <c r="O10">
+        <v>0</v>
+      </c>
+      <c r="P10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A11">
         <v>-100</v>
       </c>
@@ -849,8 +968,20 @@
         <f t="shared" si="3"/>
         <v>60</v>
       </c>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="M11">
+        <v>0</v>
+      </c>
+      <c r="N11">
+        <v>0</v>
+      </c>
+      <c r="O11">
+        <v>0</v>
+      </c>
+      <c r="P11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A12">
         <v>-120</v>
       </c>
@@ -890,8 +1021,20 @@
         <f t="shared" si="3"/>
         <v>60</v>
       </c>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="M12">
+        <v>0</v>
+      </c>
+      <c r="N12">
+        <v>0</v>
+      </c>
+      <c r="O12">
+        <v>0</v>
+      </c>
+      <c r="P12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A13">
         <v>-140</v>
       </c>
@@ -931,8 +1074,20 @@
         <f t="shared" si="3"/>
         <v>60</v>
       </c>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="M13">
+        <v>0</v>
+      </c>
+      <c r="N13">
+        <v>0</v>
+      </c>
+      <c r="O13">
+        <v>0</v>
+      </c>
+      <c r="P13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A14">
         <v>-160</v>
       </c>
@@ -972,8 +1127,20 @@
         <f t="shared" si="3"/>
         <v>60</v>
       </c>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="M14">
+        <v>0</v>
+      </c>
+      <c r="N14">
+        <v>0</v>
+      </c>
+      <c r="O14">
+        <v>0</v>
+      </c>
+      <c r="P14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A15">
         <v>-180</v>
       </c>
@@ -1013,8 +1180,20 @@
         <f t="shared" si="3"/>
         <v>60</v>
       </c>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="M15">
+        <v>0</v>
+      </c>
+      <c r="N15">
+        <v>0</v>
+      </c>
+      <c r="O15">
+        <v>0</v>
+      </c>
+      <c r="P15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A16">
         <v>-200</v>
       </c>
@@ -1054,8 +1233,20 @@
         <f t="shared" si="3"/>
         <v>60</v>
       </c>
-    </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="M16">
+        <v>0</v>
+      </c>
+      <c r="N16">
+        <v>0</v>
+      </c>
+      <c r="O16">
+        <v>0</v>
+      </c>
+      <c r="P16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A17">
         <v>-180</v>
       </c>
@@ -1095,8 +1286,20 @@
         <f t="shared" si="3"/>
         <v>20</v>
       </c>
-    </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="M17">
+        <v>0</v>
+      </c>
+      <c r="N17">
+        <v>0</v>
+      </c>
+      <c r="O17">
+        <v>0</v>
+      </c>
+      <c r="P17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A18">
         <v>-180</v>
       </c>
@@ -1136,8 +1339,20 @@
         <f t="shared" si="3"/>
         <v>20</v>
       </c>
-    </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="M18">
+        <v>0</v>
+      </c>
+      <c r="N18">
+        <v>0</v>
+      </c>
+      <c r="O18">
+        <v>0</v>
+      </c>
+      <c r="P18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A19">
         <v>-180</v>
       </c>
@@ -1177,8 +1392,20 @@
         <f t="shared" si="3"/>
         <v>20</v>
       </c>
-    </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="M19">
+        <v>0</v>
+      </c>
+      <c r="N19">
+        <v>0</v>
+      </c>
+      <c r="O19">
+        <v>0</v>
+      </c>
+      <c r="P19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A20">
         <v>-180</v>
       </c>
@@ -1218,8 +1445,20 @@
         <f t="shared" si="3"/>
         <v>20</v>
       </c>
-    </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="M20">
+        <v>0</v>
+      </c>
+      <c r="N20">
+        <v>0</v>
+      </c>
+      <c r="O20">
+        <v>0</v>
+      </c>
+      <c r="P20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A21">
         <v>-180</v>
       </c>
@@ -1259,8 +1498,20 @@
         <f t="shared" si="3"/>
         <v>20</v>
       </c>
-    </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="M21">
+        <v>0</v>
+      </c>
+      <c r="N21">
+        <v>0</v>
+      </c>
+      <c r="O21">
+        <v>0</v>
+      </c>
+      <c r="P21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A22">
         <v>-200</v>
       </c>
@@ -1300,8 +1551,20 @@
         <f t="shared" si="3"/>
         <v>60</v>
       </c>
-    </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="M22">
+        <v>0</v>
+      </c>
+      <c r="N22">
+        <v>0</v>
+      </c>
+      <c r="O22">
+        <v>0</v>
+      </c>
+      <c r="P22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A23">
         <v>-180</v>
       </c>
@@ -1341,8 +1604,20 @@
         <f t="shared" si="3"/>
         <v>60</v>
       </c>
-    </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="M23">
+        <v>0</v>
+      </c>
+      <c r="N23">
+        <v>0</v>
+      </c>
+      <c r="O23">
+        <v>0</v>
+      </c>
+      <c r="P23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A24">
         <v>-160</v>
       </c>
@@ -1382,8 +1657,20 @@
         <f t="shared" si="3"/>
         <v>60</v>
       </c>
-    </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="M24">
+        <v>0</v>
+      </c>
+      <c r="N24">
+        <v>0</v>
+      </c>
+      <c r="O24">
+        <v>0</v>
+      </c>
+      <c r="P24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A25">
         <v>-140</v>
       </c>
@@ -1423,8 +1710,20 @@
         <f t="shared" si="3"/>
         <v>60</v>
       </c>
-    </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="M25">
+        <v>0</v>
+      </c>
+      <c r="N25">
+        <v>0</v>
+      </c>
+      <c r="O25">
+        <v>0</v>
+      </c>
+      <c r="P25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A26">
         <v>-120</v>
       </c>
@@ -1464,8 +1763,20 @@
         <f t="shared" si="3"/>
         <v>60</v>
       </c>
-    </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="M26">
+        <v>0</v>
+      </c>
+      <c r="N26">
+        <v>0</v>
+      </c>
+      <c r="O26">
+        <v>0</v>
+      </c>
+      <c r="P26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A27">
         <v>-100</v>
       </c>
@@ -1505,8 +1816,20 @@
         <f t="shared" si="3"/>
         <v>60</v>
       </c>
-    </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="M27">
+        <v>0</v>
+      </c>
+      <c r="N27">
+        <v>0</v>
+      </c>
+      <c r="O27">
+        <v>0</v>
+      </c>
+      <c r="P27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A28">
         <v>-60</v>
       </c>
@@ -1546,8 +1869,20 @@
         <f t="shared" ref="L28:L91" si="6">I28*20</f>
         <v>60</v>
       </c>
-    </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="M28">
+        <v>0</v>
+      </c>
+      <c r="N28">
+        <v>0</v>
+      </c>
+      <c r="O28">
+        <v>0</v>
+      </c>
+      <c r="P28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A29">
         <v>-40</v>
       </c>
@@ -1587,8 +1922,20 @@
         <f t="shared" si="6"/>
         <v>60</v>
       </c>
-    </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="M29">
+        <v>0</v>
+      </c>
+      <c r="N29">
+        <v>0</v>
+      </c>
+      <c r="O29">
+        <v>0</v>
+      </c>
+      <c r="P29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A30">
         <v>-20</v>
       </c>
@@ -1628,8 +1975,20 @@
         <f t="shared" si="6"/>
         <v>60</v>
       </c>
-    </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="M30">
+        <v>0</v>
+      </c>
+      <c r="N30">
+        <v>0</v>
+      </c>
+      <c r="O30">
+        <v>0</v>
+      </c>
+      <c r="P30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A31">
         <v>20</v>
       </c>
@@ -1669,8 +2028,20 @@
         <f t="shared" si="6"/>
         <v>60</v>
       </c>
-    </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="M31">
+        <v>0</v>
+      </c>
+      <c r="N31">
+        <v>0</v>
+      </c>
+      <c r="O31">
+        <v>0</v>
+      </c>
+      <c r="P31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A32">
         <v>40</v>
       </c>
@@ -1710,8 +2081,20 @@
         <f t="shared" si="6"/>
         <v>60</v>
       </c>
-    </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="M32">
+        <v>0</v>
+      </c>
+      <c r="N32">
+        <v>0</v>
+      </c>
+      <c r="O32">
+        <v>0</v>
+      </c>
+      <c r="P32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A33">
         <v>60</v>
       </c>
@@ -1751,8 +2134,20 @@
         <f t="shared" si="6"/>
         <v>60</v>
       </c>
-    </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="M33">
+        <v>0</v>
+      </c>
+      <c r="N33">
+        <v>0</v>
+      </c>
+      <c r="O33">
+        <v>0</v>
+      </c>
+      <c r="P33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A34">
         <v>100</v>
       </c>
@@ -1792,8 +2187,20 @@
         <f t="shared" si="6"/>
         <v>60</v>
       </c>
-    </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="M34">
+        <v>0</v>
+      </c>
+      <c r="N34">
+        <v>0</v>
+      </c>
+      <c r="O34">
+        <v>0</v>
+      </c>
+      <c r="P34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A35">
         <v>120</v>
       </c>
@@ -1833,8 +2240,20 @@
         <f t="shared" si="6"/>
         <v>60</v>
       </c>
-    </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="M35">
+        <v>0</v>
+      </c>
+      <c r="N35">
+        <v>0</v>
+      </c>
+      <c r="O35">
+        <v>0</v>
+      </c>
+      <c r="P35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A36">
         <v>140</v>
       </c>
@@ -1874,8 +2293,20 @@
         <f t="shared" si="6"/>
         <v>60</v>
       </c>
-    </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="M36">
+        <v>0</v>
+      </c>
+      <c r="N36">
+        <v>0</v>
+      </c>
+      <c r="O36">
+        <v>0</v>
+      </c>
+      <c r="P36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A37">
         <v>180</v>
       </c>
@@ -1915,8 +2346,20 @@
         <f t="shared" si="6"/>
         <v>60</v>
       </c>
-    </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="M37">
+        <v>0</v>
+      </c>
+      <c r="N37">
+        <v>0</v>
+      </c>
+      <c r="O37">
+        <v>0</v>
+      </c>
+      <c r="P37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A38">
         <v>200</v>
       </c>
@@ -1956,8 +2399,20 @@
         <f t="shared" si="6"/>
         <v>60</v>
       </c>
-    </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="M38">
+        <v>0</v>
+      </c>
+      <c r="N38">
+        <v>0</v>
+      </c>
+      <c r="O38">
+        <v>0</v>
+      </c>
+      <c r="P38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A39">
         <v>220</v>
       </c>
@@ -1997,8 +2452,20 @@
         <f t="shared" si="6"/>
         <v>60</v>
       </c>
-    </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="M39">
+        <v>0</v>
+      </c>
+      <c r="N39">
+        <v>0</v>
+      </c>
+      <c r="O39">
+        <v>0</v>
+      </c>
+      <c r="P39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A40">
         <v>260</v>
       </c>
@@ -2038,8 +2505,20 @@
         <f t="shared" si="6"/>
         <v>20</v>
       </c>
-    </row>
-    <row r="41" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="M40">
+        <v>0</v>
+      </c>
+      <c r="N40">
+        <v>0</v>
+      </c>
+      <c r="O40">
+        <v>0</v>
+      </c>
+      <c r="P40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A41">
         <v>260</v>
       </c>
@@ -2079,8 +2558,20 @@
         <f t="shared" si="6"/>
         <v>20</v>
       </c>
-    </row>
-    <row r="42" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="M41">
+        <v>0</v>
+      </c>
+      <c r="N41">
+        <v>0</v>
+      </c>
+      <c r="O41">
+        <v>0</v>
+      </c>
+      <c r="P41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A42">
         <v>260</v>
       </c>
@@ -2120,8 +2611,20 @@
         <f t="shared" si="6"/>
         <v>20</v>
       </c>
-    </row>
-    <row r="43" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="M42">
+        <v>0</v>
+      </c>
+      <c r="N42">
+        <v>0</v>
+      </c>
+      <c r="O42">
+        <v>0</v>
+      </c>
+      <c r="P42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A43">
         <v>260</v>
       </c>
@@ -2161,8 +2664,20 @@
         <f t="shared" si="6"/>
         <v>20</v>
       </c>
-    </row>
-    <row r="44" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="M43">
+        <v>0</v>
+      </c>
+      <c r="N43">
+        <v>0</v>
+      </c>
+      <c r="O43">
+        <v>0</v>
+      </c>
+      <c r="P43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A44">
         <v>260</v>
       </c>
@@ -2202,8 +2717,20 @@
         <f t="shared" si="6"/>
         <v>20</v>
       </c>
-    </row>
-    <row r="45" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="M44">
+        <v>0</v>
+      </c>
+      <c r="N44">
+        <v>0</v>
+      </c>
+      <c r="O44">
+        <v>0</v>
+      </c>
+      <c r="P44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A45">
         <v>260</v>
       </c>
@@ -2243,8 +2770,20 @@
         <f t="shared" si="6"/>
         <v>20</v>
       </c>
-    </row>
-    <row r="46" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="M45">
+        <v>0</v>
+      </c>
+      <c r="N45">
+        <v>0</v>
+      </c>
+      <c r="O45">
+        <v>0</v>
+      </c>
+      <c r="P45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A46">
         <v>260</v>
       </c>
@@ -2284,8 +2823,20 @@
         <f t="shared" si="6"/>
         <v>20</v>
       </c>
-    </row>
-    <row r="47" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="M46">
+        <v>0</v>
+      </c>
+      <c r="N46">
+        <v>0</v>
+      </c>
+      <c r="O46">
+        <v>0</v>
+      </c>
+      <c r="P46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A47">
         <v>260</v>
       </c>
@@ -2325,8 +2876,20 @@
         <f t="shared" si="6"/>
         <v>20</v>
       </c>
-    </row>
-    <row r="48" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="M47">
+        <v>0</v>
+      </c>
+      <c r="N47">
+        <v>0</v>
+      </c>
+      <c r="O47">
+        <v>0</v>
+      </c>
+      <c r="P47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A48">
         <v>260</v>
       </c>
@@ -2366,8 +2929,20 @@
         <f t="shared" si="6"/>
         <v>20</v>
       </c>
-    </row>
-    <row r="49" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="M48">
+        <v>0</v>
+      </c>
+      <c r="N48">
+        <v>0</v>
+      </c>
+      <c r="O48">
+        <v>0</v>
+      </c>
+      <c r="P48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A49">
         <v>340</v>
       </c>
@@ -2407,8 +2982,20 @@
         <f t="shared" si="6"/>
         <v>20</v>
       </c>
-    </row>
-    <row r="50" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="M49">
+        <v>0</v>
+      </c>
+      <c r="N49">
+        <v>0</v>
+      </c>
+      <c r="O49">
+        <v>0</v>
+      </c>
+      <c r="P49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A50">
         <v>340</v>
       </c>
@@ -2448,8 +3035,20 @@
         <f t="shared" si="6"/>
         <v>20</v>
       </c>
-    </row>
-    <row r="51" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="M50">
+        <v>0</v>
+      </c>
+      <c r="N50">
+        <v>0</v>
+      </c>
+      <c r="O50">
+        <v>0</v>
+      </c>
+      <c r="P50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A51">
         <v>340</v>
       </c>
@@ -2489,8 +3088,20 @@
         <f t="shared" si="6"/>
         <v>20</v>
       </c>
-    </row>
-    <row r="52" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="M51">
+        <v>0</v>
+      </c>
+      <c r="N51">
+        <v>0</v>
+      </c>
+      <c r="O51">
+        <v>0</v>
+      </c>
+      <c r="P51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A52">
         <v>420</v>
       </c>
@@ -2530,8 +3141,20 @@
         <f t="shared" si="6"/>
         <v>20</v>
       </c>
-    </row>
-    <row r="53" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="M52">
+        <v>0</v>
+      </c>
+      <c r="N52">
+        <v>0</v>
+      </c>
+      <c r="O52">
+        <v>0</v>
+      </c>
+      <c r="P52">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A53">
         <v>420</v>
       </c>
@@ -2571,8 +3194,20 @@
         <f t="shared" si="6"/>
         <v>20</v>
       </c>
-    </row>
-    <row r="54" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="M53">
+        <v>0</v>
+      </c>
+      <c r="N53">
+        <v>0</v>
+      </c>
+      <c r="O53">
+        <v>0</v>
+      </c>
+      <c r="P53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A54">
         <v>420</v>
       </c>
@@ -2612,8 +3247,20 @@
         <f t="shared" si="6"/>
         <v>20</v>
       </c>
-    </row>
-    <row r="55" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="M54">
+        <v>0</v>
+      </c>
+      <c r="N54">
+        <v>0</v>
+      </c>
+      <c r="O54">
+        <v>0</v>
+      </c>
+      <c r="P54">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A55">
         <v>420</v>
       </c>
@@ -2653,8 +3300,20 @@
         <f t="shared" si="6"/>
         <v>20</v>
       </c>
-    </row>
-    <row r="56" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="M55">
+        <v>0</v>
+      </c>
+      <c r="N55">
+        <v>0</v>
+      </c>
+      <c r="O55">
+        <v>0</v>
+      </c>
+      <c r="P55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A56">
         <v>420</v>
       </c>
@@ -2694,8 +3353,20 @@
         <f t="shared" si="6"/>
         <v>20</v>
       </c>
-    </row>
-    <row r="57" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="M56">
+        <v>0</v>
+      </c>
+      <c r="N56">
+        <v>0</v>
+      </c>
+      <c r="O56">
+        <v>0</v>
+      </c>
+      <c r="P56">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A57">
         <v>420</v>
       </c>
@@ -2735,8 +3406,20 @@
         <f t="shared" si="6"/>
         <v>20</v>
       </c>
-    </row>
-    <row r="58" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="M57">
+        <v>0</v>
+      </c>
+      <c r="N57">
+        <v>0</v>
+      </c>
+      <c r="O57">
+        <v>0</v>
+      </c>
+      <c r="P57">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A58">
         <v>420</v>
       </c>
@@ -2776,8 +3459,20 @@
         <f t="shared" si="6"/>
         <v>20</v>
       </c>
-    </row>
-    <row r="59" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="M58">
+        <v>0</v>
+      </c>
+      <c r="N58">
+        <v>0</v>
+      </c>
+      <c r="O58">
+        <v>0</v>
+      </c>
+      <c r="P58">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A59">
         <v>420</v>
       </c>
@@ -2817,8 +3512,20 @@
         <f t="shared" si="6"/>
         <v>20</v>
       </c>
-    </row>
-    <row r="60" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="M59">
+        <v>0</v>
+      </c>
+      <c r="N59">
+        <v>0</v>
+      </c>
+      <c r="O59">
+        <v>0</v>
+      </c>
+      <c r="P59">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A60">
         <v>420</v>
       </c>
@@ -2858,8 +3565,20 @@
         <f t="shared" si="6"/>
         <v>20</v>
       </c>
-    </row>
-    <row r="61" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="M60">
+        <v>0</v>
+      </c>
+      <c r="N60">
+        <v>0</v>
+      </c>
+      <c r="O60">
+        <v>0</v>
+      </c>
+      <c r="P60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A61">
         <v>420</v>
       </c>
@@ -2899,8 +3618,29 @@
         <f t="shared" si="6"/>
         <v>60</v>
       </c>
-    </row>
-    <row r="62" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="M61">
+        <v>420</v>
+      </c>
+      <c r="N61">
+        <v>280</v>
+      </c>
+      <c r="O61">
+        <v>240</v>
+      </c>
+      <c r="P61">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="62" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A62">
+        <v>0</v>
+      </c>
+      <c r="B62">
+        <v>0</v>
+      </c>
+      <c r="C62">
+        <v>0</v>
+      </c>
       <c r="D62">
         <v>0</v>
       </c>
@@ -2931,8 +3671,29 @@
         <f t="shared" si="6"/>
         <v>20</v>
       </c>
-    </row>
-    <row r="63" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="M62">
+        <v>0</v>
+      </c>
+      <c r="N62">
+        <v>0</v>
+      </c>
+      <c r="O62">
+        <v>0</v>
+      </c>
+      <c r="P62">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A63">
+        <v>0</v>
+      </c>
+      <c r="B63">
+        <v>0</v>
+      </c>
+      <c r="C63">
+        <v>0</v>
+      </c>
       <c r="D63">
         <v>0</v>
       </c>
@@ -2963,8 +3724,29 @@
         <f t="shared" si="6"/>
         <v>20</v>
       </c>
-    </row>
-    <row r="64" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="M63">
+        <v>0</v>
+      </c>
+      <c r="N63">
+        <v>0</v>
+      </c>
+      <c r="O63">
+        <v>0</v>
+      </c>
+      <c r="P63">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A64">
+        <v>0</v>
+      </c>
+      <c r="B64">
+        <v>0</v>
+      </c>
+      <c r="C64">
+        <v>0</v>
+      </c>
       <c r="D64">
         <v>0</v>
       </c>
@@ -2995,8 +3777,29 @@
         <f t="shared" si="6"/>
         <v>20</v>
       </c>
-    </row>
-    <row r="65" spans="4:12" x14ac:dyDescent="0.4">
+      <c r="M64">
+        <v>0</v>
+      </c>
+      <c r="N64">
+        <v>0</v>
+      </c>
+      <c r="O64">
+        <v>0</v>
+      </c>
+      <c r="P64">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A65">
+        <v>0</v>
+      </c>
+      <c r="B65">
+        <v>0</v>
+      </c>
+      <c r="C65">
+        <v>0</v>
+      </c>
       <c r="D65">
         <v>0</v>
       </c>
@@ -3027,8 +3830,29 @@
         <f t="shared" si="6"/>
         <v>20</v>
       </c>
-    </row>
-    <row r="66" spans="4:12" x14ac:dyDescent="0.4">
+      <c r="M65">
+        <v>0</v>
+      </c>
+      <c r="N65">
+        <v>0</v>
+      </c>
+      <c r="O65">
+        <v>0</v>
+      </c>
+      <c r="P65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A66">
+        <v>0</v>
+      </c>
+      <c r="B66">
+        <v>0</v>
+      </c>
+      <c r="C66">
+        <v>0</v>
+      </c>
       <c r="D66">
         <v>0</v>
       </c>
@@ -3059,8 +3883,29 @@
         <f t="shared" si="6"/>
         <v>20</v>
       </c>
-    </row>
-    <row r="67" spans="4:12" x14ac:dyDescent="0.4">
+      <c r="M66">
+        <v>0</v>
+      </c>
+      <c r="N66">
+        <v>0</v>
+      </c>
+      <c r="O66">
+        <v>0</v>
+      </c>
+      <c r="P66">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A67">
+        <v>0</v>
+      </c>
+      <c r="B67">
+        <v>0</v>
+      </c>
+      <c r="C67">
+        <v>0</v>
+      </c>
       <c r="D67">
         <v>0</v>
       </c>
@@ -3091,8 +3936,29 @@
         <f t="shared" si="6"/>
         <v>20</v>
       </c>
-    </row>
-    <row r="68" spans="4:12" x14ac:dyDescent="0.4">
+      <c r="M67">
+        <v>0</v>
+      </c>
+      <c r="N67">
+        <v>0</v>
+      </c>
+      <c r="O67">
+        <v>0</v>
+      </c>
+      <c r="P67">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A68">
+        <v>0</v>
+      </c>
+      <c r="B68">
+        <v>0</v>
+      </c>
+      <c r="C68">
+        <v>0</v>
+      </c>
       <c r="D68">
         <v>0</v>
       </c>
@@ -3123,8 +3989,29 @@
         <f t="shared" si="6"/>
         <v>20</v>
       </c>
-    </row>
-    <row r="69" spans="4:12" x14ac:dyDescent="0.4">
+      <c r="M68">
+        <v>0</v>
+      </c>
+      <c r="N68">
+        <v>0</v>
+      </c>
+      <c r="O68">
+        <v>0</v>
+      </c>
+      <c r="P68">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A69">
+        <v>0</v>
+      </c>
+      <c r="B69">
+        <v>0</v>
+      </c>
+      <c r="C69">
+        <v>0</v>
+      </c>
       <c r="D69">
         <v>0</v>
       </c>
@@ -3155,8 +4042,29 @@
         <f t="shared" si="6"/>
         <v>20</v>
       </c>
-    </row>
-    <row r="70" spans="4:12" x14ac:dyDescent="0.4">
+      <c r="M69">
+        <v>0</v>
+      </c>
+      <c r="N69">
+        <v>0</v>
+      </c>
+      <c r="O69">
+        <v>0</v>
+      </c>
+      <c r="P69">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A70">
+        <v>0</v>
+      </c>
+      <c r="B70">
+        <v>0</v>
+      </c>
+      <c r="C70">
+        <v>0</v>
+      </c>
       <c r="D70">
         <v>0</v>
       </c>
@@ -3187,8 +4095,29 @@
         <f t="shared" si="6"/>
         <v>20</v>
       </c>
-    </row>
-    <row r="71" spans="4:12" x14ac:dyDescent="0.4">
+      <c r="M70">
+        <v>0</v>
+      </c>
+      <c r="N70">
+        <v>0</v>
+      </c>
+      <c r="O70">
+        <v>0</v>
+      </c>
+      <c r="P70">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A71">
+        <v>0</v>
+      </c>
+      <c r="B71">
+        <v>0</v>
+      </c>
+      <c r="C71">
+        <v>0</v>
+      </c>
       <c r="D71">
         <v>0</v>
       </c>
@@ -3219,8 +4148,29 @@
         <f t="shared" si="6"/>
         <v>20</v>
       </c>
-    </row>
-    <row r="72" spans="4:12" x14ac:dyDescent="0.4">
+      <c r="M71">
+        <v>0</v>
+      </c>
+      <c r="N71">
+        <v>0</v>
+      </c>
+      <c r="O71">
+        <v>0</v>
+      </c>
+      <c r="P71">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A72">
+        <v>0</v>
+      </c>
+      <c r="B72">
+        <v>0</v>
+      </c>
+      <c r="C72">
+        <v>0</v>
+      </c>
       <c r="D72">
         <v>0</v>
       </c>
@@ -3251,8 +4201,29 @@
         <f t="shared" si="6"/>
         <v>20</v>
       </c>
-    </row>
-    <row r="73" spans="4:12" x14ac:dyDescent="0.4">
+      <c r="M72">
+        <v>0</v>
+      </c>
+      <c r="N72">
+        <v>0</v>
+      </c>
+      <c r="O72">
+        <v>0</v>
+      </c>
+      <c r="P72">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A73">
+        <v>0</v>
+      </c>
+      <c r="B73">
+        <v>0</v>
+      </c>
+      <c r="C73">
+        <v>0</v>
+      </c>
       <c r="D73">
         <v>0</v>
       </c>
@@ -3283,8 +4254,29 @@
         <f t="shared" si="6"/>
         <v>20</v>
       </c>
-    </row>
-    <row r="74" spans="4:12" x14ac:dyDescent="0.4">
+      <c r="M73">
+        <v>0</v>
+      </c>
+      <c r="N73">
+        <v>0</v>
+      </c>
+      <c r="O73">
+        <v>0</v>
+      </c>
+      <c r="P73">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A74">
+        <v>0</v>
+      </c>
+      <c r="B74">
+        <v>0</v>
+      </c>
+      <c r="C74">
+        <v>0</v>
+      </c>
       <c r="D74">
         <v>0</v>
       </c>
@@ -3315,8 +4307,29 @@
         <f t="shared" si="6"/>
         <v>20</v>
       </c>
-    </row>
-    <row r="75" spans="4:12" x14ac:dyDescent="0.4">
+      <c r="M74">
+        <v>0</v>
+      </c>
+      <c r="N74">
+        <v>0</v>
+      </c>
+      <c r="O74">
+        <v>0</v>
+      </c>
+      <c r="P74">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A75">
+        <v>0</v>
+      </c>
+      <c r="B75">
+        <v>0</v>
+      </c>
+      <c r="C75">
+        <v>0</v>
+      </c>
       <c r="D75">
         <v>0</v>
       </c>
@@ -3347,8 +4360,29 @@
         <f t="shared" si="6"/>
         <v>20</v>
       </c>
-    </row>
-    <row r="76" spans="4:12" x14ac:dyDescent="0.4">
+      <c r="M75">
+        <v>0</v>
+      </c>
+      <c r="N75">
+        <v>0</v>
+      </c>
+      <c r="O75">
+        <v>0</v>
+      </c>
+      <c r="P75">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A76">
+        <v>0</v>
+      </c>
+      <c r="B76">
+        <v>0</v>
+      </c>
+      <c r="C76">
+        <v>0</v>
+      </c>
       <c r="D76">
         <v>0</v>
       </c>
@@ -3379,8 +4413,29 @@
         <f t="shared" si="6"/>
         <v>20</v>
       </c>
-    </row>
-    <row r="77" spans="4:12" x14ac:dyDescent="0.4">
+      <c r="M76">
+        <v>0</v>
+      </c>
+      <c r="N76">
+        <v>0</v>
+      </c>
+      <c r="O76">
+        <v>0</v>
+      </c>
+      <c r="P76">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A77">
+        <v>0</v>
+      </c>
+      <c r="B77">
+        <v>0</v>
+      </c>
+      <c r="C77">
+        <v>0</v>
+      </c>
       <c r="D77">
         <v>0</v>
       </c>
@@ -3411,8 +4466,29 @@
         <f t="shared" si="6"/>
         <v>20</v>
       </c>
-    </row>
-    <row r="78" spans="4:12" x14ac:dyDescent="0.4">
+      <c r="M77">
+        <v>0</v>
+      </c>
+      <c r="N77">
+        <v>0</v>
+      </c>
+      <c r="O77">
+        <v>0</v>
+      </c>
+      <c r="P77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A78">
+        <v>0</v>
+      </c>
+      <c r="B78">
+        <v>0</v>
+      </c>
+      <c r="C78">
+        <v>0</v>
+      </c>
       <c r="D78">
         <v>0</v>
       </c>
@@ -3443,8 +4519,29 @@
         <f t="shared" si="6"/>
         <v>20</v>
       </c>
-    </row>
-    <row r="79" spans="4:12" x14ac:dyDescent="0.4">
+      <c r="M78">
+        <v>0</v>
+      </c>
+      <c r="N78">
+        <v>0</v>
+      </c>
+      <c r="O78">
+        <v>0</v>
+      </c>
+      <c r="P78">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A79">
+        <v>0</v>
+      </c>
+      <c r="B79">
+        <v>0</v>
+      </c>
+      <c r="C79">
+        <v>0</v>
+      </c>
       <c r="D79">
         <v>0</v>
       </c>
@@ -3475,8 +4572,29 @@
         <f t="shared" si="6"/>
         <v>20</v>
       </c>
-    </row>
-    <row r="80" spans="4:12" x14ac:dyDescent="0.4">
+      <c r="M79">
+        <v>0</v>
+      </c>
+      <c r="N79">
+        <v>0</v>
+      </c>
+      <c r="O79">
+        <v>0</v>
+      </c>
+      <c r="P79">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A80">
+        <v>0</v>
+      </c>
+      <c r="B80">
+        <v>0</v>
+      </c>
+      <c r="C80">
+        <v>0</v>
+      </c>
       <c r="D80">
         <v>0</v>
       </c>
@@ -3507,8 +4625,29 @@
         <f t="shared" si="6"/>
         <v>20</v>
       </c>
-    </row>
-    <row r="81" spans="4:12" x14ac:dyDescent="0.4">
+      <c r="M80">
+        <v>0</v>
+      </c>
+      <c r="N80">
+        <v>0</v>
+      </c>
+      <c r="O80">
+        <v>0</v>
+      </c>
+      <c r="P80">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A81">
+        <v>0</v>
+      </c>
+      <c r="B81">
+        <v>0</v>
+      </c>
+      <c r="C81">
+        <v>0</v>
+      </c>
       <c r="D81">
         <v>0</v>
       </c>
@@ -3539,8 +4678,29 @@
         <f t="shared" si="6"/>
         <v>20</v>
       </c>
-    </row>
-    <row r="82" spans="4:12" x14ac:dyDescent="0.4">
+      <c r="M81">
+        <v>0</v>
+      </c>
+      <c r="N81">
+        <v>0</v>
+      </c>
+      <c r="O81">
+        <v>0</v>
+      </c>
+      <c r="P81">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A82">
+        <v>0</v>
+      </c>
+      <c r="B82">
+        <v>0</v>
+      </c>
+      <c r="C82">
+        <v>0</v>
+      </c>
       <c r="D82">
         <v>0</v>
       </c>
@@ -3571,8 +4731,29 @@
         <f t="shared" si="6"/>
         <v>20</v>
       </c>
-    </row>
-    <row r="83" spans="4:12" x14ac:dyDescent="0.4">
+      <c r="M82">
+        <v>0</v>
+      </c>
+      <c r="N82">
+        <v>0</v>
+      </c>
+      <c r="O82">
+        <v>0</v>
+      </c>
+      <c r="P82">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A83">
+        <v>0</v>
+      </c>
+      <c r="B83">
+        <v>0</v>
+      </c>
+      <c r="C83">
+        <v>0</v>
+      </c>
       <c r="D83">
         <v>0</v>
       </c>
@@ -3603,8 +4784,29 @@
         <f t="shared" si="6"/>
         <v>20</v>
       </c>
-    </row>
-    <row r="84" spans="4:12" x14ac:dyDescent="0.4">
+      <c r="M83">
+        <v>0</v>
+      </c>
+      <c r="N83">
+        <v>0</v>
+      </c>
+      <c r="O83">
+        <v>0</v>
+      </c>
+      <c r="P83">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A84">
+        <v>0</v>
+      </c>
+      <c r="B84">
+        <v>0</v>
+      </c>
+      <c r="C84">
+        <v>0</v>
+      </c>
       <c r="D84">
         <v>0</v>
       </c>
@@ -3635,8 +4837,29 @@
         <f t="shared" si="6"/>
         <v>20</v>
       </c>
-    </row>
-    <row r="85" spans="4:12" x14ac:dyDescent="0.4">
+      <c r="M84">
+        <v>0</v>
+      </c>
+      <c r="N84">
+        <v>0</v>
+      </c>
+      <c r="O84">
+        <v>0</v>
+      </c>
+      <c r="P84">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A85">
+        <v>0</v>
+      </c>
+      <c r="B85">
+        <v>0</v>
+      </c>
+      <c r="C85">
+        <v>0</v>
+      </c>
       <c r="D85">
         <v>0</v>
       </c>
@@ -3667,8 +4890,29 @@
         <f t="shared" si="6"/>
         <v>20</v>
       </c>
-    </row>
-    <row r="86" spans="4:12" x14ac:dyDescent="0.4">
+      <c r="M85">
+        <v>0</v>
+      </c>
+      <c r="N85">
+        <v>0</v>
+      </c>
+      <c r="O85">
+        <v>0</v>
+      </c>
+      <c r="P85">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A86">
+        <v>0</v>
+      </c>
+      <c r="B86">
+        <v>0</v>
+      </c>
+      <c r="C86">
+        <v>0</v>
+      </c>
       <c r="D86">
         <v>0</v>
       </c>
@@ -3699,8 +4943,29 @@
         <f t="shared" si="6"/>
         <v>20</v>
       </c>
-    </row>
-    <row r="87" spans="4:12" x14ac:dyDescent="0.4">
+      <c r="M86">
+        <v>0</v>
+      </c>
+      <c r="N86">
+        <v>0</v>
+      </c>
+      <c r="O86">
+        <v>0</v>
+      </c>
+      <c r="P86">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A87">
+        <v>0</v>
+      </c>
+      <c r="B87">
+        <v>0</v>
+      </c>
+      <c r="C87">
+        <v>0</v>
+      </c>
       <c r="D87">
         <v>0</v>
       </c>
@@ -3731,8 +4996,29 @@
         <f t="shared" si="6"/>
         <v>20</v>
       </c>
-    </row>
-    <row r="88" spans="4:12" x14ac:dyDescent="0.4">
+      <c r="M87">
+        <v>0</v>
+      </c>
+      <c r="N87">
+        <v>0</v>
+      </c>
+      <c r="O87">
+        <v>0</v>
+      </c>
+      <c r="P87">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A88">
+        <v>0</v>
+      </c>
+      <c r="B88">
+        <v>0</v>
+      </c>
+      <c r="C88">
+        <v>0</v>
+      </c>
       <c r="D88">
         <v>0</v>
       </c>
@@ -3763,8 +5049,29 @@
         <f t="shared" si="6"/>
         <v>20</v>
       </c>
-    </row>
-    <row r="89" spans="4:12" x14ac:dyDescent="0.4">
+      <c r="M88">
+        <v>0</v>
+      </c>
+      <c r="N88">
+        <v>0</v>
+      </c>
+      <c r="O88">
+        <v>0</v>
+      </c>
+      <c r="P88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A89">
+        <v>0</v>
+      </c>
+      <c r="B89">
+        <v>0</v>
+      </c>
+      <c r="C89">
+        <v>0</v>
+      </c>
       <c r="D89">
         <v>0</v>
       </c>
@@ -3795,8 +5102,29 @@
         <f t="shared" si="6"/>
         <v>20</v>
       </c>
-    </row>
-    <row r="90" spans="4:12" x14ac:dyDescent="0.4">
+      <c r="M89">
+        <v>0</v>
+      </c>
+      <c r="N89">
+        <v>0</v>
+      </c>
+      <c r="O89">
+        <v>0</v>
+      </c>
+      <c r="P89">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A90">
+        <v>0</v>
+      </c>
+      <c r="B90">
+        <v>0</v>
+      </c>
+      <c r="C90">
+        <v>0</v>
+      </c>
       <c r="D90">
         <v>0</v>
       </c>
@@ -3827,8 +5155,29 @@
         <f t="shared" si="6"/>
         <v>20</v>
       </c>
-    </row>
-    <row r="91" spans="4:12" x14ac:dyDescent="0.4">
+      <c r="M90">
+        <v>0</v>
+      </c>
+      <c r="N90">
+        <v>0</v>
+      </c>
+      <c r="O90">
+        <v>0</v>
+      </c>
+      <c r="P90">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A91">
+        <v>0</v>
+      </c>
+      <c r="B91">
+        <v>0</v>
+      </c>
+      <c r="C91">
+        <v>0</v>
+      </c>
       <c r="D91">
         <v>0</v>
       </c>
@@ -3859,8 +5208,29 @@
         <f t="shared" si="6"/>
         <v>20</v>
       </c>
-    </row>
-    <row r="92" spans="4:12" x14ac:dyDescent="0.4">
+      <c r="M91">
+        <v>0</v>
+      </c>
+      <c r="N91">
+        <v>0</v>
+      </c>
+      <c r="O91">
+        <v>0</v>
+      </c>
+      <c r="P91">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A92">
+        <v>0</v>
+      </c>
+      <c r="B92">
+        <v>0</v>
+      </c>
+      <c r="C92">
+        <v>0</v>
+      </c>
       <c r="D92">
         <v>0</v>
       </c>
@@ -3891,8 +5261,29 @@
         <f t="shared" ref="L92:L100" si="9">I92*20</f>
         <v>20</v>
       </c>
-    </row>
-    <row r="93" spans="4:12" x14ac:dyDescent="0.4">
+      <c r="M92">
+        <v>0</v>
+      </c>
+      <c r="N92">
+        <v>0</v>
+      </c>
+      <c r="O92">
+        <v>0</v>
+      </c>
+      <c r="P92">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A93">
+        <v>0</v>
+      </c>
+      <c r="B93">
+        <v>0</v>
+      </c>
+      <c r="C93">
+        <v>0</v>
+      </c>
       <c r="D93">
         <v>0</v>
       </c>
@@ -3923,8 +5314,29 @@
         <f t="shared" si="9"/>
         <v>20</v>
       </c>
-    </row>
-    <row r="94" spans="4:12" x14ac:dyDescent="0.4">
+      <c r="M93">
+        <v>0</v>
+      </c>
+      <c r="N93">
+        <v>0</v>
+      </c>
+      <c r="O93">
+        <v>0</v>
+      </c>
+      <c r="P93">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A94">
+        <v>0</v>
+      </c>
+      <c r="B94">
+        <v>0</v>
+      </c>
+      <c r="C94">
+        <v>0</v>
+      </c>
       <c r="D94">
         <v>0</v>
       </c>
@@ -3955,8 +5367,29 @@
         <f t="shared" si="9"/>
         <v>20</v>
       </c>
-    </row>
-    <row r="95" spans="4:12" x14ac:dyDescent="0.4">
+      <c r="M94">
+        <v>0</v>
+      </c>
+      <c r="N94">
+        <v>0</v>
+      </c>
+      <c r="O94">
+        <v>0</v>
+      </c>
+      <c r="P94">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A95">
+        <v>0</v>
+      </c>
+      <c r="B95">
+        <v>0</v>
+      </c>
+      <c r="C95">
+        <v>0</v>
+      </c>
       <c r="D95">
         <v>0</v>
       </c>
@@ -3987,8 +5420,29 @@
         <f t="shared" si="9"/>
         <v>20</v>
       </c>
-    </row>
-    <row r="96" spans="4:12" x14ac:dyDescent="0.4">
+      <c r="M95">
+        <v>0</v>
+      </c>
+      <c r="N95">
+        <v>0</v>
+      </c>
+      <c r="O95">
+        <v>0</v>
+      </c>
+      <c r="P95">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A96">
+        <v>0</v>
+      </c>
+      <c r="B96">
+        <v>0</v>
+      </c>
+      <c r="C96">
+        <v>0</v>
+      </c>
       <c r="D96">
         <v>0</v>
       </c>
@@ -4019,8 +5473,29 @@
         <f t="shared" si="9"/>
         <v>20</v>
       </c>
-    </row>
-    <row r="97" spans="4:12" x14ac:dyDescent="0.4">
+      <c r="M96">
+        <v>0</v>
+      </c>
+      <c r="N96">
+        <v>0</v>
+      </c>
+      <c r="O96">
+        <v>0</v>
+      </c>
+      <c r="P96">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A97">
+        <v>0</v>
+      </c>
+      <c r="B97">
+        <v>0</v>
+      </c>
+      <c r="C97">
+        <v>0</v>
+      </c>
       <c r="D97">
         <v>0</v>
       </c>
@@ -4051,8 +5526,29 @@
         <f t="shared" si="9"/>
         <v>20</v>
       </c>
-    </row>
-    <row r="98" spans="4:12" x14ac:dyDescent="0.4">
+      <c r="M97">
+        <v>0</v>
+      </c>
+      <c r="N97">
+        <v>0</v>
+      </c>
+      <c r="O97">
+        <v>0</v>
+      </c>
+      <c r="P97">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A98">
+        <v>0</v>
+      </c>
+      <c r="B98">
+        <v>0</v>
+      </c>
+      <c r="C98">
+        <v>0</v>
+      </c>
       <c r="D98">
         <v>0</v>
       </c>
@@ -4083,8 +5579,29 @@
         <f t="shared" si="9"/>
         <v>20</v>
       </c>
-    </row>
-    <row r="99" spans="4:12" x14ac:dyDescent="0.4">
+      <c r="M98">
+        <v>0</v>
+      </c>
+      <c r="N98">
+        <v>0</v>
+      </c>
+      <c r="O98">
+        <v>0</v>
+      </c>
+      <c r="P98">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A99">
+        <v>0</v>
+      </c>
+      <c r="B99">
+        <v>0</v>
+      </c>
+      <c r="C99">
+        <v>0</v>
+      </c>
       <c r="D99">
         <v>0</v>
       </c>
@@ -4115,8 +5632,29 @@
         <f t="shared" si="9"/>
         <v>20</v>
       </c>
-    </row>
-    <row r="100" spans="4:12" x14ac:dyDescent="0.4">
+      <c r="M99">
+        <v>0</v>
+      </c>
+      <c r="N99">
+        <v>0</v>
+      </c>
+      <c r="O99">
+        <v>0</v>
+      </c>
+      <c r="P99">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A100">
+        <v>0</v>
+      </c>
+      <c r="B100">
+        <v>0</v>
+      </c>
+      <c r="C100">
+        <v>0</v>
+      </c>
       <c r="D100">
         <v>0</v>
       </c>
@@ -4146,6 +5684,18 @@
       <c r="L100">
         <f t="shared" si="9"/>
         <v>20</v>
+      </c>
+      <c r="M100">
+        <v>0</v>
+      </c>
+      <c r="N100">
+        <v>0</v>
+      </c>
+      <c r="O100">
+        <v>0</v>
+      </c>
+      <c r="P100">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/ActionGame-リファクタリング-/Data/CSV/Stage/Stage.xlsx
+++ b/ActionGame-リファクタリング-/Data/CSV/Stage/Stage.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ita20\OneDrive\デスクトップ\GameProject\ActionGame-リファクタリング-\Data\CSV\Stage\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\2409404\Desktop\GameProject\ActionGame-リファクタリング-\Data\CSV\Stage\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{012FE5E8-A356-4935-96C9-507751FC9FA0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28EBB936-F724-4626-8A1B-4FF5B4D200A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{62A58253-9505-4C17-A0D0-B4C12E04E8CC}"/>
   </bookViews>
@@ -96,9 +96,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 テーマ">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office テーマ">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -136,7 +136,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -242,7 +242,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -384,7 +384,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -3651,7 +3651,7 @@
         <v>0</v>
       </c>
       <c r="G62">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H62">
         <v>1</v>
@@ -3660,8 +3660,8 @@
         <v>1</v>
       </c>
       <c r="J62">
-        <f t="shared" si="4"/>
-        <v>20</v>
+        <f>G62*20</f>
+        <v>60</v>
       </c>
       <c r="K62">
         <f t="shared" si="5"/>
@@ -3686,10 +3686,10 @@
     </row>
     <row r="63" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A63">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="B63">
-        <v>0</v>
+        <v>-20</v>
       </c>
       <c r="C63">
         <v>0</v>
@@ -3704,7 +3704,7 @@
         <v>0</v>
       </c>
       <c r="G63">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H63">
         <v>1</v>
@@ -3713,8 +3713,8 @@
         <v>1</v>
       </c>
       <c r="J63">
-        <f t="shared" si="4"/>
-        <v>20</v>
+        <f t="shared" ref="J63:J65" si="7">G63*20</f>
+        <v>60</v>
       </c>
       <c r="K63">
         <f t="shared" si="5"/>
@@ -3766,7 +3766,7 @@
         <v>1</v>
       </c>
       <c r="J64">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>20</v>
       </c>
       <c r="K64">
@@ -3819,7 +3819,7 @@
         <v>1</v>
       </c>
       <c r="J65">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>20</v>
       </c>
       <c r="K65">
@@ -5250,15 +5250,15 @@
         <v>1</v>
       </c>
       <c r="J92">
-        <f t="shared" ref="J92:J100" si="7">G92*20</f>
+        <f t="shared" ref="J92:J100" si="8">G92*20</f>
         <v>20</v>
       </c>
       <c r="K92">
-        <f t="shared" ref="K92:K100" si="8">H92*20</f>
+        <f t="shared" ref="K92:K100" si="9">H92*20</f>
         <v>20</v>
       </c>
       <c r="L92">
-        <f t="shared" ref="L92:L100" si="9">I92*20</f>
+        <f t="shared" ref="L92:L100" si="10">I92*20</f>
         <v>20</v>
       </c>
       <c r="M92">
@@ -5303,15 +5303,15 @@
         <v>1</v>
       </c>
       <c r="J93">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>20</v>
       </c>
       <c r="K93">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>20</v>
       </c>
       <c r="L93">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>20</v>
       </c>
       <c r="M93">
@@ -5356,15 +5356,15 @@
         <v>1</v>
       </c>
       <c r="J94">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>20</v>
       </c>
       <c r="K94">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>20</v>
       </c>
       <c r="L94">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>20</v>
       </c>
       <c r="M94">
@@ -5409,15 +5409,15 @@
         <v>1</v>
       </c>
       <c r="J95">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>20</v>
       </c>
       <c r="K95">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>20</v>
       </c>
       <c r="L95">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>20</v>
       </c>
       <c r="M95">
@@ -5462,15 +5462,15 @@
         <v>1</v>
       </c>
       <c r="J96">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>20</v>
       </c>
       <c r="K96">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>20</v>
       </c>
       <c r="L96">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>20</v>
       </c>
       <c r="M96">
@@ -5515,15 +5515,15 @@
         <v>1</v>
       </c>
       <c r="J97">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>20</v>
       </c>
       <c r="K97">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>20</v>
       </c>
       <c r="L97">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>20</v>
       </c>
       <c r="M97">
@@ -5568,15 +5568,15 @@
         <v>1</v>
       </c>
       <c r="J98">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>20</v>
       </c>
       <c r="K98">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>20</v>
       </c>
       <c r="L98">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>20</v>
       </c>
       <c r="M98">
@@ -5621,15 +5621,15 @@
         <v>1</v>
       </c>
       <c r="J99">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>20</v>
       </c>
       <c r="K99">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>20</v>
       </c>
       <c r="L99">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>20</v>
       </c>
       <c r="M99">
@@ -5674,15 +5674,15 @@
         <v>1</v>
       </c>
       <c r="J100">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>20</v>
       </c>
       <c r="K100">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>20</v>
       </c>
       <c r="L100">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>20</v>
       </c>
       <c r="M100">

--- a/ActionGame-リファクタリング-/Data/CSV/Stage/Stage.xlsx
+++ b/ActionGame-リファクタリング-/Data/CSV/Stage/Stage.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\2409404\Desktop\GameProject\ActionGame-リファクタリング-\Data\CSV\Stage\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28EBB936-F724-4626-8A1B-4FF5B4D200A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C623A8B2-902C-454D-BA7B-90C1F2B5A157}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{62A58253-9505-4C17-A0D0-B4C12E04E8CC}"/>
   </bookViews>
@@ -406,7 +406,7 @@
         <v>0</v>
       </c>
       <c r="C1">
-        <v>-20</v>
+        <v>0</v>
       </c>
       <c r="D1">
         <v>0</v>
@@ -459,7 +459,7 @@
         <v>0</v>
       </c>
       <c r="C2">
-        <v>-40</v>
+        <v>20</v>
       </c>
       <c r="D2">
         <v>0</v>
@@ -512,7 +512,7 @@
         <v>0</v>
       </c>
       <c r="C3">
-        <v>-60</v>
+        <v>-20</v>
       </c>
       <c r="D3">
         <v>0</v>
@@ -533,15 +533,15 @@
         <v>1</v>
       </c>
       <c r="J3">
-        <f t="shared" si="1"/>
+        <f>G3*20</f>
         <v>60</v>
       </c>
       <c r="K3">
-        <f t="shared" si="2"/>
+        <f t="shared" ref="K3:K63" si="4">H3*20</f>
         <v>20</v>
       </c>
       <c r="L3">
-        <f t="shared" si="3"/>
+        <f t="shared" ref="L3:L63" si="5">I3*20</f>
         <v>20</v>
       </c>
       <c r="M3">
@@ -565,7 +565,7 @@
         <v>0</v>
       </c>
       <c r="C4">
-        <v>-80</v>
+        <v>-40</v>
       </c>
       <c r="D4">
         <v>0</v>
@@ -586,15 +586,15 @@
         <v>1</v>
       </c>
       <c r="J4">
-        <f t="shared" si="1"/>
+        <f t="shared" ref="J4:J65" si="6">G4*20</f>
         <v>60</v>
       </c>
       <c r="K4">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>20</v>
       </c>
       <c r="L4">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>20</v>
       </c>
       <c r="M4">
@@ -612,13 +612,13 @@
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A5">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="B5">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="C5">
-        <v>-140</v>
+        <v>-60</v>
       </c>
       <c r="D5">
         <v>0</v>
@@ -630,25 +630,25 @@
         <v>0</v>
       </c>
       <c r="G5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H5">
         <v>1</v>
       </c>
       <c r="I5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J5">
-        <f t="shared" si="1"/>
-        <v>20</v>
+        <f t="shared" si="6"/>
+        <v>60</v>
       </c>
       <c r="K5">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>20</v>
       </c>
       <c r="L5">
-        <f t="shared" si="3"/>
-        <v>60</v>
+        <f t="shared" si="5"/>
+        <v>20</v>
       </c>
       <c r="M5">
         <v>0</v>
@@ -668,10 +668,10 @@
         <v>0</v>
       </c>
       <c r="B6">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="C6">
-        <v>-140</v>
+        <v>-80</v>
       </c>
       <c r="D6">
         <v>0</v>
@@ -683,25 +683,25 @@
         <v>0</v>
       </c>
       <c r="G6">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H6">
         <v>1</v>
       </c>
       <c r="I6">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J6">
-        <f t="shared" si="1"/>
-        <v>20</v>
+        <f t="shared" si="6"/>
+        <v>60</v>
       </c>
       <c r="K6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>20</v>
       </c>
       <c r="L6">
-        <f t="shared" si="3"/>
-        <v>60</v>
+        <f t="shared" si="5"/>
+        <v>20</v>
       </c>
       <c r="M6">
         <v>0</v>
@@ -718,7 +718,7 @@
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A7">
-        <v>-20</v>
+        <v>20</v>
       </c>
       <c r="B7">
         <v>20</v>
@@ -745,15 +745,15 @@
         <v>3</v>
       </c>
       <c r="J7">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>20</v>
       </c>
       <c r="K7">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>20</v>
       </c>
       <c r="L7">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>60</v>
       </c>
       <c r="M7">
@@ -771,7 +771,7 @@
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A8">
-        <v>-40</v>
+        <v>0</v>
       </c>
       <c r="B8">
         <v>20</v>
@@ -798,15 +798,15 @@
         <v>3</v>
       </c>
       <c r="J8">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>20</v>
       </c>
       <c r="K8">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>20</v>
       </c>
       <c r="L8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>60</v>
       </c>
       <c r="M8">
@@ -824,7 +824,7 @@
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A9">
-        <v>-60</v>
+        <v>-20</v>
       </c>
       <c r="B9">
         <v>20</v>
@@ -851,15 +851,15 @@
         <v>3</v>
       </c>
       <c r="J9">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>20</v>
       </c>
       <c r="K9">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>20</v>
       </c>
       <c r="L9">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>60</v>
       </c>
       <c r="M9">
@@ -877,7 +877,7 @@
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A10">
-        <v>-80</v>
+        <v>-40</v>
       </c>
       <c r="B10">
         <v>20</v>
@@ -904,15 +904,15 @@
         <v>3</v>
       </c>
       <c r="J10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>20</v>
       </c>
       <c r="K10">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>20</v>
       </c>
       <c r="L10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>60</v>
       </c>
       <c r="M10">
@@ -930,7 +930,7 @@
     </row>
     <row r="11" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A11">
-        <v>-100</v>
+        <v>-60</v>
       </c>
       <c r="B11">
         <v>20</v>
@@ -957,15 +957,15 @@
         <v>3</v>
       </c>
       <c r="J11">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>20</v>
       </c>
       <c r="K11">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>20</v>
       </c>
       <c r="L11">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>60</v>
       </c>
       <c r="M11">
@@ -983,7 +983,7 @@
     </row>
     <row r="12" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A12">
-        <v>-120</v>
+        <v>-80</v>
       </c>
       <c r="B12">
         <v>20</v>
@@ -1010,15 +1010,15 @@
         <v>3</v>
       </c>
       <c r="J12">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>20</v>
       </c>
       <c r="K12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>20</v>
       </c>
       <c r="L12">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>60</v>
       </c>
       <c r="M12">
@@ -1036,7 +1036,7 @@
     </row>
     <row r="13" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A13">
-        <v>-140</v>
+        <v>-100</v>
       </c>
       <c r="B13">
         <v>20</v>
@@ -1063,15 +1063,15 @@
         <v>3</v>
       </c>
       <c r="J13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>20</v>
       </c>
       <c r="K13">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>20</v>
       </c>
       <c r="L13">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>60</v>
       </c>
       <c r="M13">
@@ -1089,7 +1089,7 @@
     </row>
     <row r="14" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A14">
-        <v>-160</v>
+        <v>-120</v>
       </c>
       <c r="B14">
         <v>20</v>
@@ -1116,15 +1116,15 @@
         <v>3</v>
       </c>
       <c r="J14">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>20</v>
       </c>
       <c r="K14">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>20</v>
       </c>
       <c r="L14">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>60</v>
       </c>
       <c r="M14">
@@ -1142,7 +1142,7 @@
     </row>
     <row r="15" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A15">
-        <v>-180</v>
+        <v>-140</v>
       </c>
       <c r="B15">
         <v>20</v>
@@ -1169,15 +1169,15 @@
         <v>3</v>
       </c>
       <c r="J15">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>20</v>
       </c>
       <c r="K15">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>20</v>
       </c>
       <c r="L15">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>60</v>
       </c>
       <c r="M15">
@@ -1195,7 +1195,7 @@
     </row>
     <row r="16" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A16">
-        <v>-200</v>
+        <v>-160</v>
       </c>
       <c r="B16">
         <v>20</v>
@@ -1222,15 +1222,15 @@
         <v>3</v>
       </c>
       <c r="J16">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>20</v>
       </c>
       <c r="K16">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>20</v>
       </c>
       <c r="L16">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>60</v>
       </c>
       <c r="M16">
@@ -1254,7 +1254,7 @@
         <v>20</v>
       </c>
       <c r="C17">
-        <v>-180</v>
+        <v>-140</v>
       </c>
       <c r="D17">
         <v>0</v>
@@ -1266,25 +1266,25 @@
         <v>0</v>
       </c>
       <c r="G17">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H17">
         <v>1</v>
       </c>
       <c r="I17">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J17">
-        <f t="shared" si="1"/>
-        <v>60</v>
+        <f t="shared" si="6"/>
+        <v>20</v>
       </c>
       <c r="K17">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>20</v>
       </c>
       <c r="L17">
-        <f t="shared" si="3"/>
-        <v>20</v>
+        <f t="shared" si="5"/>
+        <v>60</v>
       </c>
       <c r="M17">
         <v>0</v>
@@ -1301,13 +1301,13 @@
     </row>
     <row r="18" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A18">
-        <v>-180</v>
+        <v>-200</v>
       </c>
       <c r="B18">
         <v>20</v>
       </c>
       <c r="C18">
-        <v>-200</v>
+        <v>-140</v>
       </c>
       <c r="D18">
         <v>0</v>
@@ -1319,25 +1319,25 @@
         <v>0</v>
       </c>
       <c r="G18">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H18">
         <v>1</v>
       </c>
       <c r="I18">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J18">
-        <f t="shared" si="1"/>
-        <v>60</v>
+        <f t="shared" si="6"/>
+        <v>20</v>
       </c>
       <c r="K18">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>20</v>
       </c>
       <c r="L18">
-        <f t="shared" si="3"/>
-        <v>20</v>
+        <f t="shared" si="5"/>
+        <v>60</v>
       </c>
       <c r="M18">
         <v>0</v>
@@ -1360,7 +1360,7 @@
         <v>20</v>
       </c>
       <c r="C19">
-        <v>-220</v>
+        <v>-180</v>
       </c>
       <c r="D19">
         <v>0</v>
@@ -1381,15 +1381,15 @@
         <v>1</v>
       </c>
       <c r="J19">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>60</v>
       </c>
       <c r="K19">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>20</v>
       </c>
       <c r="L19">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>20</v>
       </c>
       <c r="M19">
@@ -1413,7 +1413,7 @@
         <v>20</v>
       </c>
       <c r="C20">
-        <v>-240</v>
+        <v>-200</v>
       </c>
       <c r="D20">
         <v>0</v>
@@ -1434,15 +1434,15 @@
         <v>1</v>
       </c>
       <c r="J20">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>60</v>
       </c>
       <c r="K20">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>20</v>
       </c>
       <c r="L20">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>20</v>
       </c>
       <c r="M20">
@@ -1466,7 +1466,7 @@
         <v>20</v>
       </c>
       <c r="C21">
-        <v>-260</v>
+        <v>-220</v>
       </c>
       <c r="D21">
         <v>0</v>
@@ -1487,15 +1487,15 @@
         <v>1</v>
       </c>
       <c r="J21">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>60</v>
       </c>
       <c r="K21">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>20</v>
       </c>
       <c r="L21">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>20</v>
       </c>
       <c r="M21">
@@ -1513,13 +1513,13 @@
     </row>
     <row r="22" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A22">
-        <v>-200</v>
+        <v>-180</v>
       </c>
       <c r="B22">
         <v>20</v>
       </c>
       <c r="C22">
-        <v>-300</v>
+        <v>-240</v>
       </c>
       <c r="D22">
         <v>0</v>
@@ -1531,25 +1531,25 @@
         <v>0</v>
       </c>
       <c r="G22">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H22">
         <v>1</v>
       </c>
       <c r="I22">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J22">
-        <f t="shared" si="1"/>
-        <v>20</v>
+        <f t="shared" si="6"/>
+        <v>60</v>
       </c>
       <c r="K22">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>20</v>
       </c>
       <c r="L22">
-        <f t="shared" si="3"/>
-        <v>60</v>
+        <f t="shared" si="5"/>
+        <v>20</v>
       </c>
       <c r="M22">
         <v>0</v>
@@ -1572,7 +1572,7 @@
         <v>20</v>
       </c>
       <c r="C23">
-        <v>-300</v>
+        <v>-260</v>
       </c>
       <c r="D23">
         <v>0</v>
@@ -1584,25 +1584,25 @@
         <v>0</v>
       </c>
       <c r="G23">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H23">
         <v>1</v>
       </c>
       <c r="I23">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J23">
-        <f t="shared" si="1"/>
-        <v>20</v>
+        <f t="shared" si="6"/>
+        <v>60</v>
       </c>
       <c r="K23">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>20</v>
       </c>
       <c r="L23">
-        <f t="shared" si="3"/>
-        <v>60</v>
+        <f t="shared" si="5"/>
+        <v>20</v>
       </c>
       <c r="M23">
         <v>0</v>
@@ -1619,7 +1619,7 @@
     </row>
     <row r="24" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A24">
-        <v>-160</v>
+        <v>-200</v>
       </c>
       <c r="B24">
         <v>20</v>
@@ -1646,15 +1646,15 @@
         <v>3</v>
       </c>
       <c r="J24">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>20</v>
       </c>
       <c r="K24">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>20</v>
       </c>
       <c r="L24">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>60</v>
       </c>
       <c r="M24">
@@ -1672,7 +1672,7 @@
     </row>
     <row r="25" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A25">
-        <v>-140</v>
+        <v>-180</v>
       </c>
       <c r="B25">
         <v>20</v>
@@ -1699,15 +1699,15 @@
         <v>3</v>
       </c>
       <c r="J25">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>20</v>
       </c>
       <c r="K25">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>20</v>
       </c>
       <c r="L25">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>60</v>
       </c>
       <c r="M25">
@@ -1725,7 +1725,7 @@
     </row>
     <row r="26" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A26">
-        <v>-120</v>
+        <v>-160</v>
       </c>
       <c r="B26">
         <v>20</v>
@@ -1752,15 +1752,15 @@
         <v>3</v>
       </c>
       <c r="J26">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>20</v>
       </c>
       <c r="K26">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>20</v>
       </c>
       <c r="L26">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>60</v>
       </c>
       <c r="M26">
@@ -1778,7 +1778,7 @@
     </row>
     <row r="27" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A27">
-        <v>-100</v>
+        <v>-140</v>
       </c>
       <c r="B27">
         <v>20</v>
@@ -1805,15 +1805,15 @@
         <v>3</v>
       </c>
       <c r="J27">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>20</v>
       </c>
       <c r="K27">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>20</v>
       </c>
       <c r="L27">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>60</v>
       </c>
       <c r="M27">
@@ -1831,10 +1831,10 @@
     </row>
     <row r="28" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A28">
-        <v>-60</v>
+        <v>-120</v>
       </c>
       <c r="B28">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="C28">
         <v>-300</v>
@@ -1858,15 +1858,15 @@
         <v>3</v>
       </c>
       <c r="J28">
-        <f t="shared" ref="J28:J91" si="4">G28*20</f>
+        <f t="shared" si="6"/>
         <v>20</v>
       </c>
       <c r="K28">
-        <f t="shared" ref="K28:K91" si="5">H28*20</f>
+        <f t="shared" si="4"/>
         <v>20</v>
       </c>
       <c r="L28">
-        <f t="shared" ref="L28:L91" si="6">I28*20</f>
+        <f t="shared" si="5"/>
         <v>60</v>
       </c>
       <c r="M28">
@@ -1884,10 +1884,10 @@
     </row>
     <row r="29" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A29">
-        <v>-40</v>
+        <v>-100</v>
       </c>
       <c r="B29">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="C29">
         <v>-300</v>
@@ -1911,15 +1911,15 @@
         <v>3</v>
       </c>
       <c r="J29">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>20</v>
       </c>
       <c r="K29">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>20</v>
       </c>
       <c r="L29">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>60</v>
       </c>
       <c r="M29">
@@ -1937,7 +1937,7 @@
     </row>
     <row r="30" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A30">
-        <v>-20</v>
+        <v>-60</v>
       </c>
       <c r="B30">
         <v>40</v>
@@ -1964,15 +1964,15 @@
         <v>3</v>
       </c>
       <c r="J30">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>20</v>
       </c>
       <c r="K30">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>20</v>
       </c>
       <c r="L30">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>60</v>
       </c>
       <c r="M30">
@@ -1990,10 +1990,10 @@
     </row>
     <row r="31" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A31">
-        <v>20</v>
+        <v>-40</v>
       </c>
       <c r="B31">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="C31">
         <v>-300</v>
@@ -2017,15 +2017,15 @@
         <v>3</v>
       </c>
       <c r="J31">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>20</v>
       </c>
       <c r="K31">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>20</v>
       </c>
       <c r="L31">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>60</v>
       </c>
       <c r="M31">
@@ -2043,10 +2043,10 @@
     </row>
     <row r="32" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A32">
+        <v>-20</v>
+      </c>
+      <c r="B32">
         <v>40</v>
-      </c>
-      <c r="B32">
-        <v>60</v>
       </c>
       <c r="C32">
         <v>-300</v>
@@ -2070,15 +2070,15 @@
         <v>3</v>
       </c>
       <c r="J32">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>20</v>
       </c>
       <c r="K32">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>20</v>
       </c>
       <c r="L32">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>60</v>
       </c>
       <c r="M32">
@@ -2096,7 +2096,7 @@
     </row>
     <row r="33" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A33">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="B33">
         <v>60</v>
@@ -2123,15 +2123,15 @@
         <v>3</v>
       </c>
       <c r="J33">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>20</v>
       </c>
       <c r="K33">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>20</v>
       </c>
       <c r="L33">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>60</v>
       </c>
       <c r="M33">
@@ -2149,10 +2149,10 @@
     </row>
     <row r="34" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A34">
-        <v>100</v>
+        <v>40</v>
       </c>
       <c r="B34">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="C34">
         <v>-300</v>
@@ -2176,15 +2176,15 @@
         <v>3</v>
       </c>
       <c r="J34">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>20</v>
       </c>
       <c r="K34">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>20</v>
       </c>
       <c r="L34">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>60</v>
       </c>
       <c r="M34">
@@ -2202,10 +2202,10 @@
     </row>
     <row r="35" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A35">
-        <v>120</v>
+        <v>60</v>
       </c>
       <c r="B35">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="C35">
         <v>-300</v>
@@ -2229,15 +2229,15 @@
         <v>3</v>
       </c>
       <c r="J35">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>20</v>
       </c>
       <c r="K35">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>20</v>
       </c>
       <c r="L35">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>60</v>
       </c>
       <c r="M35">
@@ -2255,7 +2255,7 @@
     </row>
     <row r="36" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A36">
-        <v>140</v>
+        <v>100</v>
       </c>
       <c r="B36">
         <v>80</v>
@@ -2282,15 +2282,15 @@
         <v>3</v>
       </c>
       <c r="J36">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>20</v>
       </c>
       <c r="K36">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>20</v>
       </c>
       <c r="L36">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>60</v>
       </c>
       <c r="M36">
@@ -2308,10 +2308,10 @@
     </row>
     <row r="37" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A37">
-        <v>180</v>
+        <v>120</v>
       </c>
       <c r="B37">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="C37">
         <v>-300</v>
@@ -2335,15 +2335,15 @@
         <v>3</v>
       </c>
       <c r="J37">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>20</v>
       </c>
       <c r="K37">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>20</v>
       </c>
       <c r="L37">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>60</v>
       </c>
       <c r="M37">
@@ -2361,10 +2361,10 @@
     </row>
     <row r="38" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A38">
-        <v>200</v>
+        <v>140</v>
       </c>
       <c r="B38">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="C38">
         <v>-300</v>
@@ -2388,15 +2388,15 @@
         <v>3</v>
       </c>
       <c r="J38">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>20</v>
       </c>
       <c r="K38">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>20</v>
       </c>
       <c r="L38">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>60</v>
       </c>
       <c r="M38">
@@ -2414,7 +2414,7 @@
     </row>
     <row r="39" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A39">
-        <v>220</v>
+        <v>180</v>
       </c>
       <c r="B39">
         <v>100</v>
@@ -2441,15 +2441,15 @@
         <v>3</v>
       </c>
       <c r="J39">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>20</v>
       </c>
       <c r="K39">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>20</v>
       </c>
       <c r="L39">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>60</v>
       </c>
       <c r="M39">
@@ -2467,13 +2467,13 @@
     </row>
     <row r="40" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A40">
-        <v>260</v>
+        <v>200</v>
       </c>
       <c r="B40">
         <v>100</v>
       </c>
       <c r="C40">
-        <v>-320</v>
+        <v>-300</v>
       </c>
       <c r="D40">
         <v>0</v>
@@ -2485,25 +2485,25 @@
         <v>0</v>
       </c>
       <c r="G40">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H40">
         <v>1</v>
       </c>
       <c r="I40">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J40">
-        <f t="shared" si="4"/>
-        <v>60</v>
+        <f t="shared" si="6"/>
+        <v>20</v>
       </c>
       <c r="K40">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>20</v>
       </c>
       <c r="L40">
-        <f t="shared" si="6"/>
-        <v>20</v>
+        <f t="shared" si="5"/>
+        <v>60</v>
       </c>
       <c r="M40">
         <v>0</v>
@@ -2520,7 +2520,7 @@
     </row>
     <row r="41" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A41">
-        <v>260</v>
+        <v>220</v>
       </c>
       <c r="B41">
         <v>100</v>
@@ -2538,25 +2538,25 @@
         <v>0</v>
       </c>
       <c r="G41">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H41">
         <v>1</v>
       </c>
       <c r="I41">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J41">
-        <f t="shared" si="4"/>
-        <v>60</v>
+        <f t="shared" si="6"/>
+        <v>20</v>
       </c>
       <c r="K41">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>20</v>
       </c>
       <c r="L41">
-        <f t="shared" si="6"/>
-        <v>20</v>
+        <f t="shared" si="5"/>
+        <v>60</v>
       </c>
       <c r="M41">
         <v>0</v>
@@ -2579,7 +2579,7 @@
         <v>100</v>
       </c>
       <c r="C42">
-        <v>-280</v>
+        <v>-320</v>
       </c>
       <c r="D42">
         <v>0</v>
@@ -2600,15 +2600,15 @@
         <v>1</v>
       </c>
       <c r="J42">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>60</v>
       </c>
       <c r="K42">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>20</v>
       </c>
       <c r="L42">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>20</v>
       </c>
       <c r="M42">
@@ -2632,7 +2632,7 @@
         <v>100</v>
       </c>
       <c r="C43">
-        <v>-260</v>
+        <v>-300</v>
       </c>
       <c r="D43">
         <v>0</v>
@@ -2653,15 +2653,15 @@
         <v>1</v>
       </c>
       <c r="J43">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>60</v>
       </c>
       <c r="K43">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>20</v>
       </c>
       <c r="L43">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>20</v>
       </c>
       <c r="M43">
@@ -2685,7 +2685,7 @@
         <v>100</v>
       </c>
       <c r="C44">
-        <v>-240</v>
+        <v>-280</v>
       </c>
       <c r="D44">
         <v>0</v>
@@ -2706,15 +2706,15 @@
         <v>1</v>
       </c>
       <c r="J44">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>60</v>
       </c>
       <c r="K44">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>20</v>
       </c>
       <c r="L44">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>20</v>
       </c>
       <c r="M44">
@@ -2738,7 +2738,7 @@
         <v>100</v>
       </c>
       <c r="C45">
-        <v>-220</v>
+        <v>-260</v>
       </c>
       <c r="D45">
         <v>0</v>
@@ -2759,15 +2759,15 @@
         <v>1</v>
       </c>
       <c r="J45">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>60</v>
       </c>
       <c r="K45">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>20</v>
       </c>
       <c r="L45">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>20</v>
       </c>
       <c r="M45">
@@ -2791,7 +2791,7 @@
         <v>100</v>
       </c>
       <c r="C46">
-        <v>-200</v>
+        <v>-240</v>
       </c>
       <c r="D46">
         <v>0</v>
@@ -2812,15 +2812,15 @@
         <v>1</v>
       </c>
       <c r="J46">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>60</v>
       </c>
       <c r="K46">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>20</v>
       </c>
       <c r="L46">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>20</v>
       </c>
       <c r="M46">
@@ -2844,7 +2844,7 @@
         <v>100</v>
       </c>
       <c r="C47">
-        <v>-180</v>
+        <v>-220</v>
       </c>
       <c r="D47">
         <v>0</v>
@@ -2865,15 +2865,15 @@
         <v>1</v>
       </c>
       <c r="J47">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>60</v>
       </c>
       <c r="K47">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>20</v>
       </c>
       <c r="L47">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>20</v>
       </c>
       <c r="M47">
@@ -2897,7 +2897,7 @@
         <v>100</v>
       </c>
       <c r="C48">
-        <v>-160</v>
+        <v>-200</v>
       </c>
       <c r="D48">
         <v>0</v>
@@ -2918,15 +2918,15 @@
         <v>1</v>
       </c>
       <c r="J48">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>60</v>
       </c>
       <c r="K48">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>20</v>
       </c>
       <c r="L48">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>20</v>
       </c>
       <c r="M48">
@@ -2944,13 +2944,13 @@
     </row>
     <row r="49" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A49">
-        <v>340</v>
+        <v>260</v>
       </c>
       <c r="B49">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="C49">
-        <v>-120</v>
+        <v>-180</v>
       </c>
       <c r="D49">
         <v>0</v>
@@ -2971,15 +2971,15 @@
         <v>1</v>
       </c>
       <c r="J49">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>60</v>
       </c>
       <c r="K49">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>20</v>
       </c>
       <c r="L49">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>20</v>
       </c>
       <c r="M49">
@@ -2997,13 +2997,13 @@
     </row>
     <row r="50" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A50">
-        <v>340</v>
+        <v>260</v>
       </c>
       <c r="B50">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="C50">
-        <v>-100</v>
+        <v>-160</v>
       </c>
       <c r="D50">
         <v>0</v>
@@ -3024,15 +3024,15 @@
         <v>1</v>
       </c>
       <c r="J50">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>60</v>
       </c>
       <c r="K50">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>20</v>
       </c>
       <c r="L50">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>20</v>
       </c>
       <c r="M50">
@@ -3056,7 +3056,7 @@
         <v>120</v>
       </c>
       <c r="C51">
-        <v>-80</v>
+        <v>-120</v>
       </c>
       <c r="D51">
         <v>0</v>
@@ -3077,15 +3077,15 @@
         <v>1</v>
       </c>
       <c r="J51">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>60</v>
       </c>
       <c r="K51">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>20</v>
       </c>
       <c r="L51">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>20</v>
       </c>
       <c r="M51">
@@ -3103,13 +3103,13 @@
     </row>
     <row r="52" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A52">
-        <v>420</v>
+        <v>340</v>
       </c>
       <c r="B52">
-        <v>140</v>
+        <v>120</v>
       </c>
       <c r="C52">
-        <v>-40</v>
+        <v>-100</v>
       </c>
       <c r="D52">
         <v>0</v>
@@ -3130,15 +3130,15 @@
         <v>1</v>
       </c>
       <c r="J52">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>60</v>
       </c>
       <c r="K52">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>20</v>
       </c>
       <c r="L52">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>20</v>
       </c>
       <c r="M52">
@@ -3156,13 +3156,13 @@
     </row>
     <row r="53" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A53">
-        <v>420</v>
+        <v>340</v>
       </c>
       <c r="B53">
-        <v>140</v>
+        <v>120</v>
       </c>
       <c r="C53">
-        <v>-20</v>
+        <v>-80</v>
       </c>
       <c r="D53">
         <v>0</v>
@@ -3183,15 +3183,15 @@
         <v>1</v>
       </c>
       <c r="J53">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>60</v>
       </c>
       <c r="K53">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>20</v>
       </c>
       <c r="L53">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>20</v>
       </c>
       <c r="M53">
@@ -3215,7 +3215,7 @@
         <v>140</v>
       </c>
       <c r="C54">
-        <v>0</v>
+        <v>-40</v>
       </c>
       <c r="D54">
         <v>0</v>
@@ -3236,15 +3236,15 @@
         <v>1</v>
       </c>
       <c r="J54">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>60</v>
       </c>
       <c r="K54">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>20</v>
       </c>
       <c r="L54">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>20</v>
       </c>
       <c r="M54">
@@ -3265,10 +3265,10 @@
         <v>420</v>
       </c>
       <c r="B55">
-        <v>160</v>
+        <v>140</v>
       </c>
       <c r="C55">
-        <v>60</v>
+        <v>-20</v>
       </c>
       <c r="D55">
         <v>0</v>
@@ -3289,15 +3289,15 @@
         <v>1</v>
       </c>
       <c r="J55">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>60</v>
       </c>
       <c r="K55">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>20</v>
       </c>
       <c r="L55">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>20</v>
       </c>
       <c r="M55">
@@ -3318,10 +3318,10 @@
         <v>420</v>
       </c>
       <c r="B56">
-        <v>160</v>
+        <v>140</v>
       </c>
       <c r="C56">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="D56">
         <v>0</v>
@@ -3342,15 +3342,15 @@
         <v>1</v>
       </c>
       <c r="J56">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>60</v>
       </c>
       <c r="K56">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>20</v>
       </c>
       <c r="L56">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>20</v>
       </c>
       <c r="M56">
@@ -3374,7 +3374,7 @@
         <v>160</v>
       </c>
       <c r="C57">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="D57">
         <v>0</v>
@@ -3395,15 +3395,15 @@
         <v>1</v>
       </c>
       <c r="J57">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>60</v>
       </c>
       <c r="K57">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>20</v>
       </c>
       <c r="L57">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>20</v>
       </c>
       <c r="M57">
@@ -3424,10 +3424,10 @@
         <v>420</v>
       </c>
       <c r="B58">
-        <v>180</v>
+        <v>160</v>
       </c>
       <c r="C58">
-        <v>160</v>
+        <v>80</v>
       </c>
       <c r="D58">
         <v>0</v>
@@ -3448,15 +3448,15 @@
         <v>1</v>
       </c>
       <c r="J58">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>60</v>
       </c>
       <c r="K58">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>20</v>
       </c>
       <c r="L58">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>20</v>
       </c>
       <c r="M58">
@@ -3477,10 +3477,10 @@
         <v>420</v>
       </c>
       <c r="B59">
-        <v>180</v>
+        <v>160</v>
       </c>
       <c r="C59">
-        <v>180</v>
+        <v>100</v>
       </c>
       <c r="D59">
         <v>0</v>
@@ -3501,15 +3501,15 @@
         <v>1</v>
       </c>
       <c r="J59">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>60</v>
       </c>
       <c r="K59">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>20</v>
       </c>
       <c r="L59">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>20</v>
       </c>
       <c r="M59">
@@ -3533,7 +3533,7 @@
         <v>180</v>
       </c>
       <c r="C60">
-        <v>200</v>
+        <v>160</v>
       </c>
       <c r="D60">
         <v>0</v>
@@ -3554,15 +3554,15 @@
         <v>1</v>
       </c>
       <c r="J60">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>60</v>
       </c>
       <c r="K60">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>20</v>
       </c>
       <c r="L60">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>20</v>
       </c>
       <c r="M60">
@@ -3586,7 +3586,7 @@
         <v>180</v>
       </c>
       <c r="C61">
-        <v>240</v>
+        <v>180</v>
       </c>
       <c r="D61">
         <v>0</v>
@@ -3604,42 +3604,42 @@
         <v>1</v>
       </c>
       <c r="I61">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J61">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>60</v>
       </c>
       <c r="K61">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>20</v>
       </c>
       <c r="L61">
-        <f t="shared" si="6"/>
-        <v>60</v>
+        <f t="shared" si="5"/>
+        <v>20</v>
       </c>
       <c r="M61">
-        <v>420</v>
+        <v>0</v>
       </c>
       <c r="N61">
-        <v>280</v>
+        <v>0</v>
       </c>
       <c r="O61">
-        <v>240</v>
+        <v>0</v>
       </c>
       <c r="P61">
-        <v>0.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="62" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A62">
-        <v>0</v>
+        <v>420</v>
       </c>
       <c r="B62">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="C62">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="D62">
         <v>0</v>
@@ -3660,15 +3660,15 @@
         <v>1</v>
       </c>
       <c r="J62">
-        <f>G62*20</f>
+        <f t="shared" si="6"/>
         <v>60</v>
       </c>
       <c r="K62">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>20</v>
       </c>
       <c r="L62">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>20</v>
       </c>
       <c r="M62">
@@ -3686,13 +3686,13 @@
     </row>
     <row r="63" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A63">
-        <v>60</v>
+        <v>420</v>
       </c>
       <c r="B63">
-        <v>-20</v>
+        <v>180</v>
       </c>
       <c r="C63">
-        <v>0</v>
+        <v>240</v>
       </c>
       <c r="D63">
         <v>0</v>
@@ -3710,31 +3710,31 @@
         <v>1</v>
       </c>
       <c r="I63">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J63">
-        <f t="shared" ref="J63:J65" si="7">G63*20</f>
+        <f t="shared" si="6"/>
         <v>60</v>
       </c>
       <c r="K63">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>20</v>
       </c>
       <c r="L63">
-        <f t="shared" si="6"/>
-        <v>20</v>
+        <f t="shared" si="5"/>
+        <v>60</v>
       </c>
       <c r="M63">
-        <v>0</v>
+        <v>420</v>
       </c>
       <c r="N63">
-        <v>0</v>
+        <v>280</v>
       </c>
       <c r="O63">
-        <v>0</v>
+        <v>240</v>
       </c>
       <c r="P63">
-        <v>0</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="64" spans="1:16" x14ac:dyDescent="0.4">
@@ -3766,15 +3766,15 @@
         <v>1</v>
       </c>
       <c r="J64">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>20</v>
       </c>
       <c r="K64">
-        <f t="shared" si="5"/>
+        <f t="shared" ref="K28:K91" si="7">H64*20</f>
         <v>20</v>
       </c>
       <c r="L64">
-        <f t="shared" si="6"/>
+        <f t="shared" ref="L28:L91" si="8">I64*20</f>
         <v>20</v>
       </c>
       <c r="M64">
@@ -3819,15 +3819,15 @@
         <v>1</v>
       </c>
       <c r="J65">
+        <f t="shared" si="6"/>
+        <v>20</v>
+      </c>
+      <c r="K65">
         <f t="shared" si="7"/>
         <v>20</v>
       </c>
-      <c r="K65">
-        <f t="shared" si="5"/>
-        <v>20</v>
-      </c>
       <c r="L65">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>20</v>
       </c>
       <c r="M65">
@@ -3872,15 +3872,15 @@
         <v>1</v>
       </c>
       <c r="J66">
-        <f t="shared" si="4"/>
+        <f t="shared" ref="J28:J91" si="9">G66*20</f>
         <v>20</v>
       </c>
       <c r="K66">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>20</v>
       </c>
       <c r="L66">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>20</v>
       </c>
       <c r="M66">
@@ -3925,15 +3925,15 @@
         <v>1</v>
       </c>
       <c r="J67">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>20</v>
       </c>
       <c r="K67">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>20</v>
       </c>
       <c r="L67">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>20</v>
       </c>
       <c r="M67">
@@ -3978,15 +3978,15 @@
         <v>1</v>
       </c>
       <c r="J68">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>20</v>
       </c>
       <c r="K68">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>20</v>
       </c>
       <c r="L68">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>20</v>
       </c>
       <c r="M68">
@@ -4031,15 +4031,15 @@
         <v>1</v>
       </c>
       <c r="J69">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>20</v>
       </c>
       <c r="K69">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>20</v>
       </c>
       <c r="L69">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>20</v>
       </c>
       <c r="M69">
@@ -4084,15 +4084,15 @@
         <v>1</v>
       </c>
       <c r="J70">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>20</v>
       </c>
       <c r="K70">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>20</v>
       </c>
       <c r="L70">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>20</v>
       </c>
       <c r="M70">
@@ -4137,15 +4137,15 @@
         <v>1</v>
       </c>
       <c r="J71">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>20</v>
       </c>
       <c r="K71">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>20</v>
       </c>
       <c r="L71">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>20</v>
       </c>
       <c r="M71">
@@ -4190,15 +4190,15 @@
         <v>1</v>
       </c>
       <c r="J72">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>20</v>
       </c>
       <c r="K72">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>20</v>
       </c>
       <c r="L72">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>20</v>
       </c>
       <c r="M72">
@@ -4243,15 +4243,15 @@
         <v>1</v>
       </c>
       <c r="J73">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>20</v>
       </c>
       <c r="K73">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>20</v>
       </c>
       <c r="L73">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>20</v>
       </c>
       <c r="M73">
@@ -4296,15 +4296,15 @@
         <v>1</v>
       </c>
       <c r="J74">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>20</v>
       </c>
       <c r="K74">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>20</v>
       </c>
       <c r="L74">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>20</v>
       </c>
       <c r="M74">
@@ -4349,15 +4349,15 @@
         <v>1</v>
       </c>
       <c r="J75">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>20</v>
       </c>
       <c r="K75">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>20</v>
       </c>
       <c r="L75">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>20</v>
       </c>
       <c r="M75">
@@ -4402,15 +4402,15 @@
         <v>1</v>
       </c>
       <c r="J76">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>20</v>
       </c>
       <c r="K76">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>20</v>
       </c>
       <c r="L76">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>20</v>
       </c>
       <c r="M76">
@@ -4455,15 +4455,15 @@
         <v>1</v>
       </c>
       <c r="J77">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>20</v>
       </c>
       <c r="K77">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>20</v>
       </c>
       <c r="L77">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>20</v>
       </c>
       <c r="M77">
@@ -4508,15 +4508,15 @@
         <v>1</v>
       </c>
       <c r="J78">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>20</v>
       </c>
       <c r="K78">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>20</v>
       </c>
       <c r="L78">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>20</v>
       </c>
       <c r="M78">
@@ -4561,15 +4561,15 @@
         <v>1</v>
       </c>
       <c r="J79">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>20</v>
       </c>
       <c r="K79">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>20</v>
       </c>
       <c r="L79">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>20</v>
       </c>
       <c r="M79">
@@ -4614,15 +4614,15 @@
         <v>1</v>
       </c>
       <c r="J80">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>20</v>
       </c>
       <c r="K80">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>20</v>
       </c>
       <c r="L80">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>20</v>
       </c>
       <c r="M80">
@@ -4667,15 +4667,15 @@
         <v>1</v>
       </c>
       <c r="J81">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>20</v>
       </c>
       <c r="K81">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>20</v>
       </c>
       <c r="L81">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>20</v>
       </c>
       <c r="M81">
@@ -4720,15 +4720,15 @@
         <v>1</v>
       </c>
       <c r="J82">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>20</v>
       </c>
       <c r="K82">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>20</v>
       </c>
       <c r="L82">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>20</v>
       </c>
       <c r="M82">
@@ -4773,15 +4773,15 @@
         <v>1</v>
       </c>
       <c r="J83">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>20</v>
       </c>
       <c r="K83">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>20</v>
       </c>
       <c r="L83">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>20</v>
       </c>
       <c r="M83">
@@ -4826,15 +4826,15 @@
         <v>1</v>
       </c>
       <c r="J84">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>20</v>
       </c>
       <c r="K84">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>20</v>
       </c>
       <c r="L84">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>20</v>
       </c>
       <c r="M84">
@@ -4879,15 +4879,15 @@
         <v>1</v>
       </c>
       <c r="J85">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>20</v>
       </c>
       <c r="K85">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>20</v>
       </c>
       <c r="L85">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>20</v>
       </c>
       <c r="M85">
@@ -4932,15 +4932,15 @@
         <v>1</v>
       </c>
       <c r="J86">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>20</v>
       </c>
       <c r="K86">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>20</v>
       </c>
       <c r="L86">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>20</v>
       </c>
       <c r="M86">
@@ -4985,15 +4985,15 @@
         <v>1</v>
       </c>
       <c r="J87">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>20</v>
       </c>
       <c r="K87">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>20</v>
       </c>
       <c r="L87">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>20</v>
       </c>
       <c r="M87">
@@ -5038,15 +5038,15 @@
         <v>1</v>
       </c>
       <c r="J88">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>20</v>
       </c>
       <c r="K88">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>20</v>
       </c>
       <c r="L88">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>20</v>
       </c>
       <c r="M88">
@@ -5091,15 +5091,15 @@
         <v>1</v>
       </c>
       <c r="J89">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>20</v>
       </c>
       <c r="K89">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>20</v>
       </c>
       <c r="L89">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>20</v>
       </c>
       <c r="M89">
@@ -5144,15 +5144,15 @@
         <v>1</v>
       </c>
       <c r="J90">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>20</v>
       </c>
       <c r="K90">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>20</v>
       </c>
       <c r="L90">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>20</v>
       </c>
       <c r="M90">
@@ -5197,15 +5197,15 @@
         <v>1</v>
       </c>
       <c r="J91">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>20</v>
       </c>
       <c r="K91">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>20</v>
       </c>
       <c r="L91">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>20</v>
       </c>
       <c r="M91">
@@ -5250,15 +5250,15 @@
         <v>1</v>
       </c>
       <c r="J92">
-        <f t="shared" ref="J92:J100" si="8">G92*20</f>
+        <f t="shared" ref="J92:J100" si="10">G92*20</f>
         <v>20</v>
       </c>
       <c r="K92">
-        <f t="shared" ref="K92:K100" si="9">H92*20</f>
+        <f t="shared" ref="K92:K100" si="11">H92*20</f>
         <v>20</v>
       </c>
       <c r="L92">
-        <f t="shared" ref="L92:L100" si="10">I92*20</f>
+        <f t="shared" ref="L92:L100" si="12">I92*20</f>
         <v>20</v>
       </c>
       <c r="M92">
@@ -5303,15 +5303,15 @@
         <v>1</v>
       </c>
       <c r="J93">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>20</v>
       </c>
       <c r="K93">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>20</v>
       </c>
       <c r="L93">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>20</v>
       </c>
       <c r="M93">
@@ -5356,15 +5356,15 @@
         <v>1</v>
       </c>
       <c r="J94">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>20</v>
       </c>
       <c r="K94">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>20</v>
       </c>
       <c r="L94">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>20</v>
       </c>
       <c r="M94">
@@ -5409,15 +5409,15 @@
         <v>1</v>
       </c>
       <c r="J95">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>20</v>
       </c>
       <c r="K95">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>20</v>
       </c>
       <c r="L95">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>20</v>
       </c>
       <c r="M95">
@@ -5462,15 +5462,15 @@
         <v>1</v>
       </c>
       <c r="J96">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>20</v>
       </c>
       <c r="K96">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>20</v>
       </c>
       <c r="L96">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>20</v>
       </c>
       <c r="M96">
@@ -5515,15 +5515,15 @@
         <v>1</v>
       </c>
       <c r="J97">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>20</v>
       </c>
       <c r="K97">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>20</v>
       </c>
       <c r="L97">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>20</v>
       </c>
       <c r="M97">
@@ -5568,15 +5568,15 @@
         <v>1</v>
       </c>
       <c r="J98">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>20</v>
       </c>
       <c r="K98">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>20</v>
       </c>
       <c r="L98">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>20</v>
       </c>
       <c r="M98">
@@ -5621,15 +5621,15 @@
         <v>1</v>
       </c>
       <c r="J99">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>20</v>
       </c>
       <c r="K99">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>20</v>
       </c>
       <c r="L99">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>20</v>
       </c>
       <c r="M99">
@@ -5674,15 +5674,15 @@
         <v>1</v>
       </c>
       <c r="J100">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>20</v>
       </c>
       <c r="K100">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>20</v>
       </c>
       <c r="L100">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>20</v>
       </c>
       <c r="M100">

--- a/ActionGame-リファクタリング-/Data/CSV/Stage/Stage.xlsx
+++ b/ActionGame-リファクタリング-/Data/CSV/Stage/Stage.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\2409404\Desktop\GameProject\ActionGame-リファクタリング-\Data\CSV\Stage\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C623A8B2-902C-454D-BA7B-90C1F2B5A157}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E53130C8-45F0-4FDB-8395-4AC8F07C0056}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{62A58253-9505-4C17-A0D0-B4C12E04E8CC}"/>
   </bookViews>
@@ -480,15 +480,15 @@
         <v>1</v>
       </c>
       <c r="J2">
-        <f t="shared" ref="J2:J27" si="1">G2*20</f>
+        <f t="shared" ref="J2" si="1">G2*20</f>
         <v>60</v>
       </c>
       <c r="K2">
-        <f t="shared" ref="K2:K27" si="2">H2*20</f>
+        <f t="shared" ref="K2" si="2">H2*20</f>
         <v>20</v>
       </c>
       <c r="L2">
-        <f t="shared" ref="L2:L27" si="3">I2*20</f>
+        <f t="shared" ref="L2" si="3">I2*20</f>
         <v>20</v>
       </c>
       <c r="M2">
@@ -3770,11 +3770,11 @@
         <v>20</v>
       </c>
       <c r="K64">
-        <f t="shared" ref="K28:K91" si="7">H64*20</f>
+        <f t="shared" ref="K64:K91" si="7">H64*20</f>
         <v>20</v>
       </c>
       <c r="L64">
-        <f t="shared" ref="L28:L91" si="8">I64*20</f>
+        <f t="shared" ref="L64:L91" si="8">I64*20</f>
         <v>20</v>
       </c>
       <c r="M64">
@@ -3872,7 +3872,7 @@
         <v>1</v>
       </c>
       <c r="J66">
-        <f t="shared" ref="J28:J91" si="9">G66*20</f>
+        <f t="shared" ref="J66:J91" si="9">G66*20</f>
         <v>20</v>
       </c>
       <c r="K66">

--- a/ActionGame-リファクタリング-/Data/CSV/Stage/Stage.xlsx
+++ b/ActionGame-リファクタリング-/Data/CSV/Stage/Stage.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\2409404\Desktop\GameProject\ActionGame-リファクタリング-\Data\CSV\Stage\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E53130C8-45F0-4FDB-8395-4AC8F07C0056}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D126F97A-27E3-4213-9A76-4FA6832D8D58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{62A58253-9505-4C17-A0D0-B4C12E04E8CC}"/>
+    <workbookView xWindow="3510" yWindow="3510" windowWidth="21600" windowHeight="11295" xr2:uid="{62A58253-9505-4C17-A0D0-B4C12E04E8CC}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -3728,13 +3728,13 @@
         <v>420</v>
       </c>
       <c r="N63">
-        <v>280</v>
+        <v>380</v>
       </c>
       <c r="O63">
         <v>240</v>
       </c>
       <c r="P63">
-        <v>0.5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="64" spans="1:16" x14ac:dyDescent="0.4">

--- a/ActionGame-リファクタリング-/Data/CSV/Stage/Stage.xlsx
+++ b/ActionGame-リファクタリング-/Data/CSV/Stage/Stage.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\2409404\Desktop\GameProject\ActionGame-リファクタリング-\Data\CSV\Stage\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D126F97A-27E3-4213-9A76-4FA6832D8D58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CADC4476-F706-4337-BCEB-C7A91221B2B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3510" yWindow="3510" windowWidth="21600" windowHeight="11295" xr2:uid="{62A58253-9505-4C17-A0D0-B4C12E04E8CC}"/>
+    <workbookView xWindow="2955" yWindow="3030" windowWidth="21600" windowHeight="11295" xr2:uid="{62A58253-9505-4C17-A0D0-B4C12E04E8CC}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -537,11 +537,11 @@
         <v>60</v>
       </c>
       <c r="K3">
-        <f t="shared" ref="K3:K63" si="4">H3*20</f>
+        <f t="shared" ref="K3:K6" si="4">H3*20</f>
         <v>20</v>
       </c>
       <c r="L3">
-        <f t="shared" ref="L3:L63" si="5">I3*20</f>
+        <f t="shared" ref="L3:L6" si="5">I3*20</f>
         <v>20</v>
       </c>
       <c r="M3">
@@ -586,7 +586,7 @@
         <v>1</v>
       </c>
       <c r="J4">
-        <f t="shared" ref="J4:J65" si="6">G4*20</f>
+        <f t="shared" ref="J4:J6" si="6">G4*20</f>
         <v>60</v>
       </c>
       <c r="K4">
@@ -718,13 +718,13 @@
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A7">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="B7">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="C7">
-        <v>-140</v>
+        <v>-100</v>
       </c>
       <c r="D7">
         <v>0</v>
@@ -736,25 +736,25 @@
         <v>0</v>
       </c>
       <c r="G7">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H7">
         <v>1</v>
       </c>
       <c r="I7">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J7">
-        <f t="shared" si="6"/>
-        <v>20</v>
+        <f t="shared" ref="J7" si="7">G7*20</f>
+        <v>60</v>
       </c>
       <c r="K7">
-        <f t="shared" si="4"/>
+        <f t="shared" ref="K7" si="8">H7*20</f>
         <v>20</v>
       </c>
       <c r="L7">
-        <f t="shared" si="5"/>
-        <v>60</v>
+        <f t="shared" ref="L7" si="9">I7*20</f>
+        <v>20</v>
       </c>
       <c r="M7">
         <v>0</v>
@@ -771,7 +771,7 @@
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A8">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="B8">
         <v>20</v>
@@ -798,15 +798,15 @@
         <v>3</v>
       </c>
       <c r="J8">
-        <f t="shared" si="6"/>
+        <f t="shared" ref="J8:J9" si="10">G8*20</f>
         <v>20</v>
       </c>
       <c r="K8">
-        <f t="shared" si="4"/>
+        <f t="shared" ref="K8" si="11">H8*20</f>
         <v>20</v>
       </c>
       <c r="L8">
-        <f t="shared" si="5"/>
+        <f t="shared" ref="L8" si="12">I8*20</f>
         <v>60</v>
       </c>
       <c r="M8">
@@ -824,7 +824,7 @@
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A9">
-        <v>-20</v>
+        <v>0</v>
       </c>
       <c r="B9">
         <v>20</v>
@@ -851,15 +851,15 @@
         <v>3</v>
       </c>
       <c r="J9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>20</v>
       </c>
       <c r="K9">
-        <f t="shared" si="4"/>
+        <f t="shared" ref="K9:K12" si="13">H9*20</f>
         <v>20</v>
       </c>
       <c r="L9">
-        <f t="shared" si="5"/>
+        <f t="shared" ref="L9:L12" si="14">I9*20</f>
         <v>60</v>
       </c>
       <c r="M9">
@@ -877,7 +877,7 @@
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A10">
-        <v>-40</v>
+        <v>-20</v>
       </c>
       <c r="B10">
         <v>20</v>
@@ -904,15 +904,15 @@
         <v>3</v>
       </c>
       <c r="J10">
-        <f t="shared" si="6"/>
+        <f t="shared" ref="J10:J12" si="15">G10*20</f>
         <v>20</v>
       </c>
       <c r="K10">
-        <f t="shared" si="4"/>
+        <f t="shared" si="13"/>
         <v>20</v>
       </c>
       <c r="L10">
-        <f t="shared" si="5"/>
+        <f t="shared" si="14"/>
         <v>60</v>
       </c>
       <c r="M10">
@@ -930,7 +930,7 @@
     </row>
     <row r="11" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A11">
-        <v>-60</v>
+        <v>-40</v>
       </c>
       <c r="B11">
         <v>20</v>
@@ -957,15 +957,15 @@
         <v>3</v>
       </c>
       <c r="J11">
-        <f t="shared" si="6"/>
+        <f t="shared" si="15"/>
         <v>20</v>
       </c>
       <c r="K11">
-        <f t="shared" si="4"/>
+        <f t="shared" si="13"/>
         <v>20</v>
       </c>
       <c r="L11">
-        <f t="shared" si="5"/>
+        <f t="shared" si="14"/>
         <v>60</v>
       </c>
       <c r="M11">
@@ -983,7 +983,7 @@
     </row>
     <row r="12" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A12">
-        <v>-80</v>
+        <v>-60</v>
       </c>
       <c r="B12">
         <v>20</v>
@@ -1010,15 +1010,15 @@
         <v>3</v>
       </c>
       <c r="J12">
-        <f t="shared" si="6"/>
+        <f t="shared" si="15"/>
         <v>20</v>
       </c>
       <c r="K12">
-        <f t="shared" si="4"/>
+        <f t="shared" si="13"/>
         <v>20</v>
       </c>
       <c r="L12">
-        <f t="shared" si="5"/>
+        <f t="shared" si="14"/>
         <v>60</v>
       </c>
       <c r="M12">
@@ -1036,7 +1036,7 @@
     </row>
     <row r="13" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A13">
-        <v>-100</v>
+        <v>-80</v>
       </c>
       <c r="B13">
         <v>20</v>
@@ -1063,15 +1063,15 @@
         <v>3</v>
       </c>
       <c r="J13">
-        <f t="shared" si="6"/>
+        <f t="shared" ref="J13:J15" si="16">G13*20</f>
         <v>20</v>
       </c>
       <c r="K13">
-        <f t="shared" si="4"/>
+        <f t="shared" ref="K13:K16" si="17">H13*20</f>
         <v>20</v>
       </c>
       <c r="L13">
-        <f t="shared" si="5"/>
+        <f t="shared" ref="L13:L16" si="18">I13*20</f>
         <v>60</v>
       </c>
       <c r="M13">
@@ -1089,7 +1089,7 @@
     </row>
     <row r="14" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A14">
-        <v>-120</v>
+        <v>-100</v>
       </c>
       <c r="B14">
         <v>20</v>
@@ -1116,15 +1116,15 @@
         <v>3</v>
       </c>
       <c r="J14">
-        <f t="shared" si="6"/>
+        <f t="shared" si="16"/>
         <v>20</v>
       </c>
       <c r="K14">
-        <f t="shared" si="4"/>
+        <f t="shared" si="17"/>
         <v>20</v>
       </c>
       <c r="L14">
-        <f t="shared" si="5"/>
+        <f t="shared" si="18"/>
         <v>60</v>
       </c>
       <c r="M14">
@@ -1142,7 +1142,7 @@
     </row>
     <row r="15" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A15">
-        <v>-140</v>
+        <v>-120</v>
       </c>
       <c r="B15">
         <v>20</v>
@@ -1169,15 +1169,15 @@
         <v>3</v>
       </c>
       <c r="J15">
-        <f t="shared" si="6"/>
+        <f t="shared" si="16"/>
         <v>20</v>
       </c>
       <c r="K15">
-        <f t="shared" si="4"/>
+        <f t="shared" si="17"/>
         <v>20</v>
       </c>
       <c r="L15">
-        <f t="shared" si="5"/>
+        <f t="shared" si="18"/>
         <v>60</v>
       </c>
       <c r="M15">
@@ -1195,7 +1195,7 @@
     </row>
     <row r="16" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A16">
-        <v>-160</v>
+        <v>-140</v>
       </c>
       <c r="B16">
         <v>20</v>
@@ -1222,15 +1222,15 @@
         <v>3</v>
       </c>
       <c r="J16">
-        <f t="shared" si="6"/>
+        <f t="shared" ref="J16:J18" si="19">G16*20</f>
         <v>20</v>
       </c>
       <c r="K16">
-        <f t="shared" si="4"/>
+        <f t="shared" si="17"/>
         <v>20</v>
       </c>
       <c r="L16">
-        <f t="shared" si="5"/>
+        <f t="shared" si="18"/>
         <v>60</v>
       </c>
       <c r="M16">
@@ -1248,7 +1248,7 @@
     </row>
     <row r="17" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A17">
-        <v>-180</v>
+        <v>-160</v>
       </c>
       <c r="B17">
         <v>20</v>
@@ -1275,15 +1275,15 @@
         <v>3</v>
       </c>
       <c r="J17">
-        <f t="shared" si="6"/>
+        <f t="shared" si="19"/>
         <v>20</v>
       </c>
       <c r="K17">
-        <f t="shared" si="4"/>
+        <f t="shared" ref="K17:K20" si="20">H17*20</f>
         <v>20</v>
       </c>
       <c r="L17">
-        <f t="shared" si="5"/>
+        <f t="shared" ref="L17:L20" si="21">I17*20</f>
         <v>60</v>
       </c>
       <c r="M17">
@@ -1301,7 +1301,7 @@
     </row>
     <row r="18" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A18">
-        <v>-200</v>
+        <v>-180</v>
       </c>
       <c r="B18">
         <v>20</v>
@@ -1328,15 +1328,15 @@
         <v>3</v>
       </c>
       <c r="J18">
-        <f t="shared" si="6"/>
+        <f t="shared" si="19"/>
         <v>20</v>
       </c>
       <c r="K18">
-        <f t="shared" si="4"/>
+        <f t="shared" si="20"/>
         <v>20</v>
       </c>
       <c r="L18">
-        <f t="shared" si="5"/>
+        <f t="shared" si="21"/>
         <v>60</v>
       </c>
       <c r="M18">
@@ -1354,13 +1354,13 @@
     </row>
     <row r="19" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A19">
-        <v>-180</v>
+        <v>-200</v>
       </c>
       <c r="B19">
         <v>20</v>
       </c>
       <c r="C19">
-        <v>-180</v>
+        <v>-140</v>
       </c>
       <c r="D19">
         <v>0</v>
@@ -1372,25 +1372,25 @@
         <v>0</v>
       </c>
       <c r="G19">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H19">
         <v>1</v>
       </c>
       <c r="I19">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J19">
-        <f t="shared" si="6"/>
-        <v>60</v>
+        <f t="shared" ref="J19:J21" si="22">G19*20</f>
+        <v>20</v>
       </c>
       <c r="K19">
-        <f t="shared" si="4"/>
+        <f t="shared" si="20"/>
         <v>20</v>
       </c>
       <c r="L19">
-        <f t="shared" si="5"/>
-        <v>20</v>
+        <f t="shared" si="21"/>
+        <v>60</v>
       </c>
       <c r="M19">
         <v>0</v>
@@ -1413,7 +1413,7 @@
         <v>20</v>
       </c>
       <c r="C20">
-        <v>-200</v>
+        <v>-180</v>
       </c>
       <c r="D20">
         <v>0</v>
@@ -1434,15 +1434,15 @@
         <v>1</v>
       </c>
       <c r="J20">
-        <f t="shared" si="6"/>
+        <f t="shared" si="22"/>
         <v>60</v>
       </c>
       <c r="K20">
-        <f t="shared" si="4"/>
+        <f t="shared" si="20"/>
         <v>20</v>
       </c>
       <c r="L20">
-        <f t="shared" si="5"/>
+        <f t="shared" si="21"/>
         <v>20</v>
       </c>
       <c r="M20">
@@ -1466,7 +1466,7 @@
         <v>20</v>
       </c>
       <c r="C21">
-        <v>-220</v>
+        <v>-200</v>
       </c>
       <c r="D21">
         <v>0</v>
@@ -1487,15 +1487,15 @@
         <v>1</v>
       </c>
       <c r="J21">
-        <f t="shared" si="6"/>
+        <f t="shared" si="22"/>
         <v>60</v>
       </c>
       <c r="K21">
-        <f t="shared" si="4"/>
+        <f t="shared" ref="K21:K24" si="23">H21*20</f>
         <v>20</v>
       </c>
       <c r="L21">
-        <f t="shared" si="5"/>
+        <f t="shared" ref="L21:L24" si="24">I21*20</f>
         <v>20</v>
       </c>
       <c r="M21">
@@ -1519,7 +1519,7 @@
         <v>20</v>
       </c>
       <c r="C22">
-        <v>-240</v>
+        <v>-220</v>
       </c>
       <c r="D22">
         <v>0</v>
@@ -1540,15 +1540,15 @@
         <v>1</v>
       </c>
       <c r="J22">
-        <f t="shared" si="6"/>
+        <f t="shared" ref="J22:J24" si="25">G22*20</f>
         <v>60</v>
       </c>
       <c r="K22">
-        <f t="shared" si="4"/>
+        <f t="shared" si="23"/>
         <v>20</v>
       </c>
       <c r="L22">
-        <f t="shared" si="5"/>
+        <f t="shared" si="24"/>
         <v>20</v>
       </c>
       <c r="M22">
@@ -1572,7 +1572,7 @@
         <v>20</v>
       </c>
       <c r="C23">
-        <v>-260</v>
+        <v>-240</v>
       </c>
       <c r="D23">
         <v>0</v>
@@ -1593,15 +1593,15 @@
         <v>1</v>
       </c>
       <c r="J23">
-        <f t="shared" si="6"/>
+        <f t="shared" si="25"/>
         <v>60</v>
       </c>
       <c r="K23">
-        <f t="shared" si="4"/>
+        <f t="shared" si="23"/>
         <v>20</v>
       </c>
       <c r="L23">
-        <f t="shared" si="5"/>
+        <f t="shared" si="24"/>
         <v>20</v>
       </c>
       <c r="M23">
@@ -1619,13 +1619,13 @@
     </row>
     <row r="24" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A24">
-        <v>-200</v>
+        <v>-180</v>
       </c>
       <c r="B24">
         <v>20</v>
       </c>
       <c r="C24">
-        <v>-300</v>
+        <v>-260</v>
       </c>
       <c r="D24">
         <v>0</v>
@@ -1637,25 +1637,25 @@
         <v>0</v>
       </c>
       <c r="G24">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H24">
         <v>1</v>
       </c>
       <c r="I24">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J24">
-        <f t="shared" si="6"/>
-        <v>20</v>
+        <f t="shared" si="25"/>
+        <v>60</v>
       </c>
       <c r="K24">
-        <f t="shared" si="4"/>
+        <f t="shared" si="23"/>
         <v>20</v>
       </c>
       <c r="L24">
-        <f t="shared" si="5"/>
-        <v>60</v>
+        <f t="shared" si="24"/>
+        <v>20</v>
       </c>
       <c r="M24">
         <v>0</v>
@@ -1672,7 +1672,7 @@
     </row>
     <row r="25" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A25">
-        <v>-180</v>
+        <v>-200</v>
       </c>
       <c r="B25">
         <v>20</v>
@@ -1699,15 +1699,15 @@
         <v>3</v>
       </c>
       <c r="J25">
-        <f t="shared" si="6"/>
+        <f t="shared" ref="J25:J27" si="26">G25*20</f>
         <v>20</v>
       </c>
       <c r="K25">
-        <f t="shared" si="4"/>
+        <f t="shared" ref="K25:K28" si="27">H25*20</f>
         <v>20</v>
       </c>
       <c r="L25">
-        <f t="shared" si="5"/>
+        <f t="shared" ref="L25:L28" si="28">I25*20</f>
         <v>60</v>
       </c>
       <c r="M25">
@@ -1725,7 +1725,7 @@
     </row>
     <row r="26" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A26">
-        <v>-160</v>
+        <v>-180</v>
       </c>
       <c r="B26">
         <v>20</v>
@@ -1752,15 +1752,15 @@
         <v>3</v>
       </c>
       <c r="J26">
-        <f t="shared" si="6"/>
+        <f t="shared" si="26"/>
         <v>20</v>
       </c>
       <c r="K26">
-        <f t="shared" si="4"/>
+        <f t="shared" si="27"/>
         <v>20</v>
       </c>
       <c r="L26">
-        <f t="shared" si="5"/>
+        <f t="shared" si="28"/>
         <v>60</v>
       </c>
       <c r="M26">
@@ -1778,7 +1778,7 @@
     </row>
     <row r="27" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A27">
-        <v>-140</v>
+        <v>-160</v>
       </c>
       <c r="B27">
         <v>20</v>
@@ -1805,15 +1805,15 @@
         <v>3</v>
       </c>
       <c r="J27">
-        <f t="shared" si="6"/>
+        <f t="shared" si="26"/>
         <v>20</v>
       </c>
       <c r="K27">
-        <f t="shared" si="4"/>
+        <f t="shared" si="27"/>
         <v>20</v>
       </c>
       <c r="L27">
-        <f t="shared" si="5"/>
+        <f t="shared" si="28"/>
         <v>60</v>
       </c>
       <c r="M27">
@@ -1831,7 +1831,7 @@
     </row>
     <row r="28" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A28">
-        <v>-120</v>
+        <v>-140</v>
       </c>
       <c r="B28">
         <v>20</v>
@@ -1858,15 +1858,15 @@
         <v>3</v>
       </c>
       <c r="J28">
-        <f t="shared" si="6"/>
+        <f t="shared" ref="J28:J30" si="29">G28*20</f>
         <v>20</v>
       </c>
       <c r="K28">
-        <f t="shared" si="4"/>
+        <f t="shared" si="27"/>
         <v>20</v>
       </c>
       <c r="L28">
-        <f t="shared" si="5"/>
+        <f t="shared" si="28"/>
         <v>60</v>
       </c>
       <c r="M28">
@@ -1884,7 +1884,7 @@
     </row>
     <row r="29" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A29">
-        <v>-100</v>
+        <v>-120</v>
       </c>
       <c r="B29">
         <v>20</v>
@@ -1911,15 +1911,15 @@
         <v>3</v>
       </c>
       <c r="J29">
-        <f t="shared" si="6"/>
+        <f t="shared" si="29"/>
         <v>20</v>
       </c>
       <c r="K29">
-        <f t="shared" si="4"/>
+        <f t="shared" ref="K29:K32" si="30">H29*20</f>
         <v>20</v>
       </c>
       <c r="L29">
-        <f t="shared" si="5"/>
+        <f t="shared" ref="L29:L32" si="31">I29*20</f>
         <v>60</v>
       </c>
       <c r="M29">
@@ -1937,10 +1937,10 @@
     </row>
     <row r="30" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A30">
-        <v>-60</v>
+        <v>-100</v>
       </c>
       <c r="B30">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="C30">
         <v>-300</v>
@@ -1964,15 +1964,15 @@
         <v>3</v>
       </c>
       <c r="J30">
-        <f t="shared" si="6"/>
+        <f t="shared" si="29"/>
         <v>20</v>
       </c>
       <c r="K30">
-        <f t="shared" si="4"/>
+        <f t="shared" si="30"/>
         <v>20</v>
       </c>
       <c r="L30">
-        <f t="shared" si="5"/>
+        <f t="shared" si="31"/>
         <v>60</v>
       </c>
       <c r="M30">
@@ -1990,7 +1990,7 @@
     </row>
     <row r="31" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A31">
-        <v>-40</v>
+        <v>-60</v>
       </c>
       <c r="B31">
         <v>40</v>
@@ -2017,15 +2017,15 @@
         <v>3</v>
       </c>
       <c r="J31">
-        <f t="shared" si="6"/>
+        <f t="shared" ref="J31:J33" si="32">G31*20</f>
         <v>20</v>
       </c>
       <c r="K31">
-        <f t="shared" si="4"/>
+        <f t="shared" si="30"/>
         <v>20</v>
       </c>
       <c r="L31">
-        <f t="shared" si="5"/>
+        <f t="shared" si="31"/>
         <v>60</v>
       </c>
       <c r="M31">
@@ -2043,7 +2043,7 @@
     </row>
     <row r="32" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A32">
-        <v>-20</v>
+        <v>-40</v>
       </c>
       <c r="B32">
         <v>40</v>
@@ -2070,15 +2070,15 @@
         <v>3</v>
       </c>
       <c r="J32">
-        <f t="shared" si="6"/>
+        <f t="shared" si="32"/>
         <v>20</v>
       </c>
       <c r="K32">
-        <f t="shared" si="4"/>
+        <f t="shared" si="30"/>
         <v>20</v>
       </c>
       <c r="L32">
-        <f t="shared" si="5"/>
+        <f t="shared" si="31"/>
         <v>60</v>
       </c>
       <c r="M32">
@@ -2096,10 +2096,10 @@
     </row>
     <row r="33" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A33">
-        <v>20</v>
+        <v>-20</v>
       </c>
       <c r="B33">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="C33">
         <v>-300</v>
@@ -2123,15 +2123,15 @@
         <v>3</v>
       </c>
       <c r="J33">
-        <f t="shared" si="6"/>
+        <f t="shared" si="32"/>
         <v>20</v>
       </c>
       <c r="K33">
-        <f t="shared" si="4"/>
+        <f t="shared" ref="K33:K36" si="33">H33*20</f>
         <v>20</v>
       </c>
       <c r="L33">
-        <f t="shared" si="5"/>
+        <f t="shared" ref="L33:L36" si="34">I33*20</f>
         <v>60</v>
       </c>
       <c r="M33">
@@ -2149,7 +2149,7 @@
     </row>
     <row r="34" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A34">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="B34">
         <v>60</v>
@@ -2176,15 +2176,15 @@
         <v>3</v>
       </c>
       <c r="J34">
-        <f t="shared" si="6"/>
+        <f t="shared" ref="J34:J36" si="35">G34*20</f>
         <v>20</v>
       </c>
       <c r="K34">
-        <f t="shared" si="4"/>
+        <f t="shared" si="33"/>
         <v>20</v>
       </c>
       <c r="L34">
-        <f t="shared" si="5"/>
+        <f t="shared" si="34"/>
         <v>60</v>
       </c>
       <c r="M34">
@@ -2202,7 +2202,7 @@
     </row>
     <row r="35" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A35">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="B35">
         <v>60</v>
@@ -2229,15 +2229,15 @@
         <v>3</v>
       </c>
       <c r="J35">
-        <f t="shared" si="6"/>
+        <f t="shared" si="35"/>
         <v>20</v>
       </c>
       <c r="K35">
-        <f t="shared" si="4"/>
+        <f t="shared" si="33"/>
         <v>20</v>
       </c>
       <c r="L35">
-        <f t="shared" si="5"/>
+        <f t="shared" si="34"/>
         <v>60</v>
       </c>
       <c r="M35">
@@ -2255,10 +2255,10 @@
     </row>
     <row r="36" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A36">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="B36">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="C36">
         <v>-300</v>
@@ -2282,15 +2282,15 @@
         <v>3</v>
       </c>
       <c r="J36">
-        <f t="shared" si="6"/>
+        <f t="shared" si="35"/>
         <v>20</v>
       </c>
       <c r="K36">
-        <f t="shared" si="4"/>
+        <f t="shared" si="33"/>
         <v>20</v>
       </c>
       <c r="L36">
-        <f t="shared" si="5"/>
+        <f t="shared" si="34"/>
         <v>60</v>
       </c>
       <c r="M36">
@@ -2308,7 +2308,7 @@
     </row>
     <row r="37" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A37">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="B37">
         <v>80</v>
@@ -2335,15 +2335,15 @@
         <v>3</v>
       </c>
       <c r="J37">
-        <f t="shared" si="6"/>
+        <f t="shared" ref="J37:J100" si="36">G37*20</f>
         <v>20</v>
       </c>
       <c r="K37">
-        <f t="shared" si="4"/>
+        <f t="shared" ref="K37:K100" si="37">H37*20</f>
         <v>20</v>
       </c>
       <c r="L37">
-        <f t="shared" si="5"/>
+        <f t="shared" ref="L37:L100" si="38">I37*20</f>
         <v>60</v>
       </c>
       <c r="M37">
@@ -2361,7 +2361,7 @@
     </row>
     <row r="38" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A38">
-        <v>140</v>
+        <v>120</v>
       </c>
       <c r="B38">
         <v>80</v>
@@ -2388,15 +2388,15 @@
         <v>3</v>
       </c>
       <c r="J38">
-        <f t="shared" si="6"/>
+        <f t="shared" si="36"/>
         <v>20</v>
       </c>
       <c r="K38">
-        <f t="shared" si="4"/>
+        <f t="shared" si="37"/>
         <v>20</v>
       </c>
       <c r="L38">
-        <f t="shared" si="5"/>
+        <f t="shared" si="38"/>
         <v>60</v>
       </c>
       <c r="M38">
@@ -2414,10 +2414,10 @@
     </row>
     <row r="39" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A39">
-        <v>180</v>
+        <v>140</v>
       </c>
       <c r="B39">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="C39">
         <v>-300</v>
@@ -2441,15 +2441,15 @@
         <v>3</v>
       </c>
       <c r="J39">
-        <f t="shared" si="6"/>
+        <f t="shared" si="36"/>
         <v>20</v>
       </c>
       <c r="K39">
-        <f t="shared" si="4"/>
+        <f t="shared" si="37"/>
         <v>20</v>
       </c>
       <c r="L39">
-        <f t="shared" si="5"/>
+        <f t="shared" si="38"/>
         <v>60</v>
       </c>
       <c r="M39">
@@ -2467,7 +2467,7 @@
     </row>
     <row r="40" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A40">
-        <v>200</v>
+        <v>180</v>
       </c>
       <c r="B40">
         <v>100</v>
@@ -2494,15 +2494,15 @@
         <v>3</v>
       </c>
       <c r="J40">
-        <f t="shared" si="6"/>
+        <f t="shared" si="36"/>
         <v>20</v>
       </c>
       <c r="K40">
-        <f t="shared" si="4"/>
+        <f t="shared" si="37"/>
         <v>20</v>
       </c>
       <c r="L40">
-        <f t="shared" si="5"/>
+        <f t="shared" si="38"/>
         <v>60</v>
       </c>
       <c r="M40">
@@ -2520,7 +2520,7 @@
     </row>
     <row r="41" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A41">
-        <v>220</v>
+        <v>200</v>
       </c>
       <c r="B41">
         <v>100</v>
@@ -2547,15 +2547,15 @@
         <v>3</v>
       </c>
       <c r="J41">
-        <f t="shared" si="6"/>
+        <f t="shared" si="36"/>
         <v>20</v>
       </c>
       <c r="K41">
-        <f t="shared" si="4"/>
+        <f t="shared" si="37"/>
         <v>20</v>
       </c>
       <c r="L41">
-        <f t="shared" si="5"/>
+        <f t="shared" si="38"/>
         <v>60</v>
       </c>
       <c r="M41">
@@ -2573,13 +2573,13 @@
     </row>
     <row r="42" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A42">
-        <v>260</v>
+        <v>220</v>
       </c>
       <c r="B42">
         <v>100</v>
       </c>
       <c r="C42">
-        <v>-320</v>
+        <v>-300</v>
       </c>
       <c r="D42">
         <v>0</v>
@@ -2591,25 +2591,25 @@
         <v>0</v>
       </c>
       <c r="G42">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H42">
         <v>1</v>
       </c>
       <c r="I42">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J42">
-        <f t="shared" si="6"/>
-        <v>60</v>
+        <f t="shared" si="36"/>
+        <v>20</v>
       </c>
       <c r="K42">
-        <f t="shared" si="4"/>
+        <f t="shared" si="37"/>
         <v>20</v>
       </c>
       <c r="L42">
-        <f t="shared" si="5"/>
-        <v>20</v>
+        <f t="shared" si="38"/>
+        <v>60</v>
       </c>
       <c r="M42">
         <v>0</v>
@@ -2632,7 +2632,7 @@
         <v>100</v>
       </c>
       <c r="C43">
-        <v>-300</v>
+        <v>-320</v>
       </c>
       <c r="D43">
         <v>0</v>
@@ -2653,15 +2653,15 @@
         <v>1</v>
       </c>
       <c r="J43">
-        <f t="shared" si="6"/>
+        <f t="shared" si="36"/>
         <v>60</v>
       </c>
       <c r="K43">
-        <f t="shared" si="4"/>
+        <f t="shared" si="37"/>
         <v>20</v>
       </c>
       <c r="L43">
-        <f t="shared" si="5"/>
+        <f t="shared" si="38"/>
         <v>20</v>
       </c>
       <c r="M43">
@@ -2685,7 +2685,7 @@
         <v>100</v>
       </c>
       <c r="C44">
-        <v>-280</v>
+        <v>-300</v>
       </c>
       <c r="D44">
         <v>0</v>
@@ -2706,15 +2706,15 @@
         <v>1</v>
       </c>
       <c r="J44">
-        <f t="shared" si="6"/>
+        <f t="shared" si="36"/>
         <v>60</v>
       </c>
       <c r="K44">
-        <f t="shared" si="4"/>
+        <f t="shared" si="37"/>
         <v>20</v>
       </c>
       <c r="L44">
-        <f t="shared" si="5"/>
+        <f t="shared" si="38"/>
         <v>20</v>
       </c>
       <c r="M44">
@@ -2738,7 +2738,7 @@
         <v>100</v>
       </c>
       <c r="C45">
-        <v>-260</v>
+        <v>-280</v>
       </c>
       <c r="D45">
         <v>0</v>
@@ -2759,15 +2759,15 @@
         <v>1</v>
       </c>
       <c r="J45">
-        <f t="shared" si="6"/>
+        <f t="shared" si="36"/>
         <v>60</v>
       </c>
       <c r="K45">
-        <f t="shared" si="4"/>
+        <f t="shared" si="37"/>
         <v>20</v>
       </c>
       <c r="L45">
-        <f t="shared" si="5"/>
+        <f t="shared" si="38"/>
         <v>20</v>
       </c>
       <c r="M45">
@@ -2791,7 +2791,7 @@
         <v>100</v>
       </c>
       <c r="C46">
-        <v>-240</v>
+        <v>-260</v>
       </c>
       <c r="D46">
         <v>0</v>
@@ -2812,15 +2812,15 @@
         <v>1</v>
       </c>
       <c r="J46">
-        <f t="shared" si="6"/>
+        <f t="shared" si="36"/>
         <v>60</v>
       </c>
       <c r="K46">
-        <f t="shared" si="4"/>
+        <f t="shared" si="37"/>
         <v>20</v>
       </c>
       <c r="L46">
-        <f t="shared" si="5"/>
+        <f t="shared" si="38"/>
         <v>20</v>
       </c>
       <c r="M46">
@@ -2844,7 +2844,7 @@
         <v>100</v>
       </c>
       <c r="C47">
-        <v>-220</v>
+        <v>-240</v>
       </c>
       <c r="D47">
         <v>0</v>
@@ -2865,15 +2865,15 @@
         <v>1</v>
       </c>
       <c r="J47">
-        <f t="shared" si="6"/>
+        <f t="shared" si="36"/>
         <v>60</v>
       </c>
       <c r="K47">
-        <f t="shared" si="4"/>
+        <f t="shared" si="37"/>
         <v>20</v>
       </c>
       <c r="L47">
-        <f t="shared" si="5"/>
+        <f t="shared" si="38"/>
         <v>20</v>
       </c>
       <c r="M47">
@@ -2897,7 +2897,7 @@
         <v>100</v>
       </c>
       <c r="C48">
-        <v>-200</v>
+        <v>-220</v>
       </c>
       <c r="D48">
         <v>0</v>
@@ -2918,15 +2918,15 @@
         <v>1</v>
       </c>
       <c r="J48">
-        <f t="shared" si="6"/>
+        <f t="shared" si="36"/>
         <v>60</v>
       </c>
       <c r="K48">
-        <f t="shared" si="4"/>
+        <f t="shared" si="37"/>
         <v>20</v>
       </c>
       <c r="L48">
-        <f t="shared" si="5"/>
+        <f t="shared" si="38"/>
         <v>20</v>
       </c>
       <c r="M48">
@@ -2950,7 +2950,7 @@
         <v>100</v>
       </c>
       <c r="C49">
-        <v>-180</v>
+        <v>-200</v>
       </c>
       <c r="D49">
         <v>0</v>
@@ -2971,15 +2971,15 @@
         <v>1</v>
       </c>
       <c r="J49">
-        <f t="shared" si="6"/>
+        <f t="shared" si="36"/>
         <v>60</v>
       </c>
       <c r="K49">
-        <f t="shared" si="4"/>
+        <f t="shared" si="37"/>
         <v>20</v>
       </c>
       <c r="L49">
-        <f t="shared" si="5"/>
+        <f t="shared" si="38"/>
         <v>20</v>
       </c>
       <c r="M49">
@@ -3003,7 +3003,7 @@
         <v>100</v>
       </c>
       <c r="C50">
-        <v>-160</v>
+        <v>-180</v>
       </c>
       <c r="D50">
         <v>0</v>
@@ -3024,15 +3024,15 @@
         <v>1</v>
       </c>
       <c r="J50">
-        <f t="shared" si="6"/>
+        <f t="shared" si="36"/>
         <v>60</v>
       </c>
       <c r="K50">
-        <f t="shared" si="4"/>
+        <f t="shared" si="37"/>
         <v>20</v>
       </c>
       <c r="L50">
-        <f t="shared" si="5"/>
+        <f t="shared" si="38"/>
         <v>20</v>
       </c>
       <c r="M50">
@@ -3050,13 +3050,13 @@
     </row>
     <row r="51" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A51">
-        <v>340</v>
+        <v>260</v>
       </c>
       <c r="B51">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="C51">
-        <v>-120</v>
+        <v>-160</v>
       </c>
       <c r="D51">
         <v>0</v>
@@ -3077,15 +3077,15 @@
         <v>1</v>
       </c>
       <c r="J51">
-        <f t="shared" si="6"/>
+        <f t="shared" si="36"/>
         <v>60</v>
       </c>
       <c r="K51">
-        <f t="shared" si="4"/>
+        <f t="shared" si="37"/>
         <v>20</v>
       </c>
       <c r="L51">
-        <f t="shared" si="5"/>
+        <f t="shared" si="38"/>
         <v>20</v>
       </c>
       <c r="M51">
@@ -3109,7 +3109,7 @@
         <v>120</v>
       </c>
       <c r="C52">
-        <v>-100</v>
+        <v>-120</v>
       </c>
       <c r="D52">
         <v>0</v>
@@ -3130,15 +3130,15 @@
         <v>1</v>
       </c>
       <c r="J52">
-        <f t="shared" si="6"/>
+        <f t="shared" si="36"/>
         <v>60</v>
       </c>
       <c r="K52">
-        <f t="shared" si="4"/>
+        <f t="shared" si="37"/>
         <v>20</v>
       </c>
       <c r="L52">
-        <f t="shared" si="5"/>
+        <f t="shared" si="38"/>
         <v>20</v>
       </c>
       <c r="M52">
@@ -3162,7 +3162,7 @@
         <v>120</v>
       </c>
       <c r="C53">
-        <v>-80</v>
+        <v>-100</v>
       </c>
       <c r="D53">
         <v>0</v>
@@ -3183,15 +3183,15 @@
         <v>1</v>
       </c>
       <c r="J53">
-        <f t="shared" si="6"/>
+        <f t="shared" si="36"/>
         <v>60</v>
       </c>
       <c r="K53">
-        <f t="shared" si="4"/>
+        <f t="shared" si="37"/>
         <v>20</v>
       </c>
       <c r="L53">
-        <f t="shared" si="5"/>
+        <f t="shared" si="38"/>
         <v>20</v>
       </c>
       <c r="M53">
@@ -3209,13 +3209,13 @@
     </row>
     <row r="54" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A54">
-        <v>420</v>
+        <v>340</v>
       </c>
       <c r="B54">
-        <v>140</v>
+        <v>120</v>
       </c>
       <c r="C54">
-        <v>-40</v>
+        <v>-80</v>
       </c>
       <c r="D54">
         <v>0</v>
@@ -3236,15 +3236,15 @@
         <v>1</v>
       </c>
       <c r="J54">
-        <f t="shared" si="6"/>
+        <f t="shared" si="36"/>
         <v>60</v>
       </c>
       <c r="K54">
-        <f t="shared" si="4"/>
+        <f t="shared" si="37"/>
         <v>20</v>
       </c>
       <c r="L54">
-        <f t="shared" si="5"/>
+        <f t="shared" si="38"/>
         <v>20</v>
       </c>
       <c r="M54">
@@ -3268,7 +3268,7 @@
         <v>140</v>
       </c>
       <c r="C55">
-        <v>-20</v>
+        <v>-40</v>
       </c>
       <c r="D55">
         <v>0</v>
@@ -3289,15 +3289,15 @@
         <v>1</v>
       </c>
       <c r="J55">
-        <f t="shared" si="6"/>
+        <f t="shared" si="36"/>
         <v>60</v>
       </c>
       <c r="K55">
-        <f t="shared" si="4"/>
+        <f t="shared" si="37"/>
         <v>20</v>
       </c>
       <c r="L55">
-        <f t="shared" si="5"/>
+        <f t="shared" si="38"/>
         <v>20</v>
       </c>
       <c r="M55">
@@ -3321,7 +3321,7 @@
         <v>140</v>
       </c>
       <c r="C56">
-        <v>0</v>
+        <v>-20</v>
       </c>
       <c r="D56">
         <v>0</v>
@@ -3342,15 +3342,15 @@
         <v>1</v>
       </c>
       <c r="J56">
-        <f t="shared" si="6"/>
+        <f t="shared" si="36"/>
         <v>60</v>
       </c>
       <c r="K56">
-        <f t="shared" si="4"/>
+        <f t="shared" si="37"/>
         <v>20</v>
       </c>
       <c r="L56">
-        <f t="shared" si="5"/>
+        <f t="shared" si="38"/>
         <v>20</v>
       </c>
       <c r="M56">
@@ -3371,10 +3371,10 @@
         <v>420</v>
       </c>
       <c r="B57">
-        <v>160</v>
+        <v>140</v>
       </c>
       <c r="C57">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="D57">
         <v>0</v>
@@ -3395,15 +3395,15 @@
         <v>1</v>
       </c>
       <c r="J57">
-        <f t="shared" si="6"/>
+        <f t="shared" si="36"/>
         <v>60</v>
       </c>
       <c r="K57">
-        <f t="shared" si="4"/>
+        <f t="shared" si="37"/>
         <v>20</v>
       </c>
       <c r="L57">
-        <f t="shared" si="5"/>
+        <f t="shared" si="38"/>
         <v>20</v>
       </c>
       <c r="M57">
@@ -3427,7 +3427,7 @@
         <v>160</v>
       </c>
       <c r="C58">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="D58">
         <v>0</v>
@@ -3448,15 +3448,15 @@
         <v>1</v>
       </c>
       <c r="J58">
-        <f t="shared" si="6"/>
+        <f t="shared" si="36"/>
         <v>60</v>
       </c>
       <c r="K58">
-        <f t="shared" si="4"/>
+        <f t="shared" si="37"/>
         <v>20</v>
       </c>
       <c r="L58">
-        <f t="shared" si="5"/>
+        <f t="shared" si="38"/>
         <v>20</v>
       </c>
       <c r="M58">
@@ -3480,7 +3480,7 @@
         <v>160</v>
       </c>
       <c r="C59">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="D59">
         <v>0</v>
@@ -3501,15 +3501,15 @@
         <v>1</v>
       </c>
       <c r="J59">
-        <f t="shared" si="6"/>
+        <f t="shared" si="36"/>
         <v>60</v>
       </c>
       <c r="K59">
-        <f t="shared" si="4"/>
+        <f t="shared" si="37"/>
         <v>20</v>
       </c>
       <c r="L59">
-        <f t="shared" si="5"/>
+        <f t="shared" si="38"/>
         <v>20</v>
       </c>
       <c r="M59">
@@ -3530,10 +3530,10 @@
         <v>420</v>
       </c>
       <c r="B60">
-        <v>180</v>
+        <v>160</v>
       </c>
       <c r="C60">
-        <v>160</v>
+        <v>100</v>
       </c>
       <c r="D60">
         <v>0</v>
@@ -3554,15 +3554,15 @@
         <v>1</v>
       </c>
       <c r="J60">
-        <f t="shared" si="6"/>
+        <f t="shared" si="36"/>
         <v>60</v>
       </c>
       <c r="K60">
-        <f t="shared" si="4"/>
+        <f t="shared" si="37"/>
         <v>20</v>
       </c>
       <c r="L60">
-        <f t="shared" si="5"/>
+        <f t="shared" si="38"/>
         <v>20</v>
       </c>
       <c r="M60">
@@ -3586,7 +3586,7 @@
         <v>180</v>
       </c>
       <c r="C61">
-        <v>180</v>
+        <v>160</v>
       </c>
       <c r="D61">
         <v>0</v>
@@ -3607,15 +3607,15 @@
         <v>1</v>
       </c>
       <c r="J61">
-        <f t="shared" si="6"/>
+        <f t="shared" si="36"/>
         <v>60</v>
       </c>
       <c r="K61">
-        <f t="shared" si="4"/>
+        <f t="shared" si="37"/>
         <v>20</v>
       </c>
       <c r="L61">
-        <f t="shared" si="5"/>
+        <f t="shared" si="38"/>
         <v>20</v>
       </c>
       <c r="M61">
@@ -3639,7 +3639,7 @@
         <v>180</v>
       </c>
       <c r="C62">
-        <v>200</v>
+        <v>180</v>
       </c>
       <c r="D62">
         <v>0</v>
@@ -3660,15 +3660,15 @@
         <v>1</v>
       </c>
       <c r="J62">
-        <f t="shared" si="6"/>
+        <f t="shared" si="36"/>
         <v>60</v>
       </c>
       <c r="K62">
-        <f t="shared" si="4"/>
+        <f t="shared" si="37"/>
         <v>20</v>
       </c>
       <c r="L62">
-        <f t="shared" si="5"/>
+        <f t="shared" si="38"/>
         <v>20</v>
       </c>
       <c r="M62">
@@ -3692,7 +3692,7 @@
         <v>180</v>
       </c>
       <c r="C63">
-        <v>240</v>
+        <v>200</v>
       </c>
       <c r="D63">
         <v>0</v>
@@ -3710,42 +3710,42 @@
         <v>1</v>
       </c>
       <c r="I63">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J63">
-        <f t="shared" si="6"/>
+        <f t="shared" si="36"/>
         <v>60</v>
       </c>
       <c r="K63">
-        <f t="shared" si="4"/>
+        <f t="shared" si="37"/>
         <v>20</v>
       </c>
       <c r="L63">
-        <f t="shared" si="5"/>
-        <v>60</v>
+        <f t="shared" si="38"/>
+        <v>20</v>
       </c>
       <c r="M63">
-        <v>420</v>
+        <v>0</v>
       </c>
       <c r="N63">
-        <v>380</v>
+        <v>0</v>
       </c>
       <c r="O63">
-        <v>240</v>
+        <v>0</v>
       </c>
       <c r="P63">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="64" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A64">
-        <v>0</v>
+        <v>420</v>
       </c>
       <c r="B64">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="C64">
-        <v>0</v>
+        <v>240</v>
       </c>
       <c r="D64">
         <v>0</v>
@@ -3757,48 +3757,48 @@
         <v>0</v>
       </c>
       <c r="G64">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H64">
         <v>1</v>
       </c>
       <c r="I64">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J64">
-        <f t="shared" si="6"/>
-        <v>20</v>
+        <f t="shared" si="36"/>
+        <v>60</v>
       </c>
       <c r="K64">
-        <f t="shared" ref="K64:K91" si="7">H64*20</f>
+        <f t="shared" si="37"/>
         <v>20</v>
       </c>
       <c r="L64">
-        <f t="shared" ref="L64:L91" si="8">I64*20</f>
-        <v>20</v>
+        <f t="shared" si="38"/>
+        <v>60</v>
       </c>
       <c r="M64">
-        <v>0</v>
+        <v>420</v>
       </c>
       <c r="N64">
-        <v>0</v>
+        <v>280</v>
       </c>
       <c r="O64">
-        <v>0</v>
+        <v>240</v>
       </c>
       <c r="P64">
-        <v>0</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="65" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A65">
-        <v>0</v>
+        <v>420</v>
       </c>
       <c r="B65">
-        <v>0</v>
+        <v>280</v>
       </c>
       <c r="C65">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="D65">
         <v>0</v>
@@ -3810,25 +3810,25 @@
         <v>0</v>
       </c>
       <c r="G65">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H65">
         <v>1</v>
       </c>
       <c r="I65">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J65">
-        <f t="shared" si="6"/>
-        <v>20</v>
+        <f t="shared" si="36"/>
+        <v>60</v>
       </c>
       <c r="K65">
-        <f t="shared" si="7"/>
+        <f t="shared" si="37"/>
         <v>20</v>
       </c>
       <c r="L65">
-        <f t="shared" si="8"/>
-        <v>20</v>
+        <f t="shared" si="38"/>
+        <v>60</v>
       </c>
       <c r="M65">
         <v>0</v>
@@ -3845,13 +3845,13 @@
     </row>
     <row r="66" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A66">
-        <v>0</v>
+        <v>360</v>
       </c>
       <c r="B66">
-        <v>0</v>
+        <v>280</v>
       </c>
       <c r="C66">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="D66">
         <v>0</v>
@@ -3863,48 +3863,48 @@
         <v>0</v>
       </c>
       <c r="G66">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H66">
         <v>1</v>
       </c>
       <c r="I66">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J66">
-        <f t="shared" ref="J66:J91" si="9">G66*20</f>
-        <v>20</v>
+        <f t="shared" si="36"/>
+        <v>60</v>
       </c>
       <c r="K66">
-        <f t="shared" si="7"/>
+        <f t="shared" si="37"/>
         <v>20</v>
       </c>
       <c r="L66">
-        <f t="shared" si="8"/>
-        <v>20</v>
+        <f t="shared" si="38"/>
+        <v>60</v>
       </c>
       <c r="M66">
-        <v>0</v>
+        <v>160</v>
       </c>
       <c r="N66">
-        <v>0</v>
+        <v>280</v>
       </c>
       <c r="O66">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="P66">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="67" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A67">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="B67">
-        <v>0</v>
+        <v>280</v>
       </c>
       <c r="C67">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="D67">
         <v>0</v>
@@ -3922,19 +3922,19 @@
         <v>1</v>
       </c>
       <c r="I67">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J67">
-        <f t="shared" si="9"/>
+        <f t="shared" si="36"/>
         <v>20</v>
       </c>
       <c r="K67">
-        <f t="shared" si="7"/>
+        <f t="shared" si="37"/>
         <v>20</v>
       </c>
       <c r="L67">
-        <f t="shared" si="8"/>
-        <v>20</v>
+        <f t="shared" si="38"/>
+        <v>60</v>
       </c>
       <c r="M67">
         <v>0</v>
@@ -3951,13 +3951,13 @@
     </row>
     <row r="68" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A68">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="B68">
-        <v>0</v>
+        <v>280</v>
       </c>
       <c r="C68">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="D68">
         <v>0</v>
@@ -3975,19 +3975,19 @@
         <v>1</v>
       </c>
       <c r="I68">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J68">
-        <f t="shared" si="9"/>
+        <f t="shared" si="36"/>
         <v>20</v>
       </c>
       <c r="K68">
-        <f t="shared" si="7"/>
+        <f t="shared" si="37"/>
         <v>20</v>
       </c>
       <c r="L68">
-        <f t="shared" si="8"/>
-        <v>20</v>
+        <f t="shared" si="38"/>
+        <v>60</v>
       </c>
       <c r="M68">
         <v>0</v>
@@ -4004,13 +4004,13 @@
     </row>
     <row r="69" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A69">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="B69">
-        <v>0</v>
+        <v>280</v>
       </c>
       <c r="C69">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="D69">
         <v>0</v>
@@ -4028,19 +4028,19 @@
         <v>1</v>
       </c>
       <c r="I69">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J69">
-        <f t="shared" si="9"/>
+        <f t="shared" si="36"/>
         <v>20</v>
       </c>
       <c r="K69">
-        <f t="shared" si="7"/>
+        <f t="shared" si="37"/>
         <v>20</v>
       </c>
       <c r="L69">
-        <f t="shared" si="8"/>
-        <v>20</v>
+        <f t="shared" si="38"/>
+        <v>60</v>
       </c>
       <c r="M69">
         <v>0</v>
@@ -4057,13 +4057,13 @@
     </row>
     <row r="70" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A70">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="B70">
-        <v>0</v>
+        <v>280</v>
       </c>
       <c r="C70">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="D70">
         <v>0</v>
@@ -4075,48 +4075,48 @@
         <v>0</v>
       </c>
       <c r="G70">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H70">
         <v>1</v>
       </c>
       <c r="I70">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J70">
-        <f t="shared" si="9"/>
-        <v>20</v>
+        <f t="shared" si="36"/>
+        <v>60</v>
       </c>
       <c r="K70">
-        <f t="shared" si="7"/>
+        <f t="shared" si="37"/>
         <v>20</v>
       </c>
       <c r="L70">
-        <f t="shared" si="8"/>
-        <v>20</v>
+        <f t="shared" si="38"/>
+        <v>60</v>
       </c>
       <c r="M70">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="N70">
-        <v>0</v>
+        <v>480</v>
       </c>
       <c r="O70">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P70">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="71" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A71">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="B71">
-        <v>0</v>
+        <v>480</v>
       </c>
       <c r="C71">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="D71">
         <v>0</v>
@@ -4128,7 +4128,7 @@
         <v>0</v>
       </c>
       <c r="G71">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H71">
         <v>1</v>
@@ -4137,15 +4137,15 @@
         <v>1</v>
       </c>
       <c r="J71">
-        <f t="shared" si="9"/>
-        <v>20</v>
+        <f t="shared" si="36"/>
+        <v>60</v>
       </c>
       <c r="K71">
-        <f t="shared" si="7"/>
+        <f t="shared" si="37"/>
         <v>20</v>
       </c>
       <c r="L71">
-        <f t="shared" si="8"/>
+        <f t="shared" si="38"/>
         <v>20</v>
       </c>
       <c r="M71">
@@ -4166,7 +4166,7 @@
         <v>0</v>
       </c>
       <c r="B72">
-        <v>0</v>
+        <v>480</v>
       </c>
       <c r="C72">
         <v>0</v>
@@ -4181,7 +4181,7 @@
         <v>0</v>
       </c>
       <c r="G72">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H72">
         <v>1</v>
@@ -4190,15 +4190,15 @@
         <v>1</v>
       </c>
       <c r="J72">
-        <f t="shared" si="9"/>
-        <v>20</v>
+        <f t="shared" si="36"/>
+        <v>60</v>
       </c>
       <c r="K72">
-        <f t="shared" si="7"/>
+        <f t="shared" si="37"/>
         <v>20</v>
       </c>
       <c r="L72">
-        <f t="shared" si="8"/>
+        <f t="shared" si="38"/>
         <v>20</v>
       </c>
       <c r="M72">
@@ -4222,7 +4222,7 @@
         <v>0</v>
       </c>
       <c r="C73">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="D73">
         <v>0</v>
@@ -4234,7 +4234,7 @@
         <v>0</v>
       </c>
       <c r="G73">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H73">
         <v>1</v>
@@ -4243,15 +4243,15 @@
         <v>1</v>
       </c>
       <c r="J73">
-        <f t="shared" si="9"/>
-        <v>20</v>
+        <f t="shared" si="36"/>
+        <v>60</v>
       </c>
       <c r="K73">
-        <f t="shared" si="7"/>
+        <f t="shared" si="37"/>
         <v>20</v>
       </c>
       <c r="L73">
-        <f t="shared" si="8"/>
+        <f t="shared" si="38"/>
         <v>20</v>
       </c>
       <c r="M73">
@@ -4275,7 +4275,7 @@
         <v>0</v>
       </c>
       <c r="C74">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="D74">
         <v>0</v>
@@ -4287,7 +4287,7 @@
         <v>0</v>
       </c>
       <c r="G74">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H74">
         <v>1</v>
@@ -4296,15 +4296,15 @@
         <v>1</v>
       </c>
       <c r="J74">
-        <f t="shared" si="9"/>
-        <v>20</v>
+        <f t="shared" si="36"/>
+        <v>60</v>
       </c>
       <c r="K74">
-        <f t="shared" si="7"/>
+        <f t="shared" si="37"/>
         <v>20</v>
       </c>
       <c r="L74">
-        <f t="shared" si="8"/>
+        <f t="shared" si="38"/>
         <v>20</v>
       </c>
       <c r="M74">
@@ -4328,7 +4328,7 @@
         <v>0</v>
       </c>
       <c r="C75">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="D75">
         <v>0</v>
@@ -4340,7 +4340,7 @@
         <v>0</v>
       </c>
       <c r="G75">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H75">
         <v>1</v>
@@ -4349,15 +4349,15 @@
         <v>1</v>
       </c>
       <c r="J75">
-        <f t="shared" si="9"/>
-        <v>20</v>
+        <f t="shared" si="36"/>
+        <v>40</v>
       </c>
       <c r="K75">
-        <f t="shared" si="7"/>
+        <f t="shared" si="37"/>
         <v>20</v>
       </c>
       <c r="L75">
-        <f t="shared" si="8"/>
+        <f t="shared" si="38"/>
         <v>20</v>
       </c>
       <c r="M75">
@@ -4381,7 +4381,7 @@
         <v>0</v>
       </c>
       <c r="C76">
-        <v>0</v>
+        <v>160</v>
       </c>
       <c r="D76">
         <v>0</v>
@@ -4393,7 +4393,7 @@
         <v>0</v>
       </c>
       <c r="G76">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H76">
         <v>1</v>
@@ -4402,15 +4402,15 @@
         <v>1</v>
       </c>
       <c r="J76">
-        <f t="shared" si="9"/>
-        <v>20</v>
+        <f t="shared" si="36"/>
+        <v>40</v>
       </c>
       <c r="K76">
-        <f t="shared" si="7"/>
+        <f t="shared" si="37"/>
         <v>20</v>
       </c>
       <c r="L76">
-        <f t="shared" si="8"/>
+        <f t="shared" si="38"/>
         <v>20</v>
       </c>
       <c r="M76">
@@ -4434,7 +4434,7 @@
         <v>0</v>
       </c>
       <c r="C77">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="D77">
         <v>0</v>
@@ -4446,7 +4446,7 @@
         <v>0</v>
       </c>
       <c r="G77">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H77">
         <v>1</v>
@@ -4455,15 +4455,15 @@
         <v>1</v>
       </c>
       <c r="J77">
-        <f t="shared" si="9"/>
-        <v>20</v>
+        <f t="shared" si="36"/>
+        <v>40</v>
       </c>
       <c r="K77">
-        <f t="shared" si="7"/>
+        <f t="shared" si="37"/>
         <v>20</v>
       </c>
       <c r="L77">
-        <f t="shared" si="8"/>
+        <f t="shared" si="38"/>
         <v>20</v>
       </c>
       <c r="M77">
@@ -4487,7 +4487,7 @@
         <v>0</v>
       </c>
       <c r="C78">
-        <v>0</v>
+        <v>240</v>
       </c>
       <c r="D78">
         <v>0</v>
@@ -4508,15 +4508,15 @@
         <v>1</v>
       </c>
       <c r="J78">
-        <f t="shared" si="9"/>
+        <f t="shared" si="36"/>
         <v>20</v>
       </c>
       <c r="K78">
-        <f t="shared" si="7"/>
+        <f t="shared" si="37"/>
         <v>20</v>
       </c>
       <c r="L78">
-        <f t="shared" si="8"/>
+        <f t="shared" si="38"/>
         <v>20</v>
       </c>
       <c r="M78">
@@ -4540,7 +4540,7 @@
         <v>0</v>
       </c>
       <c r="C79">
-        <v>0</v>
+        <v>280</v>
       </c>
       <c r="D79">
         <v>0</v>
@@ -4561,15 +4561,15 @@
         <v>1</v>
       </c>
       <c r="J79">
-        <f t="shared" si="9"/>
+        <f t="shared" si="36"/>
         <v>20</v>
       </c>
       <c r="K79">
-        <f t="shared" si="7"/>
+        <f t="shared" si="37"/>
         <v>20</v>
       </c>
       <c r="L79">
-        <f t="shared" si="8"/>
+        <f t="shared" si="38"/>
         <v>20</v>
       </c>
       <c r="M79">
@@ -4593,7 +4593,7 @@
         <v>0</v>
       </c>
       <c r="C80">
-        <v>0</v>
+        <v>320</v>
       </c>
       <c r="D80">
         <v>0</v>
@@ -4614,15 +4614,15 @@
         <v>1</v>
       </c>
       <c r="J80">
-        <f t="shared" si="9"/>
+        <f t="shared" si="36"/>
         <v>20</v>
       </c>
       <c r="K80">
-        <f t="shared" si="7"/>
+        <f t="shared" si="37"/>
         <v>20</v>
       </c>
       <c r="L80">
-        <f t="shared" si="8"/>
+        <f t="shared" si="38"/>
         <v>20</v>
       </c>
       <c r="M80">
@@ -4667,15 +4667,15 @@
         <v>1</v>
       </c>
       <c r="J81">
-        <f t="shared" si="9"/>
+        <f t="shared" si="36"/>
         <v>20</v>
       </c>
       <c r="K81">
-        <f t="shared" si="7"/>
+        <f t="shared" si="37"/>
         <v>20</v>
       </c>
       <c r="L81">
-        <f t="shared" si="8"/>
+        <f t="shared" si="38"/>
         <v>20</v>
       </c>
       <c r="M81">
@@ -4720,15 +4720,15 @@
         <v>1</v>
       </c>
       <c r="J82">
-        <f t="shared" si="9"/>
+        <f t="shared" si="36"/>
         <v>20</v>
       </c>
       <c r="K82">
-        <f t="shared" si="7"/>
+        <f t="shared" si="37"/>
         <v>20</v>
       </c>
       <c r="L82">
-        <f t="shared" si="8"/>
+        <f t="shared" si="38"/>
         <v>20</v>
       </c>
       <c r="M82">
@@ -4773,15 +4773,15 @@
         <v>1</v>
       </c>
       <c r="J83">
-        <f t="shared" si="9"/>
+        <f t="shared" si="36"/>
         <v>20</v>
       </c>
       <c r="K83">
-        <f t="shared" si="7"/>
+        <f t="shared" si="37"/>
         <v>20</v>
       </c>
       <c r="L83">
-        <f t="shared" si="8"/>
+        <f t="shared" si="38"/>
         <v>20</v>
       </c>
       <c r="M83">
@@ -4826,15 +4826,15 @@
         <v>1</v>
       </c>
       <c r="J84">
-        <f t="shared" si="9"/>
+        <f t="shared" si="36"/>
         <v>20</v>
       </c>
       <c r="K84">
-        <f t="shared" si="7"/>
+        <f t="shared" si="37"/>
         <v>20</v>
       </c>
       <c r="L84">
-        <f t="shared" si="8"/>
+        <f t="shared" si="38"/>
         <v>20</v>
       </c>
       <c r="M84">
@@ -4879,15 +4879,15 @@
         <v>1</v>
       </c>
       <c r="J85">
-        <f t="shared" si="9"/>
+        <f t="shared" si="36"/>
         <v>20</v>
       </c>
       <c r="K85">
-        <f t="shared" si="7"/>
+        <f t="shared" si="37"/>
         <v>20</v>
       </c>
       <c r="L85">
-        <f t="shared" si="8"/>
+        <f t="shared" si="38"/>
         <v>20</v>
       </c>
       <c r="M85">
@@ -4932,15 +4932,15 @@
         <v>1</v>
       </c>
       <c r="J86">
-        <f t="shared" si="9"/>
+        <f t="shared" si="36"/>
         <v>20</v>
       </c>
       <c r="K86">
-        <f t="shared" si="7"/>
+        <f t="shared" si="37"/>
         <v>20</v>
       </c>
       <c r="L86">
-        <f t="shared" si="8"/>
+        <f t="shared" si="38"/>
         <v>20</v>
       </c>
       <c r="M86">
@@ -4985,15 +4985,15 @@
         <v>1</v>
       </c>
       <c r="J87">
-        <f t="shared" si="9"/>
+        <f t="shared" si="36"/>
         <v>20</v>
       </c>
       <c r="K87">
-        <f t="shared" si="7"/>
+        <f t="shared" si="37"/>
         <v>20</v>
       </c>
       <c r="L87">
-        <f t="shared" si="8"/>
+        <f t="shared" si="38"/>
         <v>20</v>
       </c>
       <c r="M87">
@@ -5038,15 +5038,15 @@
         <v>1</v>
       </c>
       <c r="J88">
-        <f t="shared" si="9"/>
+        <f t="shared" si="36"/>
         <v>20</v>
       </c>
       <c r="K88">
-        <f t="shared" si="7"/>
+        <f t="shared" si="37"/>
         <v>20</v>
       </c>
       <c r="L88">
-        <f t="shared" si="8"/>
+        <f t="shared" si="38"/>
         <v>20</v>
       </c>
       <c r="M88">
@@ -5091,15 +5091,15 @@
         <v>1</v>
       </c>
       <c r="J89">
-        <f t="shared" si="9"/>
+        <f t="shared" si="36"/>
         <v>20</v>
       </c>
       <c r="K89">
-        <f t="shared" si="7"/>
+        <f t="shared" si="37"/>
         <v>20</v>
       </c>
       <c r="L89">
-        <f t="shared" si="8"/>
+        <f t="shared" si="38"/>
         <v>20</v>
       </c>
       <c r="M89">
@@ -5144,15 +5144,15 @@
         <v>1</v>
       </c>
       <c r="J90">
-        <f t="shared" si="9"/>
+        <f t="shared" si="36"/>
         <v>20</v>
       </c>
       <c r="K90">
-        <f t="shared" si="7"/>
+        <f t="shared" si="37"/>
         <v>20</v>
       </c>
       <c r="L90">
-        <f t="shared" si="8"/>
+        <f t="shared" si="38"/>
         <v>20</v>
       </c>
       <c r="M90">
@@ -5197,15 +5197,15 @@
         <v>1</v>
       </c>
       <c r="J91">
-        <f t="shared" si="9"/>
+        <f t="shared" si="36"/>
         <v>20</v>
       </c>
       <c r="K91">
-        <f t="shared" si="7"/>
+        <f t="shared" si="37"/>
         <v>20</v>
       </c>
       <c r="L91">
-        <f t="shared" si="8"/>
+        <f t="shared" si="38"/>
         <v>20</v>
       </c>
       <c r="M91">
@@ -5250,15 +5250,15 @@
         <v>1</v>
       </c>
       <c r="J92">
-        <f t="shared" ref="J92:J100" si="10">G92*20</f>
+        <f t="shared" si="36"/>
         <v>20</v>
       </c>
       <c r="K92">
-        <f t="shared" ref="K92:K100" si="11">H92*20</f>
+        <f t="shared" si="37"/>
         <v>20</v>
       </c>
       <c r="L92">
-        <f t="shared" ref="L92:L100" si="12">I92*20</f>
+        <f t="shared" si="38"/>
         <v>20</v>
       </c>
       <c r="M92">
@@ -5303,15 +5303,15 @@
         <v>1</v>
       </c>
       <c r="J93">
-        <f t="shared" si="10"/>
+        <f t="shared" si="36"/>
         <v>20</v>
       </c>
       <c r="K93">
-        <f t="shared" si="11"/>
+        <f t="shared" si="37"/>
         <v>20</v>
       </c>
       <c r="L93">
-        <f t="shared" si="12"/>
+        <f t="shared" si="38"/>
         <v>20</v>
       </c>
       <c r="M93">
@@ -5356,15 +5356,15 @@
         <v>1</v>
       </c>
       <c r="J94">
-        <f t="shared" si="10"/>
+        <f t="shared" si="36"/>
         <v>20</v>
       </c>
       <c r="K94">
-        <f t="shared" si="11"/>
+        <f t="shared" si="37"/>
         <v>20</v>
       </c>
       <c r="L94">
-        <f t="shared" si="12"/>
+        <f t="shared" si="38"/>
         <v>20</v>
       </c>
       <c r="M94">
@@ -5409,15 +5409,15 @@
         <v>1</v>
       </c>
       <c r="J95">
-        <f t="shared" si="10"/>
+        <f t="shared" si="36"/>
         <v>20</v>
       </c>
       <c r="K95">
-        <f t="shared" si="11"/>
+        <f t="shared" si="37"/>
         <v>20</v>
       </c>
       <c r="L95">
-        <f t="shared" si="12"/>
+        <f t="shared" si="38"/>
         <v>20</v>
       </c>
       <c r="M95">
@@ -5462,15 +5462,15 @@
         <v>1</v>
       </c>
       <c r="J96">
-        <f t="shared" si="10"/>
+        <f t="shared" si="36"/>
         <v>20</v>
       </c>
       <c r="K96">
-        <f t="shared" si="11"/>
+        <f t="shared" si="37"/>
         <v>20</v>
       </c>
       <c r="L96">
-        <f t="shared" si="12"/>
+        <f t="shared" si="38"/>
         <v>20</v>
       </c>
       <c r="M96">
@@ -5515,15 +5515,15 @@
         <v>1</v>
       </c>
       <c r="J97">
-        <f t="shared" si="10"/>
+        <f t="shared" si="36"/>
         <v>20</v>
       </c>
       <c r="K97">
-        <f t="shared" si="11"/>
+        <f t="shared" si="37"/>
         <v>20</v>
       </c>
       <c r="L97">
-        <f t="shared" si="12"/>
+        <f t="shared" si="38"/>
         <v>20</v>
       </c>
       <c r="M97">
@@ -5568,15 +5568,15 @@
         <v>1</v>
       </c>
       <c r="J98">
-        <f t="shared" si="10"/>
+        <f t="shared" si="36"/>
         <v>20</v>
       </c>
       <c r="K98">
-        <f t="shared" si="11"/>
+        <f t="shared" si="37"/>
         <v>20</v>
       </c>
       <c r="L98">
-        <f t="shared" si="12"/>
+        <f t="shared" si="38"/>
         <v>20</v>
       </c>
       <c r="M98">
@@ -5621,15 +5621,15 @@
         <v>1</v>
       </c>
       <c r="J99">
-        <f t="shared" si="10"/>
+        <f t="shared" si="36"/>
         <v>20</v>
       </c>
       <c r="K99">
-        <f t="shared" si="11"/>
+        <f t="shared" si="37"/>
         <v>20</v>
       </c>
       <c r="L99">
-        <f t="shared" si="12"/>
+        <f t="shared" si="38"/>
         <v>20</v>
       </c>
       <c r="M99">
@@ -5674,15 +5674,15 @@
         <v>1</v>
       </c>
       <c r="J100">
-        <f t="shared" si="10"/>
+        <f t="shared" si="36"/>
         <v>20</v>
       </c>
       <c r="K100">
-        <f t="shared" si="11"/>
+        <f t="shared" si="37"/>
         <v>20</v>
       </c>
       <c r="L100">
-        <f t="shared" si="12"/>
+        <f t="shared" si="38"/>
         <v>20</v>
       </c>
       <c r="M100">

--- a/ActionGame-リファクタリング-/Data/CSV/Stage/Stage.xlsx
+++ b/ActionGame-リファクタリング-/Data/CSV/Stage/Stage.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\2409404\Desktop\GameProject\ActionGame-リファクタリング-\Data\CSV\Stage\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CADC4476-F706-4337-BCEB-C7A91221B2B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F5DB79C-AB2F-4FC7-B0A4-CDE7C571A37A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2955" yWindow="3030" windowWidth="21600" windowHeight="11295" xr2:uid="{62A58253-9505-4C17-A0D0-B4C12E04E8CC}"/>
+    <workbookView xWindow="7200" yWindow="4185" windowWidth="21600" windowHeight="11295" xr2:uid="{62A58253-9505-4C17-A0D0-B4C12E04E8CC}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -424,7 +424,7 @@
         <v>1</v>
       </c>
       <c r="I1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J1">
         <f>G1*20</f>
@@ -436,7 +436,7 @@
       </c>
       <c r="L1">
         <f t="shared" si="0"/>
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="M1">
         <v>0</v>
@@ -456,10 +456,10 @@
         <v>0</v>
       </c>
       <c r="B2">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C2">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="D2">
         <v>0</v>
@@ -477,42 +477,42 @@
         <v>1</v>
       </c>
       <c r="I2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J2">
-        <f t="shared" ref="J2" si="1">G2*20</f>
+        <f t="shared" ref="J2:J5" si="1">G2*20</f>
         <v>60</v>
       </c>
       <c r="K2">
-        <f t="shared" ref="K2" si="2">H2*20</f>
+        <f t="shared" ref="K2:K5" si="2">H2*20</f>
         <v>20</v>
       </c>
       <c r="L2">
-        <f t="shared" ref="L2" si="3">I2*20</f>
-        <v>20</v>
+        <f t="shared" ref="L2:L5" si="3">I2*20</f>
+        <v>60</v>
       </c>
       <c r="M2">
         <v>0</v>
       </c>
       <c r="N2">
-        <v>0</v>
+        <v>-400</v>
       </c>
       <c r="O2">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="P2">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A3">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="B3">
         <v>0</v>
       </c>
       <c r="C3">
-        <v>-20</v>
+        <v>0</v>
       </c>
       <c r="D3">
         <v>0</v>
@@ -530,22 +530,22 @@
         <v>1</v>
       </c>
       <c r="I3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J3">
-        <f>G3*20</f>
+        <f t="shared" si="1"/>
         <v>60</v>
       </c>
       <c r="K3">
-        <f t="shared" ref="K3:K6" si="4">H3*20</f>
+        <f t="shared" si="2"/>
         <v>20</v>
       </c>
       <c r="L3">
-        <f t="shared" ref="L3:L6" si="5">I3*20</f>
-        <v>20</v>
+        <f t="shared" si="3"/>
+        <v>60</v>
       </c>
       <c r="M3">
-        <v>0</v>
+        <v>160</v>
       </c>
       <c r="N3">
         <v>0</v>
@@ -554,18 +554,18 @@
         <v>0</v>
       </c>
       <c r="P3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A4">
-        <v>0</v>
+        <v>-60</v>
       </c>
       <c r="B4">
         <v>0</v>
       </c>
       <c r="C4">
-        <v>-40</v>
+        <v>0</v>
       </c>
       <c r="D4">
         <v>0</v>
@@ -583,22 +583,22 @@
         <v>1</v>
       </c>
       <c r="I4">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J4">
-        <f t="shared" ref="J4:J6" si="6">G4*20</f>
+        <f t="shared" si="1"/>
         <v>60</v>
       </c>
       <c r="K4">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>20</v>
       </c>
       <c r="L4">
-        <f t="shared" si="5"/>
-        <v>20</v>
+        <f t="shared" si="3"/>
+        <v>60</v>
       </c>
       <c r="M4">
-        <v>0</v>
+        <v>-260</v>
       </c>
       <c r="N4">
         <v>0</v>
@@ -607,7 +607,7 @@
         <v>0</v>
       </c>
       <c r="P4">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.4">
@@ -636,42 +636,42 @@
         <v>1</v>
       </c>
       <c r="I5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J5">
-        <f t="shared" si="6"/>
+        <f t="shared" si="1"/>
         <v>60</v>
       </c>
       <c r="K5">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>20</v>
       </c>
       <c r="L5">
-        <f t="shared" si="5"/>
-        <v>20</v>
+        <f t="shared" si="3"/>
+        <v>60</v>
       </c>
       <c r="M5">
         <v>0</v>
       </c>
       <c r="N5">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="O5">
-        <v>0</v>
+        <v>-60</v>
       </c>
       <c r="P5">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="B6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="C6">
-        <v>-80</v>
+        <v>1000</v>
       </c>
       <c r="D6">
         <v>0</v>
@@ -689,19 +689,19 @@
         <v>1</v>
       </c>
       <c r="I6">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J6">
-        <f t="shared" si="6"/>
+        <f t="shared" ref="J6:J69" si="4">G6*20</f>
         <v>60</v>
       </c>
       <c r="K6">
-        <f t="shared" si="4"/>
+        <f t="shared" ref="K6:K69" si="5">H6*20</f>
         <v>20</v>
       </c>
       <c r="L6">
-        <f t="shared" si="5"/>
-        <v>20</v>
+        <f t="shared" ref="L6:L69" si="6">I6*20</f>
+        <v>60</v>
       </c>
       <c r="M6">
         <v>0</v>
@@ -718,13 +718,13 @@
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="B7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="C7">
-        <v>-100</v>
+        <v>1000</v>
       </c>
       <c r="D7">
         <v>0</v>
@@ -742,19 +742,19 @@
         <v>1</v>
       </c>
       <c r="I7">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J7">
-        <f t="shared" ref="J7" si="7">G7*20</f>
+        <f t="shared" si="4"/>
         <v>60</v>
       </c>
       <c r="K7">
-        <f t="shared" ref="K7" si="8">H7*20</f>
+        <f t="shared" si="5"/>
         <v>20</v>
       </c>
       <c r="L7">
-        <f t="shared" ref="L7" si="9">I7*20</f>
-        <v>20</v>
+        <f t="shared" si="6"/>
+        <v>60</v>
       </c>
       <c r="M7">
         <v>0</v>
@@ -771,13 +771,13 @@
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A8">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="B8">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="C8">
-        <v>-140</v>
+        <v>1000</v>
       </c>
       <c r="D8">
         <v>0</v>
@@ -789,7 +789,7 @@
         <v>0</v>
       </c>
       <c r="G8">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H8">
         <v>1</v>
@@ -798,15 +798,15 @@
         <v>3</v>
       </c>
       <c r="J8">
-        <f t="shared" ref="J8:J9" si="10">G8*20</f>
-        <v>20</v>
+        <f t="shared" si="4"/>
+        <v>60</v>
       </c>
       <c r="K8">
-        <f t="shared" ref="K8" si="11">H8*20</f>
+        <f t="shared" si="5"/>
         <v>20</v>
       </c>
       <c r="L8">
-        <f t="shared" ref="L8" si="12">I8*20</f>
+        <f t="shared" si="6"/>
         <v>60</v>
       </c>
       <c r="M8">
@@ -824,13 +824,13 @@
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="B9">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="C9">
-        <v>-140</v>
+        <v>1000</v>
       </c>
       <c r="D9">
         <v>0</v>
@@ -842,7 +842,7 @@
         <v>0</v>
       </c>
       <c r="G9">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H9">
         <v>1</v>
@@ -851,15 +851,15 @@
         <v>3</v>
       </c>
       <c r="J9">
-        <f t="shared" si="10"/>
-        <v>20</v>
+        <f t="shared" si="4"/>
+        <v>60</v>
       </c>
       <c r="K9">
-        <f t="shared" ref="K9:K12" si="13">H9*20</f>
+        <f t="shared" si="5"/>
         <v>20</v>
       </c>
       <c r="L9">
-        <f t="shared" ref="L9:L12" si="14">I9*20</f>
+        <f t="shared" si="6"/>
         <v>60</v>
       </c>
       <c r="M9">
@@ -877,13 +877,13 @@
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A10">
-        <v>-20</v>
+        <v>1000</v>
       </c>
       <c r="B10">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="C10">
-        <v>-140</v>
+        <v>1000</v>
       </c>
       <c r="D10">
         <v>0</v>
@@ -895,7 +895,7 @@
         <v>0</v>
       </c>
       <c r="G10">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H10">
         <v>1</v>
@@ -904,15 +904,15 @@
         <v>3</v>
       </c>
       <c r="J10">
-        <f t="shared" ref="J10:J12" si="15">G10*20</f>
-        <v>20</v>
+        <f t="shared" si="4"/>
+        <v>60</v>
       </c>
       <c r="K10">
-        <f t="shared" si="13"/>
+        <f t="shared" si="5"/>
         <v>20</v>
       </c>
       <c r="L10">
-        <f t="shared" si="14"/>
+        <f t="shared" si="6"/>
         <v>60</v>
       </c>
       <c r="M10">
@@ -930,13 +930,13 @@
     </row>
     <row r="11" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A11">
-        <v>-40</v>
+        <v>1000</v>
       </c>
       <c r="B11">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="C11">
-        <v>-140</v>
+        <v>1000</v>
       </c>
       <c r="D11">
         <v>0</v>
@@ -948,7 +948,7 @@
         <v>0</v>
       </c>
       <c r="G11">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H11">
         <v>1</v>
@@ -957,15 +957,15 @@
         <v>3</v>
       </c>
       <c r="J11">
-        <f t="shared" si="15"/>
-        <v>20</v>
+        <f t="shared" si="4"/>
+        <v>60</v>
       </c>
       <c r="K11">
-        <f t="shared" si="13"/>
+        <f t="shared" si="5"/>
         <v>20</v>
       </c>
       <c r="L11">
-        <f t="shared" si="14"/>
+        <f t="shared" si="6"/>
         <v>60</v>
       </c>
       <c r="M11">
@@ -983,13 +983,13 @@
     </row>
     <row r="12" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A12">
-        <v>-60</v>
+        <v>1000</v>
       </c>
       <c r="B12">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="C12">
-        <v>-140</v>
+        <v>1000</v>
       </c>
       <c r="D12">
         <v>0</v>
@@ -1001,7 +1001,7 @@
         <v>0</v>
       </c>
       <c r="G12">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H12">
         <v>1</v>
@@ -1010,15 +1010,15 @@
         <v>3</v>
       </c>
       <c r="J12">
-        <f t="shared" si="15"/>
-        <v>20</v>
+        <f t="shared" si="4"/>
+        <v>60</v>
       </c>
       <c r="K12">
-        <f t="shared" si="13"/>
+        <f t="shared" si="5"/>
         <v>20</v>
       </c>
       <c r="L12">
-        <f t="shared" si="14"/>
+        <f t="shared" si="6"/>
         <v>60</v>
       </c>
       <c r="M12">
@@ -1036,13 +1036,13 @@
     </row>
     <row r="13" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A13">
-        <v>-80</v>
+        <v>1000</v>
       </c>
       <c r="B13">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="C13">
-        <v>-140</v>
+        <v>1000</v>
       </c>
       <c r="D13">
         <v>0</v>
@@ -1054,7 +1054,7 @@
         <v>0</v>
       </c>
       <c r="G13">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H13">
         <v>1</v>
@@ -1063,15 +1063,15 @@
         <v>3</v>
       </c>
       <c r="J13">
-        <f t="shared" ref="J13:J15" si="16">G13*20</f>
-        <v>20</v>
+        <f t="shared" si="4"/>
+        <v>60</v>
       </c>
       <c r="K13">
-        <f t="shared" ref="K13:K16" si="17">H13*20</f>
+        <f t="shared" si="5"/>
         <v>20</v>
       </c>
       <c r="L13">
-        <f t="shared" ref="L13:L16" si="18">I13*20</f>
+        <f t="shared" si="6"/>
         <v>60</v>
       </c>
       <c r="M13">
@@ -1089,13 +1089,13 @@
     </row>
     <row r="14" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A14">
-        <v>-100</v>
+        <v>1000</v>
       </c>
       <c r="B14">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="C14">
-        <v>-140</v>
+        <v>1000</v>
       </c>
       <c r="D14">
         <v>0</v>
@@ -1107,7 +1107,7 @@
         <v>0</v>
       </c>
       <c r="G14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H14">
         <v>1</v>
@@ -1116,15 +1116,15 @@
         <v>3</v>
       </c>
       <c r="J14">
-        <f t="shared" si="16"/>
-        <v>20</v>
+        <f t="shared" si="4"/>
+        <v>60</v>
       </c>
       <c r="K14">
-        <f t="shared" si="17"/>
+        <f t="shared" si="5"/>
         <v>20</v>
       </c>
       <c r="L14">
-        <f t="shared" si="18"/>
+        <f t="shared" si="6"/>
         <v>60</v>
       </c>
       <c r="M14">
@@ -1142,13 +1142,13 @@
     </row>
     <row r="15" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A15">
-        <v>-120</v>
+        <v>1000</v>
       </c>
       <c r="B15">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="C15">
-        <v>-140</v>
+        <v>1000</v>
       </c>
       <c r="D15">
         <v>0</v>
@@ -1160,7 +1160,7 @@
         <v>0</v>
       </c>
       <c r="G15">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H15">
         <v>1</v>
@@ -1169,15 +1169,15 @@
         <v>3</v>
       </c>
       <c r="J15">
-        <f t="shared" si="16"/>
-        <v>20</v>
+        <f t="shared" si="4"/>
+        <v>60</v>
       </c>
       <c r="K15">
-        <f t="shared" si="17"/>
+        <f t="shared" si="5"/>
         <v>20</v>
       </c>
       <c r="L15">
-        <f t="shared" si="18"/>
+        <f t="shared" si="6"/>
         <v>60</v>
       </c>
       <c r="M15">
@@ -1195,13 +1195,13 @@
     </row>
     <row r="16" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A16">
-        <v>-140</v>
+        <v>1000</v>
       </c>
       <c r="B16">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="C16">
-        <v>-140</v>
+        <v>1000</v>
       </c>
       <c r="D16">
         <v>0</v>
@@ -1213,7 +1213,7 @@
         <v>0</v>
       </c>
       <c r="G16">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H16">
         <v>1</v>
@@ -1222,15 +1222,15 @@
         <v>3</v>
       </c>
       <c r="J16">
-        <f t="shared" ref="J16:J18" si="19">G16*20</f>
-        <v>20</v>
+        <f t="shared" si="4"/>
+        <v>60</v>
       </c>
       <c r="K16">
-        <f t="shared" si="17"/>
+        <f t="shared" si="5"/>
         <v>20</v>
       </c>
       <c r="L16">
-        <f t="shared" si="18"/>
+        <f t="shared" si="6"/>
         <v>60</v>
       </c>
       <c r="M16">
@@ -1248,13 +1248,13 @@
     </row>
     <row r="17" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A17">
-        <v>-160</v>
+        <v>1000</v>
       </c>
       <c r="B17">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="C17">
-        <v>-140</v>
+        <v>1000</v>
       </c>
       <c r="D17">
         <v>0</v>
@@ -1266,7 +1266,7 @@
         <v>0</v>
       </c>
       <c r="G17">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H17">
         <v>1</v>
@@ -1275,15 +1275,15 @@
         <v>3</v>
       </c>
       <c r="J17">
-        <f t="shared" si="19"/>
-        <v>20</v>
+        <f t="shared" si="4"/>
+        <v>60</v>
       </c>
       <c r="K17">
-        <f t="shared" ref="K17:K20" si="20">H17*20</f>
+        <f t="shared" si="5"/>
         <v>20</v>
       </c>
       <c r="L17">
-        <f t="shared" ref="L17:L20" si="21">I17*20</f>
+        <f t="shared" si="6"/>
         <v>60</v>
       </c>
       <c r="M17">
@@ -1301,13 +1301,13 @@
     </row>
     <row r="18" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A18">
-        <v>-180</v>
+        <v>1000</v>
       </c>
       <c r="B18">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="C18">
-        <v>-140</v>
+        <v>1000</v>
       </c>
       <c r="D18">
         <v>0</v>
@@ -1319,7 +1319,7 @@
         <v>0</v>
       </c>
       <c r="G18">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H18">
         <v>1</v>
@@ -1328,15 +1328,15 @@
         <v>3</v>
       </c>
       <c r="J18">
-        <f t="shared" si="19"/>
-        <v>20</v>
+        <f t="shared" si="4"/>
+        <v>60</v>
       </c>
       <c r="K18">
-        <f t="shared" si="20"/>
+        <f t="shared" si="5"/>
         <v>20</v>
       </c>
       <c r="L18">
-        <f t="shared" si="21"/>
+        <f t="shared" si="6"/>
         <v>60</v>
       </c>
       <c r="M18">
@@ -1354,13 +1354,13 @@
     </row>
     <row r="19" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A19">
-        <v>-200</v>
+        <v>1000</v>
       </c>
       <c r="B19">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="C19">
-        <v>-140</v>
+        <v>1000</v>
       </c>
       <c r="D19">
         <v>0</v>
@@ -1372,7 +1372,7 @@
         <v>0</v>
       </c>
       <c r="G19">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H19">
         <v>1</v>
@@ -1381,15 +1381,15 @@
         <v>3</v>
       </c>
       <c r="J19">
-        <f t="shared" ref="J19:J21" si="22">G19*20</f>
-        <v>20</v>
+        <f t="shared" si="4"/>
+        <v>60</v>
       </c>
       <c r="K19">
-        <f t="shared" si="20"/>
+        <f t="shared" si="5"/>
         <v>20</v>
       </c>
       <c r="L19">
-        <f t="shared" si="21"/>
+        <f t="shared" si="6"/>
         <v>60</v>
       </c>
       <c r="M19">
@@ -1407,13 +1407,13 @@
     </row>
     <row r="20" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A20">
-        <v>-180</v>
+        <v>1000</v>
       </c>
       <c r="B20">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="C20">
-        <v>-180</v>
+        <v>1000</v>
       </c>
       <c r="D20">
         <v>0</v>
@@ -1431,19 +1431,19 @@
         <v>1</v>
       </c>
       <c r="I20">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J20">
-        <f t="shared" si="22"/>
+        <f t="shared" si="4"/>
         <v>60</v>
       </c>
       <c r="K20">
-        <f t="shared" si="20"/>
+        <f t="shared" si="5"/>
         <v>20</v>
       </c>
       <c r="L20">
-        <f t="shared" si="21"/>
-        <v>20</v>
+        <f t="shared" si="6"/>
+        <v>60</v>
       </c>
       <c r="M20">
         <v>0</v>
@@ -1460,13 +1460,13 @@
     </row>
     <row r="21" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A21">
-        <v>-180</v>
+        <v>1000</v>
       </c>
       <c r="B21">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="C21">
-        <v>-200</v>
+        <v>1000</v>
       </c>
       <c r="D21">
         <v>0</v>
@@ -1484,19 +1484,19 @@
         <v>1</v>
       </c>
       <c r="I21">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J21">
-        <f t="shared" si="22"/>
+        <f t="shared" si="4"/>
         <v>60</v>
       </c>
       <c r="K21">
-        <f t="shared" ref="K21:K24" si="23">H21*20</f>
+        <f t="shared" si="5"/>
         <v>20</v>
       </c>
       <c r="L21">
-        <f t="shared" ref="L21:L24" si="24">I21*20</f>
-        <v>20</v>
+        <f t="shared" si="6"/>
+        <v>60</v>
       </c>
       <c r="M21">
         <v>0</v>
@@ -1513,13 +1513,13 @@
     </row>
     <row r="22" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A22">
-        <v>-180</v>
+        <v>1000</v>
       </c>
       <c r="B22">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="C22">
-        <v>-220</v>
+        <v>1000</v>
       </c>
       <c r="D22">
         <v>0</v>
@@ -1537,19 +1537,19 @@
         <v>1</v>
       </c>
       <c r="I22">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J22">
-        <f t="shared" ref="J22:J24" si="25">G22*20</f>
+        <f t="shared" si="4"/>
         <v>60</v>
       </c>
       <c r="K22">
-        <f t="shared" si="23"/>
+        <f t="shared" si="5"/>
         <v>20</v>
       </c>
       <c r="L22">
-        <f t="shared" si="24"/>
-        <v>20</v>
+        <f t="shared" si="6"/>
+        <v>60</v>
       </c>
       <c r="M22">
         <v>0</v>
@@ -1566,13 +1566,13 @@
     </row>
     <row r="23" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A23">
-        <v>-180</v>
+        <v>1000</v>
       </c>
       <c r="B23">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="C23">
-        <v>-240</v>
+        <v>1000</v>
       </c>
       <c r="D23">
         <v>0</v>
@@ -1590,19 +1590,19 @@
         <v>1</v>
       </c>
       <c r="I23">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J23">
-        <f t="shared" si="25"/>
+        <f t="shared" si="4"/>
         <v>60</v>
       </c>
       <c r="K23">
-        <f t="shared" si="23"/>
+        <f t="shared" si="5"/>
         <v>20</v>
       </c>
       <c r="L23">
-        <f t="shared" si="24"/>
-        <v>20</v>
+        <f t="shared" si="6"/>
+        <v>60</v>
       </c>
       <c r="M23">
         <v>0</v>
@@ -1619,13 +1619,13 @@
     </row>
     <row r="24" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A24">
-        <v>-180</v>
+        <v>1000</v>
       </c>
       <c r="B24">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="C24">
-        <v>-260</v>
+        <v>1000</v>
       </c>
       <c r="D24">
         <v>0</v>
@@ -1643,19 +1643,19 @@
         <v>1</v>
       </c>
       <c r="I24">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J24">
-        <f t="shared" si="25"/>
+        <f t="shared" si="4"/>
         <v>60</v>
       </c>
       <c r="K24">
-        <f t="shared" si="23"/>
+        <f t="shared" si="5"/>
         <v>20</v>
       </c>
       <c r="L24">
-        <f t="shared" si="24"/>
-        <v>20</v>
+        <f t="shared" si="6"/>
+        <v>60</v>
       </c>
       <c r="M24">
         <v>0</v>
@@ -1672,13 +1672,13 @@
     </row>
     <row r="25" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A25">
-        <v>-200</v>
+        <v>1000</v>
       </c>
       <c r="B25">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="C25">
-        <v>-300</v>
+        <v>1000</v>
       </c>
       <c r="D25">
         <v>0</v>
@@ -1690,7 +1690,7 @@
         <v>0</v>
       </c>
       <c r="G25">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H25">
         <v>1</v>
@@ -1699,15 +1699,15 @@
         <v>3</v>
       </c>
       <c r="J25">
-        <f t="shared" ref="J25:J27" si="26">G25*20</f>
-        <v>20</v>
+        <f t="shared" si="4"/>
+        <v>60</v>
       </c>
       <c r="K25">
-        <f t="shared" ref="K25:K28" si="27">H25*20</f>
+        <f t="shared" si="5"/>
         <v>20</v>
       </c>
       <c r="L25">
-        <f t="shared" ref="L25:L28" si="28">I25*20</f>
+        <f t="shared" si="6"/>
         <v>60</v>
       </c>
       <c r="M25">
@@ -1725,13 +1725,13 @@
     </row>
     <row r="26" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A26">
-        <v>-180</v>
+        <v>1000</v>
       </c>
       <c r="B26">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="C26">
-        <v>-300</v>
+        <v>1000</v>
       </c>
       <c r="D26">
         <v>0</v>
@@ -1743,7 +1743,7 @@
         <v>0</v>
       </c>
       <c r="G26">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H26">
         <v>1</v>
@@ -1752,15 +1752,15 @@
         <v>3</v>
       </c>
       <c r="J26">
-        <f t="shared" si="26"/>
-        <v>20</v>
+        <f t="shared" si="4"/>
+        <v>60</v>
       </c>
       <c r="K26">
-        <f t="shared" si="27"/>
+        <f t="shared" si="5"/>
         <v>20</v>
       </c>
       <c r="L26">
-        <f t="shared" si="28"/>
+        <f t="shared" si="6"/>
         <v>60</v>
       </c>
       <c r="M26">
@@ -1778,13 +1778,13 @@
     </row>
     <row r="27" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A27">
-        <v>-160</v>
+        <v>1000</v>
       </c>
       <c r="B27">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="C27">
-        <v>-300</v>
+        <v>1000</v>
       </c>
       <c r="D27">
         <v>0</v>
@@ -1796,7 +1796,7 @@
         <v>0</v>
       </c>
       <c r="G27">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H27">
         <v>1</v>
@@ -1805,15 +1805,15 @@
         <v>3</v>
       </c>
       <c r="J27">
-        <f t="shared" si="26"/>
-        <v>20</v>
+        <f t="shared" si="4"/>
+        <v>60</v>
       </c>
       <c r="K27">
-        <f t="shared" si="27"/>
+        <f t="shared" si="5"/>
         <v>20</v>
       </c>
       <c r="L27">
-        <f t="shared" si="28"/>
+        <f t="shared" si="6"/>
         <v>60</v>
       </c>
       <c r="M27">
@@ -1831,13 +1831,13 @@
     </row>
     <row r="28" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A28">
-        <v>-140</v>
+        <v>1000</v>
       </c>
       <c r="B28">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="C28">
-        <v>-300</v>
+        <v>1000</v>
       </c>
       <c r="D28">
         <v>0</v>
@@ -1849,7 +1849,7 @@
         <v>0</v>
       </c>
       <c r="G28">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H28">
         <v>1</v>
@@ -1858,15 +1858,15 @@
         <v>3</v>
       </c>
       <c r="J28">
-        <f t="shared" ref="J28:J30" si="29">G28*20</f>
-        <v>20</v>
+        <f t="shared" si="4"/>
+        <v>60</v>
       </c>
       <c r="K28">
-        <f t="shared" si="27"/>
+        <f t="shared" si="5"/>
         <v>20</v>
       </c>
       <c r="L28">
-        <f t="shared" si="28"/>
+        <f t="shared" si="6"/>
         <v>60</v>
       </c>
       <c r="M28">
@@ -1884,13 +1884,13 @@
     </row>
     <row r="29" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A29">
-        <v>-120</v>
+        <v>1000</v>
       </c>
       <c r="B29">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="C29">
-        <v>-300</v>
+        <v>1000</v>
       </c>
       <c r="D29">
         <v>0</v>
@@ -1902,7 +1902,7 @@
         <v>0</v>
       </c>
       <c r="G29">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H29">
         <v>1</v>
@@ -1911,15 +1911,15 @@
         <v>3</v>
       </c>
       <c r="J29">
-        <f t="shared" si="29"/>
-        <v>20</v>
+        <f t="shared" si="4"/>
+        <v>60</v>
       </c>
       <c r="K29">
-        <f t="shared" ref="K29:K32" si="30">H29*20</f>
+        <f t="shared" si="5"/>
         <v>20</v>
       </c>
       <c r="L29">
-        <f t="shared" ref="L29:L32" si="31">I29*20</f>
+        <f t="shared" si="6"/>
         <v>60</v>
       </c>
       <c r="M29">
@@ -1937,13 +1937,13 @@
     </row>
     <row r="30" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A30">
-        <v>-100</v>
+        <v>1000</v>
       </c>
       <c r="B30">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="C30">
-        <v>-300</v>
+        <v>1000</v>
       </c>
       <c r="D30">
         <v>0</v>
@@ -1955,7 +1955,7 @@
         <v>0</v>
       </c>
       <c r="G30">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H30">
         <v>1</v>
@@ -1964,15 +1964,15 @@
         <v>3</v>
       </c>
       <c r="J30">
-        <f t="shared" si="29"/>
-        <v>20</v>
+        <f t="shared" si="4"/>
+        <v>60</v>
       </c>
       <c r="K30">
-        <f t="shared" si="30"/>
+        <f t="shared" si="5"/>
         <v>20</v>
       </c>
       <c r="L30">
-        <f t="shared" si="31"/>
+        <f t="shared" si="6"/>
         <v>60</v>
       </c>
       <c r="M30">
@@ -1990,13 +1990,13 @@
     </row>
     <row r="31" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A31">
-        <v>-60</v>
+        <v>1000</v>
       </c>
       <c r="B31">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="C31">
-        <v>-300</v>
+        <v>1000</v>
       </c>
       <c r="D31">
         <v>0</v>
@@ -2008,7 +2008,7 @@
         <v>0</v>
       </c>
       <c r="G31">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H31">
         <v>1</v>
@@ -2017,15 +2017,15 @@
         <v>3</v>
       </c>
       <c r="J31">
-        <f t="shared" ref="J31:J33" si="32">G31*20</f>
-        <v>20</v>
+        <f t="shared" si="4"/>
+        <v>60</v>
       </c>
       <c r="K31">
-        <f t="shared" si="30"/>
+        <f t="shared" si="5"/>
         <v>20</v>
       </c>
       <c r="L31">
-        <f t="shared" si="31"/>
+        <f t="shared" si="6"/>
         <v>60</v>
       </c>
       <c r="M31">
@@ -2043,13 +2043,13 @@
     </row>
     <row r="32" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A32">
-        <v>-40</v>
+        <v>1000</v>
       </c>
       <c r="B32">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="C32">
-        <v>-300</v>
+        <v>1000</v>
       </c>
       <c r="D32">
         <v>0</v>
@@ -2061,7 +2061,7 @@
         <v>0</v>
       </c>
       <c r="G32">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H32">
         <v>1</v>
@@ -2070,15 +2070,15 @@
         <v>3</v>
       </c>
       <c r="J32">
-        <f t="shared" si="32"/>
-        <v>20</v>
+        <f t="shared" si="4"/>
+        <v>60</v>
       </c>
       <c r="K32">
-        <f t="shared" si="30"/>
+        <f t="shared" si="5"/>
         <v>20</v>
       </c>
       <c r="L32">
-        <f t="shared" si="31"/>
+        <f t="shared" si="6"/>
         <v>60</v>
       </c>
       <c r="M32">
@@ -2096,13 +2096,13 @@
     </row>
     <row r="33" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A33">
-        <v>-20</v>
+        <v>1000</v>
       </c>
       <c r="B33">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="C33">
-        <v>-300</v>
+        <v>1000</v>
       </c>
       <c r="D33">
         <v>0</v>
@@ -2114,7 +2114,7 @@
         <v>0</v>
       </c>
       <c r="G33">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H33">
         <v>1</v>
@@ -2123,15 +2123,15 @@
         <v>3</v>
       </c>
       <c r="J33">
-        <f t="shared" si="32"/>
-        <v>20</v>
+        <f t="shared" si="4"/>
+        <v>60</v>
       </c>
       <c r="K33">
-        <f t="shared" ref="K33:K36" si="33">H33*20</f>
+        <f t="shared" si="5"/>
         <v>20</v>
       </c>
       <c r="L33">
-        <f t="shared" ref="L33:L36" si="34">I33*20</f>
+        <f t="shared" si="6"/>
         <v>60</v>
       </c>
       <c r="M33">
@@ -2149,13 +2149,13 @@
     </row>
     <row r="34" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A34">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="B34">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="C34">
-        <v>-300</v>
+        <v>1000</v>
       </c>
       <c r="D34">
         <v>0</v>
@@ -2167,7 +2167,7 @@
         <v>0</v>
       </c>
       <c r="G34">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H34">
         <v>1</v>
@@ -2176,15 +2176,15 @@
         <v>3</v>
       </c>
       <c r="J34">
-        <f t="shared" ref="J34:J36" si="35">G34*20</f>
-        <v>20</v>
+        <f t="shared" si="4"/>
+        <v>60</v>
       </c>
       <c r="K34">
-        <f t="shared" si="33"/>
+        <f t="shared" si="5"/>
         <v>20</v>
       </c>
       <c r="L34">
-        <f t="shared" si="34"/>
+        <f t="shared" si="6"/>
         <v>60</v>
       </c>
       <c r="M34">
@@ -2202,13 +2202,13 @@
     </row>
     <row r="35" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A35">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="B35">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="C35">
-        <v>-300</v>
+        <v>1000</v>
       </c>
       <c r="D35">
         <v>0</v>
@@ -2220,7 +2220,7 @@
         <v>0</v>
       </c>
       <c r="G35">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H35">
         <v>1</v>
@@ -2229,15 +2229,15 @@
         <v>3</v>
       </c>
       <c r="J35">
-        <f t="shared" si="35"/>
-        <v>20</v>
+        <f t="shared" si="4"/>
+        <v>60</v>
       </c>
       <c r="K35">
-        <f t="shared" si="33"/>
+        <f t="shared" si="5"/>
         <v>20</v>
       </c>
       <c r="L35">
-        <f t="shared" si="34"/>
+        <f t="shared" si="6"/>
         <v>60</v>
       </c>
       <c r="M35">
@@ -2255,13 +2255,13 @@
     </row>
     <row r="36" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A36">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="B36">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="C36">
-        <v>-300</v>
+        <v>1000</v>
       </c>
       <c r="D36">
         <v>0</v>
@@ -2273,7 +2273,7 @@
         <v>0</v>
       </c>
       <c r="G36">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H36">
         <v>1</v>
@@ -2282,15 +2282,15 @@
         <v>3</v>
       </c>
       <c r="J36">
-        <f t="shared" si="35"/>
-        <v>20</v>
+        <f t="shared" si="4"/>
+        <v>60</v>
       </c>
       <c r="K36">
-        <f t="shared" si="33"/>
+        <f t="shared" si="5"/>
         <v>20</v>
       </c>
       <c r="L36">
-        <f t="shared" si="34"/>
+        <f t="shared" si="6"/>
         <v>60</v>
       </c>
       <c r="M36">
@@ -2308,13 +2308,13 @@
     </row>
     <row r="37" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A37">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="B37">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="C37">
-        <v>-300</v>
+        <v>1000</v>
       </c>
       <c r="D37">
         <v>0</v>
@@ -2326,7 +2326,7 @@
         <v>0</v>
       </c>
       <c r="G37">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H37">
         <v>1</v>
@@ -2335,15 +2335,15 @@
         <v>3</v>
       </c>
       <c r="J37">
-        <f t="shared" ref="J37:J100" si="36">G37*20</f>
-        <v>20</v>
+        <f t="shared" si="4"/>
+        <v>60</v>
       </c>
       <c r="K37">
-        <f t="shared" ref="K37:K100" si="37">H37*20</f>
+        <f t="shared" si="5"/>
         <v>20</v>
       </c>
       <c r="L37">
-        <f t="shared" ref="L37:L100" si="38">I37*20</f>
+        <f t="shared" si="6"/>
         <v>60</v>
       </c>
       <c r="M37">
@@ -2361,13 +2361,13 @@
     </row>
     <row r="38" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A38">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="B38">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="C38">
-        <v>-300</v>
+        <v>1000</v>
       </c>
       <c r="D38">
         <v>0</v>
@@ -2379,7 +2379,7 @@
         <v>0</v>
       </c>
       <c r="G38">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H38">
         <v>1</v>
@@ -2388,15 +2388,15 @@
         <v>3</v>
       </c>
       <c r="J38">
-        <f t="shared" si="36"/>
-        <v>20</v>
+        <f t="shared" si="4"/>
+        <v>60</v>
       </c>
       <c r="K38">
-        <f t="shared" si="37"/>
+        <f t="shared" si="5"/>
         <v>20</v>
       </c>
       <c r="L38">
-        <f t="shared" si="38"/>
+        <f t="shared" si="6"/>
         <v>60</v>
       </c>
       <c r="M38">
@@ -2414,13 +2414,13 @@
     </row>
     <row r="39" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A39">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="B39">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="C39">
-        <v>-300</v>
+        <v>1000</v>
       </c>
       <c r="D39">
         <v>0</v>
@@ -2432,7 +2432,7 @@
         <v>0</v>
       </c>
       <c r="G39">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H39">
         <v>1</v>
@@ -2441,15 +2441,15 @@
         <v>3</v>
       </c>
       <c r="J39">
-        <f t="shared" si="36"/>
-        <v>20</v>
+        <f t="shared" si="4"/>
+        <v>60</v>
       </c>
       <c r="K39">
-        <f t="shared" si="37"/>
+        <f t="shared" si="5"/>
         <v>20</v>
       </c>
       <c r="L39">
-        <f t="shared" si="38"/>
+        <f t="shared" si="6"/>
         <v>60</v>
       </c>
       <c r="M39">
@@ -2467,13 +2467,13 @@
     </row>
     <row r="40" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A40">
-        <v>180</v>
+        <v>1000</v>
       </c>
       <c r="B40">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="C40">
-        <v>-300</v>
+        <v>1000</v>
       </c>
       <c r="D40">
         <v>0</v>
@@ -2485,7 +2485,7 @@
         <v>0</v>
       </c>
       <c r="G40">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H40">
         <v>1</v>
@@ -2494,15 +2494,15 @@
         <v>3</v>
       </c>
       <c r="J40">
-        <f t="shared" si="36"/>
-        <v>20</v>
+        <f t="shared" si="4"/>
+        <v>60</v>
       </c>
       <c r="K40">
-        <f t="shared" si="37"/>
+        <f t="shared" si="5"/>
         <v>20</v>
       </c>
       <c r="L40">
-        <f t="shared" si="38"/>
+        <f t="shared" si="6"/>
         <v>60</v>
       </c>
       <c r="M40">
@@ -2520,13 +2520,13 @@
     </row>
     <row r="41" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A41">
-        <v>200</v>
+        <v>1000</v>
       </c>
       <c r="B41">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="C41">
-        <v>-300</v>
+        <v>1000</v>
       </c>
       <c r="D41">
         <v>0</v>
@@ -2538,7 +2538,7 @@
         <v>0</v>
       </c>
       <c r="G41">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H41">
         <v>1</v>
@@ -2547,15 +2547,15 @@
         <v>3</v>
       </c>
       <c r="J41">
-        <f t="shared" si="36"/>
-        <v>20</v>
+        <f t="shared" si="4"/>
+        <v>60</v>
       </c>
       <c r="K41">
-        <f t="shared" si="37"/>
+        <f t="shared" si="5"/>
         <v>20</v>
       </c>
       <c r="L41">
-        <f t="shared" si="38"/>
+        <f t="shared" si="6"/>
         <v>60</v>
       </c>
       <c r="M41">
@@ -2573,13 +2573,13 @@
     </row>
     <row r="42" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A42">
-        <v>220</v>
+        <v>1000</v>
       </c>
       <c r="B42">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="C42">
-        <v>-300</v>
+        <v>1000</v>
       </c>
       <c r="D42">
         <v>0</v>
@@ -2591,7 +2591,7 @@
         <v>0</v>
       </c>
       <c r="G42">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H42">
         <v>1</v>
@@ -2600,15 +2600,15 @@
         <v>3</v>
       </c>
       <c r="J42">
-        <f t="shared" si="36"/>
-        <v>20</v>
+        <f t="shared" si="4"/>
+        <v>60</v>
       </c>
       <c r="K42">
-        <f t="shared" si="37"/>
+        <f t="shared" si="5"/>
         <v>20</v>
       </c>
       <c r="L42">
-        <f t="shared" si="38"/>
+        <f t="shared" si="6"/>
         <v>60</v>
       </c>
       <c r="M42">
@@ -2626,13 +2626,13 @@
     </row>
     <row r="43" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A43">
-        <v>260</v>
+        <v>1000</v>
       </c>
       <c r="B43">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="C43">
-        <v>-320</v>
+        <v>1000</v>
       </c>
       <c r="D43">
         <v>0</v>
@@ -2650,19 +2650,19 @@
         <v>1</v>
       </c>
       <c r="I43">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J43">
-        <f t="shared" si="36"/>
+        <f t="shared" si="4"/>
         <v>60</v>
       </c>
       <c r="K43">
-        <f t="shared" si="37"/>
+        <f t="shared" si="5"/>
         <v>20</v>
       </c>
       <c r="L43">
-        <f t="shared" si="38"/>
-        <v>20</v>
+        <f t="shared" si="6"/>
+        <v>60</v>
       </c>
       <c r="M43">
         <v>0</v>
@@ -2679,13 +2679,13 @@
     </row>
     <row r="44" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A44">
-        <v>260</v>
+        <v>1000</v>
       </c>
       <c r="B44">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="C44">
-        <v>-300</v>
+        <v>1000</v>
       </c>
       <c r="D44">
         <v>0</v>
@@ -2703,19 +2703,19 @@
         <v>1</v>
       </c>
       <c r="I44">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J44">
-        <f t="shared" si="36"/>
+        <f t="shared" si="4"/>
         <v>60</v>
       </c>
       <c r="K44">
-        <f t="shared" si="37"/>
+        <f t="shared" si="5"/>
         <v>20</v>
       </c>
       <c r="L44">
-        <f t="shared" si="38"/>
-        <v>20</v>
+        <f t="shared" si="6"/>
+        <v>60</v>
       </c>
       <c r="M44">
         <v>0</v>
@@ -2732,13 +2732,13 @@
     </row>
     <row r="45" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A45">
-        <v>260</v>
+        <v>1000</v>
       </c>
       <c r="B45">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="C45">
-        <v>-280</v>
+        <v>1000</v>
       </c>
       <c r="D45">
         <v>0</v>
@@ -2756,19 +2756,19 @@
         <v>1</v>
       </c>
       <c r="I45">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J45">
-        <f t="shared" si="36"/>
+        <f t="shared" si="4"/>
         <v>60</v>
       </c>
       <c r="K45">
-        <f t="shared" si="37"/>
+        <f t="shared" si="5"/>
         <v>20</v>
       </c>
       <c r="L45">
-        <f t="shared" si="38"/>
-        <v>20</v>
+        <f t="shared" si="6"/>
+        <v>60</v>
       </c>
       <c r="M45">
         <v>0</v>
@@ -2785,13 +2785,13 @@
     </row>
     <row r="46" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A46">
-        <v>260</v>
+        <v>1000</v>
       </c>
       <c r="B46">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="C46">
-        <v>-260</v>
+        <v>1000</v>
       </c>
       <c r="D46">
         <v>0</v>
@@ -2809,19 +2809,19 @@
         <v>1</v>
       </c>
       <c r="I46">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J46">
-        <f t="shared" si="36"/>
+        <f t="shared" si="4"/>
         <v>60</v>
       </c>
       <c r="K46">
-        <f t="shared" si="37"/>
+        <f t="shared" si="5"/>
         <v>20</v>
       </c>
       <c r="L46">
-        <f t="shared" si="38"/>
-        <v>20</v>
+        <f t="shared" si="6"/>
+        <v>60</v>
       </c>
       <c r="M46">
         <v>0</v>
@@ -2838,13 +2838,13 @@
     </row>
     <row r="47" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A47">
-        <v>260</v>
+        <v>1000</v>
       </c>
       <c r="B47">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="C47">
-        <v>-240</v>
+        <v>1000</v>
       </c>
       <c r="D47">
         <v>0</v>
@@ -2862,19 +2862,19 @@
         <v>1</v>
       </c>
       <c r="I47">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J47">
-        <f t="shared" si="36"/>
+        <f t="shared" si="4"/>
         <v>60</v>
       </c>
       <c r="K47">
-        <f t="shared" si="37"/>
+        <f t="shared" si="5"/>
         <v>20</v>
       </c>
       <c r="L47">
-        <f t="shared" si="38"/>
-        <v>20</v>
+        <f t="shared" si="6"/>
+        <v>60</v>
       </c>
       <c r="M47">
         <v>0</v>
@@ -2891,13 +2891,13 @@
     </row>
     <row r="48" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A48">
-        <v>260</v>
+        <v>1000</v>
       </c>
       <c r="B48">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="C48">
-        <v>-220</v>
+        <v>1000</v>
       </c>
       <c r="D48">
         <v>0</v>
@@ -2915,19 +2915,19 @@
         <v>1</v>
       </c>
       <c r="I48">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J48">
-        <f t="shared" si="36"/>
+        <f t="shared" si="4"/>
         <v>60</v>
       </c>
       <c r="K48">
-        <f t="shared" si="37"/>
+        <f t="shared" si="5"/>
         <v>20</v>
       </c>
       <c r="L48">
-        <f t="shared" si="38"/>
-        <v>20</v>
+        <f t="shared" si="6"/>
+        <v>60</v>
       </c>
       <c r="M48">
         <v>0</v>
@@ -2944,13 +2944,13 @@
     </row>
     <row r="49" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A49">
-        <v>260</v>
+        <v>1000</v>
       </c>
       <c r="B49">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="C49">
-        <v>-200</v>
+        <v>1000</v>
       </c>
       <c r="D49">
         <v>0</v>
@@ -2968,19 +2968,19 @@
         <v>1</v>
       </c>
       <c r="I49">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J49">
-        <f t="shared" si="36"/>
+        <f t="shared" si="4"/>
         <v>60</v>
       </c>
       <c r="K49">
-        <f t="shared" si="37"/>
+        <f t="shared" si="5"/>
         <v>20</v>
       </c>
       <c r="L49">
-        <f t="shared" si="38"/>
-        <v>20</v>
+        <f t="shared" si="6"/>
+        <v>60</v>
       </c>
       <c r="M49">
         <v>0</v>
@@ -2997,13 +2997,13 @@
     </row>
     <row r="50" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A50">
-        <v>260</v>
+        <v>1000</v>
       </c>
       <c r="B50">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="C50">
-        <v>-180</v>
+        <v>1000</v>
       </c>
       <c r="D50">
         <v>0</v>
@@ -3021,19 +3021,19 @@
         <v>1</v>
       </c>
       <c r="I50">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J50">
-        <f t="shared" si="36"/>
+        <f t="shared" si="4"/>
         <v>60</v>
       </c>
       <c r="K50">
-        <f t="shared" si="37"/>
+        <f t="shared" si="5"/>
         <v>20</v>
       </c>
       <c r="L50">
-        <f t="shared" si="38"/>
-        <v>20</v>
+        <f t="shared" si="6"/>
+        <v>60</v>
       </c>
       <c r="M50">
         <v>0</v>
@@ -3050,13 +3050,13 @@
     </row>
     <row r="51" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A51">
-        <v>260</v>
+        <v>1000</v>
       </c>
       <c r="B51">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="C51">
-        <v>-160</v>
+        <v>1000</v>
       </c>
       <c r="D51">
         <v>0</v>
@@ -3074,19 +3074,19 @@
         <v>1</v>
       </c>
       <c r="I51">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J51">
-        <f t="shared" si="36"/>
+        <f t="shared" si="4"/>
         <v>60</v>
       </c>
       <c r="K51">
-        <f t="shared" si="37"/>
+        <f t="shared" si="5"/>
         <v>20</v>
       </c>
       <c r="L51">
-        <f t="shared" si="38"/>
-        <v>20</v>
+        <f t="shared" si="6"/>
+        <v>60</v>
       </c>
       <c r="M51">
         <v>0</v>
@@ -3103,13 +3103,13 @@
     </row>
     <row r="52" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A52">
-        <v>340</v>
+        <v>1000</v>
       </c>
       <c r="B52">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="C52">
-        <v>-120</v>
+        <v>1000</v>
       </c>
       <c r="D52">
         <v>0</v>
@@ -3127,19 +3127,19 @@
         <v>1</v>
       </c>
       <c r="I52">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J52">
-        <f t="shared" si="36"/>
+        <f t="shared" si="4"/>
         <v>60</v>
       </c>
       <c r="K52">
-        <f t="shared" si="37"/>
+        <f t="shared" si="5"/>
         <v>20</v>
       </c>
       <c r="L52">
-        <f t="shared" si="38"/>
-        <v>20</v>
+        <f t="shared" si="6"/>
+        <v>60</v>
       </c>
       <c r="M52">
         <v>0</v>
@@ -3156,13 +3156,13 @@
     </row>
     <row r="53" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A53">
-        <v>340</v>
+        <v>1000</v>
       </c>
       <c r="B53">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="C53">
-        <v>-100</v>
+        <v>1000</v>
       </c>
       <c r="D53">
         <v>0</v>
@@ -3180,19 +3180,19 @@
         <v>1</v>
       </c>
       <c r="I53">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J53">
-        <f t="shared" si="36"/>
+        <f t="shared" si="4"/>
         <v>60</v>
       </c>
       <c r="K53">
-        <f t="shared" si="37"/>
+        <f t="shared" si="5"/>
         <v>20</v>
       </c>
       <c r="L53">
-        <f t="shared" si="38"/>
-        <v>20</v>
+        <f t="shared" si="6"/>
+        <v>60</v>
       </c>
       <c r="M53">
         <v>0</v>
@@ -3209,13 +3209,13 @@
     </row>
     <row r="54" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A54">
-        <v>340</v>
+        <v>1000</v>
       </c>
       <c r="B54">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="C54">
-        <v>-80</v>
+        <v>1000</v>
       </c>
       <c r="D54">
         <v>0</v>
@@ -3233,19 +3233,19 @@
         <v>1</v>
       </c>
       <c r="I54">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J54">
-        <f t="shared" si="36"/>
+        <f t="shared" si="4"/>
         <v>60</v>
       </c>
       <c r="K54">
-        <f t="shared" si="37"/>
+        <f t="shared" si="5"/>
         <v>20</v>
       </c>
       <c r="L54">
-        <f t="shared" si="38"/>
-        <v>20</v>
+        <f t="shared" si="6"/>
+        <v>60</v>
       </c>
       <c r="M54">
         <v>0</v>
@@ -3262,13 +3262,13 @@
     </row>
     <row r="55" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A55">
-        <v>420</v>
+        <v>1000</v>
       </c>
       <c r="B55">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="C55">
-        <v>-40</v>
+        <v>1000</v>
       </c>
       <c r="D55">
         <v>0</v>
@@ -3286,19 +3286,19 @@
         <v>1</v>
       </c>
       <c r="I55">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J55">
-        <f t="shared" si="36"/>
+        <f t="shared" si="4"/>
         <v>60</v>
       </c>
       <c r="K55">
-        <f t="shared" si="37"/>
+        <f t="shared" si="5"/>
         <v>20</v>
       </c>
       <c r="L55">
-        <f t="shared" si="38"/>
-        <v>20</v>
+        <f t="shared" si="6"/>
+        <v>60</v>
       </c>
       <c r="M55">
         <v>0</v>
@@ -3315,13 +3315,13 @@
     </row>
     <row r="56" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A56">
-        <v>420</v>
+        <v>1000</v>
       </c>
       <c r="B56">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="C56">
-        <v>-20</v>
+        <v>1000</v>
       </c>
       <c r="D56">
         <v>0</v>
@@ -3339,19 +3339,19 @@
         <v>1</v>
       </c>
       <c r="I56">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J56">
-        <f t="shared" si="36"/>
+        <f t="shared" si="4"/>
         <v>60</v>
       </c>
       <c r="K56">
-        <f t="shared" si="37"/>
+        <f t="shared" si="5"/>
         <v>20</v>
       </c>
       <c r="L56">
-        <f t="shared" si="38"/>
-        <v>20</v>
+        <f t="shared" si="6"/>
+        <v>60</v>
       </c>
       <c r="M56">
         <v>0</v>
@@ -3368,13 +3368,13 @@
     </row>
     <row r="57" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A57">
-        <v>420</v>
+        <v>1000</v>
       </c>
       <c r="B57">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="C57">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="D57">
         <v>0</v>
@@ -3392,19 +3392,19 @@
         <v>1</v>
       </c>
       <c r="I57">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J57">
-        <f t="shared" si="36"/>
+        <f t="shared" si="4"/>
         <v>60</v>
       </c>
       <c r="K57">
-        <f t="shared" si="37"/>
+        <f t="shared" si="5"/>
         <v>20</v>
       </c>
       <c r="L57">
-        <f t="shared" si="38"/>
-        <v>20</v>
+        <f t="shared" si="6"/>
+        <v>60</v>
       </c>
       <c r="M57">
         <v>0</v>
@@ -3421,13 +3421,13 @@
     </row>
     <row r="58" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A58">
-        <v>420</v>
+        <v>1000</v>
       </c>
       <c r="B58">
-        <v>160</v>
+        <v>1000</v>
       </c>
       <c r="C58">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="D58">
         <v>0</v>
@@ -3445,19 +3445,19 @@
         <v>1</v>
       </c>
       <c r="I58">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J58">
-        <f t="shared" si="36"/>
+        <f t="shared" si="4"/>
         <v>60</v>
       </c>
       <c r="K58">
-        <f t="shared" si="37"/>
+        <f t="shared" si="5"/>
         <v>20</v>
       </c>
       <c r="L58">
-        <f t="shared" si="38"/>
-        <v>20</v>
+        <f t="shared" si="6"/>
+        <v>60</v>
       </c>
       <c r="M58">
         <v>0</v>
@@ -3474,13 +3474,13 @@
     </row>
     <row r="59" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A59">
-        <v>420</v>
+        <v>1000</v>
       </c>
       <c r="B59">
-        <v>160</v>
+        <v>1000</v>
       </c>
       <c r="C59">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="D59">
         <v>0</v>
@@ -3498,19 +3498,19 @@
         <v>1</v>
       </c>
       <c r="I59">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J59">
-        <f t="shared" si="36"/>
+        <f t="shared" si="4"/>
         <v>60</v>
       </c>
       <c r="K59">
-        <f t="shared" si="37"/>
+        <f t="shared" si="5"/>
         <v>20</v>
       </c>
       <c r="L59">
-        <f t="shared" si="38"/>
-        <v>20</v>
+        <f t="shared" si="6"/>
+        <v>60</v>
       </c>
       <c r="M59">
         <v>0</v>
@@ -3527,13 +3527,13 @@
     </row>
     <row r="60" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A60">
-        <v>420</v>
+        <v>1000</v>
       </c>
       <c r="B60">
-        <v>160</v>
+        <v>1000</v>
       </c>
       <c r="C60">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="D60">
         <v>0</v>
@@ -3551,19 +3551,19 @@
         <v>1</v>
       </c>
       <c r="I60">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J60">
-        <f t="shared" si="36"/>
+        <f t="shared" si="4"/>
         <v>60</v>
       </c>
       <c r="K60">
-        <f t="shared" si="37"/>
+        <f t="shared" si="5"/>
         <v>20</v>
       </c>
       <c r="L60">
-        <f t="shared" si="38"/>
-        <v>20</v>
+        <f t="shared" si="6"/>
+        <v>60</v>
       </c>
       <c r="M60">
         <v>0</v>
@@ -3580,13 +3580,13 @@
     </row>
     <row r="61" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A61">
-        <v>420</v>
+        <v>1000</v>
       </c>
       <c r="B61">
-        <v>180</v>
+        <v>1000</v>
       </c>
       <c r="C61">
-        <v>160</v>
+        <v>1000</v>
       </c>
       <c r="D61">
         <v>0</v>
@@ -3604,19 +3604,19 @@
         <v>1</v>
       </c>
       <c r="I61">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J61">
-        <f t="shared" si="36"/>
+        <f t="shared" si="4"/>
         <v>60</v>
       </c>
       <c r="K61">
-        <f t="shared" si="37"/>
+        <f t="shared" si="5"/>
         <v>20</v>
       </c>
       <c r="L61">
-        <f t="shared" si="38"/>
-        <v>20</v>
+        <f t="shared" si="6"/>
+        <v>60</v>
       </c>
       <c r="M61">
         <v>0</v>
@@ -3633,13 +3633,13 @@
     </row>
     <row r="62" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A62">
-        <v>420</v>
+        <v>1000</v>
       </c>
       <c r="B62">
-        <v>180</v>
+        <v>1000</v>
       </c>
       <c r="C62">
-        <v>180</v>
+        <v>1000</v>
       </c>
       <c r="D62">
         <v>0</v>
@@ -3657,19 +3657,19 @@
         <v>1</v>
       </c>
       <c r="I62">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J62">
-        <f t="shared" si="36"/>
+        <f t="shared" si="4"/>
         <v>60</v>
       </c>
       <c r="K62">
-        <f t="shared" si="37"/>
+        <f t="shared" si="5"/>
         <v>20</v>
       </c>
       <c r="L62">
-        <f t="shared" si="38"/>
-        <v>20</v>
+        <f t="shared" si="6"/>
+        <v>60</v>
       </c>
       <c r="M62">
         <v>0</v>
@@ -3686,13 +3686,13 @@
     </row>
     <row r="63" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A63">
-        <v>420</v>
+        <v>1000</v>
       </c>
       <c r="B63">
-        <v>180</v>
+        <v>1000</v>
       </c>
       <c r="C63">
-        <v>200</v>
+        <v>1000</v>
       </c>
       <c r="D63">
         <v>0</v>
@@ -3710,19 +3710,19 @@
         <v>1</v>
       </c>
       <c r="I63">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J63">
-        <f t="shared" si="36"/>
+        <f t="shared" si="4"/>
         <v>60</v>
       </c>
       <c r="K63">
-        <f t="shared" si="37"/>
+        <f t="shared" si="5"/>
         <v>20</v>
       </c>
       <c r="L63">
-        <f t="shared" si="38"/>
-        <v>20</v>
+        <f t="shared" si="6"/>
+        <v>60</v>
       </c>
       <c r="M63">
         <v>0</v>
@@ -3739,13 +3739,13 @@
     </row>
     <row r="64" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A64">
-        <v>420</v>
+        <v>1000</v>
       </c>
       <c r="B64">
-        <v>180</v>
+        <v>1000</v>
       </c>
       <c r="C64">
-        <v>240</v>
+        <v>1000</v>
       </c>
       <c r="D64">
         <v>0</v>
@@ -3766,39 +3766,39 @@
         <v>3</v>
       </c>
       <c r="J64">
-        <f t="shared" si="36"/>
+        <f t="shared" si="4"/>
         <v>60</v>
       </c>
       <c r="K64">
-        <f t="shared" si="37"/>
+        <f t="shared" si="5"/>
         <v>20</v>
       </c>
       <c r="L64">
-        <f t="shared" si="38"/>
+        <f t="shared" si="6"/>
         <v>60</v>
       </c>
       <c r="M64">
-        <v>420</v>
+        <v>0</v>
       </c>
       <c r="N64">
-        <v>280</v>
+        <v>0</v>
       </c>
       <c r="O64">
-        <v>240</v>
+        <v>0</v>
       </c>
       <c r="P64">
-        <v>0.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="65" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A65">
-        <v>420</v>
+        <v>1000</v>
       </c>
       <c r="B65">
-        <v>280</v>
+        <v>1000</v>
       </c>
       <c r="C65">
-        <v>300</v>
+        <v>1000</v>
       </c>
       <c r="D65">
         <v>0</v>
@@ -3819,15 +3819,15 @@
         <v>3</v>
       </c>
       <c r="J65">
-        <f t="shared" si="36"/>
+        <f t="shared" si="4"/>
         <v>60</v>
       </c>
       <c r="K65">
-        <f t="shared" si="37"/>
+        <f t="shared" si="5"/>
         <v>20</v>
       </c>
       <c r="L65">
-        <f t="shared" si="38"/>
+        <f t="shared" si="6"/>
         <v>60</v>
       </c>
       <c r="M65">
@@ -3845,13 +3845,13 @@
     </row>
     <row r="66" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A66">
-        <v>360</v>
+        <v>1000</v>
       </c>
       <c r="B66">
-        <v>280</v>
+        <v>1000</v>
       </c>
       <c r="C66">
-        <v>300</v>
+        <v>1000</v>
       </c>
       <c r="D66">
         <v>0</v>
@@ -3872,39 +3872,39 @@
         <v>3</v>
       </c>
       <c r="J66">
-        <f t="shared" si="36"/>
+        <f t="shared" si="4"/>
         <v>60</v>
       </c>
       <c r="K66">
-        <f t="shared" si="37"/>
+        <f t="shared" si="5"/>
         <v>20</v>
       </c>
       <c r="L66">
-        <f t="shared" si="38"/>
+        <f t="shared" si="6"/>
         <v>60</v>
       </c>
       <c r="M66">
-        <v>160</v>
+        <v>0</v>
       </c>
       <c r="N66">
-        <v>280</v>
+        <v>0</v>
       </c>
       <c r="O66">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="P66">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="67" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A67">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="B67">
-        <v>280</v>
+        <v>1000</v>
       </c>
       <c r="C67">
-        <v>300</v>
+        <v>1000</v>
       </c>
       <c r="D67">
         <v>0</v>
@@ -3916,7 +3916,7 @@
         <v>0</v>
       </c>
       <c r="G67">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H67">
         <v>1</v>
@@ -3925,15 +3925,15 @@
         <v>3</v>
       </c>
       <c r="J67">
-        <f t="shared" si="36"/>
-        <v>20</v>
+        <f t="shared" si="4"/>
+        <v>60</v>
       </c>
       <c r="K67">
-        <f t="shared" si="37"/>
+        <f t="shared" si="5"/>
         <v>20</v>
       </c>
       <c r="L67">
-        <f t="shared" si="38"/>
+        <f t="shared" si="6"/>
         <v>60</v>
       </c>
       <c r="M67">
@@ -3951,13 +3951,13 @@
     </row>
     <row r="68" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A68">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="B68">
-        <v>280</v>
+        <v>1000</v>
       </c>
       <c r="C68">
-        <v>300</v>
+        <v>1000</v>
       </c>
       <c r="D68">
         <v>0</v>
@@ -3969,7 +3969,7 @@
         <v>0</v>
       </c>
       <c r="G68">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H68">
         <v>1</v>
@@ -3978,15 +3978,15 @@
         <v>3</v>
       </c>
       <c r="J68">
-        <f t="shared" si="36"/>
-        <v>20</v>
+        <f t="shared" si="4"/>
+        <v>60</v>
       </c>
       <c r="K68">
-        <f t="shared" si="37"/>
+        <f t="shared" si="5"/>
         <v>20</v>
       </c>
       <c r="L68">
-        <f t="shared" si="38"/>
+        <f t="shared" si="6"/>
         <v>60</v>
       </c>
       <c r="M68">
@@ -4004,13 +4004,13 @@
     </row>
     <row r="69" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A69">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="B69">
-        <v>280</v>
+        <v>1000</v>
       </c>
       <c r="C69">
-        <v>300</v>
+        <v>1000</v>
       </c>
       <c r="D69">
         <v>0</v>
@@ -4022,7 +4022,7 @@
         <v>0</v>
       </c>
       <c r="G69">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H69">
         <v>1</v>
@@ -4031,15 +4031,15 @@
         <v>3</v>
       </c>
       <c r="J69">
-        <f t="shared" si="36"/>
-        <v>20</v>
+        <f t="shared" si="4"/>
+        <v>60</v>
       </c>
       <c r="K69">
-        <f t="shared" si="37"/>
+        <f t="shared" si="5"/>
         <v>20</v>
       </c>
       <c r="L69">
-        <f t="shared" si="38"/>
+        <f t="shared" si="6"/>
         <v>60</v>
       </c>
       <c r="M69">
@@ -4057,13 +4057,13 @@
     </row>
     <row r="70" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A70">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="B70">
-        <v>280</v>
+        <v>1000</v>
       </c>
       <c r="C70">
-        <v>300</v>
+        <v>1000</v>
       </c>
       <c r="D70">
         <v>0</v>
@@ -4084,39 +4084,39 @@
         <v>3</v>
       </c>
       <c r="J70">
-        <f t="shared" si="36"/>
+        <f t="shared" ref="J70:J100" si="7">G70*20</f>
         <v>60</v>
       </c>
       <c r="K70">
-        <f t="shared" si="37"/>
+        <f t="shared" ref="K70:K100" si="8">H70*20</f>
         <v>20</v>
       </c>
       <c r="L70">
-        <f t="shared" si="38"/>
+        <f t="shared" ref="L70:L100" si="9">I70*20</f>
         <v>60</v>
       </c>
       <c r="M70">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="N70">
-        <v>480</v>
+        <v>0</v>
       </c>
       <c r="O70">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="P70">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="71" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A71">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="B71">
-        <v>480</v>
+        <v>1000</v>
       </c>
       <c r="C71">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="D71">
         <v>0</v>
@@ -4134,19 +4134,19 @@
         <v>1</v>
       </c>
       <c r="I71">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J71">
-        <f t="shared" si="36"/>
+        <f t="shared" si="7"/>
         <v>60</v>
       </c>
       <c r="K71">
-        <f t="shared" si="37"/>
+        <f t="shared" si="8"/>
         <v>20</v>
       </c>
       <c r="L71">
-        <f t="shared" si="38"/>
-        <v>20</v>
+        <f t="shared" si="9"/>
+        <v>60</v>
       </c>
       <c r="M71">
         <v>0</v>
@@ -4163,13 +4163,13 @@
     </row>
     <row r="72" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A72">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="B72">
-        <v>480</v>
+        <v>1000</v>
       </c>
       <c r="C72">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="D72">
         <v>0</v>
@@ -4187,19 +4187,19 @@
         <v>1</v>
       </c>
       <c r="I72">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J72">
-        <f t="shared" si="36"/>
+        <f t="shared" si="7"/>
         <v>60</v>
       </c>
       <c r="K72">
-        <f t="shared" si="37"/>
+        <f t="shared" si="8"/>
         <v>20</v>
       </c>
       <c r="L72">
-        <f t="shared" si="38"/>
-        <v>20</v>
+        <f t="shared" si="9"/>
+        <v>60</v>
       </c>
       <c r="M72">
         <v>0</v>
@@ -4216,13 +4216,13 @@
     </row>
     <row r="73" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A73">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="B73">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="C73">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="D73">
         <v>0</v>
@@ -4240,19 +4240,19 @@
         <v>1</v>
       </c>
       <c r="I73">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J73">
-        <f t="shared" si="36"/>
+        <f t="shared" si="7"/>
         <v>60</v>
       </c>
       <c r="K73">
-        <f t="shared" si="37"/>
+        <f t="shared" si="8"/>
         <v>20</v>
       </c>
       <c r="L73">
-        <f t="shared" si="38"/>
-        <v>20</v>
+        <f t="shared" si="9"/>
+        <v>60</v>
       </c>
       <c r="M73">
         <v>0</v>
@@ -4269,13 +4269,13 @@
     </row>
     <row r="74" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A74">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="B74">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="C74">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="D74">
         <v>0</v>
@@ -4293,19 +4293,19 @@
         <v>1</v>
       </c>
       <c r="I74">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J74">
-        <f t="shared" si="36"/>
+        <f t="shared" si="7"/>
         <v>60</v>
       </c>
       <c r="K74">
-        <f t="shared" si="37"/>
+        <f t="shared" si="8"/>
         <v>20</v>
       </c>
       <c r="L74">
-        <f t="shared" si="38"/>
-        <v>20</v>
+        <f t="shared" si="9"/>
+        <v>60</v>
       </c>
       <c r="M74">
         <v>0</v>
@@ -4322,13 +4322,13 @@
     </row>
     <row r="75" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A75">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="B75">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="C75">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="D75">
         <v>0</v>
@@ -4340,25 +4340,25 @@
         <v>0</v>
       </c>
       <c r="G75">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H75">
         <v>1</v>
       </c>
       <c r="I75">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J75">
-        <f t="shared" si="36"/>
-        <v>40</v>
+        <f t="shared" si="7"/>
+        <v>60</v>
       </c>
       <c r="K75">
-        <f t="shared" si="37"/>
+        <f t="shared" si="8"/>
         <v>20</v>
       </c>
       <c r="L75">
-        <f t="shared" si="38"/>
-        <v>20</v>
+        <f t="shared" si="9"/>
+        <v>60</v>
       </c>
       <c r="M75">
         <v>0</v>
@@ -4375,13 +4375,13 @@
     </row>
     <row r="76" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A76">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="B76">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="C76">
-        <v>160</v>
+        <v>1000</v>
       </c>
       <c r="D76">
         <v>0</v>
@@ -4393,25 +4393,25 @@
         <v>0</v>
       </c>
       <c r="G76">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H76">
         <v>1</v>
       </c>
       <c r="I76">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J76">
-        <f t="shared" si="36"/>
-        <v>40</v>
+        <f t="shared" si="7"/>
+        <v>60</v>
       </c>
       <c r="K76">
-        <f t="shared" si="37"/>
+        <f t="shared" si="8"/>
         <v>20</v>
       </c>
       <c r="L76">
-        <f t="shared" si="38"/>
-        <v>20</v>
+        <f t="shared" si="9"/>
+        <v>60</v>
       </c>
       <c r="M76">
         <v>0</v>
@@ -4428,13 +4428,13 @@
     </row>
     <row r="77" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A77">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="B77">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="C77">
-        <v>200</v>
+        <v>1000</v>
       </c>
       <c r="D77">
         <v>0</v>
@@ -4446,25 +4446,25 @@
         <v>0</v>
       </c>
       <c r="G77">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H77">
         <v>1</v>
       </c>
       <c r="I77">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J77">
-        <f t="shared" si="36"/>
-        <v>40</v>
+        <f t="shared" si="7"/>
+        <v>60</v>
       </c>
       <c r="K77">
-        <f t="shared" si="37"/>
+        <f t="shared" si="8"/>
         <v>20</v>
       </c>
       <c r="L77">
-        <f t="shared" si="38"/>
-        <v>20</v>
+        <f t="shared" si="9"/>
+        <v>60</v>
       </c>
       <c r="M77">
         <v>0</v>
@@ -4481,13 +4481,13 @@
     </row>
     <row r="78" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A78">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="B78">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="C78">
-        <v>240</v>
+        <v>1000</v>
       </c>
       <c r="D78">
         <v>0</v>
@@ -4499,25 +4499,25 @@
         <v>0</v>
       </c>
       <c r="G78">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H78">
         <v>1</v>
       </c>
       <c r="I78">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J78">
-        <f t="shared" si="36"/>
-        <v>20</v>
+        <f t="shared" si="7"/>
+        <v>60</v>
       </c>
       <c r="K78">
-        <f t="shared" si="37"/>
+        <f t="shared" si="8"/>
         <v>20</v>
       </c>
       <c r="L78">
-        <f t="shared" si="38"/>
-        <v>20</v>
+        <f t="shared" si="9"/>
+        <v>60</v>
       </c>
       <c r="M78">
         <v>0</v>
@@ -4534,13 +4534,13 @@
     </row>
     <row r="79" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A79">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="B79">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="C79">
-        <v>280</v>
+        <v>1000</v>
       </c>
       <c r="D79">
         <v>0</v>
@@ -4552,25 +4552,25 @@
         <v>0</v>
       </c>
       <c r="G79">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H79">
         <v>1</v>
       </c>
       <c r="I79">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J79">
-        <f t="shared" si="36"/>
-        <v>20</v>
+        <f t="shared" si="7"/>
+        <v>60</v>
       </c>
       <c r="K79">
-        <f t="shared" si="37"/>
+        <f t="shared" si="8"/>
         <v>20</v>
       </c>
       <c r="L79">
-        <f t="shared" si="38"/>
-        <v>20</v>
+        <f t="shared" si="9"/>
+        <v>60</v>
       </c>
       <c r="M79">
         <v>0</v>
@@ -4587,13 +4587,13 @@
     </row>
     <row r="80" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A80">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="B80">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="C80">
-        <v>320</v>
+        <v>1000</v>
       </c>
       <c r="D80">
         <v>0</v>
@@ -4605,25 +4605,25 @@
         <v>0</v>
       </c>
       <c r="G80">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H80">
         <v>1</v>
       </c>
       <c r="I80">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J80">
-        <f t="shared" si="36"/>
-        <v>20</v>
+        <f t="shared" si="7"/>
+        <v>60</v>
       </c>
       <c r="K80">
-        <f t="shared" si="37"/>
+        <f t="shared" si="8"/>
         <v>20</v>
       </c>
       <c r="L80">
-        <f t="shared" si="38"/>
-        <v>20</v>
+        <f t="shared" si="9"/>
+        <v>60</v>
       </c>
       <c r="M80">
         <v>0</v>
@@ -4640,13 +4640,13 @@
     </row>
     <row r="81" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A81">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="B81">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="C81">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="D81">
         <v>0</v>
@@ -4658,25 +4658,25 @@
         <v>0</v>
       </c>
       <c r="G81">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H81">
         <v>1</v>
       </c>
       <c r="I81">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J81">
-        <f t="shared" si="36"/>
-        <v>20</v>
+        <f t="shared" si="7"/>
+        <v>60</v>
       </c>
       <c r="K81">
-        <f t="shared" si="37"/>
+        <f t="shared" si="8"/>
         <v>20</v>
       </c>
       <c r="L81">
-        <f t="shared" si="38"/>
-        <v>20</v>
+        <f t="shared" si="9"/>
+        <v>60</v>
       </c>
       <c r="M81">
         <v>0</v>
@@ -4693,13 +4693,13 @@
     </row>
     <row r="82" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A82">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="B82">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="C82">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="D82">
         <v>0</v>
@@ -4711,25 +4711,25 @@
         <v>0</v>
       </c>
       <c r="G82">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H82">
         <v>1</v>
       </c>
       <c r="I82">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J82">
-        <f t="shared" si="36"/>
-        <v>20</v>
+        <f t="shared" si="7"/>
+        <v>60</v>
       </c>
       <c r="K82">
-        <f t="shared" si="37"/>
+        <f t="shared" si="8"/>
         <v>20</v>
       </c>
       <c r="L82">
-        <f t="shared" si="38"/>
-        <v>20</v>
+        <f t="shared" si="9"/>
+        <v>60</v>
       </c>
       <c r="M82">
         <v>0</v>
@@ -4746,13 +4746,13 @@
     </row>
     <row r="83" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A83">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="B83">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="C83">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="D83">
         <v>0</v>
@@ -4764,25 +4764,25 @@
         <v>0</v>
       </c>
       <c r="G83">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H83">
         <v>1</v>
       </c>
       <c r="I83">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J83">
-        <f t="shared" si="36"/>
-        <v>20</v>
+        <f t="shared" si="7"/>
+        <v>60</v>
       </c>
       <c r="K83">
-        <f t="shared" si="37"/>
+        <f t="shared" si="8"/>
         <v>20</v>
       </c>
       <c r="L83">
-        <f t="shared" si="38"/>
-        <v>20</v>
+        <f t="shared" si="9"/>
+        <v>60</v>
       </c>
       <c r="M83">
         <v>0</v>
@@ -4799,13 +4799,13 @@
     </row>
     <row r="84" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A84">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="B84">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="C84">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="D84">
         <v>0</v>
@@ -4817,25 +4817,25 @@
         <v>0</v>
       </c>
       <c r="G84">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H84">
         <v>1</v>
       </c>
       <c r="I84">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J84">
-        <f t="shared" si="36"/>
-        <v>20</v>
+        <f t="shared" si="7"/>
+        <v>60</v>
       </c>
       <c r="K84">
-        <f t="shared" si="37"/>
+        <f t="shared" si="8"/>
         <v>20</v>
       </c>
       <c r="L84">
-        <f t="shared" si="38"/>
-        <v>20</v>
+        <f t="shared" si="9"/>
+        <v>60</v>
       </c>
       <c r="M84">
         <v>0</v>
@@ -4852,13 +4852,13 @@
     </row>
     <row r="85" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A85">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="B85">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="C85">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="D85">
         <v>0</v>
@@ -4870,25 +4870,25 @@
         <v>0</v>
       </c>
       <c r="G85">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H85">
         <v>1</v>
       </c>
       <c r="I85">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J85">
-        <f t="shared" si="36"/>
-        <v>20</v>
+        <f t="shared" si="7"/>
+        <v>60</v>
       </c>
       <c r="K85">
-        <f t="shared" si="37"/>
+        <f t="shared" si="8"/>
         <v>20</v>
       </c>
       <c r="L85">
-        <f t="shared" si="38"/>
-        <v>20</v>
+        <f t="shared" si="9"/>
+        <v>60</v>
       </c>
       <c r="M85">
         <v>0</v>
@@ -4905,13 +4905,13 @@
     </row>
     <row r="86" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A86">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="B86">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="C86">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="D86">
         <v>0</v>
@@ -4923,25 +4923,25 @@
         <v>0</v>
       </c>
       <c r="G86">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H86">
         <v>1</v>
       </c>
       <c r="I86">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J86">
-        <f t="shared" si="36"/>
-        <v>20</v>
+        <f t="shared" si="7"/>
+        <v>60</v>
       </c>
       <c r="K86">
-        <f t="shared" si="37"/>
+        <f t="shared" si="8"/>
         <v>20</v>
       </c>
       <c r="L86">
-        <f t="shared" si="38"/>
-        <v>20</v>
+        <f t="shared" si="9"/>
+        <v>60</v>
       </c>
       <c r="M86">
         <v>0</v>
@@ -4958,13 +4958,13 @@
     </row>
     <row r="87" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A87">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="B87">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="C87">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="D87">
         <v>0</v>
@@ -4976,25 +4976,25 @@
         <v>0</v>
       </c>
       <c r="G87">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H87">
         <v>1</v>
       </c>
       <c r="I87">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J87">
-        <f t="shared" si="36"/>
-        <v>20</v>
+        <f t="shared" si="7"/>
+        <v>60</v>
       </c>
       <c r="K87">
-        <f t="shared" si="37"/>
+        <f t="shared" si="8"/>
         <v>20</v>
       </c>
       <c r="L87">
-        <f t="shared" si="38"/>
-        <v>20</v>
+        <f t="shared" si="9"/>
+        <v>60</v>
       </c>
       <c r="M87">
         <v>0</v>
@@ -5011,13 +5011,13 @@
     </row>
     <row r="88" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A88">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="B88">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="C88">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="D88">
         <v>0</v>
@@ -5029,25 +5029,25 @@
         <v>0</v>
       </c>
       <c r="G88">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H88">
         <v>1</v>
       </c>
       <c r="I88">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J88">
-        <f t="shared" si="36"/>
-        <v>20</v>
+        <f t="shared" si="7"/>
+        <v>60</v>
       </c>
       <c r="K88">
-        <f t="shared" si="37"/>
+        <f t="shared" si="8"/>
         <v>20</v>
       </c>
       <c r="L88">
-        <f t="shared" si="38"/>
-        <v>20</v>
+        <f t="shared" si="9"/>
+        <v>60</v>
       </c>
       <c r="M88">
         <v>0</v>
@@ -5064,13 +5064,13 @@
     </row>
     <row r="89" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A89">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="B89">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="C89">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="D89">
         <v>0</v>
@@ -5082,25 +5082,25 @@
         <v>0</v>
       </c>
       <c r="G89">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H89">
         <v>1</v>
       </c>
       <c r="I89">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J89">
-        <f t="shared" si="36"/>
-        <v>20</v>
+        <f t="shared" si="7"/>
+        <v>60</v>
       </c>
       <c r="K89">
-        <f t="shared" si="37"/>
+        <f t="shared" si="8"/>
         <v>20</v>
       </c>
       <c r="L89">
-        <f t="shared" si="38"/>
-        <v>20</v>
+        <f t="shared" si="9"/>
+        <v>60</v>
       </c>
       <c r="M89">
         <v>0</v>
@@ -5117,13 +5117,13 @@
     </row>
     <row r="90" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A90">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="B90">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="C90">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="D90">
         <v>0</v>
@@ -5135,25 +5135,25 @@
         <v>0</v>
       </c>
       <c r="G90">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H90">
         <v>1</v>
       </c>
       <c r="I90">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J90">
-        <f t="shared" si="36"/>
-        <v>20</v>
+        <f t="shared" si="7"/>
+        <v>60</v>
       </c>
       <c r="K90">
-        <f t="shared" si="37"/>
+        <f t="shared" si="8"/>
         <v>20</v>
       </c>
       <c r="L90">
-        <f t="shared" si="38"/>
-        <v>20</v>
+        <f t="shared" si="9"/>
+        <v>60</v>
       </c>
       <c r="M90">
         <v>0</v>
@@ -5170,13 +5170,13 @@
     </row>
     <row r="91" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A91">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="B91">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="C91">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="D91">
         <v>0</v>
@@ -5188,25 +5188,25 @@
         <v>0</v>
       </c>
       <c r="G91">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H91">
         <v>1</v>
       </c>
       <c r="I91">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J91">
-        <f t="shared" si="36"/>
-        <v>20</v>
+        <f t="shared" si="7"/>
+        <v>60</v>
       </c>
       <c r="K91">
-        <f t="shared" si="37"/>
+        <f t="shared" si="8"/>
         <v>20</v>
       </c>
       <c r="L91">
-        <f t="shared" si="38"/>
-        <v>20</v>
+        <f t="shared" si="9"/>
+        <v>60</v>
       </c>
       <c r="M91">
         <v>0</v>
@@ -5223,13 +5223,13 @@
     </row>
     <row r="92" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A92">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="B92">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="C92">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="D92">
         <v>0</v>
@@ -5241,25 +5241,25 @@
         <v>0</v>
       </c>
       <c r="G92">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H92">
         <v>1</v>
       </c>
       <c r="I92">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J92">
-        <f t="shared" si="36"/>
-        <v>20</v>
+        <f t="shared" si="7"/>
+        <v>60</v>
       </c>
       <c r="K92">
-        <f t="shared" si="37"/>
+        <f t="shared" si="8"/>
         <v>20</v>
       </c>
       <c r="L92">
-        <f t="shared" si="38"/>
-        <v>20</v>
+        <f t="shared" si="9"/>
+        <v>60</v>
       </c>
       <c r="M92">
         <v>0</v>
@@ -5276,13 +5276,13 @@
     </row>
     <row r="93" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A93">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="B93">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="C93">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="D93">
         <v>0</v>
@@ -5294,25 +5294,25 @@
         <v>0</v>
       </c>
       <c r="G93">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H93">
         <v>1</v>
       </c>
       <c r="I93">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J93">
-        <f t="shared" si="36"/>
-        <v>20</v>
+        <f t="shared" si="7"/>
+        <v>60</v>
       </c>
       <c r="K93">
-        <f t="shared" si="37"/>
+        <f t="shared" si="8"/>
         <v>20</v>
       </c>
       <c r="L93">
-        <f t="shared" si="38"/>
-        <v>20</v>
+        <f t="shared" si="9"/>
+        <v>60</v>
       </c>
       <c r="M93">
         <v>0</v>
@@ -5329,13 +5329,13 @@
     </row>
     <row r="94" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A94">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="B94">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="C94">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="D94">
         <v>0</v>
@@ -5347,25 +5347,25 @@
         <v>0</v>
       </c>
       <c r="G94">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H94">
         <v>1</v>
       </c>
       <c r="I94">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J94">
-        <f t="shared" si="36"/>
-        <v>20</v>
+        <f t="shared" si="7"/>
+        <v>60</v>
       </c>
       <c r="K94">
-        <f t="shared" si="37"/>
+        <f t="shared" si="8"/>
         <v>20</v>
       </c>
       <c r="L94">
-        <f t="shared" si="38"/>
-        <v>20</v>
+        <f t="shared" si="9"/>
+        <v>60</v>
       </c>
       <c r="M94">
         <v>0</v>
@@ -5382,13 +5382,13 @@
     </row>
     <row r="95" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A95">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="B95">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="C95">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="D95">
         <v>0</v>
@@ -5400,25 +5400,25 @@
         <v>0</v>
       </c>
       <c r="G95">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H95">
         <v>1</v>
       </c>
       <c r="I95">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J95">
-        <f t="shared" si="36"/>
-        <v>20</v>
+        <f t="shared" si="7"/>
+        <v>60</v>
       </c>
       <c r="K95">
-        <f t="shared" si="37"/>
+        <f t="shared" si="8"/>
         <v>20</v>
       </c>
       <c r="L95">
-        <f t="shared" si="38"/>
-        <v>20</v>
+        <f t="shared" si="9"/>
+        <v>60</v>
       </c>
       <c r="M95">
         <v>0</v>
@@ -5435,13 +5435,13 @@
     </row>
     <row r="96" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A96">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="B96">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="C96">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="D96">
         <v>0</v>
@@ -5453,25 +5453,25 @@
         <v>0</v>
       </c>
       <c r="G96">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H96">
         <v>1</v>
       </c>
       <c r="I96">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J96">
-        <f t="shared" si="36"/>
-        <v>20</v>
+        <f t="shared" si="7"/>
+        <v>60</v>
       </c>
       <c r="K96">
-        <f t="shared" si="37"/>
+        <f t="shared" si="8"/>
         <v>20</v>
       </c>
       <c r="L96">
-        <f t="shared" si="38"/>
-        <v>20</v>
+        <f t="shared" si="9"/>
+        <v>60</v>
       </c>
       <c r="M96">
         <v>0</v>
@@ -5488,13 +5488,13 @@
     </row>
     <row r="97" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A97">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="B97">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="C97">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="D97">
         <v>0</v>
@@ -5506,25 +5506,25 @@
         <v>0</v>
       </c>
       <c r="G97">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H97">
         <v>1</v>
       </c>
       <c r="I97">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J97">
-        <f t="shared" si="36"/>
-        <v>20</v>
+        <f t="shared" si="7"/>
+        <v>60</v>
       </c>
       <c r="K97">
-        <f t="shared" si="37"/>
+        <f t="shared" si="8"/>
         <v>20</v>
       </c>
       <c r="L97">
-        <f t="shared" si="38"/>
-        <v>20</v>
+        <f t="shared" si="9"/>
+        <v>60</v>
       </c>
       <c r="M97">
         <v>0</v>
@@ -5541,13 +5541,13 @@
     </row>
     <row r="98" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A98">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="B98">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="C98">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="D98">
         <v>0</v>
@@ -5559,25 +5559,25 @@
         <v>0</v>
       </c>
       <c r="G98">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H98">
         <v>1</v>
       </c>
       <c r="I98">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J98">
-        <f t="shared" si="36"/>
-        <v>20</v>
+        <f t="shared" si="7"/>
+        <v>60</v>
       </c>
       <c r="K98">
-        <f t="shared" si="37"/>
+        <f t="shared" si="8"/>
         <v>20</v>
       </c>
       <c r="L98">
-        <f t="shared" si="38"/>
-        <v>20</v>
+        <f t="shared" si="9"/>
+        <v>60</v>
       </c>
       <c r="M98">
         <v>0</v>
@@ -5594,13 +5594,13 @@
     </row>
     <row r="99" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A99">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="B99">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="C99">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="D99">
         <v>0</v>
@@ -5612,25 +5612,25 @@
         <v>0</v>
       </c>
       <c r="G99">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H99">
         <v>1</v>
       </c>
       <c r="I99">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J99">
-        <f t="shared" si="36"/>
-        <v>20</v>
+        <f t="shared" si="7"/>
+        <v>60</v>
       </c>
       <c r="K99">
-        <f t="shared" si="37"/>
+        <f t="shared" si="8"/>
         <v>20</v>
       </c>
       <c r="L99">
-        <f t="shared" si="38"/>
-        <v>20</v>
+        <f t="shared" si="9"/>
+        <v>60</v>
       </c>
       <c r="M99">
         <v>0</v>
@@ -5647,13 +5647,13 @@
     </row>
     <row r="100" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A100">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="B100">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="C100">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="D100">
         <v>0</v>
@@ -5665,25 +5665,25 @@
         <v>0</v>
       </c>
       <c r="G100">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H100">
         <v>1</v>
       </c>
       <c r="I100">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J100">
-        <f t="shared" si="36"/>
-        <v>20</v>
+        <f t="shared" si="7"/>
+        <v>60</v>
       </c>
       <c r="K100">
-        <f t="shared" si="37"/>
+        <f t="shared" si="8"/>
         <v>20</v>
       </c>
       <c r="L100">
-        <f t="shared" si="38"/>
-        <v>20</v>
+        <f t="shared" si="9"/>
+        <v>60</v>
       </c>
       <c r="M100">
         <v>0</v>

--- a/ActionGame-リファクタリング-/Data/CSV/Stage/Stage.xlsx
+++ b/ActionGame-リファクタリング-/Data/CSV/Stage/Stage.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\2409404\Desktop\GameProject\ActionGame-リファクタリング-\Data\CSV\Stage\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F5DB79C-AB2F-4FC7-B0A4-CDE7C571A37A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F46A6034-414D-4E1B-88CE-F36F72D77D38}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="7200" yWindow="4185" windowWidth="21600" windowHeight="11295" xr2:uid="{62A58253-9505-4C17-A0D0-B4C12E04E8CC}"/>
   </bookViews>
@@ -495,7 +495,7 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>-400</v>
+        <v>-100</v>
       </c>
       <c r="O2">
         <v>60</v>
@@ -506,13 +506,13 @@
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A3">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="B3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="C3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="D3">
         <v>0</v>
@@ -559,13 +559,13 @@
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A4">
-        <v>-60</v>
+        <v>1000</v>
       </c>
       <c r="B4">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="C4">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="D4">
         <v>0</v>
@@ -612,13 +612,13 @@
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="B5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="C5">
-        <v>-60</v>
+        <v>1000</v>
       </c>
       <c r="D5">
         <v>0</v>

--- a/ActionGame-リファクタリング-/Data/CSV/Stage/Stage.xlsx
+++ b/ActionGame-リファクタリング-/Data/CSV/Stage/Stage.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\2409404\Desktop\GameProject\ActionGame-リファクタリング-\Data\CSV\Stage\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F46A6034-414D-4E1B-88CE-F36F72D77D38}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{260C087E-050F-4C15-A92B-BD3A6ADDE3E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7200" yWindow="4185" windowWidth="21600" windowHeight="11295" xr2:uid="{62A58253-9505-4C17-A0D0-B4C12E04E8CC}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{62A58253-9505-4C17-A0D0-B4C12E04E8CC}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -424,7 +424,7 @@
         <v>1</v>
       </c>
       <c r="I1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J1">
         <f>G1*20</f>
@@ -436,7 +436,7 @@
       </c>
       <c r="L1">
         <f t="shared" si="0"/>
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="M1">
         <v>0</v>
@@ -456,10 +456,10 @@
         <v>0</v>
       </c>
       <c r="B2">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="C2">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="D2">
         <v>0</v>
@@ -477,42 +477,42 @@
         <v>1</v>
       </c>
       <c r="I2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J2">
-        <f t="shared" ref="J2:J5" si="1">G2*20</f>
+        <f t="shared" ref="J2" si="1">G2*20</f>
         <v>60</v>
       </c>
       <c r="K2">
-        <f t="shared" ref="K2:K5" si="2">H2*20</f>
+        <f t="shared" ref="K2" si="2">H2*20</f>
         <v>20</v>
       </c>
       <c r="L2">
-        <f t="shared" ref="L2:L5" si="3">I2*20</f>
-        <v>60</v>
+        <f t="shared" ref="L2" si="3">I2*20</f>
+        <v>20</v>
       </c>
       <c r="M2">
         <v>0</v>
       </c>
       <c r="N2">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="O2">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="P2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A3">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="B3">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="C3">
-        <v>1000</v>
+        <v>-20</v>
       </c>
       <c r="D3">
         <v>0</v>
@@ -530,22 +530,22 @@
         <v>1</v>
       </c>
       <c r="I3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J3">
-        <f t="shared" si="1"/>
+        <f>G3*20</f>
         <v>60</v>
       </c>
       <c r="K3">
-        <f t="shared" si="2"/>
+        <f t="shared" ref="K3:K6" si="4">H3*20</f>
         <v>20</v>
       </c>
       <c r="L3">
-        <f t="shared" si="3"/>
-        <v>60</v>
+        <f t="shared" ref="L3:L6" si="5">I3*20</f>
+        <v>20</v>
       </c>
       <c r="M3">
-        <v>160</v>
+        <v>0</v>
       </c>
       <c r="N3">
         <v>0</v>
@@ -554,18 +554,18 @@
         <v>0</v>
       </c>
       <c r="P3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A4">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="B4">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="C4">
-        <v>1000</v>
+        <v>-40</v>
       </c>
       <c r="D4">
         <v>0</v>
@@ -583,22 +583,22 @@
         <v>1</v>
       </c>
       <c r="I4">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J4">
-        <f t="shared" si="1"/>
+        <f t="shared" ref="J4:J6" si="6">G4*20</f>
         <v>60</v>
       </c>
       <c r="K4">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>20</v>
       </c>
       <c r="L4">
-        <f t="shared" si="3"/>
-        <v>60</v>
+        <f t="shared" si="5"/>
+        <v>20</v>
       </c>
       <c r="M4">
-        <v>-260</v>
+        <v>0</v>
       </c>
       <c r="N4">
         <v>0</v>
@@ -607,18 +607,18 @@
         <v>0</v>
       </c>
       <c r="P4">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A5">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="B5">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="C5">
-        <v>1000</v>
+        <v>-60</v>
       </c>
       <c r="D5">
         <v>0</v>
@@ -636,42 +636,42 @@
         <v>1</v>
       </c>
       <c r="I5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J5">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>60</v>
       </c>
       <c r="K5">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>20</v>
       </c>
       <c r="L5">
-        <f t="shared" si="3"/>
-        <v>60</v>
+        <f t="shared" si="5"/>
+        <v>20</v>
       </c>
       <c r="M5">
         <v>0</v>
       </c>
       <c r="N5">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="O5">
-        <v>-60</v>
+        <v>0</v>
       </c>
       <c r="P5">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A6">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="B6">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="C6">
-        <v>1000</v>
+        <v>-80</v>
       </c>
       <c r="D6">
         <v>0</v>
@@ -689,19 +689,19 @@
         <v>1</v>
       </c>
       <c r="I6">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J6">
-        <f t="shared" ref="J6:J69" si="4">G6*20</f>
+        <f t="shared" si="6"/>
         <v>60</v>
       </c>
       <c r="K6">
-        <f t="shared" ref="K6:K69" si="5">H6*20</f>
+        <f t="shared" si="4"/>
         <v>20</v>
       </c>
       <c r="L6">
-        <f t="shared" ref="L6:L69" si="6">I6*20</f>
-        <v>60</v>
+        <f t="shared" si="5"/>
+        <v>20</v>
       </c>
       <c r="M6">
         <v>0</v>
@@ -718,13 +718,13 @@
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A7">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="B7">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="C7">
-        <v>1000</v>
+        <v>-100</v>
       </c>
       <c r="D7">
         <v>0</v>
@@ -742,19 +742,19 @@
         <v>1</v>
       </c>
       <c r="I7">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J7">
-        <f t="shared" si="4"/>
+        <f t="shared" ref="J7" si="7">G7*20</f>
         <v>60</v>
       </c>
       <c r="K7">
-        <f t="shared" si="5"/>
+        <f t="shared" ref="K7" si="8">H7*20</f>
         <v>20</v>
       </c>
       <c r="L7">
-        <f t="shared" si="6"/>
-        <v>60</v>
+        <f t="shared" ref="L7" si="9">I7*20</f>
+        <v>20</v>
       </c>
       <c r="M7">
         <v>0</v>
@@ -771,13 +771,13 @@
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A8">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="B8">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="C8">
-        <v>1000</v>
+        <v>-140</v>
       </c>
       <c r="D8">
         <v>0</v>
@@ -789,7 +789,7 @@
         <v>0</v>
       </c>
       <c r="G8">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H8">
         <v>1</v>
@@ -798,15 +798,15 @@
         <v>3</v>
       </c>
       <c r="J8">
-        <f t="shared" si="4"/>
-        <v>60</v>
+        <f t="shared" ref="J8:J9" si="10">G8*20</f>
+        <v>20</v>
       </c>
       <c r="K8">
-        <f t="shared" si="5"/>
+        <f t="shared" ref="K8" si="11">H8*20</f>
         <v>20</v>
       </c>
       <c r="L8">
-        <f t="shared" si="6"/>
+        <f t="shared" ref="L8" si="12">I8*20</f>
         <v>60</v>
       </c>
       <c r="M8">
@@ -824,13 +824,13 @@
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A9">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="B9">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="C9">
-        <v>1000</v>
+        <v>-140</v>
       </c>
       <c r="D9">
         <v>0</v>
@@ -842,7 +842,7 @@
         <v>0</v>
       </c>
       <c r="G9">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H9">
         <v>1</v>
@@ -851,15 +851,15 @@
         <v>3</v>
       </c>
       <c r="J9">
-        <f t="shared" si="4"/>
-        <v>60</v>
+        <f t="shared" si="10"/>
+        <v>20</v>
       </c>
       <c r="K9">
-        <f t="shared" si="5"/>
+        <f t="shared" ref="K9:K12" si="13">H9*20</f>
         <v>20</v>
       </c>
       <c r="L9">
-        <f t="shared" si="6"/>
+        <f t="shared" ref="L9:L12" si="14">I9*20</f>
         <v>60</v>
       </c>
       <c r="M9">
@@ -877,13 +877,13 @@
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A10">
-        <v>1000</v>
+        <v>-20</v>
       </c>
       <c r="B10">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="C10">
-        <v>1000</v>
+        <v>-140</v>
       </c>
       <c r="D10">
         <v>0</v>
@@ -895,7 +895,7 @@
         <v>0</v>
       </c>
       <c r="G10">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H10">
         <v>1</v>
@@ -904,15 +904,15 @@
         <v>3</v>
       </c>
       <c r="J10">
-        <f t="shared" si="4"/>
-        <v>60</v>
+        <f t="shared" ref="J10:J12" si="15">G10*20</f>
+        <v>20</v>
       </c>
       <c r="K10">
-        <f t="shared" si="5"/>
+        <f t="shared" si="13"/>
         <v>20</v>
       </c>
       <c r="L10">
-        <f t="shared" si="6"/>
+        <f t="shared" si="14"/>
         <v>60</v>
       </c>
       <c r="M10">
@@ -930,13 +930,13 @@
     </row>
     <row r="11" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A11">
-        <v>1000</v>
+        <v>-40</v>
       </c>
       <c r="B11">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="C11">
-        <v>1000</v>
+        <v>-140</v>
       </c>
       <c r="D11">
         <v>0</v>
@@ -948,7 +948,7 @@
         <v>0</v>
       </c>
       <c r="G11">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H11">
         <v>1</v>
@@ -957,15 +957,15 @@
         <v>3</v>
       </c>
       <c r="J11">
-        <f t="shared" si="4"/>
-        <v>60</v>
+        <f t="shared" si="15"/>
+        <v>20</v>
       </c>
       <c r="K11">
-        <f t="shared" si="5"/>
+        <f t="shared" si="13"/>
         <v>20</v>
       </c>
       <c r="L11">
-        <f t="shared" si="6"/>
+        <f t="shared" si="14"/>
         <v>60</v>
       </c>
       <c r="M11">
@@ -983,13 +983,13 @@
     </row>
     <row r="12" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A12">
-        <v>1000</v>
+        <v>-60</v>
       </c>
       <c r="B12">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="C12">
-        <v>1000</v>
+        <v>-140</v>
       </c>
       <c r="D12">
         <v>0</v>
@@ -1001,7 +1001,7 @@
         <v>0</v>
       </c>
       <c r="G12">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H12">
         <v>1</v>
@@ -1010,15 +1010,15 @@
         <v>3</v>
       </c>
       <c r="J12">
-        <f t="shared" si="4"/>
-        <v>60</v>
+        <f t="shared" si="15"/>
+        <v>20</v>
       </c>
       <c r="K12">
-        <f t="shared" si="5"/>
+        <f t="shared" si="13"/>
         <v>20</v>
       </c>
       <c r="L12">
-        <f t="shared" si="6"/>
+        <f t="shared" si="14"/>
         <v>60</v>
       </c>
       <c r="M12">
@@ -1036,13 +1036,13 @@
     </row>
     <row r="13" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A13">
-        <v>1000</v>
+        <v>-80</v>
       </c>
       <c r="B13">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="C13">
-        <v>1000</v>
+        <v>-140</v>
       </c>
       <c r="D13">
         <v>0</v>
@@ -1054,7 +1054,7 @@
         <v>0</v>
       </c>
       <c r="G13">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H13">
         <v>1</v>
@@ -1063,15 +1063,15 @@
         <v>3</v>
       </c>
       <c r="J13">
-        <f t="shared" si="4"/>
-        <v>60</v>
+        <f t="shared" ref="J13:J15" si="16">G13*20</f>
+        <v>20</v>
       </c>
       <c r="K13">
-        <f t="shared" si="5"/>
+        <f t="shared" ref="K13:K16" si="17">H13*20</f>
         <v>20</v>
       </c>
       <c r="L13">
-        <f t="shared" si="6"/>
+        <f t="shared" ref="L13:L16" si="18">I13*20</f>
         <v>60</v>
       </c>
       <c r="M13">
@@ -1089,13 +1089,13 @@
     </row>
     <row r="14" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A14">
-        <v>1000</v>
+        <v>-100</v>
       </c>
       <c r="B14">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="C14">
-        <v>1000</v>
+        <v>-140</v>
       </c>
       <c r="D14">
         <v>0</v>
@@ -1107,7 +1107,7 @@
         <v>0</v>
       </c>
       <c r="G14">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H14">
         <v>1</v>
@@ -1116,15 +1116,15 @@
         <v>3</v>
       </c>
       <c r="J14">
-        <f t="shared" si="4"/>
-        <v>60</v>
+        <f t="shared" si="16"/>
+        <v>20</v>
       </c>
       <c r="K14">
-        <f t="shared" si="5"/>
+        <f t="shared" si="17"/>
         <v>20</v>
       </c>
       <c r="L14">
-        <f t="shared" si="6"/>
+        <f t="shared" si="18"/>
         <v>60</v>
       </c>
       <c r="M14">
@@ -1142,13 +1142,13 @@
     </row>
     <row r="15" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A15">
-        <v>1000</v>
+        <v>-120</v>
       </c>
       <c r="B15">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="C15">
-        <v>1000</v>
+        <v>-140</v>
       </c>
       <c r="D15">
         <v>0</v>
@@ -1160,7 +1160,7 @@
         <v>0</v>
       </c>
       <c r="G15">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H15">
         <v>1</v>
@@ -1169,15 +1169,15 @@
         <v>3</v>
       </c>
       <c r="J15">
-        <f t="shared" si="4"/>
-        <v>60</v>
+        <f t="shared" si="16"/>
+        <v>20</v>
       </c>
       <c r="K15">
-        <f t="shared" si="5"/>
+        <f t="shared" si="17"/>
         <v>20</v>
       </c>
       <c r="L15">
-        <f t="shared" si="6"/>
+        <f t="shared" si="18"/>
         <v>60</v>
       </c>
       <c r="M15">
@@ -1195,13 +1195,13 @@
     </row>
     <row r="16" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A16">
-        <v>1000</v>
+        <v>-140</v>
       </c>
       <c r="B16">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="C16">
-        <v>1000</v>
+        <v>-140</v>
       </c>
       <c r="D16">
         <v>0</v>
@@ -1213,7 +1213,7 @@
         <v>0</v>
       </c>
       <c r="G16">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H16">
         <v>1</v>
@@ -1222,15 +1222,15 @@
         <v>3</v>
       </c>
       <c r="J16">
-        <f t="shared" si="4"/>
-        <v>60</v>
+        <f t="shared" ref="J16:J18" si="19">G16*20</f>
+        <v>20</v>
       </c>
       <c r="K16">
-        <f t="shared" si="5"/>
+        <f t="shared" si="17"/>
         <v>20</v>
       </c>
       <c r="L16">
-        <f t="shared" si="6"/>
+        <f t="shared" si="18"/>
         <v>60</v>
       </c>
       <c r="M16">
@@ -1248,13 +1248,13 @@
     </row>
     <row r="17" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A17">
-        <v>1000</v>
+        <v>-160</v>
       </c>
       <c r="B17">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="C17">
-        <v>1000</v>
+        <v>-140</v>
       </c>
       <c r="D17">
         <v>0</v>
@@ -1266,7 +1266,7 @@
         <v>0</v>
       </c>
       <c r="G17">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H17">
         <v>1</v>
@@ -1275,15 +1275,15 @@
         <v>3</v>
       </c>
       <c r="J17">
-        <f t="shared" si="4"/>
-        <v>60</v>
+        <f t="shared" si="19"/>
+        <v>20</v>
       </c>
       <c r="K17">
-        <f t="shared" si="5"/>
+        <f t="shared" ref="K17:K20" si="20">H17*20</f>
         <v>20</v>
       </c>
       <c r="L17">
-        <f t="shared" si="6"/>
+        <f t="shared" ref="L17:L20" si="21">I17*20</f>
         <v>60</v>
       </c>
       <c r="M17">
@@ -1301,13 +1301,13 @@
     </row>
     <row r="18" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A18">
-        <v>1000</v>
+        <v>-180</v>
       </c>
       <c r="B18">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="C18">
-        <v>1000</v>
+        <v>-140</v>
       </c>
       <c r="D18">
         <v>0</v>
@@ -1319,7 +1319,7 @@
         <v>0</v>
       </c>
       <c r="G18">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H18">
         <v>1</v>
@@ -1328,15 +1328,15 @@
         <v>3</v>
       </c>
       <c r="J18">
-        <f t="shared" si="4"/>
-        <v>60</v>
+        <f t="shared" si="19"/>
+        <v>20</v>
       </c>
       <c r="K18">
-        <f t="shared" si="5"/>
+        <f t="shared" si="20"/>
         <v>20</v>
       </c>
       <c r="L18">
-        <f t="shared" si="6"/>
+        <f t="shared" si="21"/>
         <v>60</v>
       </c>
       <c r="M18">
@@ -1354,13 +1354,13 @@
     </row>
     <row r="19" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A19">
-        <v>1000</v>
+        <v>-200</v>
       </c>
       <c r="B19">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="C19">
-        <v>1000</v>
+        <v>-140</v>
       </c>
       <c r="D19">
         <v>0</v>
@@ -1372,7 +1372,7 @@
         <v>0</v>
       </c>
       <c r="G19">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H19">
         <v>1</v>
@@ -1381,15 +1381,15 @@
         <v>3</v>
       </c>
       <c r="J19">
-        <f t="shared" si="4"/>
-        <v>60</v>
+        <f t="shared" ref="J19:J21" si="22">G19*20</f>
+        <v>20</v>
       </c>
       <c r="K19">
-        <f t="shared" si="5"/>
+        <f t="shared" si="20"/>
         <v>20</v>
       </c>
       <c r="L19">
-        <f t="shared" si="6"/>
+        <f t="shared" si="21"/>
         <v>60</v>
       </c>
       <c r="M19">
@@ -1407,13 +1407,13 @@
     </row>
     <row r="20" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A20">
-        <v>1000</v>
+        <v>-180</v>
       </c>
       <c r="B20">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="C20">
-        <v>1000</v>
+        <v>-180</v>
       </c>
       <c r="D20">
         <v>0</v>
@@ -1431,19 +1431,19 @@
         <v>1</v>
       </c>
       <c r="I20">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J20">
-        <f t="shared" si="4"/>
+        <f t="shared" si="22"/>
         <v>60</v>
       </c>
       <c r="K20">
-        <f t="shared" si="5"/>
+        <f t="shared" si="20"/>
         <v>20</v>
       </c>
       <c r="L20">
-        <f t="shared" si="6"/>
-        <v>60</v>
+        <f t="shared" si="21"/>
+        <v>20</v>
       </c>
       <c r="M20">
         <v>0</v>
@@ -1460,13 +1460,13 @@
     </row>
     <row r="21" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A21">
-        <v>1000</v>
+        <v>-180</v>
       </c>
       <c r="B21">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="C21">
-        <v>1000</v>
+        <v>-200</v>
       </c>
       <c r="D21">
         <v>0</v>
@@ -1484,19 +1484,19 @@
         <v>1</v>
       </c>
       <c r="I21">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J21">
-        <f t="shared" si="4"/>
+        <f t="shared" si="22"/>
         <v>60</v>
       </c>
       <c r="K21">
-        <f t="shared" si="5"/>
+        <f t="shared" ref="K21:K24" si="23">H21*20</f>
         <v>20</v>
       </c>
       <c r="L21">
-        <f t="shared" si="6"/>
-        <v>60</v>
+        <f t="shared" ref="L21:L24" si="24">I21*20</f>
+        <v>20</v>
       </c>
       <c r="M21">
         <v>0</v>
@@ -1513,13 +1513,13 @@
     </row>
     <row r="22" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A22">
-        <v>1000</v>
+        <v>-180</v>
       </c>
       <c r="B22">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="C22">
-        <v>1000</v>
+        <v>-220</v>
       </c>
       <c r="D22">
         <v>0</v>
@@ -1537,19 +1537,19 @@
         <v>1</v>
       </c>
       <c r="I22">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J22">
-        <f t="shared" si="4"/>
+        <f t="shared" ref="J22:J24" si="25">G22*20</f>
         <v>60</v>
       </c>
       <c r="K22">
-        <f t="shared" si="5"/>
+        <f t="shared" si="23"/>
         <v>20</v>
       </c>
       <c r="L22">
-        <f t="shared" si="6"/>
-        <v>60</v>
+        <f t="shared" si="24"/>
+        <v>20</v>
       </c>
       <c r="M22">
         <v>0</v>
@@ -1566,13 +1566,13 @@
     </row>
     <row r="23" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A23">
-        <v>1000</v>
+        <v>-180</v>
       </c>
       <c r="B23">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="C23">
-        <v>1000</v>
+        <v>-240</v>
       </c>
       <c r="D23">
         <v>0</v>
@@ -1590,19 +1590,19 @@
         <v>1</v>
       </c>
       <c r="I23">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J23">
-        <f t="shared" si="4"/>
+        <f t="shared" si="25"/>
         <v>60</v>
       </c>
       <c r="K23">
-        <f t="shared" si="5"/>
+        <f t="shared" si="23"/>
         <v>20</v>
       </c>
       <c r="L23">
-        <f t="shared" si="6"/>
-        <v>60</v>
+        <f t="shared" si="24"/>
+        <v>20</v>
       </c>
       <c r="M23">
         <v>0</v>
@@ -1619,13 +1619,13 @@
     </row>
     <row r="24" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A24">
-        <v>1000</v>
+        <v>-180</v>
       </c>
       <c r="B24">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="C24">
-        <v>1000</v>
+        <v>-260</v>
       </c>
       <c r="D24">
         <v>0</v>
@@ -1643,19 +1643,19 @@
         <v>1</v>
       </c>
       <c r="I24">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J24">
-        <f t="shared" si="4"/>
+        <f t="shared" si="25"/>
         <v>60</v>
       </c>
       <c r="K24">
-        <f t="shared" si="5"/>
+        <f t="shared" si="23"/>
         <v>20</v>
       </c>
       <c r="L24">
-        <f t="shared" si="6"/>
-        <v>60</v>
+        <f t="shared" si="24"/>
+        <v>20</v>
       </c>
       <c r="M24">
         <v>0</v>
@@ -1672,13 +1672,13 @@
     </row>
     <row r="25" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A25">
-        <v>1000</v>
+        <v>-200</v>
       </c>
       <c r="B25">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="C25">
-        <v>1000</v>
+        <v>-300</v>
       </c>
       <c r="D25">
         <v>0</v>
@@ -1690,7 +1690,7 @@
         <v>0</v>
       </c>
       <c r="G25">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H25">
         <v>1</v>
@@ -1699,15 +1699,15 @@
         <v>3</v>
       </c>
       <c r="J25">
-        <f t="shared" si="4"/>
-        <v>60</v>
+        <f t="shared" ref="J25:J27" si="26">G25*20</f>
+        <v>20</v>
       </c>
       <c r="K25">
-        <f t="shared" si="5"/>
+        <f t="shared" ref="K25:K28" si="27">H25*20</f>
         <v>20</v>
       </c>
       <c r="L25">
-        <f t="shared" si="6"/>
+        <f t="shared" ref="L25:L28" si="28">I25*20</f>
         <v>60</v>
       </c>
       <c r="M25">
@@ -1725,13 +1725,13 @@
     </row>
     <row r="26" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A26">
-        <v>1000</v>
+        <v>-180</v>
       </c>
       <c r="B26">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="C26">
-        <v>1000</v>
+        <v>-300</v>
       </c>
       <c r="D26">
         <v>0</v>
@@ -1743,7 +1743,7 @@
         <v>0</v>
       </c>
       <c r="G26">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H26">
         <v>1</v>
@@ -1752,15 +1752,15 @@
         <v>3</v>
       </c>
       <c r="J26">
-        <f t="shared" si="4"/>
-        <v>60</v>
+        <f t="shared" si="26"/>
+        <v>20</v>
       </c>
       <c r="K26">
-        <f t="shared" si="5"/>
+        <f t="shared" si="27"/>
         <v>20</v>
       </c>
       <c r="L26">
-        <f t="shared" si="6"/>
+        <f t="shared" si="28"/>
         <v>60</v>
       </c>
       <c r="M26">
@@ -1778,13 +1778,13 @@
     </row>
     <row r="27" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A27">
-        <v>1000</v>
+        <v>-160</v>
       </c>
       <c r="B27">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="C27">
-        <v>1000</v>
+        <v>-300</v>
       </c>
       <c r="D27">
         <v>0</v>
@@ -1796,7 +1796,7 @@
         <v>0</v>
       </c>
       <c r="G27">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H27">
         <v>1</v>
@@ -1805,15 +1805,15 @@
         <v>3</v>
       </c>
       <c r="J27">
-        <f t="shared" si="4"/>
-        <v>60</v>
+        <f t="shared" si="26"/>
+        <v>20</v>
       </c>
       <c r="K27">
-        <f t="shared" si="5"/>
+        <f t="shared" si="27"/>
         <v>20</v>
       </c>
       <c r="L27">
-        <f t="shared" si="6"/>
+        <f t="shared" si="28"/>
         <v>60</v>
       </c>
       <c r="M27">
@@ -1831,13 +1831,13 @@
     </row>
     <row r="28" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A28">
-        <v>1000</v>
+        <v>-140</v>
       </c>
       <c r="B28">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="C28">
-        <v>1000</v>
+        <v>-300</v>
       </c>
       <c r="D28">
         <v>0</v>
@@ -1849,7 +1849,7 @@
         <v>0</v>
       </c>
       <c r="G28">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H28">
         <v>1</v>
@@ -1858,15 +1858,15 @@
         <v>3</v>
       </c>
       <c r="J28">
-        <f t="shared" si="4"/>
-        <v>60</v>
+        <f t="shared" ref="J28:J30" si="29">G28*20</f>
+        <v>20</v>
       </c>
       <c r="K28">
-        <f t="shared" si="5"/>
+        <f t="shared" si="27"/>
         <v>20</v>
       </c>
       <c r="L28">
-        <f t="shared" si="6"/>
+        <f t="shared" si="28"/>
         <v>60</v>
       </c>
       <c r="M28">
@@ -1884,13 +1884,13 @@
     </row>
     <row r="29" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A29">
-        <v>1000</v>
+        <v>-120</v>
       </c>
       <c r="B29">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="C29">
-        <v>1000</v>
+        <v>-300</v>
       </c>
       <c r="D29">
         <v>0</v>
@@ -1902,7 +1902,7 @@
         <v>0</v>
       </c>
       <c r="G29">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H29">
         <v>1</v>
@@ -1911,15 +1911,15 @@
         <v>3</v>
       </c>
       <c r="J29">
-        <f t="shared" si="4"/>
-        <v>60</v>
+        <f t="shared" si="29"/>
+        <v>20</v>
       </c>
       <c r="K29">
-        <f t="shared" si="5"/>
+        <f t="shared" ref="K29:K32" si="30">H29*20</f>
         <v>20</v>
       </c>
       <c r="L29">
-        <f t="shared" si="6"/>
+        <f t="shared" ref="L29:L32" si="31">I29*20</f>
         <v>60</v>
       </c>
       <c r="M29">
@@ -1937,13 +1937,13 @@
     </row>
     <row r="30" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A30">
-        <v>1000</v>
+        <v>-100</v>
       </c>
       <c r="B30">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="C30">
-        <v>1000</v>
+        <v>-300</v>
       </c>
       <c r="D30">
         <v>0</v>
@@ -1955,7 +1955,7 @@
         <v>0</v>
       </c>
       <c r="G30">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H30">
         <v>1</v>
@@ -1964,15 +1964,15 @@
         <v>3</v>
       </c>
       <c r="J30">
-        <f t="shared" si="4"/>
-        <v>60</v>
+        <f t="shared" si="29"/>
+        <v>20</v>
       </c>
       <c r="K30">
-        <f t="shared" si="5"/>
+        <f t="shared" si="30"/>
         <v>20</v>
       </c>
       <c r="L30">
-        <f t="shared" si="6"/>
+        <f t="shared" si="31"/>
         <v>60</v>
       </c>
       <c r="M30">
@@ -1990,13 +1990,13 @@
     </row>
     <row r="31" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A31">
-        <v>1000</v>
+        <v>-60</v>
       </c>
       <c r="B31">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="C31">
-        <v>1000</v>
+        <v>-300</v>
       </c>
       <c r="D31">
         <v>0</v>
@@ -2008,7 +2008,7 @@
         <v>0</v>
       </c>
       <c r="G31">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H31">
         <v>1</v>
@@ -2017,15 +2017,15 @@
         <v>3</v>
       </c>
       <c r="J31">
-        <f t="shared" si="4"/>
-        <v>60</v>
+        <f t="shared" ref="J31:J33" si="32">G31*20</f>
+        <v>20</v>
       </c>
       <c r="K31">
-        <f t="shared" si="5"/>
+        <f t="shared" si="30"/>
         <v>20</v>
       </c>
       <c r="L31">
-        <f t="shared" si="6"/>
+        <f t="shared" si="31"/>
         <v>60</v>
       </c>
       <c r="M31">
@@ -2043,13 +2043,13 @@
     </row>
     <row r="32" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A32">
-        <v>1000</v>
+        <v>-40</v>
       </c>
       <c r="B32">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="C32">
-        <v>1000</v>
+        <v>-300</v>
       </c>
       <c r="D32">
         <v>0</v>
@@ -2061,7 +2061,7 @@
         <v>0</v>
       </c>
       <c r="G32">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H32">
         <v>1</v>
@@ -2070,15 +2070,15 @@
         <v>3</v>
       </c>
       <c r="J32">
-        <f t="shared" si="4"/>
-        <v>60</v>
+        <f t="shared" si="32"/>
+        <v>20</v>
       </c>
       <c r="K32">
-        <f t="shared" si="5"/>
+        <f t="shared" si="30"/>
         <v>20</v>
       </c>
       <c r="L32">
-        <f t="shared" si="6"/>
+        <f t="shared" si="31"/>
         <v>60</v>
       </c>
       <c r="M32">
@@ -2096,13 +2096,13 @@
     </row>
     <row r="33" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A33">
-        <v>1000</v>
+        <v>-20</v>
       </c>
       <c r="B33">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="C33">
-        <v>1000</v>
+        <v>-300</v>
       </c>
       <c r="D33">
         <v>0</v>
@@ -2114,7 +2114,7 @@
         <v>0</v>
       </c>
       <c r="G33">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H33">
         <v>1</v>
@@ -2123,15 +2123,15 @@
         <v>3</v>
       </c>
       <c r="J33">
-        <f t="shared" si="4"/>
-        <v>60</v>
+        <f t="shared" si="32"/>
+        <v>20</v>
       </c>
       <c r="K33">
-        <f t="shared" si="5"/>
+        <f t="shared" ref="K33:K36" si="33">H33*20</f>
         <v>20</v>
       </c>
       <c r="L33">
-        <f t="shared" si="6"/>
+        <f t="shared" ref="L33:L36" si="34">I33*20</f>
         <v>60</v>
       </c>
       <c r="M33">
@@ -2149,13 +2149,13 @@
     </row>
     <row r="34" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A34">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="B34">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="C34">
-        <v>1000</v>
+        <v>-300</v>
       </c>
       <c r="D34">
         <v>0</v>
@@ -2167,7 +2167,7 @@
         <v>0</v>
       </c>
       <c r="G34">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H34">
         <v>1</v>
@@ -2176,15 +2176,15 @@
         <v>3</v>
       </c>
       <c r="J34">
-        <f t="shared" si="4"/>
-        <v>60</v>
+        <f t="shared" ref="J34:J36" si="35">G34*20</f>
+        <v>20</v>
       </c>
       <c r="K34">
-        <f t="shared" si="5"/>
+        <f t="shared" si="33"/>
         <v>20</v>
       </c>
       <c r="L34">
-        <f t="shared" si="6"/>
+        <f t="shared" si="34"/>
         <v>60</v>
       </c>
       <c r="M34">
@@ -2202,13 +2202,13 @@
     </row>
     <row r="35" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A35">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="B35">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="C35">
-        <v>1000</v>
+        <v>-300</v>
       </c>
       <c r="D35">
         <v>0</v>
@@ -2220,7 +2220,7 @@
         <v>0</v>
       </c>
       <c r="G35">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H35">
         <v>1</v>
@@ -2229,15 +2229,15 @@
         <v>3</v>
       </c>
       <c r="J35">
-        <f t="shared" si="4"/>
-        <v>60</v>
+        <f t="shared" si="35"/>
+        <v>20</v>
       </c>
       <c r="K35">
-        <f t="shared" si="5"/>
+        <f t="shared" si="33"/>
         <v>20</v>
       </c>
       <c r="L35">
-        <f t="shared" si="6"/>
+        <f t="shared" si="34"/>
         <v>60</v>
       </c>
       <c r="M35">
@@ -2255,13 +2255,13 @@
     </row>
     <row r="36" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A36">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="B36">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="C36">
-        <v>1000</v>
+        <v>-300</v>
       </c>
       <c r="D36">
         <v>0</v>
@@ -2273,7 +2273,7 @@
         <v>0</v>
       </c>
       <c r="G36">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H36">
         <v>1</v>
@@ -2282,15 +2282,15 @@
         <v>3</v>
       </c>
       <c r="J36">
-        <f t="shared" si="4"/>
-        <v>60</v>
+        <f t="shared" si="35"/>
+        <v>20</v>
       </c>
       <c r="K36">
-        <f t="shared" si="5"/>
+        <f t="shared" si="33"/>
         <v>20</v>
       </c>
       <c r="L36">
-        <f t="shared" si="6"/>
+        <f t="shared" si="34"/>
         <v>60</v>
       </c>
       <c r="M36">
@@ -2308,13 +2308,13 @@
     </row>
     <row r="37" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A37">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="B37">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="C37">
-        <v>1000</v>
+        <v>-300</v>
       </c>
       <c r="D37">
         <v>0</v>
@@ -2326,7 +2326,7 @@
         <v>0</v>
       </c>
       <c r="G37">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H37">
         <v>1</v>
@@ -2335,15 +2335,15 @@
         <v>3</v>
       </c>
       <c r="J37">
-        <f t="shared" si="4"/>
-        <v>60</v>
+        <f t="shared" ref="J37:J100" si="36">G37*20</f>
+        <v>20</v>
       </c>
       <c r="K37">
-        <f t="shared" si="5"/>
+        <f t="shared" ref="K37:K100" si="37">H37*20</f>
         <v>20</v>
       </c>
       <c r="L37">
-        <f t="shared" si="6"/>
+        <f t="shared" ref="L37:L100" si="38">I37*20</f>
         <v>60</v>
       </c>
       <c r="M37">
@@ -2361,13 +2361,13 @@
     </row>
     <row r="38" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A38">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="B38">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="C38">
-        <v>1000</v>
+        <v>-300</v>
       </c>
       <c r="D38">
         <v>0</v>
@@ -2379,7 +2379,7 @@
         <v>0</v>
       </c>
       <c r="G38">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H38">
         <v>1</v>
@@ -2388,15 +2388,15 @@
         <v>3</v>
       </c>
       <c r="J38">
-        <f t="shared" si="4"/>
-        <v>60</v>
+        <f t="shared" si="36"/>
+        <v>20</v>
       </c>
       <c r="K38">
-        <f t="shared" si="5"/>
+        <f t="shared" si="37"/>
         <v>20</v>
       </c>
       <c r="L38">
-        <f t="shared" si="6"/>
+        <f t="shared" si="38"/>
         <v>60</v>
       </c>
       <c r="M38">
@@ -2414,13 +2414,13 @@
     </row>
     <row r="39" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A39">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="B39">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="C39">
-        <v>1000</v>
+        <v>-300</v>
       </c>
       <c r="D39">
         <v>0</v>
@@ -2432,7 +2432,7 @@
         <v>0</v>
       </c>
       <c r="G39">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H39">
         <v>1</v>
@@ -2441,15 +2441,15 @@
         <v>3</v>
       </c>
       <c r="J39">
-        <f t="shared" si="4"/>
-        <v>60</v>
+        <f t="shared" si="36"/>
+        <v>20</v>
       </c>
       <c r="K39">
-        <f t="shared" si="5"/>
+        <f t="shared" si="37"/>
         <v>20</v>
       </c>
       <c r="L39">
-        <f t="shared" si="6"/>
+        <f t="shared" si="38"/>
         <v>60</v>
       </c>
       <c r="M39">
@@ -2467,13 +2467,13 @@
     </row>
     <row r="40" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A40">
-        <v>1000</v>
+        <v>180</v>
       </c>
       <c r="B40">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="C40">
-        <v>1000</v>
+        <v>-300</v>
       </c>
       <c r="D40">
         <v>0</v>
@@ -2485,7 +2485,7 @@
         <v>0</v>
       </c>
       <c r="G40">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H40">
         <v>1</v>
@@ -2494,15 +2494,15 @@
         <v>3</v>
       </c>
       <c r="J40">
-        <f t="shared" si="4"/>
-        <v>60</v>
+        <f t="shared" si="36"/>
+        <v>20</v>
       </c>
       <c r="K40">
-        <f t="shared" si="5"/>
+        <f t="shared" si="37"/>
         <v>20</v>
       </c>
       <c r="L40">
-        <f t="shared" si="6"/>
+        <f t="shared" si="38"/>
         <v>60</v>
       </c>
       <c r="M40">
@@ -2520,13 +2520,13 @@
     </row>
     <row r="41" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A41">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="B41">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="C41">
-        <v>1000</v>
+        <v>-300</v>
       </c>
       <c r="D41">
         <v>0</v>
@@ -2538,7 +2538,7 @@
         <v>0</v>
       </c>
       <c r="G41">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H41">
         <v>1</v>
@@ -2547,15 +2547,15 @@
         <v>3</v>
       </c>
       <c r="J41">
-        <f t="shared" si="4"/>
-        <v>60</v>
+        <f t="shared" si="36"/>
+        <v>20</v>
       </c>
       <c r="K41">
-        <f t="shared" si="5"/>
+        <f t="shared" si="37"/>
         <v>20</v>
       </c>
       <c r="L41">
-        <f t="shared" si="6"/>
+        <f t="shared" si="38"/>
         <v>60</v>
       </c>
       <c r="M41">
@@ -2573,13 +2573,13 @@
     </row>
     <row r="42" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A42">
-        <v>1000</v>
+        <v>220</v>
       </c>
       <c r="B42">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="C42">
-        <v>1000</v>
+        <v>-300</v>
       </c>
       <c r="D42">
         <v>0</v>
@@ -2591,7 +2591,7 @@
         <v>0</v>
       </c>
       <c r="G42">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H42">
         <v>1</v>
@@ -2600,15 +2600,15 @@
         <v>3</v>
       </c>
       <c r="J42">
-        <f t="shared" si="4"/>
-        <v>60</v>
+        <f t="shared" si="36"/>
+        <v>20</v>
       </c>
       <c r="K42">
-        <f t="shared" si="5"/>
+        <f t="shared" si="37"/>
         <v>20</v>
       </c>
       <c r="L42">
-        <f t="shared" si="6"/>
+        <f t="shared" si="38"/>
         <v>60</v>
       </c>
       <c r="M42">
@@ -2626,13 +2626,13 @@
     </row>
     <row r="43" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A43">
-        <v>1000</v>
+        <v>260</v>
       </c>
       <c r="B43">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="C43">
-        <v>1000</v>
+        <v>-320</v>
       </c>
       <c r="D43">
         <v>0</v>
@@ -2650,19 +2650,19 @@
         <v>1</v>
       </c>
       <c r="I43">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J43">
-        <f t="shared" si="4"/>
+        <f t="shared" si="36"/>
         <v>60</v>
       </c>
       <c r="K43">
-        <f t="shared" si="5"/>
+        <f t="shared" si="37"/>
         <v>20</v>
       </c>
       <c r="L43">
-        <f t="shared" si="6"/>
-        <v>60</v>
+        <f t="shared" si="38"/>
+        <v>20</v>
       </c>
       <c r="M43">
         <v>0</v>
@@ -2679,13 +2679,13 @@
     </row>
     <row r="44" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A44">
-        <v>1000</v>
+        <v>260</v>
       </c>
       <c r="B44">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="C44">
-        <v>1000</v>
+        <v>-300</v>
       </c>
       <c r="D44">
         <v>0</v>
@@ -2703,19 +2703,19 @@
         <v>1</v>
       </c>
       <c r="I44">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J44">
-        <f t="shared" si="4"/>
+        <f t="shared" si="36"/>
         <v>60</v>
       </c>
       <c r="K44">
-        <f t="shared" si="5"/>
+        <f t="shared" si="37"/>
         <v>20</v>
       </c>
       <c r="L44">
-        <f t="shared" si="6"/>
-        <v>60</v>
+        <f t="shared" si="38"/>
+        <v>20</v>
       </c>
       <c r="M44">
         <v>0</v>
@@ -2732,13 +2732,13 @@
     </row>
     <row r="45" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A45">
-        <v>1000</v>
+        <v>260</v>
       </c>
       <c r="B45">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="C45">
-        <v>1000</v>
+        <v>-280</v>
       </c>
       <c r="D45">
         <v>0</v>
@@ -2756,19 +2756,19 @@
         <v>1</v>
       </c>
       <c r="I45">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J45">
-        <f t="shared" si="4"/>
+        <f t="shared" si="36"/>
         <v>60</v>
       </c>
       <c r="K45">
-        <f t="shared" si="5"/>
+        <f t="shared" si="37"/>
         <v>20</v>
       </c>
       <c r="L45">
-        <f t="shared" si="6"/>
-        <v>60</v>
+        <f t="shared" si="38"/>
+        <v>20</v>
       </c>
       <c r="M45">
         <v>0</v>
@@ -2785,13 +2785,13 @@
     </row>
     <row r="46" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A46">
-        <v>1000</v>
+        <v>260</v>
       </c>
       <c r="B46">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="C46">
-        <v>1000</v>
+        <v>-260</v>
       </c>
       <c r="D46">
         <v>0</v>
@@ -2809,19 +2809,19 @@
         <v>1</v>
       </c>
       <c r="I46">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J46">
-        <f t="shared" si="4"/>
+        <f t="shared" si="36"/>
         <v>60</v>
       </c>
       <c r="K46">
-        <f t="shared" si="5"/>
+        <f t="shared" si="37"/>
         <v>20</v>
       </c>
       <c r="L46">
-        <f t="shared" si="6"/>
-        <v>60</v>
+        <f t="shared" si="38"/>
+        <v>20</v>
       </c>
       <c r="M46">
         <v>0</v>
@@ -2838,13 +2838,13 @@
     </row>
     <row r="47" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A47">
-        <v>1000</v>
+        <v>260</v>
       </c>
       <c r="B47">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="C47">
-        <v>1000</v>
+        <v>-240</v>
       </c>
       <c r="D47">
         <v>0</v>
@@ -2862,19 +2862,19 @@
         <v>1</v>
       </c>
       <c r="I47">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J47">
-        <f t="shared" si="4"/>
+        <f t="shared" si="36"/>
         <v>60</v>
       </c>
       <c r="K47">
-        <f t="shared" si="5"/>
+        <f t="shared" si="37"/>
         <v>20</v>
       </c>
       <c r="L47">
-        <f t="shared" si="6"/>
-        <v>60</v>
+        <f t="shared" si="38"/>
+        <v>20</v>
       </c>
       <c r="M47">
         <v>0</v>
@@ -2891,13 +2891,13 @@
     </row>
     <row r="48" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A48">
-        <v>1000</v>
+        <v>260</v>
       </c>
       <c r="B48">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="C48">
-        <v>1000</v>
+        <v>-220</v>
       </c>
       <c r="D48">
         <v>0</v>
@@ -2915,19 +2915,19 @@
         <v>1</v>
       </c>
       <c r="I48">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J48">
-        <f t="shared" si="4"/>
+        <f t="shared" si="36"/>
         <v>60</v>
       </c>
       <c r="K48">
-        <f t="shared" si="5"/>
+        <f t="shared" si="37"/>
         <v>20</v>
       </c>
       <c r="L48">
-        <f t="shared" si="6"/>
-        <v>60</v>
+        <f t="shared" si="38"/>
+        <v>20</v>
       </c>
       <c r="M48">
         <v>0</v>
@@ -2944,13 +2944,13 @@
     </row>
     <row r="49" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A49">
-        <v>1000</v>
+        <v>260</v>
       </c>
       <c r="B49">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="C49">
-        <v>1000</v>
+        <v>-200</v>
       </c>
       <c r="D49">
         <v>0</v>
@@ -2968,19 +2968,19 @@
         <v>1</v>
       </c>
       <c r="I49">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J49">
-        <f t="shared" si="4"/>
+        <f t="shared" si="36"/>
         <v>60</v>
       </c>
       <c r="K49">
-        <f t="shared" si="5"/>
+        <f t="shared" si="37"/>
         <v>20</v>
       </c>
       <c r="L49">
-        <f t="shared" si="6"/>
-        <v>60</v>
+        <f t="shared" si="38"/>
+        <v>20</v>
       </c>
       <c r="M49">
         <v>0</v>
@@ -2997,13 +2997,13 @@
     </row>
     <row r="50" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A50">
-        <v>1000</v>
+        <v>260</v>
       </c>
       <c r="B50">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="C50">
-        <v>1000</v>
+        <v>-180</v>
       </c>
       <c r="D50">
         <v>0</v>
@@ -3021,19 +3021,19 @@
         <v>1</v>
       </c>
       <c r="I50">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J50">
-        <f t="shared" si="4"/>
+        <f t="shared" si="36"/>
         <v>60</v>
       </c>
       <c r="K50">
-        <f t="shared" si="5"/>
+        <f t="shared" si="37"/>
         <v>20</v>
       </c>
       <c r="L50">
-        <f t="shared" si="6"/>
-        <v>60</v>
+        <f t="shared" si="38"/>
+        <v>20</v>
       </c>
       <c r="M50">
         <v>0</v>
@@ -3050,13 +3050,13 @@
     </row>
     <row r="51" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A51">
-        <v>1000</v>
+        <v>260</v>
       </c>
       <c r="B51">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="C51">
-        <v>1000</v>
+        <v>-160</v>
       </c>
       <c r="D51">
         <v>0</v>
@@ -3074,19 +3074,19 @@
         <v>1</v>
       </c>
       <c r="I51">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J51">
-        <f t="shared" si="4"/>
+        <f t="shared" si="36"/>
         <v>60</v>
       </c>
       <c r="K51">
-        <f t="shared" si="5"/>
+        <f t="shared" si="37"/>
         <v>20</v>
       </c>
       <c r="L51">
-        <f t="shared" si="6"/>
-        <v>60</v>
+        <f t="shared" si="38"/>
+        <v>20</v>
       </c>
       <c r="M51">
         <v>0</v>
@@ -3103,13 +3103,13 @@
     </row>
     <row r="52" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A52">
-        <v>1000</v>
+        <v>340</v>
       </c>
       <c r="B52">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="C52">
-        <v>1000</v>
+        <v>-120</v>
       </c>
       <c r="D52">
         <v>0</v>
@@ -3127,19 +3127,19 @@
         <v>1</v>
       </c>
       <c r="I52">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J52">
-        <f t="shared" si="4"/>
+        <f t="shared" si="36"/>
         <v>60</v>
       </c>
       <c r="K52">
-        <f t="shared" si="5"/>
+        <f t="shared" si="37"/>
         <v>20</v>
       </c>
       <c r="L52">
-        <f t="shared" si="6"/>
-        <v>60</v>
+        <f t="shared" si="38"/>
+        <v>20</v>
       </c>
       <c r="M52">
         <v>0</v>
@@ -3156,13 +3156,13 @@
     </row>
     <row r="53" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A53">
-        <v>1000</v>
+        <v>340</v>
       </c>
       <c r="B53">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="C53">
-        <v>1000</v>
+        <v>-100</v>
       </c>
       <c r="D53">
         <v>0</v>
@@ -3180,19 +3180,19 @@
         <v>1</v>
       </c>
       <c r="I53">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J53">
-        <f t="shared" si="4"/>
+        <f t="shared" si="36"/>
         <v>60</v>
       </c>
       <c r="K53">
-        <f t="shared" si="5"/>
+        <f t="shared" si="37"/>
         <v>20</v>
       </c>
       <c r="L53">
-        <f t="shared" si="6"/>
-        <v>60</v>
+        <f t="shared" si="38"/>
+        <v>20</v>
       </c>
       <c r="M53">
         <v>0</v>
@@ -3209,13 +3209,13 @@
     </row>
     <row r="54" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A54">
-        <v>1000</v>
+        <v>340</v>
       </c>
       <c r="B54">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="C54">
-        <v>1000</v>
+        <v>-80</v>
       </c>
       <c r="D54">
         <v>0</v>
@@ -3233,19 +3233,19 @@
         <v>1</v>
       </c>
       <c r="I54">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J54">
-        <f t="shared" si="4"/>
+        <f t="shared" si="36"/>
         <v>60</v>
       </c>
       <c r="K54">
-        <f t="shared" si="5"/>
+        <f t="shared" si="37"/>
         <v>20</v>
       </c>
       <c r="L54">
-        <f t="shared" si="6"/>
-        <v>60</v>
+        <f t="shared" si="38"/>
+        <v>20</v>
       </c>
       <c r="M54">
         <v>0</v>
@@ -3262,13 +3262,13 @@
     </row>
     <row r="55" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A55">
-        <v>1000</v>
+        <v>420</v>
       </c>
       <c r="B55">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="C55">
-        <v>1000</v>
+        <v>-40</v>
       </c>
       <c r="D55">
         <v>0</v>
@@ -3286,19 +3286,19 @@
         <v>1</v>
       </c>
       <c r="I55">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J55">
-        <f t="shared" si="4"/>
+        <f t="shared" si="36"/>
         <v>60</v>
       </c>
       <c r="K55">
-        <f t="shared" si="5"/>
+        <f t="shared" si="37"/>
         <v>20</v>
       </c>
       <c r="L55">
-        <f t="shared" si="6"/>
-        <v>60</v>
+        <f t="shared" si="38"/>
+        <v>20</v>
       </c>
       <c r="M55">
         <v>0</v>
@@ -3315,13 +3315,13 @@
     </row>
     <row r="56" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A56">
-        <v>1000</v>
+        <v>420</v>
       </c>
       <c r="B56">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="C56">
-        <v>1000</v>
+        <v>-20</v>
       </c>
       <c r="D56">
         <v>0</v>
@@ -3339,19 +3339,19 @@
         <v>1</v>
       </c>
       <c r="I56">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J56">
-        <f t="shared" si="4"/>
+        <f t="shared" si="36"/>
         <v>60</v>
       </c>
       <c r="K56">
-        <f t="shared" si="5"/>
+        <f t="shared" si="37"/>
         <v>20</v>
       </c>
       <c r="L56">
-        <f t="shared" si="6"/>
-        <v>60</v>
+        <f t="shared" si="38"/>
+        <v>20</v>
       </c>
       <c r="M56">
         <v>0</v>
@@ -3368,13 +3368,13 @@
     </row>
     <row r="57" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A57">
-        <v>1000</v>
+        <v>420</v>
       </c>
       <c r="B57">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="C57">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="D57">
         <v>0</v>
@@ -3392,19 +3392,19 @@
         <v>1</v>
       </c>
       <c r="I57">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J57">
-        <f t="shared" si="4"/>
+        <f t="shared" si="36"/>
         <v>60</v>
       </c>
       <c r="K57">
-        <f t="shared" si="5"/>
+        <f t="shared" si="37"/>
         <v>20</v>
       </c>
       <c r="L57">
-        <f t="shared" si="6"/>
-        <v>60</v>
+        <f t="shared" si="38"/>
+        <v>20</v>
       </c>
       <c r="M57">
         <v>0</v>
@@ -3421,13 +3421,13 @@
     </row>
     <row r="58" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A58">
-        <v>1000</v>
+        <v>420</v>
       </c>
       <c r="B58">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="C58">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="D58">
         <v>0</v>
@@ -3445,19 +3445,19 @@
         <v>1</v>
       </c>
       <c r="I58">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J58">
-        <f t="shared" si="4"/>
+        <f t="shared" si="36"/>
         <v>60</v>
       </c>
       <c r="K58">
-        <f t="shared" si="5"/>
+        <f t="shared" si="37"/>
         <v>20</v>
       </c>
       <c r="L58">
-        <f t="shared" si="6"/>
-        <v>60</v>
+        <f t="shared" si="38"/>
+        <v>20</v>
       </c>
       <c r="M58">
         <v>0</v>
@@ -3474,13 +3474,13 @@
     </row>
     <row r="59" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A59">
-        <v>1000</v>
+        <v>420</v>
       </c>
       <c r="B59">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="C59">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="D59">
         <v>0</v>
@@ -3498,19 +3498,19 @@
         <v>1</v>
       </c>
       <c r="I59">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J59">
-        <f t="shared" si="4"/>
+        <f t="shared" si="36"/>
         <v>60</v>
       </c>
       <c r="K59">
-        <f t="shared" si="5"/>
+        <f t="shared" si="37"/>
         <v>20</v>
       </c>
       <c r="L59">
-        <f t="shared" si="6"/>
-        <v>60</v>
+        <f t="shared" si="38"/>
+        <v>20</v>
       </c>
       <c r="M59">
         <v>0</v>
@@ -3527,13 +3527,13 @@
     </row>
     <row r="60" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A60">
-        <v>1000</v>
+        <v>420</v>
       </c>
       <c r="B60">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="C60">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="D60">
         <v>0</v>
@@ -3551,19 +3551,19 @@
         <v>1</v>
       </c>
       <c r="I60">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J60">
-        <f t="shared" si="4"/>
+        <f t="shared" si="36"/>
         <v>60</v>
       </c>
       <c r="K60">
-        <f t="shared" si="5"/>
+        <f t="shared" si="37"/>
         <v>20</v>
       </c>
       <c r="L60">
-        <f t="shared" si="6"/>
-        <v>60</v>
+        <f t="shared" si="38"/>
+        <v>20</v>
       </c>
       <c r="M60">
         <v>0</v>
@@ -3580,13 +3580,13 @@
     </row>
     <row r="61" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A61">
-        <v>1000</v>
+        <v>420</v>
       </c>
       <c r="B61">
-        <v>1000</v>
+        <v>180</v>
       </c>
       <c r="C61">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="D61">
         <v>0</v>
@@ -3604,19 +3604,19 @@
         <v>1</v>
       </c>
       <c r="I61">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J61">
-        <f t="shared" si="4"/>
+        <f t="shared" si="36"/>
         <v>60</v>
       </c>
       <c r="K61">
-        <f t="shared" si="5"/>
+        <f t="shared" si="37"/>
         <v>20</v>
       </c>
       <c r="L61">
-        <f t="shared" si="6"/>
-        <v>60</v>
+        <f t="shared" si="38"/>
+        <v>20</v>
       </c>
       <c r="M61">
         <v>0</v>
@@ -3633,13 +3633,13 @@
     </row>
     <row r="62" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A62">
-        <v>1000</v>
+        <v>420</v>
       </c>
       <c r="B62">
-        <v>1000</v>
+        <v>180</v>
       </c>
       <c r="C62">
-        <v>1000</v>
+        <v>180</v>
       </c>
       <c r="D62">
         <v>0</v>
@@ -3657,19 +3657,19 @@
         <v>1</v>
       </c>
       <c r="I62">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J62">
-        <f t="shared" si="4"/>
+        <f t="shared" si="36"/>
         <v>60</v>
       </c>
       <c r="K62">
-        <f t="shared" si="5"/>
+        <f t="shared" si="37"/>
         <v>20</v>
       </c>
       <c r="L62">
-        <f t="shared" si="6"/>
-        <v>60</v>
+        <f t="shared" si="38"/>
+        <v>20</v>
       </c>
       <c r="M62">
         <v>0</v>
@@ -3686,13 +3686,13 @@
     </row>
     <row r="63" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A63">
-        <v>1000</v>
+        <v>420</v>
       </c>
       <c r="B63">
-        <v>1000</v>
+        <v>180</v>
       </c>
       <c r="C63">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="D63">
         <v>0</v>
@@ -3710,19 +3710,19 @@
         <v>1</v>
       </c>
       <c r="I63">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J63">
-        <f t="shared" si="4"/>
+        <f t="shared" si="36"/>
         <v>60</v>
       </c>
       <c r="K63">
-        <f t="shared" si="5"/>
+        <f t="shared" si="37"/>
         <v>20</v>
       </c>
       <c r="L63">
-        <f t="shared" si="6"/>
-        <v>60</v>
+        <f t="shared" si="38"/>
+        <v>20</v>
       </c>
       <c r="M63">
         <v>0</v>
@@ -3739,13 +3739,13 @@
     </row>
     <row r="64" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A64">
-        <v>1000</v>
+        <v>420</v>
       </c>
       <c r="B64">
-        <v>1000</v>
+        <v>180</v>
       </c>
       <c r="C64">
-        <v>1000</v>
+        <v>240</v>
       </c>
       <c r="D64">
         <v>0</v>
@@ -3766,39 +3766,39 @@
         <v>3</v>
       </c>
       <c r="J64">
-        <f t="shared" si="4"/>
+        <f t="shared" si="36"/>
         <v>60</v>
       </c>
       <c r="K64">
-        <f t="shared" si="5"/>
+        <f t="shared" si="37"/>
         <v>20</v>
       </c>
       <c r="L64">
-        <f t="shared" si="6"/>
+        <f t="shared" si="38"/>
         <v>60</v>
       </c>
       <c r="M64">
-        <v>0</v>
+        <v>420</v>
       </c>
       <c r="N64">
-        <v>0</v>
+        <v>280</v>
       </c>
       <c r="O64">
-        <v>0</v>
+        <v>240</v>
       </c>
       <c r="P64">
-        <v>0</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="65" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A65">
-        <v>1000</v>
+        <v>420</v>
       </c>
       <c r="B65">
-        <v>1000</v>
+        <v>280</v>
       </c>
       <c r="C65">
-        <v>1000</v>
+        <v>300</v>
       </c>
       <c r="D65">
         <v>0</v>
@@ -3819,15 +3819,15 @@
         <v>3</v>
       </c>
       <c r="J65">
-        <f t="shared" si="4"/>
+        <f t="shared" si="36"/>
         <v>60</v>
       </c>
       <c r="K65">
-        <f t="shared" si="5"/>
+        <f t="shared" si="37"/>
         <v>20</v>
       </c>
       <c r="L65">
-        <f t="shared" si="6"/>
+        <f t="shared" si="38"/>
         <v>60</v>
       </c>
       <c r="M65">
@@ -3845,13 +3845,13 @@
     </row>
     <row r="66" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A66">
-        <v>1000</v>
+        <v>360</v>
       </c>
       <c r="B66">
-        <v>1000</v>
+        <v>280</v>
       </c>
       <c r="C66">
-        <v>1000</v>
+        <v>300</v>
       </c>
       <c r="D66">
         <v>0</v>
@@ -3872,39 +3872,39 @@
         <v>3</v>
       </c>
       <c r="J66">
-        <f t="shared" si="4"/>
+        <f t="shared" si="36"/>
         <v>60</v>
       </c>
       <c r="K66">
-        <f t="shared" si="5"/>
+        <f t="shared" si="37"/>
         <v>20</v>
       </c>
       <c r="L66">
-        <f t="shared" si="6"/>
+        <f t="shared" si="38"/>
         <v>60</v>
       </c>
       <c r="M66">
-        <v>0</v>
+        <v>160</v>
       </c>
       <c r="N66">
-        <v>0</v>
+        <v>280</v>
       </c>
       <c r="O66">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="P66">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="67" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A67">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="B67">
-        <v>1000</v>
+        <v>280</v>
       </c>
       <c r="C67">
-        <v>1000</v>
+        <v>300</v>
       </c>
       <c r="D67">
         <v>0</v>
@@ -3916,7 +3916,7 @@
         <v>0</v>
       </c>
       <c r="G67">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H67">
         <v>1</v>
@@ -3925,15 +3925,15 @@
         <v>3</v>
       </c>
       <c r="J67">
-        <f t="shared" si="4"/>
-        <v>60</v>
+        <f t="shared" si="36"/>
+        <v>20</v>
       </c>
       <c r="K67">
-        <f t="shared" si="5"/>
+        <f t="shared" si="37"/>
         <v>20</v>
       </c>
       <c r="L67">
-        <f t="shared" si="6"/>
+        <f t="shared" si="38"/>
         <v>60</v>
       </c>
       <c r="M67">
@@ -3951,13 +3951,13 @@
     </row>
     <row r="68" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A68">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="B68">
-        <v>1000</v>
+        <v>280</v>
       </c>
       <c r="C68">
-        <v>1000</v>
+        <v>300</v>
       </c>
       <c r="D68">
         <v>0</v>
@@ -3969,7 +3969,7 @@
         <v>0</v>
       </c>
       <c r="G68">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H68">
         <v>1</v>
@@ -3978,15 +3978,15 @@
         <v>3</v>
       </c>
       <c r="J68">
-        <f t="shared" si="4"/>
-        <v>60</v>
+        <f t="shared" si="36"/>
+        <v>20</v>
       </c>
       <c r="K68">
-        <f t="shared" si="5"/>
+        <f t="shared" si="37"/>
         <v>20</v>
       </c>
       <c r="L68">
-        <f t="shared" si="6"/>
+        <f t="shared" si="38"/>
         <v>60</v>
       </c>
       <c r="M68">
@@ -4004,13 +4004,13 @@
     </row>
     <row r="69" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A69">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="B69">
-        <v>1000</v>
+        <v>280</v>
       </c>
       <c r="C69">
-        <v>1000</v>
+        <v>300</v>
       </c>
       <c r="D69">
         <v>0</v>
@@ -4022,7 +4022,7 @@
         <v>0</v>
       </c>
       <c r="G69">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H69">
         <v>1</v>
@@ -4031,15 +4031,15 @@
         <v>3</v>
       </c>
       <c r="J69">
-        <f t="shared" si="4"/>
-        <v>60</v>
+        <f t="shared" si="36"/>
+        <v>20</v>
       </c>
       <c r="K69">
-        <f t="shared" si="5"/>
+        <f t="shared" si="37"/>
         <v>20</v>
       </c>
       <c r="L69">
-        <f t="shared" si="6"/>
+        <f t="shared" si="38"/>
         <v>60</v>
       </c>
       <c r="M69">
@@ -4057,13 +4057,13 @@
     </row>
     <row r="70" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A70">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="B70">
-        <v>1000</v>
+        <v>280</v>
       </c>
       <c r="C70">
-        <v>1000</v>
+        <v>300</v>
       </c>
       <c r="D70">
         <v>0</v>
@@ -4084,39 +4084,39 @@
         <v>3</v>
       </c>
       <c r="J70">
-        <f t="shared" ref="J70:J100" si="7">G70*20</f>
+        <f t="shared" si="36"/>
         <v>60</v>
       </c>
       <c r="K70">
-        <f t="shared" ref="K70:K100" si="8">H70*20</f>
+        <f t="shared" si="37"/>
         <v>20</v>
       </c>
       <c r="L70">
-        <f t="shared" ref="L70:L100" si="9">I70*20</f>
+        <f t="shared" si="38"/>
         <v>60</v>
       </c>
       <c r="M70">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="N70">
-        <v>0</v>
+        <v>480</v>
       </c>
       <c r="O70">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P70">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="71" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A71">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="B71">
-        <v>1000</v>
+        <v>480</v>
       </c>
       <c r="C71">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="D71">
         <v>0</v>
@@ -4134,19 +4134,19 @@
         <v>1</v>
       </c>
       <c r="I71">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J71">
-        <f t="shared" si="7"/>
+        <f t="shared" si="36"/>
         <v>60</v>
       </c>
       <c r="K71">
-        <f t="shared" si="8"/>
+        <f t="shared" si="37"/>
         <v>20</v>
       </c>
       <c r="L71">
-        <f t="shared" si="9"/>
-        <v>60</v>
+        <f t="shared" si="38"/>
+        <v>20</v>
       </c>
       <c r="M71">
         <v>0</v>
@@ -4163,13 +4163,13 @@
     </row>
     <row r="72" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A72">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="B72">
-        <v>1000</v>
+        <v>480</v>
       </c>
       <c r="C72">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="D72">
         <v>0</v>
@@ -4187,19 +4187,19 @@
         <v>1</v>
       </c>
       <c r="I72">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J72">
-        <f t="shared" si="7"/>
+        <f t="shared" si="36"/>
         <v>60</v>
       </c>
       <c r="K72">
-        <f t="shared" si="8"/>
+        <f t="shared" si="37"/>
         <v>20</v>
       </c>
       <c r="L72">
-        <f t="shared" si="9"/>
-        <v>60</v>
+        <f t="shared" si="38"/>
+        <v>20</v>
       </c>
       <c r="M72">
         <v>0</v>
@@ -4216,13 +4216,13 @@
     </row>
     <row r="73" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A73">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="B73">
-        <v>1000</v>
+        <v>480</v>
       </c>
       <c r="C73">
-        <v>1000</v>
+        <v>-40</v>
       </c>
       <c r="D73">
         <v>0</v>
@@ -4240,19 +4240,19 @@
         <v>1</v>
       </c>
       <c r="I73">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J73">
-        <f t="shared" si="7"/>
+        <f t="shared" si="36"/>
         <v>60</v>
       </c>
       <c r="K73">
-        <f t="shared" si="8"/>
+        <f t="shared" si="37"/>
         <v>20</v>
       </c>
       <c r="L73">
-        <f t="shared" si="9"/>
-        <v>60</v>
+        <f t="shared" si="38"/>
+        <v>20</v>
       </c>
       <c r="M73">
         <v>0</v>
@@ -4269,13 +4269,13 @@
     </row>
     <row r="74" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A74">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="B74">
-        <v>1000</v>
+        <v>480</v>
       </c>
       <c r="C74">
-        <v>1000</v>
+        <v>-80</v>
       </c>
       <c r="D74">
         <v>0</v>
@@ -4293,19 +4293,19 @@
         <v>1</v>
       </c>
       <c r="I74">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J74">
-        <f t="shared" si="7"/>
+        <f t="shared" si="36"/>
         <v>60</v>
       </c>
       <c r="K74">
-        <f t="shared" si="8"/>
+        <f t="shared" si="37"/>
         <v>20</v>
       </c>
       <c r="L74">
-        <f t="shared" si="9"/>
-        <v>60</v>
+        <f t="shared" si="38"/>
+        <v>20</v>
       </c>
       <c r="M74">
         <v>0</v>
@@ -4322,13 +4322,13 @@
     </row>
     <row r="75" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A75">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="B75">
-        <v>1000</v>
+        <v>480</v>
       </c>
       <c r="C75">
-        <v>1000</v>
+        <v>-120</v>
       </c>
       <c r="D75">
         <v>0</v>
@@ -4340,25 +4340,25 @@
         <v>0</v>
       </c>
       <c r="G75">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H75">
         <v>1</v>
       </c>
       <c r="I75">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J75">
-        <f t="shared" si="7"/>
-        <v>60</v>
+        <f t="shared" si="36"/>
+        <v>40</v>
       </c>
       <c r="K75">
-        <f t="shared" si="8"/>
+        <f t="shared" si="37"/>
         <v>20</v>
       </c>
       <c r="L75">
-        <f t="shared" si="9"/>
-        <v>60</v>
+        <f t="shared" si="38"/>
+        <v>20</v>
       </c>
       <c r="M75">
         <v>0</v>
@@ -4375,13 +4375,13 @@
     </row>
     <row r="76" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A76">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="B76">
-        <v>1000</v>
+        <v>480</v>
       </c>
       <c r="C76">
-        <v>1000</v>
+        <v>-160</v>
       </c>
       <c r="D76">
         <v>0</v>
@@ -4393,25 +4393,25 @@
         <v>0</v>
       </c>
       <c r="G76">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H76">
         <v>1</v>
       </c>
       <c r="I76">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J76">
-        <f t="shared" si="7"/>
-        <v>60</v>
+        <f t="shared" si="36"/>
+        <v>40</v>
       </c>
       <c r="K76">
-        <f t="shared" si="8"/>
+        <f t="shared" si="37"/>
         <v>20</v>
       </c>
       <c r="L76">
-        <f t="shared" si="9"/>
-        <v>60</v>
+        <f t="shared" si="38"/>
+        <v>20</v>
       </c>
       <c r="M76">
         <v>0</v>
@@ -4428,13 +4428,13 @@
     </row>
     <row r="77" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A77">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="B77">
-        <v>1000</v>
+        <v>480</v>
       </c>
       <c r="C77">
-        <v>1000</v>
+        <v>-200</v>
       </c>
       <c r="D77">
         <v>0</v>
@@ -4446,25 +4446,25 @@
         <v>0</v>
       </c>
       <c r="G77">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H77">
         <v>1</v>
       </c>
       <c r="I77">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J77">
-        <f t="shared" si="7"/>
-        <v>60</v>
+        <f t="shared" si="36"/>
+        <v>40</v>
       </c>
       <c r="K77">
-        <f t="shared" si="8"/>
+        <f t="shared" si="37"/>
         <v>20</v>
       </c>
       <c r="L77">
-        <f t="shared" si="9"/>
-        <v>60</v>
+        <f t="shared" si="38"/>
+        <v>20</v>
       </c>
       <c r="M77">
         <v>0</v>
@@ -4481,13 +4481,13 @@
     </row>
     <row r="78" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A78">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="B78">
-        <v>1000</v>
+        <v>480</v>
       </c>
       <c r="C78">
-        <v>1000</v>
+        <v>-240</v>
       </c>
       <c r="D78">
         <v>0</v>
@@ -4499,25 +4499,25 @@
         <v>0</v>
       </c>
       <c r="G78">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H78">
         <v>1</v>
       </c>
       <c r="I78">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J78">
-        <f t="shared" si="7"/>
-        <v>60</v>
+        <f t="shared" si="36"/>
+        <v>20</v>
       </c>
       <c r="K78">
-        <f t="shared" si="8"/>
+        <f t="shared" si="37"/>
         <v>20</v>
       </c>
       <c r="L78">
-        <f t="shared" si="9"/>
-        <v>60</v>
+        <f t="shared" si="38"/>
+        <v>20</v>
       </c>
       <c r="M78">
         <v>0</v>
@@ -4534,13 +4534,13 @@
     </row>
     <row r="79" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A79">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="B79">
-        <v>1000</v>
+        <v>480</v>
       </c>
       <c r="C79">
-        <v>1000</v>
+        <v>-280</v>
       </c>
       <c r="D79">
         <v>0</v>
@@ -4552,25 +4552,25 @@
         <v>0</v>
       </c>
       <c r="G79">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H79">
         <v>1</v>
       </c>
       <c r="I79">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J79">
-        <f t="shared" si="7"/>
-        <v>60</v>
+        <f t="shared" si="36"/>
+        <v>20</v>
       </c>
       <c r="K79">
-        <f t="shared" si="8"/>
+        <f t="shared" si="37"/>
         <v>20</v>
       </c>
       <c r="L79">
-        <f t="shared" si="9"/>
-        <v>60</v>
+        <f t="shared" si="38"/>
+        <v>20</v>
       </c>
       <c r="M79">
         <v>0</v>
@@ -4587,13 +4587,13 @@
     </row>
     <row r="80" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A80">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="B80">
-        <v>1000</v>
+        <v>480</v>
       </c>
       <c r="C80">
-        <v>1000</v>
+        <v>-320</v>
       </c>
       <c r="D80">
         <v>0</v>
@@ -4605,25 +4605,25 @@
         <v>0</v>
       </c>
       <c r="G80">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H80">
         <v>1</v>
       </c>
       <c r="I80">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J80">
-        <f t="shared" si="7"/>
-        <v>60</v>
+        <f t="shared" si="36"/>
+        <v>20</v>
       </c>
       <c r="K80">
-        <f t="shared" si="8"/>
+        <f t="shared" si="37"/>
         <v>20</v>
       </c>
       <c r="L80">
-        <f t="shared" si="9"/>
-        <v>60</v>
+        <f t="shared" si="38"/>
+        <v>20</v>
       </c>
       <c r="M80">
         <v>0</v>
@@ -4640,13 +4640,13 @@
     </row>
     <row r="81" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A81">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="B81">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="C81">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="D81">
         <v>0</v>
@@ -4658,25 +4658,25 @@
         <v>0</v>
       </c>
       <c r="G81">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H81">
         <v>1</v>
       </c>
       <c r="I81">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J81">
-        <f t="shared" si="7"/>
-        <v>60</v>
+        <f t="shared" si="36"/>
+        <v>20</v>
       </c>
       <c r="K81">
-        <f t="shared" si="8"/>
+        <f t="shared" si="37"/>
         <v>20</v>
       </c>
       <c r="L81">
-        <f t="shared" si="9"/>
-        <v>60</v>
+        <f t="shared" si="38"/>
+        <v>20</v>
       </c>
       <c r="M81">
         <v>0</v>
@@ -4693,13 +4693,13 @@
     </row>
     <row r="82" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A82">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="B82">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="C82">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="D82">
         <v>0</v>
@@ -4711,25 +4711,25 @@
         <v>0</v>
       </c>
       <c r="G82">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H82">
         <v>1</v>
       </c>
       <c r="I82">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J82">
-        <f t="shared" si="7"/>
-        <v>60</v>
+        <f t="shared" si="36"/>
+        <v>20</v>
       </c>
       <c r="K82">
-        <f t="shared" si="8"/>
+        <f t="shared" si="37"/>
         <v>20</v>
       </c>
       <c r="L82">
-        <f t="shared" si="9"/>
-        <v>60</v>
+        <f t="shared" si="38"/>
+        <v>20</v>
       </c>
       <c r="M82">
         <v>0</v>
@@ -4746,13 +4746,13 @@
     </row>
     <row r="83" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A83">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="B83">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="C83">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="D83">
         <v>0</v>
@@ -4764,25 +4764,25 @@
         <v>0</v>
       </c>
       <c r="G83">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H83">
         <v>1</v>
       </c>
       <c r="I83">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J83">
-        <f t="shared" si="7"/>
-        <v>60</v>
+        <f t="shared" si="36"/>
+        <v>20</v>
       </c>
       <c r="K83">
-        <f t="shared" si="8"/>
+        <f t="shared" si="37"/>
         <v>20</v>
       </c>
       <c r="L83">
-        <f t="shared" si="9"/>
-        <v>60</v>
+        <f t="shared" si="38"/>
+        <v>20</v>
       </c>
       <c r="M83">
         <v>0</v>
@@ -4799,13 +4799,13 @@
     </row>
     <row r="84" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A84">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="B84">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="C84">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="D84">
         <v>0</v>
@@ -4817,25 +4817,25 @@
         <v>0</v>
       </c>
       <c r="G84">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H84">
         <v>1</v>
       </c>
       <c r="I84">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J84">
-        <f t="shared" si="7"/>
-        <v>60</v>
+        <f t="shared" si="36"/>
+        <v>20</v>
       </c>
       <c r="K84">
-        <f t="shared" si="8"/>
+        <f t="shared" si="37"/>
         <v>20</v>
       </c>
       <c r="L84">
-        <f t="shared" si="9"/>
-        <v>60</v>
+        <f t="shared" si="38"/>
+        <v>20</v>
       </c>
       <c r="M84">
         <v>0</v>
@@ -4852,13 +4852,13 @@
     </row>
     <row r="85" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A85">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="B85">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="C85">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="D85">
         <v>0</v>
@@ -4870,25 +4870,25 @@
         <v>0</v>
       </c>
       <c r="G85">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H85">
         <v>1</v>
       </c>
       <c r="I85">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J85">
-        <f t="shared" si="7"/>
-        <v>60</v>
+        <f t="shared" si="36"/>
+        <v>20</v>
       </c>
       <c r="K85">
-        <f t="shared" si="8"/>
+        <f t="shared" si="37"/>
         <v>20</v>
       </c>
       <c r="L85">
-        <f t="shared" si="9"/>
-        <v>60</v>
+        <f t="shared" si="38"/>
+        <v>20</v>
       </c>
       <c r="M85">
         <v>0</v>
@@ -4905,13 +4905,13 @@
     </row>
     <row r="86" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A86">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="B86">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="C86">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="D86">
         <v>0</v>
@@ -4923,25 +4923,25 @@
         <v>0</v>
       </c>
       <c r="G86">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H86">
         <v>1</v>
       </c>
       <c r="I86">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J86">
-        <f t="shared" si="7"/>
-        <v>60</v>
+        <f t="shared" si="36"/>
+        <v>20</v>
       </c>
       <c r="K86">
-        <f t="shared" si="8"/>
+        <f t="shared" si="37"/>
         <v>20</v>
       </c>
       <c r="L86">
-        <f t="shared" si="9"/>
-        <v>60</v>
+        <f t="shared" si="38"/>
+        <v>20</v>
       </c>
       <c r="M86">
         <v>0</v>
@@ -4958,13 +4958,13 @@
     </row>
     <row r="87" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A87">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="B87">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="C87">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="D87">
         <v>0</v>
@@ -4976,25 +4976,25 @@
         <v>0</v>
       </c>
       <c r="G87">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H87">
         <v>1</v>
       </c>
       <c r="I87">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J87">
-        <f t="shared" si="7"/>
-        <v>60</v>
+        <f t="shared" si="36"/>
+        <v>20</v>
       </c>
       <c r="K87">
-        <f t="shared" si="8"/>
+        <f t="shared" si="37"/>
         <v>20</v>
       </c>
       <c r="L87">
-        <f t="shared" si="9"/>
-        <v>60</v>
+        <f t="shared" si="38"/>
+        <v>20</v>
       </c>
       <c r="M87">
         <v>0</v>
@@ -5011,13 +5011,13 @@
     </row>
     <row r="88" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A88">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="B88">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="C88">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="D88">
         <v>0</v>
@@ -5029,25 +5029,25 @@
         <v>0</v>
       </c>
       <c r="G88">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H88">
         <v>1</v>
       </c>
       <c r="I88">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J88">
-        <f t="shared" si="7"/>
-        <v>60</v>
+        <f t="shared" si="36"/>
+        <v>20</v>
       </c>
       <c r="K88">
-        <f t="shared" si="8"/>
+        <f t="shared" si="37"/>
         <v>20</v>
       </c>
       <c r="L88">
-        <f t="shared" si="9"/>
-        <v>60</v>
+        <f t="shared" si="38"/>
+        <v>20</v>
       </c>
       <c r="M88">
         <v>0</v>
@@ -5064,13 +5064,13 @@
     </row>
     <row r="89" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A89">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="B89">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="C89">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="D89">
         <v>0</v>
@@ -5082,25 +5082,25 @@
         <v>0</v>
       </c>
       <c r="G89">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H89">
         <v>1</v>
       </c>
       <c r="I89">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J89">
-        <f t="shared" si="7"/>
-        <v>60</v>
+        <f t="shared" si="36"/>
+        <v>20</v>
       </c>
       <c r="K89">
-        <f t="shared" si="8"/>
+        <f t="shared" si="37"/>
         <v>20</v>
       </c>
       <c r="L89">
-        <f t="shared" si="9"/>
-        <v>60</v>
+        <f t="shared" si="38"/>
+        <v>20</v>
       </c>
       <c r="M89">
         <v>0</v>
@@ -5117,13 +5117,13 @@
     </row>
     <row r="90" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A90">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="B90">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="C90">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="D90">
         <v>0</v>
@@ -5135,25 +5135,25 @@
         <v>0</v>
       </c>
       <c r="G90">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H90">
         <v>1</v>
       </c>
       <c r="I90">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J90">
-        <f t="shared" si="7"/>
-        <v>60</v>
+        <f t="shared" si="36"/>
+        <v>20</v>
       </c>
       <c r="K90">
-        <f t="shared" si="8"/>
+        <f t="shared" si="37"/>
         <v>20</v>
       </c>
       <c r="L90">
-        <f t="shared" si="9"/>
-        <v>60</v>
+        <f t="shared" si="38"/>
+        <v>20</v>
       </c>
       <c r="M90">
         <v>0</v>
@@ -5170,13 +5170,13 @@
     </row>
     <row r="91" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A91">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="B91">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="C91">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="D91">
         <v>0</v>
@@ -5188,25 +5188,25 @@
         <v>0</v>
       </c>
       <c r="G91">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H91">
         <v>1</v>
       </c>
       <c r="I91">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J91">
-        <f t="shared" si="7"/>
-        <v>60</v>
+        <f t="shared" si="36"/>
+        <v>20</v>
       </c>
       <c r="K91">
-        <f t="shared" si="8"/>
+        <f t="shared" si="37"/>
         <v>20</v>
       </c>
       <c r="L91">
-        <f t="shared" si="9"/>
-        <v>60</v>
+        <f t="shared" si="38"/>
+        <v>20</v>
       </c>
       <c r="M91">
         <v>0</v>
@@ -5223,13 +5223,13 @@
     </row>
     <row r="92" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A92">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="B92">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="C92">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="D92">
         <v>0</v>
@@ -5241,25 +5241,25 @@
         <v>0</v>
       </c>
       <c r="G92">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H92">
         <v>1</v>
       </c>
       <c r="I92">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J92">
-        <f t="shared" si="7"/>
-        <v>60</v>
+        <f t="shared" si="36"/>
+        <v>20</v>
       </c>
       <c r="K92">
-        <f t="shared" si="8"/>
+        <f t="shared" si="37"/>
         <v>20</v>
       </c>
       <c r="L92">
-        <f t="shared" si="9"/>
-        <v>60</v>
+        <f t="shared" si="38"/>
+        <v>20</v>
       </c>
       <c r="M92">
         <v>0</v>
@@ -5276,13 +5276,13 @@
     </row>
     <row r="93" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A93">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="B93">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="C93">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="D93">
         <v>0</v>
@@ -5294,25 +5294,25 @@
         <v>0</v>
       </c>
       <c r="G93">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H93">
         <v>1</v>
       </c>
       <c r="I93">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J93">
-        <f t="shared" si="7"/>
-        <v>60</v>
+        <f t="shared" si="36"/>
+        <v>20</v>
       </c>
       <c r="K93">
-        <f t="shared" si="8"/>
+        <f t="shared" si="37"/>
         <v>20</v>
       </c>
       <c r="L93">
-        <f t="shared" si="9"/>
-        <v>60</v>
+        <f t="shared" si="38"/>
+        <v>20</v>
       </c>
       <c r="M93">
         <v>0</v>
@@ -5329,13 +5329,13 @@
     </row>
     <row r="94" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A94">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="B94">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="C94">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="D94">
         <v>0</v>
@@ -5347,25 +5347,25 @@
         <v>0</v>
       </c>
       <c r="G94">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H94">
         <v>1</v>
       </c>
       <c r="I94">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J94">
-        <f t="shared" si="7"/>
-        <v>60</v>
+        <f t="shared" si="36"/>
+        <v>20</v>
       </c>
       <c r="K94">
-        <f t="shared" si="8"/>
+        <f t="shared" si="37"/>
         <v>20</v>
       </c>
       <c r="L94">
-        <f t="shared" si="9"/>
-        <v>60</v>
+        <f t="shared" si="38"/>
+        <v>20</v>
       </c>
       <c r="M94">
         <v>0</v>
@@ -5382,13 +5382,13 @@
     </row>
     <row r="95" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A95">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="B95">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="C95">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="D95">
         <v>0</v>
@@ -5400,25 +5400,25 @@
         <v>0</v>
       </c>
       <c r="G95">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H95">
         <v>1</v>
       </c>
       <c r="I95">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J95">
-        <f t="shared" si="7"/>
-        <v>60</v>
+        <f t="shared" si="36"/>
+        <v>20</v>
       </c>
       <c r="K95">
-        <f t="shared" si="8"/>
+        <f t="shared" si="37"/>
         <v>20</v>
       </c>
       <c r="L95">
-        <f t="shared" si="9"/>
-        <v>60</v>
+        <f t="shared" si="38"/>
+        <v>20</v>
       </c>
       <c r="M95">
         <v>0</v>
@@ -5435,13 +5435,13 @@
     </row>
     <row r="96" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A96">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="B96">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="C96">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="D96">
         <v>0</v>
@@ -5453,25 +5453,25 @@
         <v>0</v>
       </c>
       <c r="G96">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H96">
         <v>1</v>
       </c>
       <c r="I96">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J96">
-        <f t="shared" si="7"/>
-        <v>60</v>
+        <f t="shared" si="36"/>
+        <v>20</v>
       </c>
       <c r="K96">
-        <f t="shared" si="8"/>
+        <f t="shared" si="37"/>
         <v>20</v>
       </c>
       <c r="L96">
-        <f t="shared" si="9"/>
-        <v>60</v>
+        <f t="shared" si="38"/>
+        <v>20</v>
       </c>
       <c r="M96">
         <v>0</v>
@@ -5488,13 +5488,13 @@
     </row>
     <row r="97" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A97">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="B97">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="C97">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="D97">
         <v>0</v>
@@ -5506,25 +5506,25 @@
         <v>0</v>
       </c>
       <c r="G97">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H97">
         <v>1</v>
       </c>
       <c r="I97">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J97">
-        <f t="shared" si="7"/>
-        <v>60</v>
+        <f t="shared" si="36"/>
+        <v>20</v>
       </c>
       <c r="K97">
-        <f t="shared" si="8"/>
+        <f t="shared" si="37"/>
         <v>20</v>
       </c>
       <c r="L97">
-        <f t="shared" si="9"/>
-        <v>60</v>
+        <f t="shared" si="38"/>
+        <v>20</v>
       </c>
       <c r="M97">
         <v>0</v>
@@ -5541,13 +5541,13 @@
     </row>
     <row r="98" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A98">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="B98">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="C98">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="D98">
         <v>0</v>
@@ -5559,25 +5559,25 @@
         <v>0</v>
       </c>
       <c r="G98">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H98">
         <v>1</v>
       </c>
       <c r="I98">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J98">
-        <f t="shared" si="7"/>
-        <v>60</v>
+        <f t="shared" si="36"/>
+        <v>20</v>
       </c>
       <c r="K98">
-        <f t="shared" si="8"/>
+        <f t="shared" si="37"/>
         <v>20</v>
       </c>
       <c r="L98">
-        <f t="shared" si="9"/>
-        <v>60</v>
+        <f t="shared" si="38"/>
+        <v>20</v>
       </c>
       <c r="M98">
         <v>0</v>
@@ -5594,13 +5594,13 @@
     </row>
     <row r="99" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A99">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="B99">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="C99">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="D99">
         <v>0</v>
@@ -5612,25 +5612,25 @@
         <v>0</v>
       </c>
       <c r="G99">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H99">
         <v>1</v>
       </c>
       <c r="I99">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J99">
-        <f t="shared" si="7"/>
-        <v>60</v>
+        <f t="shared" si="36"/>
+        <v>20</v>
       </c>
       <c r="K99">
-        <f t="shared" si="8"/>
+        <f t="shared" si="37"/>
         <v>20</v>
       </c>
       <c r="L99">
-        <f t="shared" si="9"/>
-        <v>60</v>
+        <f t="shared" si="38"/>
+        <v>20</v>
       </c>
       <c r="M99">
         <v>0</v>
@@ -5647,13 +5647,13 @@
     </row>
     <row r="100" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A100">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="B100">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="C100">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="D100">
         <v>0</v>
@@ -5665,25 +5665,25 @@
         <v>0</v>
       </c>
       <c r="G100">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H100">
         <v>1</v>
       </c>
       <c r="I100">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J100">
-        <f t="shared" si="7"/>
-        <v>60</v>
+        <f t="shared" si="36"/>
+        <v>20</v>
       </c>
       <c r="K100">
-        <f t="shared" si="8"/>
+        <f t="shared" si="37"/>
         <v>20</v>
       </c>
       <c r="L100">
-        <f t="shared" si="9"/>
-        <v>60</v>
+        <f t="shared" si="38"/>
+        <v>20</v>
       </c>
       <c r="M100">
         <v>0</v>

--- a/ActionGame-リファクタリング-/Data/CSV/Stage/Stage.xlsx
+++ b/ActionGame-リファクタリング-/Data/CSV/Stage/Stage.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\2409404\Desktop\GameProject\ActionGame-リファクタリング-\Data\CSV\Stage\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{260C087E-050F-4C15-A92B-BD3A6ADDE3E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E71C608F-7383-4108-B392-5A243B2B506A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{62A58253-9505-4C17-A0D0-B4C12E04E8CC}"/>
+    <workbookView xWindow="7200" yWindow="2535" windowWidth="21600" windowHeight="11295" xr2:uid="{62A58253-9505-4C17-A0D0-B4C12E04E8CC}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -4325,7 +4325,7 @@
         <v>0</v>
       </c>
       <c r="B75">
-        <v>480</v>
+        <v>490</v>
       </c>
       <c r="C75">
         <v>-120</v>
@@ -4378,7 +4378,7 @@
         <v>0</v>
       </c>
       <c r="B76">
-        <v>480</v>
+        <v>490</v>
       </c>
       <c r="C76">
         <v>-160</v>
@@ -4431,7 +4431,7 @@
         <v>0</v>
       </c>
       <c r="B77">
-        <v>480</v>
+        <v>490</v>
       </c>
       <c r="C77">
         <v>-200</v>
@@ -4484,7 +4484,7 @@
         <v>0</v>
       </c>
       <c r="B78">
-        <v>480</v>
+        <v>500</v>
       </c>
       <c r="C78">
         <v>-240</v>
@@ -4537,7 +4537,7 @@
         <v>0</v>
       </c>
       <c r="B79">
-        <v>480</v>
+        <v>500</v>
       </c>
       <c r="C79">
         <v>-280</v>
@@ -4590,7 +4590,7 @@
         <v>0</v>
       </c>
       <c r="B80">
-        <v>480</v>
+        <v>500</v>
       </c>
       <c r="C80">
         <v>-320</v>
@@ -4643,10 +4643,10 @@
         <v>0</v>
       </c>
       <c r="B81">
-        <v>0</v>
+        <v>510</v>
       </c>
       <c r="C81">
-        <v>0</v>
+        <v>-380</v>
       </c>
       <c r="D81">
         <v>0</v>
@@ -4658,17 +4658,17 @@
         <v>0</v>
       </c>
       <c r="G81">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H81">
         <v>1</v>
       </c>
       <c r="I81">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J81">
         <f t="shared" si="36"/>
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="K81">
         <f t="shared" si="37"/>
@@ -4676,7 +4676,7 @@
       </c>
       <c r="L81">
         <f t="shared" si="38"/>
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="M81">
         <v>0</v>

--- a/ActionGame-リファクタリング-/Data/CSV/Stage/Stage.xlsx
+++ b/ActionGame-リファクタリング-/Data/CSV/Stage/Stage.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\2409404\Desktop\GameProject\ActionGame-リファクタリング-\Data\CSV\Stage\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E71C608F-7383-4108-B392-5A243B2B506A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5107460-A208-4FDC-A54E-DC6E760E5FE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7200" yWindow="2535" windowWidth="21600" windowHeight="11295" xr2:uid="{62A58253-9505-4C17-A0D0-B4C12E04E8CC}"/>
+    <workbookView xWindow="3810" yWindow="4185" windowWidth="21600" windowHeight="11295" xr2:uid="{62A58253-9505-4C17-A0D0-B4C12E04E8CC}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -4169,7 +4169,7 @@
         <v>480</v>
       </c>
       <c r="C72">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="D72">
         <v>0</v>
@@ -4222,7 +4222,7 @@
         <v>480</v>
       </c>
       <c r="C73">
-        <v>-40</v>
+        <v>-20</v>
       </c>
       <c r="D73">
         <v>0</v>
@@ -4275,7 +4275,7 @@
         <v>480</v>
       </c>
       <c r="C74">
-        <v>-80</v>
+        <v>-60</v>
       </c>
       <c r="D74">
         <v>0</v>
@@ -4328,7 +4328,7 @@
         <v>490</v>
       </c>
       <c r="C75">
-        <v>-120</v>
+        <v>-100</v>
       </c>
       <c r="D75">
         <v>0</v>
@@ -4381,7 +4381,7 @@
         <v>490</v>
       </c>
       <c r="C76">
-        <v>-160</v>
+        <v>-140</v>
       </c>
       <c r="D76">
         <v>0</v>
@@ -4434,7 +4434,7 @@
         <v>490</v>
       </c>
       <c r="C77">
-        <v>-200</v>
+        <v>-180</v>
       </c>
       <c r="D77">
         <v>0</v>
@@ -4487,7 +4487,7 @@
         <v>500</v>
       </c>
       <c r="C78">
-        <v>-240</v>
+        <v>-220</v>
       </c>
       <c r="D78">
         <v>0</v>
@@ -4540,7 +4540,7 @@
         <v>500</v>
       </c>
       <c r="C79">
-        <v>-280</v>
+        <v>-260</v>
       </c>
       <c r="D79">
         <v>0</v>
@@ -4593,7 +4593,7 @@
         <v>500</v>
       </c>
       <c r="C80">
-        <v>-320</v>
+        <v>-300</v>
       </c>
       <c r="D80">
         <v>0</v>
@@ -4643,10 +4643,10 @@
         <v>0</v>
       </c>
       <c r="B81">
-        <v>510</v>
+        <v>520</v>
       </c>
       <c r="C81">
-        <v>-380</v>
+        <v>-340</v>
       </c>
       <c r="D81">
         <v>0</v>
@@ -4658,17 +4658,17 @@
         <v>0</v>
       </c>
       <c r="G81">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H81">
         <v>1</v>
       </c>
       <c r="I81">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J81">
         <f t="shared" si="36"/>
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="K81">
         <f t="shared" si="37"/>
@@ -4676,7 +4676,7 @@
       </c>
       <c r="L81">
         <f t="shared" si="38"/>
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="M81">
         <v>0</v>
@@ -4693,13 +4693,13 @@
     </row>
     <row r="82" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A82">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="B82">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="C82">
-        <v>0</v>
+        <v>-420</v>
       </c>
       <c r="D82">
         <v>0</v>
@@ -4711,17 +4711,17 @@
         <v>0</v>
       </c>
       <c r="G82">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H82">
         <v>1</v>
       </c>
       <c r="I82">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J82">
         <f t="shared" si="36"/>
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="K82">
         <f t="shared" si="37"/>
@@ -4729,30 +4729,30 @@
       </c>
       <c r="L82">
         <f t="shared" si="38"/>
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="M82">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="N82">
-        <v>0</v>
+        <v>700</v>
       </c>
       <c r="O82">
-        <v>0</v>
+        <v>-420</v>
       </c>
       <c r="P82">
-        <v>0</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="83" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A83">
-        <v>0</v>
+        <v>-40</v>
       </c>
       <c r="B83">
-        <v>0</v>
+        <v>800</v>
       </c>
       <c r="C83">
-        <v>0</v>
+        <v>-420</v>
       </c>
       <c r="D83">
         <v>0</v>
@@ -4764,17 +4764,17 @@
         <v>0</v>
       </c>
       <c r="G83">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H83">
         <v>1</v>
       </c>
       <c r="I83">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J83">
         <f t="shared" si="36"/>
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="K83">
         <f t="shared" si="37"/>
@@ -4782,19 +4782,19 @@
       </c>
       <c r="L83">
         <f t="shared" si="38"/>
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="M83">
-        <v>0</v>
+        <v>-40</v>
       </c>
       <c r="N83">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="O83">
-        <v>0</v>
+        <v>-420</v>
       </c>
       <c r="P83">
-        <v>0</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="84" spans="1:16" x14ac:dyDescent="0.4">
@@ -4802,10 +4802,10 @@
         <v>0</v>
       </c>
       <c r="B84">
-        <v>0</v>
+        <v>800</v>
       </c>
       <c r="C84">
-        <v>0</v>
+        <v>-460</v>
       </c>
       <c r="D84">
         <v>0</v>
@@ -4852,13 +4852,13 @@
     </row>
     <row r="85" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A85">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="B85">
-        <v>0</v>
+        <v>800</v>
       </c>
       <c r="C85">
-        <v>0</v>
+        <v>-460</v>
       </c>
       <c r="D85">
         <v>0</v>
@@ -4905,13 +4905,13 @@
     </row>
     <row r="86" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A86">
-        <v>0</v>
+        <v>-40</v>
       </c>
       <c r="B86">
-        <v>0</v>
+        <v>800</v>
       </c>
       <c r="C86">
-        <v>0</v>
+        <v>-460</v>
       </c>
       <c r="D86">
         <v>0</v>
@@ -4961,10 +4961,10 @@
         <v>0</v>
       </c>
       <c r="B87">
-        <v>0</v>
+        <v>700</v>
       </c>
       <c r="C87">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="D87">
         <v>0</v>
@@ -4976,17 +4976,17 @@
         <v>0</v>
       </c>
       <c r="G87">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H87">
         <v>1</v>
       </c>
       <c r="I87">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J87">
         <f t="shared" si="36"/>
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="K87">
         <f t="shared" si="37"/>
@@ -4994,19 +4994,19 @@
       </c>
       <c r="L87">
         <f t="shared" si="38"/>
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="M87">
         <v>0</v>
       </c>
       <c r="N87">
-        <v>0</v>
+        <v>1200</v>
       </c>
       <c r="O87">
-        <v>0</v>
+        <v>-1500</v>
       </c>
       <c r="P87">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="88" spans="1:16" x14ac:dyDescent="0.4">
@@ -5014,10 +5014,10 @@
         <v>0</v>
       </c>
       <c r="B88">
-        <v>0</v>
+        <v>1200</v>
       </c>
       <c r="C88">
-        <v>0</v>
+        <v>-1540</v>
       </c>
       <c r="D88">
         <v>0</v>
@@ -5029,17 +5029,17 @@
         <v>0</v>
       </c>
       <c r="G88">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H88">
         <v>1</v>
       </c>
       <c r="I88">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J88">
         <f t="shared" si="36"/>
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="K88">
         <f t="shared" si="37"/>
@@ -5047,7 +5047,7 @@
       </c>
       <c r="L88">
         <f t="shared" si="38"/>
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="M88">
         <v>0</v>

--- a/ActionGame-リファクタリング-/Data/CSV/Stage/Stage.xlsx
+++ b/ActionGame-リファクタリング-/Data/CSV/Stage/Stage.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\2409404\Desktop\GameProject\ActionGame-リファクタリング-\Data\CSV\Stage\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5107460-A208-4FDC-A54E-DC6E760E5FE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{649C872F-7BCE-42A8-84FA-1DDDB0BEC027}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3810" yWindow="4185" windowWidth="21600" windowHeight="11295" xr2:uid="{62A58253-9505-4C17-A0D0-B4C12E04E8CC}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{62A58253-9505-4C17-A0D0-B4C12E04E8CC}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -4805,7 +4805,7 @@
         <v>800</v>
       </c>
       <c r="C84">
-        <v>-460</v>
+        <v>-480</v>
       </c>
       <c r="D84">
         <v>0</v>
@@ -4852,13 +4852,13 @@
     </row>
     <row r="85" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A85">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="B85">
-        <v>800</v>
+        <v>700</v>
       </c>
       <c r="C85">
-        <v>-460</v>
+        <v>-520</v>
       </c>
       <c r="D85">
         <v>0</v>
@@ -4870,17 +4870,17 @@
         <v>0</v>
       </c>
       <c r="G85">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H85">
         <v>1</v>
       </c>
       <c r="I85">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J85">
         <f t="shared" si="36"/>
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="K85">
         <f t="shared" si="37"/>
@@ -4888,30 +4888,30 @@
       </c>
       <c r="L85">
         <f t="shared" si="38"/>
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="M85">
         <v>0</v>
       </c>
       <c r="N85">
-        <v>0</v>
+        <v>1200</v>
       </c>
       <c r="O85">
-        <v>0</v>
+        <v>-1020</v>
       </c>
       <c r="P85">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="86" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A86">
-        <v>-40</v>
+        <v>0</v>
       </c>
       <c r="B86">
-        <v>800</v>
+        <v>1200</v>
       </c>
       <c r="C86">
-        <v>-460</v>
+        <v>-1080</v>
       </c>
       <c r="D86">
         <v>0</v>
@@ -4923,17 +4923,17 @@
         <v>0</v>
       </c>
       <c r="G86">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H86">
         <v>1</v>
       </c>
       <c r="I86">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J86">
         <f t="shared" si="36"/>
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="K86">
         <f t="shared" si="37"/>
@@ -4941,7 +4941,7 @@
       </c>
       <c r="L86">
         <f t="shared" si="38"/>
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="M86">
         <v>0</v>
@@ -4958,13 +4958,13 @@
     </row>
     <row r="87" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A87">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="B87">
-        <v>700</v>
+        <v>1200</v>
       </c>
       <c r="C87">
-        <v>500</v>
+        <v>-1080</v>
       </c>
       <c r="D87">
         <v>0</v>
@@ -4997,13 +4997,13 @@
         <v>60</v>
       </c>
       <c r="M87">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="N87">
         <v>1200</v>
       </c>
       <c r="O87">
-        <v>-1500</v>
+        <v>-280</v>
       </c>
       <c r="P87">
         <v>2</v>
@@ -5011,13 +5011,13 @@
     </row>
     <row r="88" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A88">
-        <v>0</v>
+        <v>-60</v>
       </c>
       <c r="B88">
         <v>1200</v>
       </c>
       <c r="C88">
-        <v>-1540</v>
+        <v>-280</v>
       </c>
       <c r="D88">
         <v>0</v>
@@ -5050,16 +5050,16 @@
         <v>60</v>
       </c>
       <c r="M88">
-        <v>0</v>
+        <v>-60</v>
       </c>
       <c r="N88">
-        <v>0</v>
+        <v>1200</v>
       </c>
       <c r="O88">
-        <v>0</v>
+        <v>-1080</v>
       </c>
       <c r="P88">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="89" spans="1:16" x14ac:dyDescent="0.4">
@@ -5067,7 +5067,7 @@
         <v>0</v>
       </c>
       <c r="B89">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="C89">
         <v>0</v>
@@ -5082,17 +5082,17 @@
         <v>0</v>
       </c>
       <c r="G89">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="H89">
         <v>1</v>
       </c>
       <c r="I89">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="J89">
         <f t="shared" si="36"/>
-        <v>20</v>
+        <v>500</v>
       </c>
       <c r="K89">
         <f t="shared" si="37"/>
@@ -5100,7 +5100,7 @@
       </c>
       <c r="L89">
         <f t="shared" si="38"/>
-        <v>20</v>
+        <v>500</v>
       </c>
       <c r="M89">
         <v>0</v>
@@ -5120,10 +5120,10 @@
         <v>0</v>
       </c>
       <c r="B90">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="C90">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="D90">
         <v>0</v>
@@ -5135,17 +5135,17 @@
         <v>0</v>
       </c>
       <c r="G90">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="H90">
         <v>1</v>
       </c>
       <c r="I90">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="J90">
         <f t="shared" si="36"/>
-        <v>20</v>
+        <v>300</v>
       </c>
       <c r="K90">
         <f t="shared" si="37"/>
@@ -5153,7 +5153,7 @@
       </c>
       <c r="L90">
         <f t="shared" si="38"/>
-        <v>20</v>
+        <v>220</v>
       </c>
       <c r="M90">
         <v>0</v>
@@ -5173,10 +5173,10 @@
         <v>0</v>
       </c>
       <c r="B91">
-        <v>0</v>
+        <v>1200</v>
       </c>
       <c r="C91">
-        <v>0</v>
+        <v>560</v>
       </c>
       <c r="D91">
         <v>0</v>
@@ -5188,25 +5188,25 @@
         <v>0</v>
       </c>
       <c r="G91">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="H91">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="I91">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J91">
         <f t="shared" si="36"/>
-        <v>20</v>
+        <v>300</v>
       </c>
       <c r="K91">
         <f t="shared" si="37"/>
-        <v>20</v>
+        <v>220</v>
       </c>
       <c r="L91">
         <f t="shared" si="38"/>
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="M91">
         <v>0</v>
@@ -5223,13 +5223,13 @@
     </row>
     <row r="92" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A92">
-        <v>0</v>
+        <v>280</v>
       </c>
       <c r="B92">
-        <v>0</v>
+        <v>1050</v>
       </c>
       <c r="C92">
-        <v>0</v>
+        <v>440</v>
       </c>
       <c r="D92">
         <v>0</v>
@@ -5241,17 +5241,17 @@
         <v>0</v>
       </c>
       <c r="G92">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H92">
         <v>1</v>
       </c>
       <c r="I92">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="J92">
         <f t="shared" si="36"/>
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="K92">
         <f t="shared" si="37"/>
@@ -5259,7 +5259,7 @@
       </c>
       <c r="L92">
         <f t="shared" si="38"/>
-        <v>20</v>
+        <v>140</v>
       </c>
       <c r="M92">
         <v>0</v>
@@ -5276,13 +5276,13 @@
     </row>
     <row r="93" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A93">
-        <v>0</v>
+        <v>-280</v>
       </c>
       <c r="B93">
-        <v>0</v>
+        <v>1100</v>
       </c>
       <c r="C93">
-        <v>0</v>
+        <v>460</v>
       </c>
       <c r="D93">
         <v>0</v>
@@ -5294,17 +5294,17 @@
         <v>0</v>
       </c>
       <c r="G93">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H93">
         <v>1</v>
       </c>
       <c r="I93">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J93">
         <f t="shared" si="36"/>
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="K93">
         <f t="shared" si="37"/>
@@ -5312,7 +5312,7 @@
       </c>
       <c r="L93">
         <f t="shared" si="38"/>
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="M93">
         <v>0</v>
@@ -5329,13 +5329,13 @@
     </row>
     <row r="94" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A94">
-        <v>0</v>
+        <v>280</v>
       </c>
       <c r="B94">
-        <v>0</v>
+        <v>1150</v>
       </c>
       <c r="C94">
-        <v>0</v>
+        <v>480</v>
       </c>
       <c r="D94">
         <v>0</v>
@@ -5347,17 +5347,17 @@
         <v>0</v>
       </c>
       <c r="G94">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H94">
         <v>1</v>
       </c>
       <c r="I94">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J94">
         <f t="shared" si="36"/>
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="K94">
         <f t="shared" si="37"/>
@@ -5365,7 +5365,7 @@
       </c>
       <c r="L94">
         <f t="shared" si="38"/>
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="M94">
         <v>0</v>

--- a/ActionGame-リファクタリング-/Data/CSV/Stage/Stage.xlsx
+++ b/ActionGame-リファクタリング-/Data/CSV/Stage/Stage.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\2409404\Desktop\GameProject\ActionGame-リファクタリング-\Data\CSV\Stage\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{649C872F-7BCE-42A8-84FA-1DDDB0BEC027}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99255174-29B3-448F-8CD9-585880B2C5BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{62A58253-9505-4C17-A0D0-B4C12E04E8CC}"/>
+    <workbookView xWindow="10245" yWindow="2940" windowWidth="21600" windowHeight="11295" xr2:uid="{62A58253-9505-4C17-A0D0-B4C12E04E8CC}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -5223,7 +5223,7 @@
     </row>
     <row r="92" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A92">
-        <v>280</v>
+        <v>120</v>
       </c>
       <c r="B92">
         <v>1050</v>
@@ -5262,21 +5262,21 @@
         <v>140</v>
       </c>
       <c r="M92">
-        <v>0</v>
+        <v>-120</v>
       </c>
       <c r="N92">
-        <v>0</v>
+        <v>1050</v>
       </c>
       <c r="O92">
-        <v>0</v>
+        <v>440</v>
       </c>
       <c r="P92">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="93" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A93">
-        <v>-280</v>
+        <v>-120</v>
       </c>
       <c r="B93">
         <v>1100</v>
@@ -5315,21 +5315,21 @@
         <v>100</v>
       </c>
       <c r="M93">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="N93">
-        <v>0</v>
+        <v>1100</v>
       </c>
       <c r="O93">
-        <v>0</v>
+        <v>460</v>
       </c>
       <c r="P93">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="94" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A94">
-        <v>280</v>
+        <v>120</v>
       </c>
       <c r="B94">
         <v>1150</v>
@@ -5368,16 +5368,16 @@
         <v>60</v>
       </c>
       <c r="M94">
-        <v>0</v>
+        <v>-120</v>
       </c>
       <c r="N94">
-        <v>0</v>
+        <v>1150</v>
       </c>
       <c r="O94">
-        <v>0</v>
+        <v>480</v>
       </c>
       <c r="P94">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="95" spans="1:16" x14ac:dyDescent="0.4">
@@ -5385,10 +5385,10 @@
         <v>0</v>
       </c>
       <c r="B95">
-        <v>0</v>
+        <v>1200</v>
       </c>
       <c r="C95">
-        <v>0</v>
+        <v>640</v>
       </c>
       <c r="D95">
         <v>0</v>
@@ -5400,17 +5400,17 @@
         <v>0</v>
       </c>
       <c r="G95">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H95">
         <v>1</v>
       </c>
       <c r="I95">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J95">
         <f t="shared" si="36"/>
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="K95">
         <f t="shared" si="37"/>
@@ -5418,7 +5418,7 @@
       </c>
       <c r="L95">
         <f t="shared" si="38"/>
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="M95">
         <v>0</v>
